--- a/outputs/tongji_summary/tongji_summary_current.xlsx
+++ b/outputs/tongji_summary/tongji_summary_current.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目标现状对比" sheetId="1" r:id="R30aa4512c4464f73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据概览" sheetId="2" r:id="R11ee2cde927a4245"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目标现状对比" sheetId="1" r:id="R2364a6ebeb1f4b0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据概览" sheetId="2" r:id="R52a1ff082082424c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -512,7 +512,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F3" s="20" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G3" s="20" t="str">
         <x:v>2026-06-30</x:v>
@@ -524,16 +524,16 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="J3" s="17" t="n">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K3" s="17" t="n">
-        <x:v>-133</x:v>
+        <x:v>-120</x:v>
       </x:c>
       <x:c r="L3" s="23" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.14285714285714285</x:v>
       </x:c>
       <x:c r="M3" s="24" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -550,10 +550,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E4" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F4" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G4" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -562,19 +562,19 @@
         <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="I4" s="18" t="n">
-        <x:v>140</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J4" s="18" t="n">
-        <x:v>12</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K4" s="18" t="n">
-        <x:v>-128</x:v>
+        <x:v>-75</x:v>
       </x:c>
       <x:c r="L4" s="25" t="n">
-        <x:v>0.08571428571428572</x:v>
+        <x:v>0.375</x:v>
       </x:c>
       <x:c r="M4" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -591,10 +591,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E5" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F5" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G5" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -603,19 +603,19 @@
         <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="I5" s="18" t="n">
-        <x:v>120</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J5" s="18" t="n">
-        <x:v>16</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="K5" s="18" t="n">
-        <x:v>-104</x:v>
+        <x:v>-107</x:v>
       </x:c>
       <x:c r="L5" s="25" t="n">
-        <x:v>0.13333333333333333</x:v>
+        <x:v>0.2357142857142857</x:v>
       </x:c>
       <x:c r="M5" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -656,7 +656,7 @@
         <x:v>1.6466666666666667</x:v>
       </x:c>
       <x:c r="M6" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -673,10 +673,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E7" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F7" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G7" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -688,16 +688,16 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="J7" s="18" t="n">
-        <x:v>209</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="K7" s="18" t="n">
-        <x:v>-391</x:v>
+        <x:v>-233</x:v>
       </x:c>
       <x:c r="L7" s="25" t="n">
-        <x:v>0.34833333333333333</x:v>
+        <x:v>0.6116666666666667</x:v>
       </x:c>
       <x:c r="M7" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -714,10 +714,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E8" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F8" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G8" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -729,16 +729,16 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="J8" s="18" t="n">
-        <x:v>261</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="K8" s="18" t="n">
-        <x:v>-339</x:v>
+        <x:v>-326</x:v>
       </x:c>
       <x:c r="L8" s="25" t="n">
-        <x:v>0.435</x:v>
+        <x:v>0.45666666666666667</x:v>
       </x:c>
       <x:c r="M8" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -758,7 +758,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F9" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G9" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -770,16 +770,16 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="J9" s="18" t="n">
-        <x:v>234</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="K9" s="18" t="n">
-        <x:v>-266</x:v>
+        <x:v>-156</x:v>
       </x:c>
       <x:c r="L9" s="25" t="n">
-        <x:v>0.468</x:v>
+        <x:v>0.688</x:v>
       </x:c>
       <x:c r="M9" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
@@ -796,10 +796,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E10" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F10" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G10" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -811,16 +811,16 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="J10" s="18" t="n">
-        <x:v>154</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="K10" s="18" t="n">
-        <x:v>-546</x:v>
+        <x:v>-405</x:v>
       </x:c>
       <x:c r="L10" s="25" t="n">
-        <x:v>0.22</x:v>
+        <x:v>0.42142857142857143</x:v>
       </x:c>
       <x:c r="M10" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
@@ -837,10 +837,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E11" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F11" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G11" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -852,16 +852,16 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="J11" s="18" t="n">
-        <x:v>179</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="K11" s="18" t="n">
-        <x:v>-521</x:v>
+        <x:v>-435</x:v>
       </x:c>
       <x:c r="L11" s="25" t="n">
-        <x:v>0.2557142857142857</x:v>
+        <x:v>0.37857142857142856</x:v>
       </x:c>
       <x:c r="M11" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -881,7 +881,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F12" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G12" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -893,16 +893,16 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J12" s="18" t="n">
-        <x:v>115</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="K12" s="18" t="n">
-        <x:v>15</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="L12" s="25" t="n">
-        <x:v>1.15</x:v>
+        <x:v>2.03</x:v>
       </x:c>
       <x:c r="M12" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -919,10 +919,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E13" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F13" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G13" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -934,16 +934,16 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="J13" s="18" t="n">
-        <x:v>82</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="K13" s="18" t="n">
-        <x:v>-568</x:v>
+        <x:v>-443</x:v>
       </x:c>
       <x:c r="L13" s="25" t="n">
-        <x:v>0.12615384615384614</x:v>
+        <x:v>0.31846153846153846</x:v>
       </x:c>
       <x:c r="M13" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -960,10 +960,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E14" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F14" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G14" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -975,16 +975,16 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="J14" s="18" t="n">
-        <x:v>128</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="K14" s="18" t="n">
-        <x:v>-522</x:v>
+        <x:v>-568</x:v>
       </x:c>
       <x:c r="L14" s="25" t="n">
-        <x:v>0.19692307692307692</x:v>
+        <x:v>0.12615384615384614</x:v>
       </x:c>
       <x:c r="M14" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -1004,7 +1004,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F15" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G15" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1016,16 +1016,16 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="J15" s="18" t="n">
-        <x:v>64</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K15" s="18" t="n">
-        <x:v>-126</x:v>
+        <x:v>-81</x:v>
       </x:c>
       <x:c r="L15" s="25" t="n">
-        <x:v>0.3368421052631579</x:v>
+        <x:v>0.5736842105263158</x:v>
       </x:c>
       <x:c r="M15" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
@@ -1042,10 +1042,10 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E16" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F16" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G16" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1054,19 +1054,19 @@
         <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="I16" s="18" t="n">
-        <x:v>300</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="J16" s="18" t="n">
-        <x:v>78</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="K16" s="18" t="n">
-        <x:v>-222</x:v>
+        <x:v>-216</x:v>
       </x:c>
       <x:c r="L16" s="25" t="n">
-        <x:v>0.26</x:v>
+        <x:v>0.4</x:v>
       </x:c>
       <x:c r="M16" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -1083,10 +1083,10 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E17" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F17" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G17" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1095,19 +1095,19 @@
         <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="I17" s="18" t="n">
-        <x:v>360</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J17" s="18" t="n">
-        <x:v>96</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="K17" s="18" t="n">
-        <x:v>-264</x:v>
+        <x:v>-175</x:v>
       </x:c>
       <x:c r="L17" s="25" t="n">
-        <x:v>0.26666666666666666</x:v>
+        <x:v>0.4166666666666667</x:v>
       </x:c>
       <x:c r="M17" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
@@ -1157,10 +1157,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E19" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F19" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G19" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1172,16 +1172,16 @@
         <x:v>400</x:v>
       </x:c>
       <x:c r="J19" s="18" t="n">
-        <x:v>245</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="K19" s="18" t="n">
-        <x:v>-155</x:v>
+        <x:v>-80</x:v>
       </x:c>
       <x:c r="L19" s="25" t="n">
-        <x:v>0.6125</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="M19" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -1198,10 +1198,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E20" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F20" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G20" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1213,16 +1213,16 @@
         <x:v>400</x:v>
       </x:c>
       <x:c r="J20" s="18" t="n">
-        <x:v>206</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="K20" s="18" t="n">
-        <x:v>-194</x:v>
+        <x:v>-35</x:v>
       </x:c>
       <x:c r="L20" s="25" t="n">
-        <x:v>0.515</x:v>
+        <x:v>0.9125</x:v>
       </x:c>
       <x:c r="M20" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -1242,7 +1242,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F21" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G21" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1254,16 +1254,16 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="J21" s="18" t="n">
-        <x:v>261</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="K21" s="18" t="n">
-        <x:v>-239</x:v>
+        <x:v>-138</x:v>
       </x:c>
       <x:c r="L21" s="25" t="n">
-        <x:v>0.522</x:v>
+        <x:v>0.724</x:v>
       </x:c>
       <x:c r="M21" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -1280,10 +1280,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E22" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F22" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G22" s="21"/>
       <x:c r="H22" s="21"/>
@@ -1291,10 +1291,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J22" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="K22" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="L22" s="25"/>
       <x:c r="M22" s="26"/>
@@ -1313,10 +1313,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E23" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F23" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G23" s="21"/>
       <x:c r="H23" s="21"/>
@@ -1324,10 +1324,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J23" s="18" t="n">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K23" s="18" t="n">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L23" s="25"/>
       <x:c r="M23" s="26"/>
@@ -1346,10 +1346,10 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E24" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F24" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G24" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1361,16 +1361,16 @@
         <x:v>950</x:v>
       </x:c>
       <x:c r="J24" s="18" t="n">
-        <x:v>171</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="K24" s="18" t="n">
-        <x:v>-779</x:v>
+        <x:v>-655</x:v>
       </x:c>
       <x:c r="L24" s="25" t="n">
-        <x:v>0.18</x:v>
+        <x:v>0.3105263157894737</x:v>
       </x:c>
       <x:c r="M24" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
@@ -1387,10 +1387,10 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E25" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F25" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G25" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1402,16 +1402,16 @@
         <x:v>950</x:v>
       </x:c>
       <x:c r="J25" s="18" t="n">
-        <x:v>201</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="K25" s="18" t="n">
-        <x:v>-749</x:v>
+        <x:v>-698</x:v>
       </x:c>
       <x:c r="L25" s="25" t="n">
-        <x:v>0.21157894736842106</x:v>
+        <x:v>0.26526315789473687</x:v>
       </x:c>
       <x:c r="M25" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
@@ -1419,7 +1419,7 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B26" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C26" s="12" t="str">
         <x:v>LLM外呼</x:v>
@@ -1431,7 +1431,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F26" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G26" s="21"/>
       <x:c r="H26" s="21"/>
@@ -1439,10 +1439,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J26" s="18" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K26" s="18" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L26" s="25"/>
       <x:c r="M26" s="26"/>
@@ -1452,7 +1452,7 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B27" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C27" s="12" t="str">
         <x:v>LLM外呼</x:v>
@@ -1461,10 +1461,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E27" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F27" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G27" s="21"/>
       <x:c r="H27" s="21"/>
@@ -1485,7 +1485,7 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B28" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C28" s="12" t="str">
         <x:v>LLM外呼</x:v>
@@ -1494,10 +1494,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E28" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F28" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G28" s="21"/>
       <x:c r="H28" s="21"/>
@@ -1505,10 +1505,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J28" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K28" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L28" s="25"/>
       <x:c r="M28" s="26"/>
@@ -1518,7 +1518,7 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B29" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C29" s="12" t="str">
         <x:v>LLM外呼</x:v>
@@ -1530,7 +1530,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F29" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G29" s="21"/>
       <x:c r="H29" s="21"/>
@@ -1538,10 +1538,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J29" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K29" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L29" s="25"/>
       <x:c r="M29" s="26"/>
@@ -1551,7 +1551,7 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B30" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C30" s="12" t="str">
         <x:v>LLM外呼</x:v>
@@ -1571,10 +1571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J30" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K30" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L30" s="25"/>
       <x:c r="M30" s="26"/>
@@ -1584,19 +1584,19 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B31" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C31" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D31" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E31" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F31" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G31" s="21"/>
       <x:c r="H31" s="21"/>
@@ -1604,10 +1604,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J31" s="18" t="n">
-        <x:v>140</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K31" s="18" t="n">
-        <x:v>140</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L31" s="25"/>
       <x:c r="M31" s="26"/>
@@ -1617,19 +1617,19 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B32" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C32" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D32" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E32" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F32" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G32" s="21"/>
       <x:c r="H32" s="21"/>
@@ -1637,10 +1637,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J32" s="18" t="n">
-        <x:v>130</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K32" s="18" t="n">
-        <x:v>130</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L32" s="25"/>
       <x:c r="M32" s="26"/>
@@ -1650,19 +1650,19 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B33" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C33" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D33" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E33" s="12" t="str">
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F33" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G33" s="21"/>
       <x:c r="H33" s="21"/>
@@ -1670,10 +1670,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J33" s="18" t="n">
-        <x:v>142</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K33" s="18" t="n">
-        <x:v>142</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L33" s="25"/>
       <x:c r="M33" s="26"/>
@@ -1686,16 +1686,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C34" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D34" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E34" s="12" t="str">
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F34" s="21" t="str">
-        <x:v>2026-06-22</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G34" s="21"/>
       <x:c r="H34" s="21"/>
@@ -1703,10 +1703,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J34" s="18" t="n">
-        <x:v>711</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="K34" s="18" t="n">
-        <x:v>711</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="L34" s="25"/>
       <x:c r="M34" s="26"/>
@@ -1719,13 +1719,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C35" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D35" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E35" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F35" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -1736,10 +1736,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J35" s="18" t="n">
-        <x:v>910</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="K35" s="18" t="n">
-        <x:v>910</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="L35" s="25"/>
       <x:c r="M35" s="26"/>
@@ -1752,16 +1752,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C36" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D36" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E36" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F36" s="21" t="str">
-        <x:v>2026-06-22</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G36" s="21"/>
       <x:c r="H36" s="21"/>
@@ -1769,10 +1769,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J36" s="18" t="n">
-        <x:v>1120</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="K36" s="18" t="n">
-        <x:v>1120</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L36" s="25"/>
       <x:c r="M36" s="26"/>
@@ -1788,13 +1788,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D37" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E37" s="12" t="str">
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F37" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G37" s="21"/>
       <x:c r="H37" s="21"/>
@@ -1802,10 +1802,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J37" s="18" t="n">
-        <x:v>479</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="K37" s="18" t="n">
-        <x:v>479</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="L37" s="25"/>
       <x:c r="M37" s="26"/>
@@ -1821,13 +1821,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D38" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E38" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F38" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G38" s="21"/>
       <x:c r="H38" s="21"/>
@@ -1835,10 +1835,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J38" s="18" t="n">
-        <x:v>318</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="K38" s="18" t="n">
-        <x:v>318</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="L38" s="25"/>
       <x:c r="M38" s="26"/>
@@ -1854,10 +1854,10 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D39" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E39" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F39" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -1868,10 +1868,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J39" s="18" t="n">
-        <x:v>385</x:v>
+        <x:v>910</x:v>
       </x:c>
       <x:c r="K39" s="18" t="n">
-        <x:v>385</x:v>
+        <x:v>910</x:v>
       </x:c>
       <x:c r="L39" s="25"/>
       <x:c r="M39" s="26"/>
@@ -1884,7 +1884,7 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C40" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D40" s="18" t="n">
         <x:v>990</x:v>
@@ -1901,10 +1901,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J40" s="18" t="n">
-        <x:v>481</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="K40" s="18" t="n">
-        <x:v>481</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="L40" s="25"/>
       <x:c r="M40" s="26"/>
@@ -1917,16 +1917,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C41" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D41" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E41" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F41" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G41" s="21"/>
       <x:c r="H41" s="21"/>
@@ -1934,10 +1934,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J41" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="K41" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="L41" s="25"/>
       <x:c r="M41" s="26"/>
@@ -1950,13 +1950,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C42" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D42" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E42" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F42" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -1967,10 +1967,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J42" s="18" t="n">
-        <x:v>504</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="K42" s="18" t="n">
-        <x:v>504</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="L42" s="25"/>
       <x:c r="M42" s="26"/>
@@ -1983,16 +1983,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C43" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D43" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E43" s="12" t="str">
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F43" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G43" s="21"/>
       <x:c r="H43" s="21"/>
@@ -2000,10 +2000,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J43" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="K43" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="L43" s="25"/>
       <x:c r="M43" s="26"/>
@@ -2016,16 +2016,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C44" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D44" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E44" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F44" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G44" s="21"/>
       <x:c r="H44" s="21"/>
@@ -2033,10 +2033,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J44" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="K44" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="L44" s="25"/>
       <x:c r="M44" s="26"/>
@@ -2049,13 +2049,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C45" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D45" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E45" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F45" s="21" t="str">
         <x:v>2026-06-21</x:v>
@@ -2066,10 +2066,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J45" s="18" t="n">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K45" s="18" t="n">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L45" s="25"/>
       <x:c r="M45" s="26"/>
@@ -2085,13 +2085,13 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D46" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E46" s="12" t="str">
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F46" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G46" s="21"/>
       <x:c r="H46" s="21"/>
@@ -2099,10 +2099,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J46" s="18" t="n">
-        <x:v>134</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K46" s="18" t="n">
-        <x:v>134</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L46" s="25"/>
       <x:c r="M46" s="26"/>
@@ -2118,13 +2118,13 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D47" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E47" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F47" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G47" s="21"/>
       <x:c r="H47" s="21"/>
@@ -2132,10 +2132,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J47" s="18" t="n">
-        <x:v>43</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K47" s="18" t="n">
-        <x:v>43</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L47" s="25"/>
       <x:c r="M47" s="26"/>
@@ -2151,13 +2151,13 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D48" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E48" s="12" t="str">
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F48" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G48" s="21"/>
       <x:c r="H48" s="21"/>
@@ -2165,10 +2165,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J48" s="18" t="n">
-        <x:v>224</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K48" s="18" t="n">
-        <x:v>224</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L48" s="25"/>
       <x:c r="M48" s="26"/>
@@ -2184,10 +2184,10 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D49" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E49" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F49" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -2198,10 +2198,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J49" s="18" t="n">
-        <x:v>256</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="K49" s="18" t="n">
-        <x:v>256</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="L49" s="25"/>
       <x:c r="M49" s="26"/>
@@ -2214,16 +2214,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C50" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D50" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E50" s="12" t="str">
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F50" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G50" s="21"/>
       <x:c r="H50" s="21"/>
@@ -2231,10 +2231,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J50" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K50" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="L50" s="25"/>
       <x:c r="M50" s="26"/>
@@ -2247,13 +2247,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C51" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D51" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E51" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F51" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -2264,10 +2264,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J51" s="18" t="n">
-        <x:v>336</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="K51" s="18" t="n">
-        <x:v>336</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="L51" s="25"/>
       <x:c r="M51" s="26"/>
@@ -2280,13 +2280,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C52" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D52" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E52" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F52" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -2297,10 +2297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J52" s="18" t="n">
-        <x:v>318</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="K52" s="18" t="n">
-        <x:v>318</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="L52" s="25"/>
       <x:c r="M52" s="26"/>
@@ -2316,13 +2316,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D53" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E53" s="12" t="str">
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F53" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G53" s="21"/>
       <x:c r="H53" s="21"/>
@@ -2330,10 +2330,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J53" s="18" t="n">
-        <x:v>326</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K53" s="18" t="n">
-        <x:v>326</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L53" s="25"/>
       <x:c r="M53" s="26"/>
@@ -2349,10 +2349,10 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D54" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E54" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F54" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -2363,10 +2363,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J54" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="K54" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="L54" s="25"/>
       <x:c r="M54" s="26"/>
@@ -2382,10 +2382,10 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D55" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E55" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F55" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -2396,10 +2396,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J55" s="18" t="n">
-        <x:v>10</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="K55" s="18" t="n">
-        <x:v>10</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="L55" s="25"/>
       <x:c r="M55" s="26"/>
@@ -2415,13 +2415,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D56" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E56" s="12" t="str">
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F56" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G56" s="21"/>
       <x:c r="H56" s="21"/>
@@ -2429,10 +2429,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J56" s="18" t="n">
-        <x:v>48</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="K56" s="18" t="n">
-        <x:v>48</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="L56" s="25"/>
       <x:c r="M56" s="26"/>
@@ -2448,10 +2448,10 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D57" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E57" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F57" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -2462,10 +2462,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J57" s="18" t="n">
-        <x:v>374</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K57" s="18" t="n">
-        <x:v>374</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L57" s="25"/>
       <x:c r="M57" s="26"/>
@@ -2481,10 +2481,10 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D58" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E58" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F58" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -2495,32 +2495,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J58" s="18" t="n">
-        <x:v>430</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K58" s="18" t="n">
-        <x:v>430</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L58" s="25"/>
       <x:c r="M58" s="26"/>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
       <x:c r="A59" s="11" t="str">
-        <x:v>小学</x:v>
+        <x:v>初中</x:v>
       </x:c>
       <x:c r="B59" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C59" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D59" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E59" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F59" s="21" t="str">
-        <x:v>2026-06-19</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G59" s="21"/>
       <x:c r="H59" s="21"/>
@@ -2528,32 +2528,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J59" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K59" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L59" s="25"/>
       <x:c r="M59" s="26"/>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
       <x:c r="A60" s="11" t="str">
-        <x:v>小学</x:v>
+        <x:v>初中</x:v>
       </x:c>
       <x:c r="B60" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C60" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D60" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E60" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F60" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G60" s="21"/>
       <x:c r="H60" s="21"/>
@@ -2561,32 +2561,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J60" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="K60" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="L60" s="25"/>
       <x:c r="M60" s="26"/>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
       <x:c r="A61" s="11" t="str">
-        <x:v>小学</x:v>
+        <x:v>初中</x:v>
       </x:c>
       <x:c r="B61" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C61" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D61" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E61" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F61" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G61" s="21"/>
       <x:c r="H61" s="21"/>
@@ -2594,10 +2594,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J61" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="K61" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="L61" s="25"/>
       <x:c r="M61" s="26"/>
@@ -2616,7 +2616,7 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E62" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F62" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -2627,10 +2627,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J62" s="18" t="n">
-        <x:v>76</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K62" s="18" t="n">
-        <x:v>76</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L62" s="25"/>
       <x:c r="M62" s="26"/>
@@ -2649,10 +2649,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E63" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F63" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-19</x:v>
       </x:c>
       <x:c r="G63" s="21"/>
       <x:c r="H63" s="21"/>
@@ -2660,10 +2660,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J63" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K63" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L63" s="25"/>
       <x:c r="M63" s="26"/>
@@ -2673,19 +2673,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B64" s="12" t="str">
-        <x:v>暑_6</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C64" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D64" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E64" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F64" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G64" s="21"/>
       <x:c r="H64" s="21"/>
@@ -2693,10 +2693,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J64" s="18" t="n">
-        <x:v>51</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K64" s="18" t="n">
-        <x:v>51</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L64" s="25"/>
       <x:c r="M64" s="26"/>
@@ -2706,19 +2706,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B65" s="12" t="str">
-        <x:v>暑_6</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C65" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D65" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E65" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F65" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G65" s="21"/>
       <x:c r="H65" s="21"/>
@@ -2726,10 +2726,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J65" s="18" t="n">
-        <x:v>35</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K65" s="18" t="n">
-        <x:v>35</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L65" s="25"/>
       <x:c r="M65" s="26"/>
@@ -2739,19 +2739,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B66" s="12" t="str">
-        <x:v>暑_6</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C66" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D66" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E66" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F66" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G66" s="21"/>
       <x:c r="H66" s="21"/>
@@ -2759,10 +2759,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J66" s="18" t="n">
-        <x:v>68</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K66" s="18" t="n">
-        <x:v>68</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="L66" s="25"/>
       <x:c r="M66" s="26"/>
@@ -2772,10 +2772,10 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B67" s="12" t="str">
-        <x:v>暑_6</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C67" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D67" s="18" t="n">
         <x:v>990</x:v>
@@ -2784,7 +2784,7 @@
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F67" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G67" s="21"/>
       <x:c r="H67" s="21"/>
@@ -2792,10 +2792,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J67" s="18" t="n">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K67" s="18" t="n">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L67" s="25"/>
       <x:c r="M67" s="26"/>
@@ -2808,16 +2808,16 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C68" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D68" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E68" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F68" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G68" s="21"/>
       <x:c r="H68" s="21"/>
@@ -2825,10 +2825,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J68" s="18" t="n">
-        <x:v>13</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K68" s="18" t="n">
-        <x:v>13</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="L68" s="25"/>
       <x:c r="M68" s="26"/>
@@ -2841,16 +2841,16 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C69" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D69" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E69" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F69" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G69" s="21"/>
       <x:c r="H69" s="21"/>
@@ -2858,10 +2858,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J69" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K69" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L69" s="25"/>
       <x:c r="M69" s="26"/>
@@ -2874,16 +2874,16 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C70" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D70" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E70" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F70" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G70" s="21"/>
       <x:c r="H70" s="21"/>
@@ -2891,10 +2891,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J70" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="K70" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="L70" s="25"/>
       <x:c r="M70" s="26"/>
@@ -2907,13 +2907,13 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C71" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D71" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E71" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F71" s="21" t="str">
         <x:v>2026-06-17</x:v>
@@ -2924,10 +2924,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J71" s="18" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K71" s="18" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L71" s="25"/>
       <x:c r="M71" s="26"/>
@@ -2940,13 +2940,13 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C72" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D72" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E72" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F72" s="21" t="str">
         <x:v>2026-06-17</x:v>
@@ -2957,10 +2957,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J72" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K72" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L72" s="25"/>
       <x:c r="M72" s="26"/>
@@ -2973,13 +2973,13 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C73" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D73" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E73" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F73" s="21" t="str">
         <x:v>2026-06-17</x:v>
@@ -2990,10 +2990,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J73" s="18" t="n">
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K73" s="18" t="n">
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L73" s="25"/>
       <x:c r="M73" s="26"/>
@@ -3003,19 +3003,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B74" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C74" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D74" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E74" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F74" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G74" s="21"/>
       <x:c r="H74" s="21"/>
@@ -3023,10 +3023,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J74" s="18" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K74" s="18" t="n">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L74" s="25"/>
       <x:c r="M74" s="26"/>
@@ -3036,19 +3036,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B75" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C75" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D75" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E75" s="12" t="str">
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F75" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G75" s="21"/>
       <x:c r="H75" s="21"/>
@@ -3056,10 +3056,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J75" s="18" t="n">
-        <x:v>28</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K75" s="18" t="n">
-        <x:v>28</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L75" s="25"/>
       <x:c r="M75" s="26"/>
@@ -3069,19 +3069,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B76" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C76" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D76" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E76" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F76" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G76" s="21"/>
       <x:c r="H76" s="21"/>
@@ -3089,10 +3089,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J76" s="18" t="n">
-        <x:v>22</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K76" s="18" t="n">
-        <x:v>22</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L76" s="25"/>
       <x:c r="M76" s="26"/>
@@ -3102,19 +3102,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B77" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C77" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D77" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E77" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F77" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G77" s="21"/>
       <x:c r="H77" s="21"/>
@@ -3122,10 +3122,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J77" s="18" t="n">
-        <x:v>24</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K77" s="18" t="n">
-        <x:v>24</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L77" s="25"/>
       <x:c r="M77" s="26"/>
@@ -3138,16 +3138,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C78" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D78" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E78" s="12" t="str">
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F78" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G78" s="21"/>
       <x:c r="H78" s="21"/>
@@ -3155,10 +3155,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J78" s="18" t="n">
-        <x:v>1968</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K78" s="18" t="n">
-        <x:v>1968</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L78" s="25"/>
       <x:c r="M78" s="26"/>
@@ -3171,16 +3171,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C79" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D79" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E79" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F79" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G79" s="21"/>
       <x:c r="H79" s="21"/>
@@ -3188,10 +3188,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J79" s="18" t="n">
-        <x:v>1513</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K79" s="18" t="n">
-        <x:v>1513</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="L79" s="25"/>
       <x:c r="M79" s="26"/>
@@ -3204,16 +3204,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C80" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D80" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E80" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F80" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G80" s="21"/>
       <x:c r="H80" s="21"/>
@@ -3221,10 +3221,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J80" s="18" t="n">
-        <x:v>1857</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="K80" s="18" t="n">
-        <x:v>1857</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="L80" s="25"/>
       <x:c r="M80" s="26"/>
@@ -3237,16 +3237,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C81" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D81" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E81" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F81" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G81" s="21"/>
       <x:c r="H81" s="21"/>
@@ -3254,10 +3254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J81" s="18" t="n">
-        <x:v>2036</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K81" s="18" t="n">
-        <x:v>2036</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L81" s="25"/>
       <x:c r="M81" s="26"/>
@@ -3273,7 +3273,7 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D82" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E82" s="12" t="str">
         <x:v>三年级</x:v>
@@ -3287,10 +3287,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J82" s="18" t="n">
-        <x:v>131</x:v>
+        <x:v>1968</x:v>
       </x:c>
       <x:c r="K82" s="18" t="n">
-        <x:v>131</x:v>
+        <x:v>1968</x:v>
       </x:c>
       <x:c r="L82" s="25"/>
       <x:c r="M82" s="26"/>
@@ -3306,13 +3306,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D83" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E83" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F83" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G83" s="21"/>
       <x:c r="H83" s="21"/>
@@ -3320,10 +3320,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J83" s="18" t="n">
-        <x:v>156</x:v>
+        <x:v>2036</x:v>
       </x:c>
       <x:c r="K83" s="18" t="n">
-        <x:v>156</x:v>
+        <x:v>2036</x:v>
       </x:c>
       <x:c r="L83" s="25"/>
       <x:c r="M83" s="26"/>
@@ -3339,13 +3339,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D84" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E84" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F84" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G84" s="21"/>
       <x:c r="H84" s="21"/>
@@ -3353,10 +3353,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J84" s="18" t="n">
-        <x:v>135</x:v>
+        <x:v>1513</x:v>
       </x:c>
       <x:c r="K84" s="18" t="n">
-        <x:v>135</x:v>
+        <x:v>1513</x:v>
       </x:c>
       <x:c r="L84" s="25"/>
       <x:c r="M84" s="26"/>
@@ -3372,13 +3372,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D85" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E85" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F85" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G85" s="21"/>
       <x:c r="H85" s="21"/>
@@ -3386,10 +3386,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J85" s="18" t="n">
-        <x:v>191</x:v>
+        <x:v>1857</x:v>
       </x:c>
       <x:c r="K85" s="18" t="n">
-        <x:v>191</x:v>
+        <x:v>1857</x:v>
       </x:c>
       <x:c r="L85" s="25"/>
       <x:c r="M85" s="26"/>
@@ -3402,7 +3402,7 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C86" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D86" s="18" t="n">
         <x:v>990</x:v>
@@ -3419,10 +3419,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J86" s="18" t="n">
-        <x:v>239</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="K86" s="18" t="n">
-        <x:v>239</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="L86" s="25"/>
       <x:c r="M86" s="26"/>
@@ -3435,16 +3435,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C87" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D87" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E87" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F87" s="21" t="str">
-        <x:v>2026-06-22</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G87" s="21"/>
       <x:c r="H87" s="21"/>
@@ -3452,10 +3452,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J87" s="18" t="n">
-        <x:v>66</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="K87" s="18" t="n">
-        <x:v>66</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="L87" s="25"/>
       <x:c r="M87" s="26"/>
@@ -3468,7 +3468,7 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C88" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D88" s="18" t="n">
         <x:v>990</x:v>
@@ -3477,7 +3477,7 @@
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F88" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G88" s="21"/>
       <x:c r="H88" s="21"/>
@@ -3485,10 +3485,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J88" s="18" t="n">
-        <x:v>235</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="K88" s="18" t="n">
-        <x:v>235</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="L88" s="25"/>
       <x:c r="M88" s="26"/>
@@ -3501,7 +3501,7 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C89" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D89" s="18" t="n">
         <x:v>990</x:v>
@@ -3518,10 +3518,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J89" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="K89" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L89" s="25"/>
       <x:c r="M89" s="26"/>
@@ -3540,10 +3540,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E90" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F90" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G90" s="21"/>
       <x:c r="H90" s="21"/>
@@ -3551,10 +3551,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J90" s="18" t="n">
-        <x:v>252</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K90" s="18" t="n">
-        <x:v>252</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="L90" s="25"/>
       <x:c r="M90" s="26"/>
@@ -3567,10 +3567,10 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C91" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D91" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E91" s="12" t="str">
         <x:v>三年级</x:v>
@@ -3584,10 +3584,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J91" s="18" t="n">
-        <x:v>181</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K91" s="18" t="n">
-        <x:v>181</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="L91" s="25"/>
       <x:c r="M91" s="26"/>
@@ -3600,16 +3600,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C92" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D92" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E92" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F92" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G92" s="21"/>
       <x:c r="H92" s="21"/>
@@ -3617,10 +3617,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J92" s="18" t="n">
-        <x:v>135</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="K92" s="18" t="n">
-        <x:v>135</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="L92" s="25"/>
       <x:c r="M92" s="26"/>
@@ -3633,13 +3633,13 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C93" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D93" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E93" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F93" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -3650,10 +3650,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J93" s="18" t="n">
-        <x:v>191</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="K93" s="18" t="n">
-        <x:v>191</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="L93" s="25"/>
       <x:c r="M93" s="26"/>
@@ -3666,16 +3666,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C94" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D94" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E94" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F94" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G94" s="21"/>
       <x:c r="H94" s="21"/>
@@ -3683,10 +3683,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J94" s="18" t="n">
-        <x:v>214</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K94" s="18" t="n">
-        <x:v>214</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L94" s="25"/>
       <x:c r="M94" s="26"/>
@@ -3699,7 +3699,7 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C95" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D95" s="18" t="n">
         <x:v>100</x:v>
@@ -3708,7 +3708,7 @@
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F95" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G95" s="21"/>
       <x:c r="H95" s="21"/>
@@ -3716,10 +3716,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J95" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="K95" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="L95" s="25"/>
       <x:c r="M95" s="26"/>
@@ -3732,16 +3732,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C96" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D96" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E96" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F96" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G96" s="21"/>
       <x:c r="H96" s="21"/>
@@ -3749,10 +3749,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J96" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="K96" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="L96" s="25"/>
       <x:c r="M96" s="26"/>
@@ -3765,16 +3765,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C97" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D97" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E97" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F97" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G97" s="21"/>
       <x:c r="H97" s="21"/>
@@ -3782,10 +3782,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J97" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="K97" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L97" s="25"/>
       <x:c r="M97" s="26"/>
@@ -3798,13 +3798,13 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C98" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D98" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E98" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F98" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -3815,10 +3815,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J98" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="K98" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="L98" s="25"/>
       <x:c r="M98" s="26"/>
@@ -3834,13 +3834,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D99" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E99" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F99" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G99" s="21"/>
       <x:c r="H99" s="21"/>
@@ -3848,10 +3848,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J99" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K99" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L99" s="25"/>
       <x:c r="M99" s="26"/>
@@ -3867,13 +3867,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D100" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E100" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F100" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G100" s="21"/>
       <x:c r="H100" s="21"/>
@@ -3881,10 +3881,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J100" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K100" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L100" s="25"/>
       <x:c r="M100" s="26"/>
@@ -3900,13 +3900,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D101" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E101" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F101" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G101" s="21"/>
       <x:c r="H101" s="21"/>
@@ -3914,10 +3914,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J101" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K101" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L101" s="25"/>
       <x:c r="M101" s="26"/>
@@ -3933,13 +3933,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D102" s="18" t="n">
-        <x:v>1880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E102" s="12" t="str">
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F102" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G102" s="21"/>
       <x:c r="H102" s="21"/>
@@ -3966,13 +3966,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D103" s="18" t="n">
-        <x:v>1880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E103" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F103" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G103" s="21"/>
       <x:c r="H103" s="21"/>
@@ -3980,10 +3980,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J103" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K103" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L103" s="25"/>
       <x:c r="M103" s="26"/>
@@ -3999,13 +3999,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D104" s="18" t="n">
-        <x:v>1880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E104" s="12" t="str">
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F104" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G104" s="21"/>
       <x:c r="H104" s="21"/>
@@ -4013,10 +4013,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J104" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K104" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L104" s="25"/>
       <x:c r="M104" s="26"/>
@@ -4032,13 +4032,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D105" s="18" t="n">
-        <x:v>1880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E105" s="12" t="str">
         <x:v>六年级</x:v>
       </x:c>
       <x:c r="F105" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G105" s="21"/>
       <x:c r="H105" s="21"/>
@@ -4046,10 +4046,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J105" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K105" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L105" s="25"/>
       <x:c r="M105" s="26"/>
@@ -4068,10 +4068,10 @@
         <x:v>1880</x:v>
       </x:c>
       <x:c r="E106" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F106" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G106" s="21"/>
       <x:c r="H106" s="21"/>
@@ -4079,10 +4079,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J106" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K106" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L106" s="25"/>
       <x:c r="M106" s="26"/>
@@ -4098,13 +4098,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D107" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>1880</x:v>
       </x:c>
       <x:c r="E107" s="12" t="str">
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F107" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G107" s="21"/>
       <x:c r="H107" s="21"/>
@@ -4112,10 +4112,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J107" s="18" t="n">
-        <x:v>227</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K107" s="18" t="n">
-        <x:v>227</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L107" s="25"/>
       <x:c r="M107" s="26"/>
@@ -4131,13 +4131,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D108" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>1880</x:v>
       </x:c>
       <x:c r="E108" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F108" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G108" s="21"/>
       <x:c r="H108" s="21"/>
@@ -4145,10 +4145,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J108" s="18" t="n">
-        <x:v>89</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K108" s="18" t="n">
-        <x:v>89</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L108" s="25"/>
       <x:c r="M108" s="26"/>
@@ -4164,13 +4164,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D109" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>1880</x:v>
       </x:c>
       <x:c r="E109" s="12" t="str">
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F109" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G109" s="21"/>
       <x:c r="H109" s="21"/>
@@ -4178,10 +4178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J109" s="18" t="n">
-        <x:v>229</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K109" s="18" t="n">
-        <x:v>229</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L109" s="25"/>
       <x:c r="M109" s="26"/>
@@ -4197,13 +4197,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D110" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>1880</x:v>
       </x:c>
       <x:c r="E110" s="12" t="str">
         <x:v>六年级</x:v>
       </x:c>
       <x:c r="F110" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G110" s="21"/>
       <x:c r="H110" s="21"/>
@@ -4211,10 +4211,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J110" s="18" t="n">
-        <x:v>264</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K110" s="18" t="n">
-        <x:v>264</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L110" s="25"/>
       <x:c r="M110" s="26"/>
@@ -4233,7 +4233,7 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E111" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F111" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -4244,10 +4244,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J111" s="18" t="n">
-        <x:v>291</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K111" s="18" t="n">
-        <x:v>291</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="L111" s="25"/>
       <x:c r="M111" s="26"/>
@@ -4257,156 +4257,132 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B112" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C112" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D112" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E112" s="12" t="str">
         <x:v>三年级</x:v>
       </x:c>
-      <x:c r="F112" s="21"/>
-      <x:c r="G112" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H112" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+      <x:c r="F112" s="21" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="G112" s="21"/>
+      <x:c r="H112" s="21"/>
       <x:c r="I112" s="18" t="n">
-        <x:v>40</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J112" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="K112" s="18" t="n">
-        <x:v>-40</x:v>
-      </x:c>
-      <x:c r="L112" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M112" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
-      </x:c>
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="L112" s="25"/>
+      <x:c r="M112" s="26"/>
     </x:row>
     <x:row r="113" ht="15" hidden="0" customHeight="1">
       <x:c r="A113" s="11" t="str">
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B113" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C113" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D113" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E113" s="12" t="str">
-        <x:v>五年级</x:v>
-      </x:c>
-      <x:c r="F113" s="21"/>
-      <x:c r="G113" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H113" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>四年级</x:v>
+      </x:c>
+      <x:c r="F113" s="21" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="G113" s="21"/>
+      <x:c r="H113" s="21"/>
       <x:c r="I113" s="18" t="n">
-        <x:v>120</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J113" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="K113" s="18" t="n">
-        <x:v>-120</x:v>
-      </x:c>
-      <x:c r="L113" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M113" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
-      </x:c>
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="L113" s="25"/>
+      <x:c r="M113" s="26"/>
     </x:row>
     <x:row r="114" ht="15" hidden="0" customHeight="1">
       <x:c r="A114" s="11" t="str">
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B114" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C114" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D114" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E114" s="12" t="str">
-        <x:v>六年级</x:v>
-      </x:c>
-      <x:c r="F114" s="21"/>
-      <x:c r="G114" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H114" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>五年级</x:v>
+      </x:c>
+      <x:c r="F114" s="21" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="G114" s="21"/>
+      <x:c r="H114" s="21"/>
       <x:c r="I114" s="18" t="n">
-        <x:v>120</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J114" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="K114" s="18" t="n">
-        <x:v>-120</x:v>
-      </x:c>
-      <x:c r="L114" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M114" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
-      </x:c>
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="L114" s="25"/>
+      <x:c r="M114" s="26"/>
     </x:row>
     <x:row r="115" ht="15" hidden="0" customHeight="1">
       <x:c r="A115" s="11" t="str">
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B115" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C115" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D115" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E115" s="12" t="str">
-        <x:v>四年级</x:v>
-      </x:c>
-      <x:c r="F115" s="21"/>
-      <x:c r="G115" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H115" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>六年级</x:v>
+      </x:c>
+      <x:c r="F115" s="21" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="G115" s="21"/>
+      <x:c r="H115" s="21"/>
       <x:c r="I115" s="18" t="n">
-        <x:v>120</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J115" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="K115" s="18" t="n">
-        <x:v>-120</x:v>
-      </x:c>
-      <x:c r="L115" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M115" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
-      </x:c>
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="L115" s="25"/>
+      <x:c r="M115" s="26"/>
     </x:row>
     <x:row r="116" ht="15" hidden="0" customHeight="1">
       <x:c r="A116" s="11" t="str">
@@ -4416,17 +4392,15 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C116" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D116" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E116" s="12" t="str">
         <x:v>三年级</x:v>
       </x:c>
-      <x:c r="F116" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+      <x:c r="F116" s="21"/>
       <x:c r="G116" s="21" t="str">
         <x:v>2026-07-01</x:v>
       </x:c>
@@ -4434,19 +4408,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I116" s="18" t="n">
-        <x:v>2300</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J116" s="18" t="n">
-        <x:v>707</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K116" s="18" t="n">
-        <x:v>-1593</x:v>
+        <x:v>-40</x:v>
       </x:c>
       <x:c r="L116" s="25" t="n">
-        <x:v>0.3073913043478261</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M116" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
@@ -4457,17 +4431,15 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C117" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D117" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E117" s="12" t="str">
-        <x:v>五年级</x:v>
-      </x:c>
-      <x:c r="F117" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>四年级</x:v>
+      </x:c>
+      <x:c r="F117" s="21"/>
       <x:c r="G117" s="21" t="str">
         <x:v>2026-07-01</x:v>
       </x:c>
@@ -4475,19 +4447,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I117" s="18" t="n">
-        <x:v>2000</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J117" s="18" t="n">
-        <x:v>645</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K117" s="18" t="n">
-        <x:v>-1355</x:v>
+        <x:v>-120</x:v>
       </x:c>
       <x:c r="L117" s="25" t="n">
-        <x:v>0.3225</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M117" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -4498,17 +4470,15 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C118" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D118" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E118" s="12" t="str">
-        <x:v>六年级</x:v>
-      </x:c>
-      <x:c r="F118" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>五年级</x:v>
+      </x:c>
+      <x:c r="F118" s="21"/>
       <x:c r="G118" s="21" t="str">
         <x:v>2026-07-01</x:v>
       </x:c>
@@ -4516,19 +4486,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I118" s="18" t="n">
-        <x:v>2300</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J118" s="18" t="n">
-        <x:v>711</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K118" s="18" t="n">
-        <x:v>-1589</x:v>
+        <x:v>-120</x:v>
       </x:c>
       <x:c r="L118" s="25" t="n">
-        <x:v>0.3091304347826087</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M118" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -4539,17 +4509,15 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C119" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D119" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E119" s="12" t="str">
-        <x:v>四年级</x:v>
-      </x:c>
-      <x:c r="F119" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>六年级</x:v>
+      </x:c>
+      <x:c r="F119" s="21"/>
       <x:c r="G119" s="21" t="str">
         <x:v>2026-07-01</x:v>
       </x:c>
@@ -4557,19 +4525,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I119" s="18" t="n">
-        <x:v>2500</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J119" s="18" t="n">
-        <x:v>857</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K119" s="18" t="n">
-        <x:v>-1643</x:v>
+        <x:v>-120</x:v>
       </x:c>
       <x:c r="L119" s="25" t="n">
-        <x:v>0.3428</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M119" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -4583,13 +4551,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D120" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E120" s="12" t="str">
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F120" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G120" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4598,19 +4566,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I120" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="J120" s="18" t="n">
-        <x:v>44</x:v>
+        <x:v>1106</x:v>
       </x:c>
       <x:c r="K120" s="18" t="n">
-        <x:v>-56</x:v>
+        <x:v>-1194</x:v>
       </x:c>
       <x:c r="L120" s="25" t="n">
-        <x:v>0.44</x:v>
+        <x:v>0.4808695652173913</x:v>
       </x:c>
       <x:c r="M120" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -4624,13 +4592,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D121" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E121" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F121" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G121" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4639,19 +4607,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I121" s="18" t="n">
-        <x:v>120</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="J121" s="18" t="n">
-        <x:v>32</x:v>
+        <x:v>1208</x:v>
       </x:c>
       <x:c r="K121" s="18" t="n">
-        <x:v>-88</x:v>
+        <x:v>-1292</x:v>
       </x:c>
       <x:c r="L121" s="25" t="n">
-        <x:v>0.26666666666666666</x:v>
+        <x:v>0.4832</x:v>
       </x:c>
       <x:c r="M121" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -4665,13 +4633,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D122" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E122" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F122" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G122" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4680,19 +4648,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I122" s="18" t="n">
-        <x:v>150</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="J122" s="18" t="n">
-        <x:v>34</x:v>
+        <x:v>972</x:v>
       </x:c>
       <x:c r="K122" s="18" t="n">
-        <x:v>-116</x:v>
+        <x:v>-1028</x:v>
       </x:c>
       <x:c r="L122" s="25" t="n">
-        <x:v>0.22666666666666666</x:v>
+        <x:v>0.486</x:v>
       </x:c>
       <x:c r="M122" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -4706,13 +4674,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D123" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E123" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F123" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G123" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4721,19 +4689,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I123" s="18" t="n">
-        <x:v>150</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="J123" s="18" t="n">
-        <x:v>44</x:v>
+        <x:v>999</x:v>
       </x:c>
       <x:c r="K123" s="18" t="n">
-        <x:v>-106</x:v>
+        <x:v>-1301</x:v>
       </x:c>
       <x:c r="L123" s="25" t="n">
-        <x:v>0.29333333333333333</x:v>
+        <x:v>0.43434782608695655</x:v>
       </x:c>
       <x:c r="M123" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -4744,7 +4712,7 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C124" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D124" s="18" t="n">
         <x:v>990</x:v>
@@ -4753,7 +4721,7 @@
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F124" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G124" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4765,16 +4733,16 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J124" s="18" t="n">
-        <x:v>42</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K124" s="18" t="n">
-        <x:v>-58</x:v>
+        <x:v>-28</x:v>
       </x:c>
       <x:c r="L124" s="25" t="n">
-        <x:v>0.42</x:v>
+        <x:v>0.72</x:v>
       </x:c>
       <x:c r="M124" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -4785,30 +4753,38 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C125" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D125" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E125" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F125" s="21" t="str">
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G125" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H125" s="21" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
-      <x:c r="G125" s="21"/>
-      <x:c r="H125" s="21"/>
       <x:c r="I125" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J125" s="18" t="n">
-        <x:v>25</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="K125" s="18" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="L125" s="25"/>
-      <x:c r="M125" s="26"/>
+        <x:v>-58</x:v>
+      </x:c>
+      <x:c r="L125" s="25" t="n">
+        <x:v>0.6133333333333333</x:v>
+      </x:c>
+      <x:c r="M125" s="26" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
       <x:c r="A126" s="11" t="str">
@@ -4818,7 +4794,7 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C126" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D126" s="18" t="n">
         <x:v>990</x:v>
@@ -4827,7 +4803,7 @@
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F126" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G126" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4836,19 +4812,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I126" s="18" t="n">
-        <x:v>200</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J126" s="18" t="n">
-        <x:v>40</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K126" s="18" t="n">
-        <x:v>-160</x:v>
+        <x:v>-59</x:v>
       </x:c>
       <x:c r="L126" s="25" t="n">
-        <x:v>0.2</x:v>
+        <x:v>0.5083333333333333</x:v>
       </x:c>
       <x:c r="M126" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -4859,7 +4835,7 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C127" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D127" s="18" t="n">
         <x:v>990</x:v>
@@ -4868,7 +4844,7 @@
         <x:v>六年级</x:v>
       </x:c>
       <x:c r="F127" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G127" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4877,19 +4853,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I127" s="18" t="n">
-        <x:v>200</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J127" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="K127" s="18" t="n">
-        <x:v>-196</x:v>
+        <x:v>-93</x:v>
       </x:c>
       <x:c r="L127" s="25" t="n">
-        <x:v>0.02</x:v>
+        <x:v>0.38</x:v>
       </x:c>
       <x:c r="M127" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -4906,32 +4882,24 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E128" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F128" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
-      <x:c r="G128" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H128" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G128" s="21"/>
+      <x:c r="H128" s="21"/>
       <x:c r="I128" s="18" t="n">
-        <x:v>300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J128" s="18" t="n">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K128" s="18" t="n">
-        <x:v>-257</x:v>
-      </x:c>
-      <x:c r="L128" s="25" t="n">
-        <x:v>0.14333333333333334</x:v>
-      </x:c>
-      <x:c r="M128" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
-      </x:c>
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="L128" s="25"/>
+      <x:c r="M128" s="26"/>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
       <x:c r="A129" s="11" t="str">
@@ -4941,30 +4909,38 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C129" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D129" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E129" s="12" t="str">
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F129" s="21" t="str">
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G129" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H129" s="21" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
-      <x:c r="G129" s="21"/>
-      <x:c r="H129" s="21"/>
       <x:c r="I129" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J129" s="18" t="n">
-        <x:v>91</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="K129" s="18" t="n">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="L129" s="25"/>
-      <x:c r="M129" s="26"/>
+        <x:v>-33</x:v>
+      </x:c>
+      <x:c r="L129" s="25" t="n">
+        <x:v>0.67</x:v>
+      </x:c>
+      <x:c r="M129" s="26" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
       <x:c r="A130" s="11" t="str">
@@ -4974,30 +4950,38 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C130" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D130" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E130" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F130" s="21" t="str">
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G130" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H130" s="21" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
-      <x:c r="G130" s="21"/>
-      <x:c r="H130" s="21"/>
       <x:c r="I130" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J130" s="18" t="n">
-        <x:v>80</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K130" s="18" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="L130" s="25"/>
-      <x:c r="M130" s="26"/>
+        <x:v>-228</x:v>
+      </x:c>
+      <x:c r="L130" s="25" t="n">
+        <x:v>0.24</x:v>
+      </x:c>
+      <x:c r="M130" s="26" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
       <x:c r="A131" s="11" t="str">
@@ -5007,30 +4991,38 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C131" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D131" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E131" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F131" s="21" t="str">
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G131" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H131" s="21" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
-      <x:c r="G131" s="21"/>
-      <x:c r="H131" s="21"/>
       <x:c r="I131" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="J131" s="18" t="n">
-        <x:v>92</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K131" s="18" t="n">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="L131" s="25"/>
-      <x:c r="M131" s="26"/>
+        <x:v>-127</x:v>
+      </x:c>
+      <x:c r="L131" s="25" t="n">
+        <x:v>0.365</x:v>
+      </x:c>
+      <x:c r="M131" s="26" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
       <x:c r="A132" s="11" t="str">
@@ -5040,30 +5032,38 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C132" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D132" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E132" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F132" s="21" t="str">
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G132" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H132" s="21" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
-      <x:c r="G132" s="21"/>
-      <x:c r="H132" s="21"/>
       <x:c r="I132" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="J132" s="18" t="n">
-        <x:v>134</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K132" s="18" t="n">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="L132" s="25"/>
-      <x:c r="M132" s="26"/>
+        <x:v>-195</x:v>
+      </x:c>
+      <x:c r="L132" s="25" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+      <x:c r="M132" s="26" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
       <x:c r="A133" s="11" t="str">
@@ -5073,38 +5073,30 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C133" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D133" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E133" s="12" t="str">
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F133" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
-      <x:c r="G133" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H133" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G133" s="21"/>
+      <x:c r="H133" s="21"/>
       <x:c r="I133" s="18" t="n">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J133" s="18" t="n">
-        <x:v>15</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="K133" s="18" t="n">
-        <x:v>-35</x:v>
-      </x:c>
-      <x:c r="L133" s="25" t="n">
-        <x:v>0.3</x:v>
-      </x:c>
-      <x:c r="M133" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
-      </x:c>
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="L133" s="25"/>
+      <x:c r="M133" s="26"/>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
       <x:c r="A134" s="11" t="str">
@@ -5114,38 +5106,30 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C134" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D134" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E134" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F134" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
-      <x:c r="G134" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H134" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G134" s="21"/>
+      <x:c r="H134" s="21"/>
       <x:c r="I134" s="18" t="n">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J134" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="K134" s="18" t="n">
-        <x:v>-15</x:v>
-      </x:c>
-      <x:c r="L134" s="25" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="M134" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
-      </x:c>
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="L134" s="25"/>
+      <x:c r="M134" s="26"/>
     </x:row>
     <x:row r="135" ht="15" hidden="0" customHeight="1">
       <x:c r="A135" s="11" t="str">
@@ -5155,38 +5139,30 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C135" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D135" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E135" s="12" t="str">
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F135" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
-      <x:c r="G135" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H135" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G135" s="21"/>
+      <x:c r="H135" s="21"/>
       <x:c r="I135" s="18" t="n">
-        <x:v>40</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J135" s="18" t="n">
-        <x:v>19</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="K135" s="18" t="n">
-        <x:v>-21</x:v>
-      </x:c>
-      <x:c r="L135" s="25" t="n">
-        <x:v>0.475</x:v>
-      </x:c>
-      <x:c r="M135" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
-      </x:c>
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="L135" s="25"/>
+      <x:c r="M135" s="26"/>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
       <x:c r="A136" s="11" t="str">
@@ -5196,38 +5172,30 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C136" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D136" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E136" s="12" t="str">
         <x:v>六年级</x:v>
       </x:c>
       <x:c r="F136" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
-      <x:c r="G136" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H136" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G136" s="21"/>
+      <x:c r="H136" s="21"/>
       <x:c r="I136" s="18" t="n">
-        <x:v>70</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J136" s="18" t="n">
-        <x:v>25</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K136" s="18" t="n">
-        <x:v>-45</x:v>
-      </x:c>
-      <x:c r="L136" s="25" t="n">
-        <x:v>0.35714285714285715</x:v>
-      </x:c>
-      <x:c r="M136" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
-      </x:c>
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="L136" s="25"/>
+      <x:c r="M136" s="26"/>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
       <x:c r="A137" s="11" t="str">
@@ -5243,10 +5211,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E137" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F137" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G137" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5255,19 +5223,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I137" s="18" t="n">
-        <x:v>70</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J137" s="18" t="n">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K137" s="18" t="n">
-        <x:v>-50</x:v>
+        <x:v>-8</x:v>
       </x:c>
       <x:c r="L137" s="25" t="n">
-        <x:v>0.2857142857142857</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="M137" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
@@ -5281,27 +5249,35 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D138" s="18" t="n">
-        <x:v>1880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E138" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F138" s="21" t="str">
-        <x:v>2026-06-24</x:v>
-      </x:c>
-      <x:c r="G138" s="21"/>
-      <x:c r="H138" s="21"/>
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G138" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H138" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I138" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J138" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K138" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L138" s="25"/>
-      <x:c r="M138" s="26"/>
+        <x:v>-23</x:v>
+      </x:c>
+      <x:c r="L138" s="25" t="n">
+        <x:v>0.54</x:v>
+      </x:c>
+      <x:c r="M138" s="26" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
     </x:row>
     <x:row r="139" ht="15" hidden="0" customHeight="1">
       <x:c r="A139" s="11" t="str">
@@ -5314,13 +5290,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D139" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E139" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F139" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G139" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5329,19 +5305,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I139" s="18" t="n">
-        <x:v>190</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J139" s="18" t="n">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="K139" s="18" t="n">
-        <x:v>-166</x:v>
+        <x:v>-39</x:v>
       </x:c>
       <x:c r="L139" s="25" t="n">
-        <x:v>0.12631578947368421</x:v>
+        <x:v>0.44285714285714284</x:v>
       </x:c>
       <x:c r="M139" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -5355,13 +5331,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D140" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E140" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F140" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G140" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5370,19 +5346,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I140" s="18" t="n">
-        <x:v>80</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J140" s="18" t="n">
-        <x:v>20</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="K140" s="18" t="n">
-        <x:v>-60</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="L140" s="25" t="n">
-        <x:v>0.25</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="M140" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -5396,13 +5372,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D141" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E141" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F141" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G141" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5411,19 +5387,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I141" s="18" t="n">
-        <x:v>240</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J141" s="18" t="n">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="K141" s="18" t="n">
-        <x:v>-190</x:v>
+        <x:v>-32</x:v>
       </x:c>
       <x:c r="L141" s="25" t="n">
-        <x:v>0.20833333333333334</x:v>
+        <x:v>0.5428571428571428</x:v>
       </x:c>
       <x:c r="M141" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -5437,35 +5413,27 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D142" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>1880</x:v>
       </x:c>
       <x:c r="E142" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F142" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
-      <x:c r="G142" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H142" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="G142" s="21"/>
+      <x:c r="H142" s="21"/>
       <x:c r="I142" s="18" t="n">
-        <x:v>260</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J142" s="18" t="n">
-        <x:v>79</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K142" s="18" t="n">
-        <x:v>-181</x:v>
-      </x:c>
-      <x:c r="L142" s="25" t="n">
-        <x:v>0.3038461538461538</x:v>
-      </x:c>
-      <x:c r="M142" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L142" s="25"/>
+      <x:c r="M142" s="26"/>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
       <x:c r="A143" s="11" t="str">
@@ -5481,10 +5449,10 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E143" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F143" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G143" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5493,19 +5461,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I143" s="18" t="n">
-        <x:v>260</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J143" s="18" t="n">
-        <x:v>63</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="K143" s="18" t="n">
-        <x:v>-197</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="L143" s="25" t="n">
-        <x:v>0.2423076923076923</x:v>
+        <x:v>0.425</x:v>
       </x:c>
       <x:c r="M143" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
@@ -5513,148 +5481,180 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B144" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C144" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D144" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E144" s="12" t="str">
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F144" s="21" t="str">
-        <x:v>2026-06-22</x:v>
-      </x:c>
-      <x:c r="G144" s="21"/>
-      <x:c r="H144" s="21"/>
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G144" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H144" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I144" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="J144" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K144" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L144" s="25"/>
-      <x:c r="M144" s="26"/>
+        <x:v>-146</x:v>
+      </x:c>
+      <x:c r="L144" s="25" t="n">
+        <x:v>0.23157894736842105</x:v>
+      </x:c>
+      <x:c r="M144" s="26" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
     </x:row>
     <x:row r="145" ht="15" hidden="0" customHeight="1">
       <x:c r="A145" s="11" t="str">
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B145" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C145" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D145" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E145" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F145" s="21" t="str">
-        <x:v>2026-06-23</x:v>
-      </x:c>
-      <x:c r="G145" s="21"/>
-      <x:c r="H145" s="21"/>
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G145" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H145" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I145" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="J145" s="18" t="n">
-        <x:v>11</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K145" s="18" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="L145" s="25"/>
-      <x:c r="M145" s="26"/>
+        <x:v>-156</x:v>
+      </x:c>
+      <x:c r="L145" s="25" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="M145" s="26" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
       <x:c r="A146" s="11" t="str">
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B146" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C146" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D146" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E146" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F146" s="21" t="str">
-        <x:v>2026-06-21</x:v>
-      </x:c>
-      <x:c r="G146" s="21"/>
-      <x:c r="H146" s="21"/>
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G146" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H146" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I146" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="J146" s="18" t="n">
-        <x:v>163</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K146" s="18" t="n">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="L146" s="25"/>
-      <x:c r="M146" s="26"/>
+        <x:v>-154</x:v>
+      </x:c>
+      <x:c r="L146" s="25" t="n">
+        <x:v>0.35833333333333334</x:v>
+      </x:c>
+      <x:c r="M146" s="26" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
       <x:c r="A147" s="11" t="str">
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B147" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C147" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D147" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E147" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F147" s="21" t="str">
-        <x:v>2026-06-22</x:v>
-      </x:c>
-      <x:c r="G147" s="21"/>
-      <x:c r="H147" s="21"/>
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G147" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H147" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I147" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="J147" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="K147" s="18" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="L147" s="25"/>
-      <x:c r="M147" s="26"/>
+        <x:v>-128</x:v>
+      </x:c>
+      <x:c r="L147" s="25" t="n">
+        <x:v>0.5076923076923077</x:v>
+      </x:c>
+      <x:c r="M147" s="26" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
       <x:c r="A148" s="11" t="str">
-        <x:v>自拼</x:v>
+        <x:v>小学</x:v>
       </x:c>
       <x:c r="B148" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C148" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D148" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E148" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F148" s="21" t="str">
         <x:v>2026-06-22</x:v>
@@ -5665,32 +5665,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J148" s="18" t="n">
-        <x:v>218</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K148" s="18" t="n">
-        <x:v>218</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L148" s="25"/>
       <x:c r="M148" s="26"/>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
       <x:c r="A149" s="11" t="str">
-        <x:v>自拼</x:v>
+        <x:v>小学</x:v>
       </x:c>
       <x:c r="B149" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C149" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D149" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E149" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F149" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G149" s="21"/>
       <x:c r="H149" s="21"/>
@@ -5698,29 +5698,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J149" s="18" t="n">
-        <x:v>79</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K149" s="18" t="n">
-        <x:v>79</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L149" s="25"/>
       <x:c r="M149" s="26"/>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
       <x:c r="A150" s="11" t="str">
-        <x:v>自拼</x:v>
+        <x:v>小学</x:v>
       </x:c>
       <x:c r="B150" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C150" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D150" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E150" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F150" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -5731,32 +5731,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J150" s="18" t="n">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K150" s="18" t="n">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L150" s="25"/>
       <x:c r="M150" s="26"/>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
       <x:c r="A151" s="11" t="str">
-        <x:v>自拼</x:v>
+        <x:v>小学</x:v>
       </x:c>
       <x:c r="B151" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C151" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D151" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E151" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F151" s="21" t="str">
-        <x:v>2026-06-22</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G151" s="21"/>
       <x:c r="H151" s="21"/>
@@ -5764,10 +5764,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J151" s="18" t="n">
-        <x:v>314</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="K151" s="18" t="n">
-        <x:v>314</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="L151" s="25"/>
       <x:c r="M151" s="26"/>
@@ -5780,16 +5780,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C152" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D152" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E152" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F152" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G152" s="21"/>
       <x:c r="H152" s="21"/>
@@ -5797,10 +5797,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J152" s="18" t="n">
-        <x:v>116</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="K152" s="18" t="n">
-        <x:v>116</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="L152" s="25"/>
       <x:c r="M152" s="26"/>
@@ -5813,13 +5813,13 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C153" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D153" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E153" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F153" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -5830,10 +5830,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J153" s="18" t="n">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="K153" s="18" t="n">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="L153" s="25"/>
       <x:c r="M153" s="26"/>
@@ -5846,16 +5846,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C154" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D154" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E154" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F154" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G154" s="21"/>
       <x:c r="H154" s="21"/>
@@ -5879,16 +5879,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C155" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D155" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E155" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F155" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G155" s="21"/>
       <x:c r="H155" s="21"/>
@@ -5896,10 +5896,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J155" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="K155" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="L155" s="25"/>
       <x:c r="M155" s="26"/>
@@ -5912,13 +5912,13 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C156" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D156" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E156" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F156" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -5929,10 +5929,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J156" s="18" t="n">
-        <x:v>11</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K156" s="18" t="n">
-        <x:v>11</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="L156" s="25"/>
       <x:c r="M156" s="26"/>
@@ -5945,16 +5945,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C157" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D157" s="18" t="n">
-        <x:v>2990</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E157" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F157" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G157" s="21"/>
       <x:c r="H157" s="21"/>
@@ -5962,10 +5962,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J157" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K157" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="L157" s="25"/>
       <x:c r="M157" s="26"/>
@@ -5978,16 +5978,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C158" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D158" s="18" t="n">
-        <x:v>2990</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E158" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F158" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G158" s="21"/>
       <x:c r="H158" s="21"/>
@@ -5995,10 +5995,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J158" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K158" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L158" s="25"/>
       <x:c r="M158" s="26"/>
@@ -6011,13 +6011,13 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C159" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D159" s="18" t="n">
-        <x:v>2990</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E159" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F159" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -6028,10 +6028,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J159" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K159" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L159" s="25"/>
       <x:c r="M159" s="26"/>
@@ -6041,19 +6041,19 @@
         <x:v>自拼</x:v>
       </x:c>
       <x:c r="B160" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C160" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D160" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E160" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F160" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G160" s="21"/>
       <x:c r="H160" s="21"/>
@@ -6061,10 +6061,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J160" s="18" t="n">
-        <x:v>156</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K160" s="18" t="n">
-        <x:v>156</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L160" s="25"/>
       <x:c r="M160" s="26"/>
@@ -6074,19 +6074,19 @@
         <x:v>自拼</x:v>
       </x:c>
       <x:c r="B161" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C161" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D161" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="E161" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F161" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G161" s="21"/>
       <x:c r="H161" s="21"/>
@@ -6094,10 +6094,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J161" s="18" t="n">
-        <x:v>46</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K161" s="18" t="n">
-        <x:v>46</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L161" s="25"/>
       <x:c r="M161" s="26"/>
@@ -6107,19 +6107,19 @@
         <x:v>自拼</x:v>
       </x:c>
       <x:c r="B162" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C162" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D162" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="E162" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F162" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G162" s="21"/>
       <x:c r="H162" s="21"/>
@@ -6127,10 +6127,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J162" s="18" t="n">
-        <x:v>45</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K162" s="18" t="n">
-        <x:v>45</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L162" s="25"/>
       <x:c r="M162" s="26"/>
@@ -6140,7 +6140,7 @@
         <x:v>自拼</x:v>
       </x:c>
       <x:c r="B163" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C163" s="12" t="str">
         <x:v>常规外呼</x:v>
@@ -6149,10 +6149,10 @@
         <x:v>2990</x:v>
       </x:c>
       <x:c r="E163" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F163" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G163" s="21"/>
       <x:c r="H163" s="21"/>
@@ -6160,10 +6160,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J163" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K163" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L163" s="25"/>
       <x:c r="M163" s="26"/>
@@ -6176,16 +6176,16 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C164" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D164" s="18" t="n">
-        <x:v>2990</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E164" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F164" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G164" s="21"/>
       <x:c r="H164" s="21"/>
@@ -6193,10 +6193,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J164" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="K164" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="L164" s="25"/>
       <x:c r="M164" s="26"/>
@@ -6209,13 +6209,13 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C165" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D165" s="18" t="n">
-        <x:v>2990</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E165" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F165" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6226,32 +6226,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J165" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K165" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L165" s="25"/>
       <x:c r="M165" s="26"/>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
       <x:c r="A166" s="11" t="str">
-        <x:v>高中</x:v>
+        <x:v>自拼</x:v>
       </x:c>
       <x:c r="B166" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C166" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D166" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E166" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F166" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G166" s="21"/>
       <x:c r="H166" s="21"/>
@@ -6259,32 +6259,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J166" s="18" t="n">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K166" s="18" t="n">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L166" s="25"/>
       <x:c r="M166" s="26"/>
     </x:row>
     <x:row r="167" ht="15" hidden="0" customHeight="1">
       <x:c r="A167" s="11" t="str">
-        <x:v>高中</x:v>
+        <x:v>自拼</x:v>
       </x:c>
       <x:c r="B167" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C167" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D167" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="E167" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F167" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G167" s="21"/>
       <x:c r="H167" s="21"/>
@@ -6292,32 +6292,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J167" s="18" t="n">
-        <x:v>96</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K167" s="18" t="n">
-        <x:v>96</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L167" s="25"/>
       <x:c r="M167" s="26"/>
     </x:row>
     <x:row r="168" ht="15" hidden="0" customHeight="1">
       <x:c r="A168" s="11" t="str">
-        <x:v>高中</x:v>
+        <x:v>自拼</x:v>
       </x:c>
       <x:c r="B168" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C168" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D168" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="E168" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F168" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G168" s="21"/>
       <x:c r="H168" s="21"/>
@@ -6325,29 +6325,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J168" s="18" t="n">
-        <x:v>115</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K168" s="18" t="n">
-        <x:v>115</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L168" s="25"/>
       <x:c r="M168" s="26"/>
     </x:row>
     <x:row r="169" ht="15" hidden="0" customHeight="1">
       <x:c r="A169" s="11" t="str">
-        <x:v>高中</x:v>
+        <x:v>自拼</x:v>
       </x:c>
       <x:c r="B169" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C169" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D169" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="E169" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F169" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6358,10 +6358,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J169" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K169" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L169" s="25"/>
       <x:c r="M169" s="26"/>
@@ -6374,13 +6374,13 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C170" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D170" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E170" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F170" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6391,10 +6391,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J170" s="18" t="n">
-        <x:v>106</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K170" s="18" t="n">
-        <x:v>106</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="L170" s="25"/>
       <x:c r="M170" s="26"/>
@@ -6407,16 +6407,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C171" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D171" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E171" s="12" t="str">
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F171" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G171" s="21"/>
       <x:c r="H171" s="21"/>
@@ -6424,10 +6424,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J171" s="18" t="n">
-        <x:v>73</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="K171" s="18" t="n">
-        <x:v>73</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="L171" s="25"/>
       <x:c r="M171" s="26"/>
@@ -6440,16 +6440,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C172" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D172" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E172" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F172" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G172" s="21"/>
       <x:c r="H172" s="21"/>
@@ -6457,10 +6457,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J172" s="18" t="n">
-        <x:v>676</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K172" s="18" t="n">
-        <x:v>676</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="L172" s="25"/>
       <x:c r="M172" s="26"/>
@@ -6473,16 +6473,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C173" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D173" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E173" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F173" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G173" s="21"/>
       <x:c r="H173" s="21"/>
@@ -6490,10 +6490,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J173" s="18" t="n">
-        <x:v>186</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K173" s="18" t="n">
-        <x:v>186</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="L173" s="25"/>
       <x:c r="M173" s="26"/>
@@ -6506,16 +6506,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C174" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D174" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E174" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F174" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G174" s="21"/>
       <x:c r="H174" s="21"/>
@@ -6523,10 +6523,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J174" s="18" t="n">
-        <x:v>9</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K174" s="18" t="n">
-        <x:v>9</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="L174" s="25"/>
       <x:c r="M174" s="26"/>
@@ -6539,7 +6539,7 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C175" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D175" s="18" t="n">
         <x:v>100</x:v>
@@ -6548,7 +6548,7 @@
         <x:v>高三</x:v>
       </x:c>
       <x:c r="F175" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G175" s="21"/>
       <x:c r="H175" s="21"/>
@@ -6556,10 +6556,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J175" s="18" t="n">
-        <x:v>6</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="K175" s="18" t="n">
-        <x:v>6</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="L175" s="25"/>
       <x:c r="M175" s="26"/>
@@ -6572,16 +6572,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C176" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D176" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E176" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F176" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G176" s="21"/>
       <x:c r="H176" s="21"/>
@@ -6589,10 +6589,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J176" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="K176" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="L176" s="25"/>
       <x:c r="M176" s="26"/>
@@ -6605,16 +6605,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C177" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D177" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E177" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F177" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G177" s="21"/>
       <x:c r="H177" s="21"/>
@@ -6622,10 +6622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J177" s="18" t="n">
-        <x:v>358</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="K177" s="18" t="n">
-        <x:v>358</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="L177" s="25"/>
       <x:c r="M177" s="26"/>
@@ -6641,13 +6641,13 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D178" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E178" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F178" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G178" s="21"/>
       <x:c r="H178" s="21"/>
@@ -6655,10 +6655,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J178" s="18" t="n">
-        <x:v>320</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K178" s="18" t="n">
-        <x:v>320</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L178" s="25"/>
       <x:c r="M178" s="26"/>
@@ -6674,13 +6674,13 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D179" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E179" s="12" t="str">
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F179" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G179" s="21"/>
       <x:c r="H179" s="21"/>
@@ -6688,10 +6688,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J179" s="18" t="n">
-        <x:v>291</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K179" s="18" t="n">
-        <x:v>291</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L179" s="25"/>
       <x:c r="M179" s="26"/>
@@ -6704,16 +6704,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C180" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D180" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E180" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F180" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G180" s="21"/>
       <x:c r="H180" s="21"/>
@@ -6721,10 +6721,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J180" s="18" t="n">
-        <x:v>697</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K180" s="18" t="n">
-        <x:v>697</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L180" s="25"/>
       <x:c r="M180" s="26"/>
@@ -6737,13 +6737,13 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C181" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D181" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E181" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F181" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6754,10 +6754,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J181" s="18" t="n">
-        <x:v>633</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="K181" s="18" t="n">
-        <x:v>633</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="L181" s="25"/>
       <x:c r="M181" s="26"/>
@@ -6770,10 +6770,10 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C182" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D182" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E182" s="12" t="str">
         <x:v>高二</x:v>
@@ -6787,10 +6787,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J182" s="18" t="n">
-        <x:v>960</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="K182" s="18" t="n">
-        <x:v>960</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="L182" s="25"/>
       <x:c r="M182" s="26"/>
@@ -6803,13 +6803,13 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C183" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D183" s="18" t="n">
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E183" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F183" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6820,10 +6820,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J183" s="18" t="n">
-        <x:v>434</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="K183" s="18" t="n">
-        <x:v>434</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="L183" s="25"/>
       <x:c r="M183" s="26"/>
@@ -6839,10 +6839,10 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D184" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E184" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F184" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6853,10 +6853,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J184" s="18" t="n">
-        <x:v>558</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="K184" s="18" t="n">
-        <x:v>558</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="L184" s="25"/>
       <x:c r="M184" s="26"/>
@@ -6872,7 +6872,7 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D185" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E185" s="12" t="str">
         <x:v>高二</x:v>
@@ -6886,10 +6886,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J185" s="18" t="n">
-        <x:v>626</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="K185" s="18" t="n">
-        <x:v>626</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="L185" s="25"/>
       <x:c r="M185" s="26"/>
@@ -6899,93 +6899,79 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B186" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C186" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D186" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E186" s="12" t="str">
-        <x:v>高一</x:v>
-      </x:c>
-      <x:c r="F186" s="21"/>
-      <x:c r="G186" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H186" s="21" t="str">
+        <x:v>高三</x:v>
+      </x:c>
+      <x:c r="F186" s="21" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
+      <x:c r="G186" s="21"/>
+      <x:c r="H186" s="21"/>
       <x:c r="I186" s="18" t="n">
-        <x:v>140</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J186" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="K186" s="18" t="n">
-        <x:v>-140</x:v>
-      </x:c>
-      <x:c r="L186" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M186" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
-      </x:c>
+        <x:v>633</x:v>
+      </x:c>
+      <x:c r="L186" s="25"/>
+      <x:c r="M186" s="26"/>
     </x:row>
     <x:row r="187" ht="15" hidden="0" customHeight="1">
       <x:c r="A187" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B187" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C187" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D187" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E187" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F187" s="21" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
-      <x:c r="G187" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H187" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+      <x:c r="G187" s="21"/>
+      <x:c r="H187" s="21"/>
       <x:c r="I187" s="18" t="n">
-        <x:v>180</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J187" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="K187" s="18" t="n">
-        <x:v>-178</x:v>
-      </x:c>
-      <x:c r="L187" s="25" t="n">
-        <x:v>0.011111111111111112</x:v>
-      </x:c>
-      <x:c r="M187" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
-      </x:c>
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="L187" s="25"/>
+      <x:c r="M187" s="26"/>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
       <x:c r="A188" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B188" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C188" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D188" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E188" s="12" t="str">
         <x:v>高二</x:v>
@@ -6993,43 +6979,35 @@
       <x:c r="F188" s="21" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
-      <x:c r="G188" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H188" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+      <x:c r="G188" s="21"/>
+      <x:c r="H188" s="21"/>
       <x:c r="I188" s="18" t="n">
-        <x:v>180</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J188" s="18" t="n">
-        <x:v>18</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="K188" s="18" t="n">
-        <x:v>-162</x:v>
-      </x:c>
-      <x:c r="L188" s="25" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="M188" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
-      </x:c>
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="L188" s="25"/>
+      <x:c r="M188" s="26"/>
     </x:row>
     <x:row r="189" ht="15" hidden="0" customHeight="1">
       <x:c r="A189" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B189" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C189" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D189" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E189" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F189" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -7040,10 +7018,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J189" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="K189" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="L189" s="25"/>
       <x:c r="M189" s="26"/>
@@ -7056,30 +7034,38 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C190" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D190" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E190" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F190" s="21" t="str">
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G190" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H190" s="21" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
-      <x:c r="G190" s="21"/>
-      <x:c r="H190" s="21"/>
       <x:c r="I190" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J190" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K190" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L190" s="25"/>
-      <x:c r="M190" s="26"/>
+        <x:v>-68</x:v>
+      </x:c>
+      <x:c r="L190" s="25" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="M190" s="26" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
       <x:c r="A191" s="11" t="str">
@@ -7089,15 +7075,17 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C191" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D191" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E191" s="12" t="str">
-        <x:v>高一</x:v>
-      </x:c>
-      <x:c r="F191" s="21"/>
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F191" s="21" t="str">
+        <x:v>2026-06-26</x:v>
+      </x:c>
       <x:c r="G191" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7105,19 +7093,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I191" s="18" t="n">
-        <x:v>300</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="J191" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K191" s="18" t="n">
-        <x:v>-300</x:v>
+        <x:v>-116</x:v>
       </x:c>
       <x:c r="L191" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>0.275</x:v>
       </x:c>
       <x:c r="M191" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
@@ -7128,15 +7116,17 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C192" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D192" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E192" s="12" t="str">
         <x:v>高三</x:v>
       </x:c>
-      <x:c r="F192" s="21"/>
+      <x:c r="F192" s="21" t="str">
+        <x:v>2026-06-26</x:v>
+      </x:c>
       <x:c r="G192" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7144,19 +7134,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I192" s="18" t="n">
-        <x:v>200</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="J192" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K192" s="18" t="n">
-        <x:v>-200</x:v>
+        <x:v>-141</x:v>
       </x:c>
       <x:c r="L192" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>0.11875</x:v>
       </x:c>
       <x:c r="M192" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -7167,15 +7157,17 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C193" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D193" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E193" s="12" t="str">
-        <x:v>高二</x:v>
-      </x:c>
-      <x:c r="F193" s="21"/>
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F193" s="21" t="str">
+        <x:v>2026-06-26</x:v>
+      </x:c>
       <x:c r="G193" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7183,19 +7175,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I193" s="18" t="n">
-        <x:v>700</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J193" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K193" s="18" t="n">
-        <x:v>-700</x:v>
+        <x:v>-95</x:v>
       </x:c>
       <x:c r="L193" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="M193" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -7206,15 +7198,17 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C194" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D194" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E194" s="12" t="str">
-        <x:v>高一</x:v>
-      </x:c>
-      <x:c r="F194" s="21"/>
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F194" s="21" t="str">
+        <x:v>2026-06-26</x:v>
+      </x:c>
       <x:c r="G194" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7222,19 +7216,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I194" s="18" t="n">
-        <x:v>20</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J194" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K194" s="18" t="n">
-        <x:v>-20</x:v>
+        <x:v>-146</x:v>
       </x:c>
       <x:c r="L194" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>0.02666666666666667</x:v>
       </x:c>
       <x:c r="M194" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
@@ -7245,7 +7239,7 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C195" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D195" s="18" t="n">
         <x:v>100</x:v>
@@ -7253,7 +7247,9 @@
       <x:c r="E195" s="12" t="str">
         <x:v>高三</x:v>
       </x:c>
-      <x:c r="F195" s="21"/>
+      <x:c r="F195" s="21" t="str">
+        <x:v>2026-06-26</x:v>
+      </x:c>
       <x:c r="G195" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7261,19 +7257,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I195" s="18" t="n">
-        <x:v>30</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J195" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K195" s="18" t="n">
-        <x:v>-30</x:v>
+        <x:v>-145</x:v>
       </x:c>
       <x:c r="L195" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>0.03333333333333333</x:v>
       </x:c>
       <x:c r="M195" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
@@ -7284,15 +7280,17 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C196" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D196" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E196" s="12" t="str">
-        <x:v>高二</x:v>
-      </x:c>
-      <x:c r="F196" s="21"/>
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F196" s="21" t="str">
+        <x:v>2026-06-26</x:v>
+      </x:c>
       <x:c r="G196" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7303,16 +7301,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="J196" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="K196" s="18" t="n">
-        <x:v>-50</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="L196" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="M196" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
@@ -7323,16 +7321,16 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C197" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D197" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E197" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F197" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G197" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7341,19 +7339,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I197" s="18" t="n">
-        <x:v>350</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="J197" s="18" t="n">
-        <x:v>37</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K197" s="18" t="n">
-        <x:v>-313</x:v>
+        <x:v>-820</x:v>
       </x:c>
       <x:c r="L197" s="25" t="n">
-        <x:v>0.10571428571428572</x:v>
+        <x:v>0.08888888888888889</x:v>
       </x:c>
       <x:c r="M197" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
@@ -7364,17 +7362,15 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C198" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D198" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E198" s="12" t="str">
         <x:v>高三</x:v>
       </x:c>
-      <x:c r="F198" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+      <x:c r="F198" s="21"/>
       <x:c r="G198" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7382,19 +7378,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I198" s="18" t="n">
-        <x:v>480</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="J198" s="18" t="n">
-        <x:v>9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K198" s="18" t="n">
-        <x:v>-471</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="L198" s="25" t="n">
-        <x:v>0.01875</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M198" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
@@ -7405,17 +7401,15 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C199" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>图书微转</x:v>
       </x:c>
       <x:c r="D199" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E199" s="12" t="str">
-        <x:v>高二</x:v>
-      </x:c>
-      <x:c r="F199" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F199" s="21"/>
       <x:c r="G199" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7423,19 +7417,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I199" s="18" t="n">
-        <x:v>520</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J199" s="18" t="n">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K199" s="18" t="n">
-        <x:v>-509</x:v>
+        <x:v>-150</x:v>
       </x:c>
       <x:c r="L199" s="25" t="n">
-        <x:v>0.021153846153846155</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M199" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
@@ -7446,17 +7440,15 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C200" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>图书微转</x:v>
       </x:c>
       <x:c r="D200" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E200" s="12" t="str">
-        <x:v>高一</x:v>
-      </x:c>
-      <x:c r="F200" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F200" s="21"/>
       <x:c r="G200" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7464,19 +7456,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I200" s="18" t="n">
-        <x:v>760</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="J200" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K200" s="18" t="n">
-        <x:v>-755</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="L200" s="25" t="n">
-        <x:v>0.006578947368421052</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M200" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
@@ -7487,7 +7479,7 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C201" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>图书微转</x:v>
       </x:c>
       <x:c r="D201" s="18" t="n">
         <x:v>100</x:v>
@@ -7495,9 +7487,7 @@
       <x:c r="E201" s="12" t="str">
         <x:v>高三</x:v>
       </x:c>
-      <x:c r="F201" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+      <x:c r="F201" s="21"/>
       <x:c r="G201" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7505,19 +7495,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I201" s="18" t="n">
-        <x:v>800</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J201" s="18" t="n">
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K201" s="18" t="n">
-        <x:v>-794</x:v>
+        <x:v>-150</x:v>
       </x:c>
       <x:c r="L201" s="25" t="n">
-        <x:v>0.0075</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M201" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
@@ -7528,16 +7518,16 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C202" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D202" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E202" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F202" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G202" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7546,19 +7536,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I202" s="18" t="n">
-        <x:v>940</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J202" s="18" t="n">
-        <x:v>158</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="K202" s="18" t="n">
-        <x:v>-782</x:v>
+        <x:v>-161</x:v>
       </x:c>
       <x:c r="L202" s="25" t="n">
-        <x:v>0.16808510638297872</x:v>
+        <x:v>0.4633333333333333</x:v>
       </x:c>
       <x:c r="M202" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
@@ -7569,15 +7559,17 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C203" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D203" s="18" t="n">
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E203" s="12" t="str">
-        <x:v>高一</x:v>
-      </x:c>
-      <x:c r="F203" s="21"/>
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F203" s="21" t="str">
+        <x:v>2026-06-26</x:v>
+      </x:c>
       <x:c r="G203" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7585,19 +7577,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I203" s="18" t="n">
-        <x:v>450</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="J203" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K203" s="18" t="n">
-        <x:v>-450</x:v>
+        <x:v>-467</x:v>
       </x:c>
       <x:c r="L203" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>0.11886792452830189</x:v>
       </x:c>
       <x:c r="M203" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -7608,7 +7600,7 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C204" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D204" s="18" t="n">
         <x:v>2880</x:v>
@@ -7617,7 +7609,7 @@
         <x:v>高三</x:v>
       </x:c>
       <x:c r="F204" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G204" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7626,19 +7618,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I204" s="18" t="n">
-        <x:v>510</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="J204" s="18" t="n">
-        <x:v>18</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K204" s="18" t="n">
-        <x:v>-492</x:v>
+        <x:v>-532</x:v>
       </x:c>
       <x:c r="L204" s="25" t="n">
-        <x:v>0.03529411764705882</x:v>
+        <x:v>0.11333333333333333</x:v>
       </x:c>
       <x:c r="M204" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -7652,13 +7644,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D205" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E205" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F205" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G205" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7667,19 +7659,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I205" s="18" t="n">
-        <x:v>470</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="J205" s="18" t="n">
-        <x:v>50</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K205" s="18" t="n">
-        <x:v>-420</x:v>
+        <x:v>-153</x:v>
       </x:c>
       <x:c r="L205" s="25" t="n">
-        <x:v>0.10638297872340426</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="M205" s="26" t="n">
-        <x:v>0.16666666666666666</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -7687,85 +7679,101 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B206" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C206" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D206" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E206" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F206" s="21" t="str">
-        <x:v>2026-06-21</x:v>
-      </x:c>
-      <x:c r="G206" s="21"/>
-      <x:c r="H206" s="21"/>
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G206" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H206" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I206" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="J206" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="K206" s="18" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="L206" s="25"/>
-      <x:c r="M206" s="26"/>
+        <x:v>-1134</x:v>
+      </x:c>
+      <x:c r="L206" s="25" t="n">
+        <x:v>0.244</x:v>
+      </x:c>
+      <x:c r="M206" s="26" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
       <x:c r="A207" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B207" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C207" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D207" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E207" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F207" s="21" t="str">
-        <x:v>2026-06-18</x:v>
-      </x:c>
-      <x:c r="G207" s="21"/>
-      <x:c r="H207" s="21"/>
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G207" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H207" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I207" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>870</x:v>
       </x:c>
       <x:c r="J207" s="18" t="n">
-        <x:v>27</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K207" s="18" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="L207" s="25"/>
-      <x:c r="M207" s="26"/>
+        <x:v>-776</x:v>
+      </x:c>
+      <x:c r="L207" s="25" t="n">
+        <x:v>0.10804597701149425</x:v>
+      </x:c>
+      <x:c r="M207" s="26" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
       <x:c r="A208" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B208" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C208" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D208" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E208" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F208" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G208" s="21"/>
       <x:c r="H208" s="21"/>
@@ -7773,10 +7781,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J208" s="18" t="n">
-        <x:v>50</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K208" s="18" t="n">
-        <x:v>50</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L208" s="25"/>
       <x:c r="M208" s="26"/>
@@ -7786,19 +7794,19 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B209" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C209" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D209" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E209" s="12" t="str">
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F209" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G209" s="21"/>
       <x:c r="H209" s="21"/>
@@ -7806,10 +7814,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J209" s="18" t="n">
-        <x:v>63</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="K209" s="18" t="n">
-        <x:v>63</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="L209" s="25"/>
       <x:c r="M209" s="26"/>
@@ -7819,19 +7827,19 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B210" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C210" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D210" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E210" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F210" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G210" s="21"/>
       <x:c r="H210" s="21"/>
@@ -7839,10 +7847,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J210" s="18" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K210" s="18" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L210" s="25"/>
       <x:c r="M210" s="26"/>
@@ -7852,106 +7860,126 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B211" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C211" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D211" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E211" s="12" t="str">
-        <x:v>高三</x:v>
-      </x:c>
-      <x:c r="F211" s="21" t="str">
-        <x:v>2026-06-17</x:v>
-      </x:c>
-      <x:c r="G211" s="21"/>
-      <x:c r="H211" s="21"/>
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F211" s="21"/>
+      <x:c r="G211" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H211" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I211" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J211" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K211" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L211" s="25"/>
-      <x:c r="M211" s="26"/>
+      <x:c r="M211" s="26" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
     </x:row>
     <x:row r="212" ht="15" hidden="0" customHeight="1">
       <x:c r="A212" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B212" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C212" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D212" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E212" s="12" t="str">
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F212" s="21" t="str">
-        <x:v>2026-06-18</x:v>
-      </x:c>
-      <x:c r="G212" s="21"/>
-      <x:c r="H212" s="21"/>
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G212" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H212" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I212" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="J212" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="K212" s="18" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="L212" s="25"/>
-      <x:c r="M212" s="26"/>
+        <x:v>-499</x:v>
+      </x:c>
+      <x:c r="L212" s="25" t="n">
+        <x:v>0.28714285714285714</x:v>
+      </x:c>
+      <x:c r="M212" s="26" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
     </x:row>
     <x:row r="213" ht="15" hidden="0" customHeight="1">
       <x:c r="A213" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B213" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C213" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D213" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E213" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F213" s="21" t="str">
-        <x:v>2026-06-20</x:v>
-      </x:c>
-      <x:c r="G213" s="21"/>
-      <x:c r="H213" s="21"/>
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="G213" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H213" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I213" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="J213" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="K213" s="18" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="L213" s="25"/>
-      <x:c r="M213" s="26"/>
+        <x:v>-447</x:v>
+      </x:c>
+      <x:c r="L213" s="25" t="n">
+        <x:v>0.3123076923076923</x:v>
+      </x:c>
+      <x:c r="M213" s="26" t="n">
+        <x:v>0.3333333333333333</x:v>
+      </x:c>
     </x:row>
     <x:row r="214" ht="15" hidden="0" customHeight="1">
       <x:c r="A214" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B214" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C214" s="12" t="str">
         <x:v>LLM外呼</x:v>
@@ -7960,10 +7988,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E214" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F214" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G214" s="21"/>
       <x:c r="H214" s="21"/>
@@ -7971,10 +7999,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J214" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K214" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L214" s="25"/>
       <x:c r="M214" s="26"/>
@@ -7984,19 +8012,19 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B215" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C215" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D215" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E215" s="12" t="str">
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F215" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G215" s="21"/>
       <x:c r="H215" s="21"/>
@@ -8004,10 +8032,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J215" s="18" t="n">
-        <x:v>146</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K215" s="18" t="n">
-        <x:v>146</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L215" s="25"/>
       <x:c r="M215" s="26"/>
@@ -8020,13 +8048,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C216" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D216" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E216" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F216" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8037,10 +8065,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J216" s="18" t="n">
-        <x:v>136</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K216" s="18" t="n">
-        <x:v>136</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L216" s="25"/>
       <x:c r="M216" s="26"/>
@@ -8053,10 +8081,10 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C217" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D217" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E217" s="12" t="str">
         <x:v>高二</x:v>
@@ -8070,10 +8098,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J217" s="18" t="n">
-        <x:v>157</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K217" s="18" t="n">
-        <x:v>157</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L217" s="25"/>
       <x:c r="M217" s="26"/>
@@ -8086,13 +8114,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C218" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D218" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E218" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F218" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8103,10 +8131,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J218" s="18" t="n">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K218" s="18" t="n">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L218" s="25"/>
       <x:c r="M218" s="26"/>
@@ -8119,13 +8147,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C219" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D219" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E219" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F219" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8136,10 +8164,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J219" s="18" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K219" s="18" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L219" s="25"/>
       <x:c r="M219" s="26"/>
@@ -8152,16 +8180,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C220" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D220" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E220" s="12" t="str">
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F220" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G220" s="21"/>
       <x:c r="H220" s="21"/>
@@ -8169,10 +8197,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J220" s="18" t="n">
-        <x:v>17</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K220" s="18" t="n">
-        <x:v>17</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L220" s="25"/>
       <x:c r="M220" s="26"/>
@@ -8185,16 +8213,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C221" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D221" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E221" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F221" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G221" s="21"/>
       <x:c r="H221" s="21"/>
@@ -8202,10 +8230,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J221" s="18" t="n">
-        <x:v>136</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K221" s="18" t="n">
-        <x:v>136</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L221" s="25"/>
       <x:c r="M221" s="26"/>
@@ -8218,16 +8246,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C222" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D222" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E222" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F222" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G222" s="21"/>
       <x:c r="H222" s="21"/>
@@ -8235,10 +8263,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J222" s="18" t="n">
-        <x:v>167</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K222" s="18" t="n">
-        <x:v>167</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L222" s="25"/>
       <x:c r="M222" s="26"/>
@@ -8251,10 +8279,10 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C223" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D223" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E223" s="12" t="str">
         <x:v>高二</x:v>
@@ -8268,10 +8296,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J223" s="18" t="n">
-        <x:v>293</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K223" s="18" t="n">
-        <x:v>293</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L223" s="25"/>
       <x:c r="M223" s="26"/>
@@ -8284,10 +8312,10 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C224" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D224" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E224" s="12" t="str">
         <x:v>高一</x:v>
@@ -8301,10 +8329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J224" s="18" t="n">
-        <x:v>92</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="K224" s="18" t="n">
-        <x:v>92</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="L224" s="25"/>
       <x:c r="M224" s="26"/>
@@ -8317,13 +8345,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C225" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D225" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E225" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F225" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8334,46 +8362,343 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J225" s="18" t="n">
-        <x:v>70</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="K225" s="18" t="n">
-        <x:v>70</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="L225" s="25"/>
       <x:c r="M225" s="26"/>
     </x:row>
     <x:row r="226" ht="15" hidden="0" customHeight="1">
-      <x:c r="A226" s="14" t="str">
+      <x:c r="A226" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
-      <x:c r="B226" s="15" t="str">
+      <x:c r="B226" s="12" t="str">
         <x:v>暑_9</x:v>
       </x:c>
-      <x:c r="C226" s="15" t="str">
+      <x:c r="C226" s="12" t="str">
+        <x:v>外部微转-*</x:v>
+      </x:c>
+      <x:c r="D226" s="18" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E226" s="12" t="str">
+        <x:v>高三</x:v>
+      </x:c>
+      <x:c r="F226" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G226" s="21"/>
+      <x:c r="H226" s="21"/>
+      <x:c r="I226" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J226" s="18" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="K226" s="18" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="L226" s="25"/>
+      <x:c r="M226" s="26"/>
+    </x:row>
+    <x:row r="227" ht="15" hidden="0" customHeight="1">
+      <x:c r="A227" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B227" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C227" s="12" t="str">
+        <x:v>外部微转-*</x:v>
+      </x:c>
+      <x:c r="D227" s="18" t="n">
+        <x:v>2880</x:v>
+      </x:c>
+      <x:c r="E227" s="12" t="str">
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F227" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G227" s="21"/>
+      <x:c r="H227" s="21"/>
+      <x:c r="I227" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J227" s="18" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K227" s="18" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="L227" s="25"/>
+      <x:c r="M227" s="26"/>
+    </x:row>
+    <x:row r="228" ht="15" hidden="0" customHeight="1">
+      <x:c r="A228" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B228" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C228" s="12" t="str">
+        <x:v>外部微转-*</x:v>
+      </x:c>
+      <x:c r="D228" s="18" t="n">
+        <x:v>2880</x:v>
+      </x:c>
+      <x:c r="E228" s="12" t="str">
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F228" s="21" t="str">
+        <x:v>2026-06-17</x:v>
+      </x:c>
+      <x:c r="G228" s="21"/>
+      <x:c r="H228" s="21"/>
+      <x:c r="I228" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J228" s="18" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K228" s="18" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="L228" s="25"/>
+      <x:c r="M228" s="26"/>
+    </x:row>
+    <x:row r="229" ht="15" hidden="0" customHeight="1">
+      <x:c r="A229" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B229" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C229" s="12" t="str">
+        <x:v>外部微转-*</x:v>
+      </x:c>
+      <x:c r="D229" s="18" t="n">
+        <x:v>2880</x:v>
+      </x:c>
+      <x:c r="E229" s="12" t="str">
+        <x:v>高三</x:v>
+      </x:c>
+      <x:c r="F229" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G229" s="21"/>
+      <x:c r="H229" s="21"/>
+      <x:c r="I229" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J229" s="18" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K229" s="18" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L229" s="25"/>
+      <x:c r="M229" s="26"/>
+    </x:row>
+    <x:row r="230" ht="15" hidden="0" customHeight="1">
+      <x:c r="A230" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B230" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C230" s="12" t="str">
         <x:v>常规外呼</x:v>
       </x:c>
-      <x:c r="D226" s="19" t="n">
+      <x:c r="D230" s="18" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E230" s="12" t="str">
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F230" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G230" s="21"/>
+      <x:c r="H230" s="21"/>
+      <x:c r="I230" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J230" s="18" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="K230" s="18" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="L230" s="25"/>
+      <x:c r="M230" s="26"/>
+    </x:row>
+    <x:row r="231" ht="15" hidden="0" customHeight="1">
+      <x:c r="A231" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B231" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C231" s="12" t="str">
+        <x:v>常规外呼</x:v>
+      </x:c>
+      <x:c r="D231" s="18" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E231" s="12" t="str">
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F231" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G231" s="21"/>
+      <x:c r="H231" s="21"/>
+      <x:c r="I231" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J231" s="18" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="K231" s="18" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="L231" s="25"/>
+      <x:c r="M231" s="26"/>
+    </x:row>
+    <x:row r="232" ht="15" hidden="0" customHeight="1">
+      <x:c r="A232" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B232" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C232" s="12" t="str">
+        <x:v>常规外呼</x:v>
+      </x:c>
+      <x:c r="D232" s="18" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E232" s="12" t="str">
+        <x:v>高三</x:v>
+      </x:c>
+      <x:c r="F232" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G232" s="21"/>
+      <x:c r="H232" s="21"/>
+      <x:c r="I232" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J232" s="18" t="n">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="K232" s="18" t="n">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="L232" s="25"/>
+      <x:c r="M232" s="26"/>
+    </x:row>
+    <x:row r="233" ht="15" hidden="0" customHeight="1">
+      <x:c r="A233" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B233" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C233" s="12" t="str">
+        <x:v>常规外呼</x:v>
+      </x:c>
+      <x:c r="D233" s="18" t="n">
         <x:v>2880</x:v>
       </x:c>
-      <x:c r="E226" s="15" t="str">
+      <x:c r="E233" s="12" t="str">
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F233" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G233" s="21"/>
+      <x:c r="H233" s="21"/>
+      <x:c r="I233" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J233" s="18" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="K233" s="18" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="L233" s="25"/>
+      <x:c r="M233" s="26"/>
+    </x:row>
+    <x:row r="234" ht="15" hidden="0" customHeight="1">
+      <x:c r="A234" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B234" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C234" s="12" t="str">
+        <x:v>常规外呼</x:v>
+      </x:c>
+      <x:c r="D234" s="18" t="n">
+        <x:v>2880</x:v>
+      </x:c>
+      <x:c r="E234" s="12" t="str">
         <x:v>高二</x:v>
       </x:c>
-      <x:c r="F226" s="22" t="str">
+      <x:c r="F234" s="21" t="str">
         <x:v>2026-06-18</x:v>
       </x:c>
-      <x:c r="G226" s="22"/>
-      <x:c r="H226" s="22"/>
-      <x:c r="I226" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J226" s="19" t="n">
+      <x:c r="G234" s="21"/>
+      <x:c r="H234" s="21"/>
+      <x:c r="I234" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J234" s="18" t="n">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="K226" s="19" t="n">
+      <x:c r="K234" s="18" t="n">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="L226" s="27"/>
-      <x:c r="M226" s="28"/>
+      <x:c r="L234" s="25"/>
+      <x:c r="M234" s="26"/>
+    </x:row>
+    <x:row r="235" ht="15" hidden="0" customHeight="1">
+      <x:c r="A235" s="14" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B235" s="15" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C235" s="15" t="str">
+        <x:v>常规外呼</x:v>
+      </x:c>
+      <x:c r="D235" s="19" t="n">
+        <x:v>2880</x:v>
+      </x:c>
+      <x:c r="E235" s="15" t="str">
+        <x:v>高三</x:v>
+      </x:c>
+      <x:c r="F235" s="22" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G235" s="22"/>
+      <x:c r="H235" s="22"/>
+      <x:c r="I235" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J235" s="19" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="K235" s="19" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="L235" s="27"/>
+      <x:c r="M235" s="28"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -8413,7 +8738,7 @@
         <x:v>现状原始行数</x:v>
       </x:c>
       <x:c r="B3" s="10" t="n">
-        <x:v>35592</x:v>
+        <x:v>40422</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -8421,7 +8746,7 @@
         <x:v>目标原始行数</x:v>
       </x:c>
       <x:c r="B4" s="13" t="n">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -8429,7 +8754,7 @@
         <x:v>聚合组合数</x:v>
       </x:c>
       <x:c r="B5" s="13" t="n">
-        <x:v>224</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -8437,7 +8762,7 @@
         <x:v>目标合计</x:v>
       </x:c>
       <x:c r="B6" s="13" t="n">
-        <x:v>28430</x:v>
+        <x:v>29130</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -8445,7 +8770,7 @@
         <x:v>现状合计</x:v>
       </x:c>
       <x:c r="B7" s="13" t="n">
-        <x:v>35592</x:v>
+        <x:v>40422</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -8453,7 +8778,7 @@
         <x:v>完成率整体</x:v>
       </x:c>
       <x:c r="B8" s="13" t="n">
-        <x:v>1.2519169890960253</x:v>
+        <x:v>1.3876416065911432</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -8477,7 +8802,7 @@
         <x:v>最新期次聚合组合数</x:v>
       </x:c>
       <x:c r="B11" s="13" t="n">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -8485,7 +8810,7 @@
         <x:v>最新期次目标合计</x:v>
       </x:c>
       <x:c r="B12" s="13" t="n">
-        <x:v>28430</x:v>
+        <x:v>29130</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -8493,7 +8818,7 @@
         <x:v>最新期次现状合计</x:v>
       </x:c>
       <x:c r="B13" s="13" t="n">
-        <x:v>7511</x:v>
+        <x:v>12127</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -8501,7 +8826,7 @@
         <x:v>最新期次完成率整体</x:v>
       </x:c>
       <x:c r="B14" s="13" t="n">
-        <x:v>0.2641927541329581</x:v>
+        <x:v>0.416306213525575</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -8630,7 +8955,7 @@
         <x:v>12100</x:v>
       </x:c>
       <x:c r="C31" s="10" t="n">
-        <x:v>3946</x:v>
+        <x:v>5920</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -8641,7 +8966,7 @@
         <x:v>9250</x:v>
       </x:c>
       <x:c r="C32" s="13" t="n">
-        <x:v>3249</x:v>
+        <x:v>4660</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
@@ -8649,10 +8974,10 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B33" s="15" t="n">
-        <x:v>7080</x:v>
+        <x:v>7780</x:v>
       </x:c>
       <x:c r="C33" s="16" t="n">
-        <x:v>316</x:v>
+        <x:v>1547</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="16.799999237060547" hidden="0" customHeight="1">
@@ -8685,7 +9010,7 @@
         <x:v>12100</x:v>
       </x:c>
       <x:c r="C38" s="10" t="n">
-        <x:v>3946</x:v>
+        <x:v>5920</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
@@ -8696,7 +9021,7 @@
         <x:v>9250</x:v>
       </x:c>
       <x:c r="C39" s="13" t="n">
-        <x:v>3249</x:v>
+        <x:v>4660</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -8704,10 +9029,10 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="B40" s="15" t="n">
-        <x:v>7080</x:v>
+        <x:v>7780</x:v>
       </x:c>
       <x:c r="C40" s="16" t="n">
-        <x:v>316</x:v>
+        <x:v>1547</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="16.799999237060547" hidden="0" customHeight="1">
@@ -8737,10 +9062,10 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="B45" s="9" t="n">
-        <x:v>13020</x:v>
+        <x:v>13420</x:v>
       </x:c>
       <x:c r="C45" s="10" t="n">
-        <x:v>4607</x:v>
+        <x:v>6620</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="15" hidden="0" customHeight="1">
@@ -8748,10 +9073,10 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="B46" s="12" t="n">
-        <x:v>8410</x:v>
+        <x:v>8380</x:v>
       </x:c>
       <x:c r="C46" s="13" t="n">
-        <x:v>1678</x:v>
+        <x:v>3114</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -8759,10 +9084,10 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="B47" s="12" t="n">
-        <x:v>2300</x:v>
+        <x:v>2280</x:v>
       </x:c>
       <x:c r="C47" s="13" t="n">
-        <x:v>692</x:v>
+        <x:v>1194</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -8770,241 +9095,252 @@
         <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="B48" s="12" t="n">
-        <x:v>3400</x:v>
+        <x:v>3350</x:v>
       </x:c>
       <x:c r="C48" s="13" t="n">
-        <x:v>479</x:v>
+        <x:v>1026</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
-      <x:c r="A49" s="14" t="str">
+      <x:c r="A49" s="11" t="str">
         <x:v>AI托管</x:v>
       </x:c>
-      <x:c r="B49" s="15" t="n">
-        <x:v>1300</x:v>
-      </x:c>
-      <x:c r="C49" s="16" t="n">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" ht="16.799999237060547" hidden="0" customHeight="1">
-      <x:c r="A52" s="4" t="str">
+      <x:c r="B49" s="12" t="n">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="C49" s="13" t="n">
+        <x:v>173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="15" hidden="0" customHeight="1">
+      <x:c r="A50" s="14" t="str">
+        <x:v>图书微转</x:v>
+      </x:c>
+      <x:c r="B50" s="15" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="C50" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A53" s="4" t="str">
         <x:v>维度分布 - 价体</x:v>
       </x:c>
-      <x:c r="B52" s="4" t="str">
+      <x:c r="B53" s="4" t="str">
         <x:v>维度分布 - 价体</x:v>
       </x:c>
-      <x:c r="C52" s="4" t="str">
+      <x:c r="C53" s="4" t="str">
         <x:v>维度分布 - 价体</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="15" hidden="0" customHeight="1">
-      <x:c r="A53" s="7" t="str">
+    <x:row r="54" ht="15" hidden="0" customHeight="1">
+      <x:c r="A54" s="7" t="str">
         <x:v>价体</x:v>
       </x:c>
-      <x:c r="B53" s="7" t="str">
+      <x:c r="B54" s="7" t="str">
         <x:v>目标</x:v>
       </x:c>
-      <x:c r="C53" s="7" t="str">
+      <x:c r="C54" s="7" t="str">
         <x:v>现状</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="15" hidden="0" customHeight="1">
-      <x:c r="A54" s="8" t="n">
+    <x:row r="55" ht="15" hidden="0" customHeight="1">
+      <x:c r="A55" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="B54" s="9" t="n">
-        <x:v>14000</x:v>
-      </x:c>
-      <x:c r="C54" s="10" t="n">
-        <x:v>4909</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" ht="15" hidden="0" customHeight="1">
-      <x:c r="A55" s="11" t="n">
-        <x:v>990</x:v>
-      </x:c>
-      <x:c r="B55" s="12" t="n">
-        <x:v>6760</x:v>
-      </x:c>
-      <x:c r="C55" s="13" t="n">
-        <x:v>1639</x:v>
+      <x:c r="B55" s="9" t="n">
+        <x:v>14850</x:v>
+      </x:c>
+      <x:c r="C55" s="10" t="n">
+        <x:v>7158</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
       <x:c r="A56" s="11" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="B56" s="12" t="n">
-        <x:v>6370</x:v>
+        <x:v>6710</x:v>
       </x:c>
       <x:c r="C56" s="13" t="n">
-        <x:v>907</x:v>
+        <x:v>2905</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="15" hidden="0" customHeight="1">
       <x:c r="A57" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="B57" s="12" t="n">
-        <x:v>1300</x:v>
+        <x:v>6370</x:v>
       </x:c>
       <x:c r="C57" s="13" t="n">
-        <x:v>55</x:v>
+        <x:v>1890</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
-      <x:c r="A58" s="14" t="n">
+      <x:c r="A58" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B58" s="12" t="n">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="C58" s="13" t="n">
+        <x:v>173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="15" hidden="0" customHeight="1">
+      <x:c r="A59" s="14" t="n">
         <x:v>1880</x:v>
       </x:c>
-      <x:c r="B58" s="15" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C58" s="16" t="n">
+      <x:c r="B59" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C59" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="16.799999237060547" hidden="0" customHeight="1">
-      <x:c r="A61" s="4" t="str">
+    <x:row r="62" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A62" s="4" t="str">
         <x:v>维度分布 - 年级</x:v>
       </x:c>
-      <x:c r="B61" s="4" t="str">
+      <x:c r="B62" s="4" t="str">
         <x:v>维度分布 - 年级</x:v>
       </x:c>
-      <x:c r="C61" s="4" t="str">
+      <x:c r="C62" s="4" t="str">
         <x:v>维度分布 - 年级</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="15" hidden="0" customHeight="1">
-      <x:c r="A62" s="7" t="str">
+    <x:row r="63" ht="15" hidden="0" customHeight="1">
+      <x:c r="A63" s="7" t="str">
         <x:v>年级</x:v>
       </x:c>
-      <x:c r="B62" s="7" t="str">
+      <x:c r="B63" s="7" t="str">
         <x:v>目标</x:v>
       </x:c>
-      <x:c r="C62" s="7" t="str">
+      <x:c r="C63" s="7" t="str">
         <x:v>现状</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="15" hidden="0" customHeight="1">
-      <x:c r="A63" s="8" t="str">
-        <x:v>初一</x:v>
-      </x:c>
-      <x:c r="B63" s="9" t="n">
-        <x:v>1730</x:v>
-      </x:c>
-      <x:c r="C63" s="10" t="n">
-        <x:v>1181</x:v>
-      </x:c>
-    </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
-      <x:c r="A64" s="11" t="str">
-        <x:v>四年级</x:v>
-      </x:c>
-      <x:c r="B64" s="12" t="n">
-        <x:v>3400</x:v>
-      </x:c>
-      <x:c r="C64" s="13" t="n">
-        <x:v>1162</x:v>
+      <x:c r="A64" s="8" t="str">
+        <x:v>初二</x:v>
+      </x:c>
+      <x:c r="B64" s="9" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="C64" s="10" t="n">
+        <x:v>1711</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
       <x:c r="A65" s="11" t="str">
-        <x:v>初二</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="B65" s="12" t="n">
-        <x:v>3780</x:v>
+        <x:v>3400</x:v>
       </x:c>
       <x:c r="C65" s="13" t="n">
-        <x:v>1109</x:v>
+        <x:v>1687</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
       <x:c r="A66" s="11" t="str">
-        <x:v>初三</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="B66" s="12" t="n">
-        <x:v>3740</x:v>
+        <x:v>1730</x:v>
       </x:c>
       <x:c r="C66" s="13" t="n">
-        <x:v>959</x:v>
+        <x:v>1538</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
       <x:c r="A67" s="11" t="str">
-        <x:v>六年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="B67" s="12" t="n">
-        <x:v>3100</x:v>
+        <x:v>2780</x:v>
       </x:c>
       <x:c r="C67" s="13" t="n">
-        <x:v>945</x:v>
+        <x:v>1442</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
       <x:c r="A68" s="11" t="str">
-        <x:v>三年级</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="B68" s="12" t="n">
-        <x:v>2780</x:v>
+        <x:v>3740</x:v>
       </x:c>
       <x:c r="C68" s="13" t="n">
-        <x:v>923</x:v>
+        <x:v>1411</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
       <x:c r="A69" s="11" t="str">
-        <x:v>五年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="B69" s="12" t="n">
-        <x:v>2720</x:v>
+        <x:v>3100</x:v>
       </x:c>
       <x:c r="C69" s="13" t="n">
-        <x:v>866</x:v>
+        <x:v>1355</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
       <x:c r="A70" s="11" t="str">
-        <x:v>高二</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="B70" s="12" t="n">
-        <x:v>2860</x:v>
+        <x:v>2720</x:v>
       </x:c>
       <x:c r="C70" s="13" t="n">
-        <x:v>238</x:v>
+        <x:v>1343</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
       <x:c r="A71" s="11" t="str">
-        <x:v>二年级</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="B71" s="12" t="n">
-        <x:v>100</x:v>
+        <x:v>4140</x:v>
       </x:c>
       <x:c r="C71" s="13" t="n">
-        <x:v>50</x:v>
+        <x:v>779</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
       <x:c r="A72" s="11" t="str">
+        <x:v>高三</x:v>
+      </x:c>
+      <x:c r="B72" s="12" t="n">
+        <x:v>2780</x:v>
+      </x:c>
+      <x:c r="C72" s="13" t="n">
+        <x:v>394</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="15" hidden="0" customHeight="1">
+      <x:c r="A73" s="11" t="str">
         <x:v>高一</x:v>
       </x:c>
-      <x:c r="B72" s="12" t="n">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c r="C72" s="13" t="n">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" ht="15" hidden="0" customHeight="1">
-      <x:c r="A73" s="14" t="str">
-        <x:v>高三</x:v>
-      </x:c>
-      <x:c r="B73" s="15" t="n">
-        <x:v>2200</x:v>
-      </x:c>
-      <x:c r="C73" s="16" t="n">
-        <x:v>35</x:v>
+      <x:c r="B73" s="12" t="n">
+        <x:v>860</x:v>
+      </x:c>
+      <x:c r="C73" s="13" t="n">
+        <x:v>374</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="15" hidden="0" customHeight="1">
+      <x:c r="A74" s="14" t="str">
+        <x:v>二年级</x:v>
+      </x:c>
+      <x:c r="B74" s="15" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C74" s="16" t="n">
+        <x:v>93</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9013,8 +9349,8 @@
     <x:mergeCell ref="A29:C29"/>
     <x:mergeCell ref="A36:C36"/>
     <x:mergeCell ref="A43:C43"/>
-    <x:mergeCell ref="A52:C52"/>
-    <x:mergeCell ref="A61:C61"/>
+    <x:mergeCell ref="A53:C53"/>
+    <x:mergeCell ref="A62:C62"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/outputs/tongji_summary/tongji_summary_current.xlsx
+++ b/outputs/tongji_summary/tongji_summary_current.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目标现状对比" sheetId="1" r:id="R2364a6ebeb1f4b0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据概览" sheetId="2" r:id="R52a1ff082082424c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目标现状对比" sheetId="1" r:id="R0d233472c4554b79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据概览" sheetId="2" r:id="Re21c6194ae114e23"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -512,7 +512,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F3" s="20" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G3" s="20" t="str">
         <x:v>2026-06-30</x:v>
@@ -524,16 +524,16 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="J3" s="17" t="n">
-        <x:v>20</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K3" s="17" t="n">
-        <x:v>-120</x:v>
+        <x:v>-94</x:v>
       </x:c>
       <x:c r="L3" s="23" t="n">
-        <x:v>0.14285714285714285</x:v>
+        <x:v>0.32857142857142857</x:v>
       </x:c>
       <x:c r="M3" s="24" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -553,7 +553,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F4" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G4" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -565,16 +565,16 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="J4" s="18" t="n">
-        <x:v>45</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K4" s="18" t="n">
-        <x:v>-75</x:v>
+        <x:v>-32</x:v>
       </x:c>
       <x:c r="L4" s="25" t="n">
-        <x:v>0.375</x:v>
+        <x:v>0.7333333333333333</x:v>
       </x:c>
       <x:c r="M4" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -594,7 +594,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F5" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G5" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -606,16 +606,16 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="J5" s="18" t="n">
-        <x:v>33</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K5" s="18" t="n">
-        <x:v>-107</x:v>
+        <x:v>-74</x:v>
       </x:c>
       <x:c r="L5" s="25" t="n">
-        <x:v>0.2357142857142857</x:v>
+        <x:v>0.4714285714285714</x:v>
       </x:c>
       <x:c r="M5" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -656,7 +656,7 @@
         <x:v>1.6466666666666667</x:v>
       </x:c>
       <x:c r="M6" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -676,7 +676,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F7" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G7" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -688,16 +688,16 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="J7" s="18" t="n">
-        <x:v>367</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="K7" s="18" t="n">
-        <x:v>-233</x:v>
+        <x:v>-95</x:v>
       </x:c>
       <x:c r="L7" s="25" t="n">
-        <x:v>0.6116666666666667</x:v>
+        <x:v>0.8416666666666667</x:v>
       </x:c>
       <x:c r="M7" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -717,7 +717,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F8" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G8" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -729,16 +729,16 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="J8" s="18" t="n">
-        <x:v>274</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="K8" s="18" t="n">
-        <x:v>-326</x:v>
+        <x:v>-234</x:v>
       </x:c>
       <x:c r="L8" s="25" t="n">
-        <x:v>0.45666666666666667</x:v>
+        <x:v>0.61</x:v>
       </x:c>
       <x:c r="M8" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -758,7 +758,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F9" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G9" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -770,16 +770,16 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="J9" s="18" t="n">
-        <x:v>344</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="K9" s="18" t="n">
-        <x:v>-156</x:v>
+        <x:v>-42</x:v>
       </x:c>
       <x:c r="L9" s="25" t="n">
-        <x:v>0.688</x:v>
+        <x:v>0.916</x:v>
       </x:c>
       <x:c r="M9" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
@@ -799,7 +799,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F10" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G10" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -811,16 +811,16 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="J10" s="18" t="n">
-        <x:v>295</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="K10" s="18" t="n">
-        <x:v>-405</x:v>
+        <x:v>-260</x:v>
       </x:c>
       <x:c r="L10" s="25" t="n">
-        <x:v>0.42142857142857143</x:v>
+        <x:v>0.6285714285714286</x:v>
       </x:c>
       <x:c r="M10" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
@@ -840,7 +840,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F11" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G11" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -852,16 +852,16 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="J11" s="18" t="n">
-        <x:v>265</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="K11" s="18" t="n">
-        <x:v>-435</x:v>
+        <x:v>-320</x:v>
       </x:c>
       <x:c r="L11" s="25" t="n">
-        <x:v>0.37857142857142856</x:v>
+        <x:v>0.5428571428571428</x:v>
       </x:c>
       <x:c r="M11" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -881,7 +881,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F12" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G12" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -893,16 +893,16 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J12" s="18" t="n">
-        <x:v>203</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="K12" s="18" t="n">
-        <x:v>103</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="L12" s="25" t="n">
-        <x:v>2.03</x:v>
+        <x:v>3.61</x:v>
       </x:c>
       <x:c r="M12" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -922,7 +922,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F13" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G13" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -934,16 +934,16 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="J13" s="18" t="n">
-        <x:v>207</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="K13" s="18" t="n">
-        <x:v>-443</x:v>
+        <x:v>-261</x:v>
       </x:c>
       <x:c r="L13" s="25" t="n">
-        <x:v>0.31846153846153846</x:v>
+        <x:v>0.5984615384615385</x:v>
       </x:c>
       <x:c r="M13" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -984,7 +984,7 @@
         <x:v>0.12615384615384614</x:v>
       </x:c>
       <x:c r="M14" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -1004,7 +1004,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F15" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G15" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1016,16 +1016,16 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="J15" s="18" t="n">
-        <x:v>109</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K15" s="18" t="n">
-        <x:v>-81</x:v>
+        <x:v>-40</x:v>
       </x:c>
       <x:c r="L15" s="25" t="n">
-        <x:v>0.5736842105263158</x:v>
+        <x:v>0.7894736842105263</x:v>
       </x:c>
       <x:c r="M15" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
@@ -1045,7 +1045,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F16" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G16" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1057,16 +1057,16 @@
         <x:v>360</x:v>
       </x:c>
       <x:c r="J16" s="18" t="n">
-        <x:v>144</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="K16" s="18" t="n">
-        <x:v>-216</x:v>
+        <x:v>-159</x:v>
       </x:c>
       <x:c r="L16" s="25" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.5583333333333333</x:v>
       </x:c>
       <x:c r="M16" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -1086,7 +1086,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F17" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G17" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1098,16 +1098,16 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J17" s="18" t="n">
-        <x:v>125</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="K17" s="18" t="n">
-        <x:v>-175</x:v>
+        <x:v>-115</x:v>
       </x:c>
       <x:c r="L17" s="25" t="n">
-        <x:v>0.4166666666666667</x:v>
+        <x:v>0.6166666666666667</x:v>
       </x:c>
       <x:c r="M17" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
@@ -1160,7 +1160,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F19" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G19" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1172,16 +1172,16 @@
         <x:v>400</x:v>
       </x:c>
       <x:c r="J19" s="18" t="n">
-        <x:v>320</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="K19" s="18" t="n">
-        <x:v>-80</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="L19" s="25" t="n">
-        <x:v>0.8</x:v>
+        <x:v>0.9775</x:v>
       </x:c>
       <x:c r="M19" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -1201,7 +1201,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F20" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G20" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1213,16 +1213,16 @@
         <x:v>400</x:v>
       </x:c>
       <x:c r="J20" s="18" t="n">
-        <x:v>365</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="K20" s="18" t="n">
-        <x:v>-35</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L20" s="25" t="n">
-        <x:v>0.9125</x:v>
+        <x:v>1.15</x:v>
       </x:c>
       <x:c r="M20" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -1242,7 +1242,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F21" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G21" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1254,16 +1254,16 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="J21" s="18" t="n">
-        <x:v>362</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="K21" s="18" t="n">
-        <x:v>-138</x:v>
+        <x:v>-32</x:v>
       </x:c>
       <x:c r="L21" s="25" t="n">
-        <x:v>0.724</x:v>
+        <x:v>0.936</x:v>
       </x:c>
       <x:c r="M21" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -1283,7 +1283,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F22" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G22" s="21"/>
       <x:c r="H22" s="21"/>
@@ -1291,10 +1291,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J22" s="18" t="n">
-        <x:v>38</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K22" s="18" t="n">
-        <x:v>38</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="L22" s="25"/>
       <x:c r="M22" s="26"/>
@@ -1316,7 +1316,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F23" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G23" s="21"/>
       <x:c r="H23" s="21"/>
@@ -1324,10 +1324,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J23" s="18" t="n">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K23" s="18" t="n">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="L23" s="25"/>
       <x:c r="M23" s="26"/>
@@ -1349,7 +1349,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F24" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G24" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1361,16 +1361,16 @@
         <x:v>950</x:v>
       </x:c>
       <x:c r="J24" s="18" t="n">
-        <x:v>295</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="K24" s="18" t="n">
-        <x:v>-655</x:v>
+        <x:v>-559</x:v>
       </x:c>
       <x:c r="L24" s="25" t="n">
-        <x:v>0.3105263157894737</x:v>
+        <x:v>0.41157894736842104</x:v>
       </x:c>
       <x:c r="M24" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
@@ -1390,7 +1390,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F25" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G25" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1402,16 +1402,16 @@
         <x:v>950</x:v>
       </x:c>
       <x:c r="J25" s="18" t="n">
-        <x:v>252</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="K25" s="18" t="n">
-        <x:v>-698</x:v>
+        <x:v>-579</x:v>
       </x:c>
       <x:c r="L25" s="25" t="n">
-        <x:v>0.26526315789473687</x:v>
+        <x:v>0.39052631578947367</x:v>
       </x:c>
       <x:c r="M25" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
@@ -1431,7 +1431,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F26" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G26" s="21"/>
       <x:c r="H26" s="21"/>
@@ -1439,10 +1439,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J26" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K26" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L26" s="25"/>
       <x:c r="M26" s="26"/>
@@ -1464,7 +1464,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F27" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G27" s="21"/>
       <x:c r="H27" s="21"/>
@@ -1472,10 +1472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J27" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K27" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L27" s="25"/>
       <x:c r="M27" s="26"/>
@@ -1497,7 +1497,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F28" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G28" s="21"/>
       <x:c r="H28" s="21"/>
@@ -1505,10 +1505,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J28" s="18" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K28" s="18" t="n">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L28" s="25"/>
       <x:c r="M28" s="26"/>
@@ -1629,7 +1629,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F32" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G32" s="21"/>
       <x:c r="H32" s="21"/>
@@ -1637,10 +1637,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J32" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K32" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L32" s="25"/>
       <x:c r="M32" s="26"/>
@@ -2718,7 +2718,7 @@
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F65" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G65" s="21"/>
       <x:c r="H65" s="21"/>
@@ -2726,10 +2726,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J65" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K65" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L65" s="25"/>
       <x:c r="M65" s="26"/>
@@ -2751,7 +2751,7 @@
         <x:v>六年级</x:v>
       </x:c>
       <x:c r="F66" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G66" s="21"/>
       <x:c r="H66" s="21"/>
@@ -2759,10 +2759,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J66" s="18" t="n">
-        <x:v>110</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="K66" s="18" t="n">
-        <x:v>110</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="L66" s="25"/>
       <x:c r="M66" s="26"/>
@@ -2805,19 +2805,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B68" s="12" t="str">
-        <x:v>暑_6</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C68" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D68" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E68" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F68" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G68" s="21"/>
       <x:c r="H68" s="21"/>
@@ -2825,10 +2825,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J68" s="18" t="n">
-        <x:v>68</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K68" s="18" t="n">
-        <x:v>68</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L68" s="25"/>
       <x:c r="M68" s="26"/>
@@ -2847,7 +2847,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E69" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F69" s="21" t="str">
         <x:v>2026-06-20</x:v>
@@ -2858,10 +2858,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J69" s="18" t="n">
-        <x:v>51</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K69" s="18" t="n">
-        <x:v>51</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="L69" s="25"/>
       <x:c r="M69" s="26"/>
@@ -2880,10 +2880,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E70" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F70" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G70" s="21"/>
       <x:c r="H70" s="21"/>
@@ -2891,10 +2891,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J70" s="18" t="n">
-        <x:v>35</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K70" s="18" t="n">
-        <x:v>35</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L70" s="25"/>
       <x:c r="M70" s="26"/>
@@ -2907,16 +2907,16 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C71" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D71" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E71" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F71" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G71" s="21"/>
       <x:c r="H71" s="21"/>
@@ -2924,10 +2924,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J71" s="18" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="K71" s="18" t="n">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="L71" s="25"/>
       <x:c r="M71" s="26"/>
@@ -2946,7 +2946,7 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E72" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F72" s="21" t="str">
         <x:v>2026-06-17</x:v>
@@ -2957,10 +2957,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J72" s="18" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K72" s="18" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L72" s="25"/>
       <x:c r="M72" s="26"/>
@@ -2973,13 +2973,13 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C73" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D73" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E73" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F73" s="21" t="str">
         <x:v>2026-06-17</x:v>
@@ -2990,10 +2990,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J73" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K73" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L73" s="25"/>
       <x:c r="M73" s="26"/>
@@ -3012,7 +3012,7 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E74" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F74" s="21" t="str">
         <x:v>2026-06-17</x:v>
@@ -3023,10 +3023,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J74" s="18" t="n">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K74" s="18" t="n">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L74" s="25"/>
       <x:c r="M74" s="26"/>
@@ -3045,7 +3045,7 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E75" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F75" s="21" t="str">
         <x:v>2026-06-17</x:v>
@@ -3056,10 +3056,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J75" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K75" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L75" s="25"/>
       <x:c r="M75" s="26"/>
@@ -3072,13 +3072,13 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C76" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D76" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E76" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F76" s="21" t="str">
         <x:v>2026-06-17</x:v>
@@ -3089,10 +3089,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J76" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K76" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L76" s="25"/>
       <x:c r="M76" s="26"/>
@@ -3111,7 +3111,7 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E77" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F77" s="21" t="str">
         <x:v>2026-06-17</x:v>
@@ -3122,10 +3122,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J77" s="18" t="n">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K77" s="18" t="n">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L77" s="25"/>
       <x:c r="M77" s="26"/>
@@ -3135,19 +3135,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B78" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C78" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D78" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E78" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F78" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G78" s="21"/>
       <x:c r="H78" s="21"/>
@@ -3155,10 +3155,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J78" s="18" t="n">
-        <x:v>20</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K78" s="18" t="n">
-        <x:v>20</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L78" s="25"/>
       <x:c r="M78" s="26"/>
@@ -3177,10 +3177,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E79" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F79" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G79" s="21"/>
       <x:c r="H79" s="21"/>
@@ -3188,10 +3188,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J79" s="18" t="n">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K79" s="18" t="n">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="L79" s="25"/>
       <x:c r="M79" s="26"/>
@@ -3210,10 +3210,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E80" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F80" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G80" s="21"/>
       <x:c r="H80" s="21"/>
@@ -3221,10 +3221,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J80" s="18" t="n">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="K80" s="18" t="n">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="L80" s="25"/>
       <x:c r="M80" s="26"/>
@@ -3243,10 +3243,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E81" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F81" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G81" s="21"/>
       <x:c r="H81" s="21"/>
@@ -3254,10 +3254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J81" s="18" t="n">
-        <x:v>30</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K81" s="18" t="n">
-        <x:v>30</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="L81" s="25"/>
       <x:c r="M81" s="26"/>
@@ -3270,16 +3270,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C82" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D82" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E82" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F82" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G82" s="21"/>
       <x:c r="H82" s="21"/>
@@ -3287,10 +3287,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J82" s="18" t="n">
-        <x:v>1968</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K82" s="18" t="n">
-        <x:v>1968</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="L82" s="25"/>
       <x:c r="M82" s="26"/>
@@ -3309,10 +3309,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E83" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F83" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G83" s="21"/>
       <x:c r="H83" s="21"/>
@@ -3320,10 +3320,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J83" s="18" t="n">
-        <x:v>2036</x:v>
+        <x:v>1968</x:v>
       </x:c>
       <x:c r="K83" s="18" t="n">
-        <x:v>2036</x:v>
+        <x:v>1968</x:v>
       </x:c>
       <x:c r="L83" s="25"/>
       <x:c r="M83" s="26"/>
@@ -3342,7 +3342,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E84" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F84" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -3353,10 +3353,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J84" s="18" t="n">
-        <x:v>1513</x:v>
+        <x:v>2036</x:v>
       </x:c>
       <x:c r="K84" s="18" t="n">
-        <x:v>1513</x:v>
+        <x:v>2036</x:v>
       </x:c>
       <x:c r="L84" s="25"/>
       <x:c r="M84" s="26"/>
@@ -3375,7 +3375,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E85" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F85" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -3386,10 +3386,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J85" s="18" t="n">
-        <x:v>1857</x:v>
+        <x:v>1513</x:v>
       </x:c>
       <x:c r="K85" s="18" t="n">
-        <x:v>1857</x:v>
+        <x:v>1513</x:v>
       </x:c>
       <x:c r="L85" s="25"/>
       <x:c r="M85" s="26"/>
@@ -3405,13 +3405,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D86" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E86" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F86" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G86" s="21"/>
       <x:c r="H86" s="21"/>
@@ -3419,10 +3419,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J86" s="18" t="n">
-        <x:v>131</x:v>
+        <x:v>1857</x:v>
       </x:c>
       <x:c r="K86" s="18" t="n">
-        <x:v>131</x:v>
+        <x:v>1857</x:v>
       </x:c>
       <x:c r="L86" s="25"/>
       <x:c r="M86" s="26"/>
@@ -3441,7 +3441,7 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E87" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F87" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -3452,10 +3452,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J87" s="18" t="n">
-        <x:v>191</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="K87" s="18" t="n">
-        <x:v>191</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="L87" s="25"/>
       <x:c r="M87" s="26"/>
@@ -3474,7 +3474,7 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E88" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F88" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -3485,10 +3485,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J88" s="18" t="n">
-        <x:v>156</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="K88" s="18" t="n">
-        <x:v>156</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="L88" s="25"/>
       <x:c r="M88" s="26"/>
@@ -3507,7 +3507,7 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E89" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F89" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -3518,10 +3518,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J89" s="18" t="n">
-        <x:v>135</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="K89" s="18" t="n">
-        <x:v>135</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="L89" s="25"/>
       <x:c r="M89" s="26"/>
@@ -3534,16 +3534,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C90" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D90" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E90" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F90" s="21" t="str">
-        <x:v>2026-06-22</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G90" s="21"/>
       <x:c r="H90" s="21"/>
@@ -3551,10 +3551,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J90" s="18" t="n">
-        <x:v>66</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="K90" s="18" t="n">
-        <x:v>66</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L90" s="25"/>
       <x:c r="M90" s="26"/>
@@ -3573,10 +3573,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E91" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F91" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G91" s="21"/>
       <x:c r="H91" s="21"/>
@@ -3584,10 +3584,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J91" s="18" t="n">
-        <x:v>239</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K91" s="18" t="n">
-        <x:v>239</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="L91" s="25"/>
       <x:c r="M91" s="26"/>
@@ -3606,7 +3606,7 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E92" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F92" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -3617,10 +3617,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J92" s="18" t="n">
-        <x:v>252</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K92" s="18" t="n">
-        <x:v>252</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="L92" s="25"/>
       <x:c r="M92" s="26"/>
@@ -3639,10 +3639,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E93" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F93" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G93" s="21"/>
       <x:c r="H93" s="21"/>
@@ -3650,10 +3650,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J93" s="18" t="n">
-        <x:v>235</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="K93" s="18" t="n">
-        <x:v>235</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="L93" s="25"/>
       <x:c r="M93" s="26"/>
@@ -3672,10 +3672,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E94" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F94" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G94" s="21"/>
       <x:c r="H94" s="21"/>
@@ -3683,10 +3683,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J94" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="K94" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="L94" s="25"/>
       <x:c r="M94" s="26"/>
@@ -3699,13 +3699,13 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C95" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D95" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E95" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F95" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -3716,10 +3716,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J95" s="18" t="n">
-        <x:v>181</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K95" s="18" t="n">
-        <x:v>181</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L95" s="25"/>
       <x:c r="M95" s="26"/>
@@ -3738,10 +3738,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E96" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F96" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G96" s="21"/>
       <x:c r="H96" s="21"/>
@@ -3749,10 +3749,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J96" s="18" t="n">
-        <x:v>214</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="K96" s="18" t="n">
-        <x:v>214</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="L96" s="25"/>
       <x:c r="M96" s="26"/>
@@ -3771,7 +3771,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E97" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F97" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -3782,10 +3782,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J97" s="18" t="n">
-        <x:v>135</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="K97" s="18" t="n">
-        <x:v>135</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="L97" s="25"/>
       <x:c r="M97" s="26"/>
@@ -3804,7 +3804,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E98" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F98" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -3815,10 +3815,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J98" s="18" t="n">
-        <x:v>191</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="K98" s="18" t="n">
-        <x:v>191</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L98" s="25"/>
       <x:c r="M98" s="26"/>
@@ -3831,16 +3831,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C99" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D99" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E99" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F99" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G99" s="21"/>
       <x:c r="H99" s="21"/>
@@ -3848,10 +3848,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J99" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="K99" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="L99" s="25"/>
       <x:c r="M99" s="26"/>
@@ -3870,7 +3870,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E100" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F100" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -3903,7 +3903,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E101" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F101" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -3933,13 +3933,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D102" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E102" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F102" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G102" s="21"/>
       <x:c r="H102" s="21"/>
@@ -3947,10 +3947,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J102" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K102" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L102" s="25"/>
       <x:c r="M102" s="26"/>
@@ -3969,10 +3969,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E103" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F103" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G103" s="21"/>
       <x:c r="H103" s="21"/>
@@ -3980,10 +3980,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J103" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K103" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L103" s="25"/>
       <x:c r="M103" s="26"/>
@@ -4002,7 +4002,7 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E104" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F104" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -4013,10 +4013,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J104" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K104" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L104" s="25"/>
       <x:c r="M104" s="26"/>
@@ -4035,7 +4035,7 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E105" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F105" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -4046,10 +4046,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J105" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K105" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L105" s="25"/>
       <x:c r="M105" s="26"/>
@@ -4065,13 +4065,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D106" s="18" t="n">
-        <x:v>1880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E106" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F106" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G106" s="21"/>
       <x:c r="H106" s="21"/>
@@ -4079,10 +4079,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J106" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K106" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L106" s="25"/>
       <x:c r="M106" s="26"/>
@@ -4101,10 +4101,10 @@
         <x:v>1880</x:v>
       </x:c>
       <x:c r="E107" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F107" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G107" s="21"/>
       <x:c r="H107" s="21"/>
@@ -4112,10 +4112,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J107" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K107" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L107" s="25"/>
       <x:c r="M107" s="26"/>
@@ -4134,10 +4134,10 @@
         <x:v>1880</x:v>
       </x:c>
       <x:c r="E108" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F108" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G108" s="21"/>
       <x:c r="H108" s="21"/>
@@ -4145,10 +4145,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J108" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K108" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L108" s="25"/>
       <x:c r="M108" s="26"/>
@@ -4167,10 +4167,10 @@
         <x:v>1880</x:v>
       </x:c>
       <x:c r="E109" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F109" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G109" s="21"/>
       <x:c r="H109" s="21"/>
@@ -4200,7 +4200,7 @@
         <x:v>1880</x:v>
       </x:c>
       <x:c r="E110" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F110" s="21" t="str">
         <x:v>2026-06-20</x:v>
@@ -4230,13 +4230,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D111" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>1880</x:v>
       </x:c>
       <x:c r="E111" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F111" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G111" s="21"/>
       <x:c r="H111" s="21"/>
@@ -4244,10 +4244,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J111" s="18" t="n">
-        <x:v>89</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K111" s="18" t="n">
-        <x:v>89</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L111" s="25"/>
       <x:c r="M111" s="26"/>
@@ -4266,7 +4266,7 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E112" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F112" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -4277,10 +4277,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J112" s="18" t="n">
-        <x:v>227</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K112" s="18" t="n">
-        <x:v>227</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="L112" s="25"/>
       <x:c r="M112" s="26"/>
@@ -4299,7 +4299,7 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E113" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F113" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -4310,10 +4310,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J113" s="18" t="n">
-        <x:v>291</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="K113" s="18" t="n">
-        <x:v>291</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="L113" s="25"/>
       <x:c r="M113" s="26"/>
@@ -4332,7 +4332,7 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E114" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F114" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -4343,10 +4343,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J114" s="18" t="n">
-        <x:v>229</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="K114" s="18" t="n">
-        <x:v>229</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="L114" s="25"/>
       <x:c r="M114" s="26"/>
@@ -4365,7 +4365,7 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E115" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F115" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -4376,10 +4376,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J115" s="18" t="n">
-        <x:v>264</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="K115" s="18" t="n">
-        <x:v>264</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="L115" s="25"/>
       <x:c r="M115" s="26"/>
@@ -4389,39 +4389,33 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B116" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C116" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D116" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E116" s="12" t="str">
-        <x:v>三年级</x:v>
-      </x:c>
-      <x:c r="F116" s="21"/>
-      <x:c r="G116" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H116" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>六年级</x:v>
+      </x:c>
+      <x:c r="F116" s="21" t="str">
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="G116" s="21"/>
+      <x:c r="H116" s="21"/>
       <x:c r="I116" s="18" t="n">
-        <x:v>40</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J116" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="K116" s="18" t="n">
-        <x:v>-40</x:v>
-      </x:c>
-      <x:c r="L116" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M116" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="L116" s="25"/>
+      <x:c r="M116" s="26"/>
     </x:row>
     <x:row r="117" ht="15" hidden="0" customHeight="1">
       <x:c r="A117" s="11" t="str">
@@ -4437,9 +4431,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E117" s="12" t="str">
-        <x:v>四年级</x:v>
-      </x:c>
-      <x:c r="F117" s="21"/>
+        <x:v>三年级</x:v>
+      </x:c>
+      <x:c r="F117" s="21" t="str">
+        <x:v>2026-06-27</x:v>
+      </x:c>
       <x:c r="G117" s="21" t="str">
         <x:v>2026-07-01</x:v>
       </x:c>
@@ -4447,19 +4443,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I117" s="18" t="n">
-        <x:v>120</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J117" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K117" s="18" t="n">
-        <x:v>-120</x:v>
+        <x:v>-32</x:v>
       </x:c>
       <x:c r="L117" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="M117" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -4476,9 +4472,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E118" s="12" t="str">
-        <x:v>五年级</x:v>
-      </x:c>
-      <x:c r="F118" s="21"/>
+        <x:v>四年级</x:v>
+      </x:c>
+      <x:c r="F118" s="21" t="str">
+        <x:v>2026-06-27</x:v>
+      </x:c>
       <x:c r="G118" s="21" t="str">
         <x:v>2026-07-01</x:v>
       </x:c>
@@ -4489,16 +4487,16 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="J118" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K118" s="18" t="n">
-        <x:v>-120</x:v>
+        <x:v>-98</x:v>
       </x:c>
       <x:c r="L118" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>0.18333333333333332</x:v>
       </x:c>
       <x:c r="M118" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -4515,9 +4513,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E119" s="12" t="str">
-        <x:v>六年级</x:v>
-      </x:c>
-      <x:c r="F119" s="21"/>
+        <x:v>五年级</x:v>
+      </x:c>
+      <x:c r="F119" s="21" t="str">
+        <x:v>2026-06-27</x:v>
+      </x:c>
       <x:c r="G119" s="21" t="str">
         <x:v>2026-07-01</x:v>
       </x:c>
@@ -4528,16 +4528,16 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="J119" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K119" s="18" t="n">
-        <x:v>-120</x:v>
+        <x:v>-108</x:v>
       </x:c>
       <x:c r="L119" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="M119" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -4548,16 +4548,16 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C120" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D120" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E120" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F120" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G120" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4566,19 +4566,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I120" s="18" t="n">
-        <x:v>2300</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J120" s="18" t="n">
-        <x:v>1106</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K120" s="18" t="n">
-        <x:v>-1194</x:v>
+        <x:v>-106</x:v>
       </x:c>
       <x:c r="L120" s="25" t="n">
-        <x:v>0.4808695652173913</x:v>
+        <x:v>0.11666666666666667</x:v>
       </x:c>
       <x:c r="M120" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -4595,10 +4595,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E121" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F121" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G121" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4607,19 +4607,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I121" s="18" t="n">
-        <x:v>2500</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="J121" s="18" t="n">
-        <x:v>1208</x:v>
+        <x:v>1473</x:v>
       </x:c>
       <x:c r="K121" s="18" t="n">
-        <x:v>-1292</x:v>
+        <x:v>-827</x:v>
       </x:c>
       <x:c r="L121" s="25" t="n">
-        <x:v>0.4832</x:v>
+        <x:v>0.6404347826086957</x:v>
       </x:c>
       <x:c r="M121" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -4636,10 +4636,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E122" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F122" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G122" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4648,19 +4648,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I122" s="18" t="n">
-        <x:v>2000</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="J122" s="18" t="n">
-        <x:v>972</x:v>
+        <x:v>1547</x:v>
       </x:c>
       <x:c r="K122" s="18" t="n">
-        <x:v>-1028</x:v>
+        <x:v>-953</x:v>
       </x:c>
       <x:c r="L122" s="25" t="n">
-        <x:v>0.486</x:v>
+        <x:v>0.6188</x:v>
       </x:c>
       <x:c r="M122" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -4677,10 +4677,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E123" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F123" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G123" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4689,19 +4689,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I123" s="18" t="n">
-        <x:v>2300</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="J123" s="18" t="n">
-        <x:v>999</x:v>
+        <x:v>1271</x:v>
       </x:c>
       <x:c r="K123" s="18" t="n">
-        <x:v>-1301</x:v>
+        <x:v>-729</x:v>
       </x:c>
       <x:c r="L123" s="25" t="n">
-        <x:v>0.43434782608695655</x:v>
+        <x:v>0.6355</x:v>
       </x:c>
       <x:c r="M123" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -4715,13 +4715,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D124" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E124" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F124" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G124" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4730,19 +4730,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I124" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="J124" s="18" t="n">
-        <x:v>72</x:v>
+        <x:v>1265</x:v>
       </x:c>
       <x:c r="K124" s="18" t="n">
-        <x:v>-28</x:v>
+        <x:v>-1035</x:v>
       </x:c>
       <x:c r="L124" s="25" t="n">
-        <x:v>0.72</x:v>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="M124" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -4759,10 +4759,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E125" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F125" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G125" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4771,19 +4771,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I125" s="18" t="n">
-        <x:v>150</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J125" s="18" t="n">
-        <x:v>92</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="K125" s="18" t="n">
-        <x:v>-58</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L125" s="25" t="n">
-        <x:v>0.6133333333333333</x:v>
+        <x:v>1.01</x:v>
       </x:c>
       <x:c r="M125" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -4800,10 +4800,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E126" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F126" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G126" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4812,19 +4812,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I126" s="18" t="n">
-        <x:v>120</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J126" s="18" t="n">
-        <x:v>61</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="K126" s="18" t="n">
-        <x:v>-59</x:v>
+        <x:v>-13</x:v>
       </x:c>
       <x:c r="L126" s="25" t="n">
-        <x:v>0.5083333333333333</x:v>
+        <x:v>0.9133333333333333</x:v>
       </x:c>
       <x:c r="M126" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -4841,10 +4841,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E127" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F127" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G127" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4853,19 +4853,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I127" s="18" t="n">
-        <x:v>150</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J127" s="18" t="n">
-        <x:v>57</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K127" s="18" t="n">
-        <x:v>-93</x:v>
+        <x:v>-34</x:v>
       </x:c>
       <x:c r="L127" s="25" t="n">
-        <x:v>0.38</x:v>
+        <x:v>0.7166666666666667</x:v>
       </x:c>
       <x:c r="M127" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -4876,30 +4876,38 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C128" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D128" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E128" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F128" s="21" t="str">
-        <x:v>2026-06-26</x:v>
-      </x:c>
-      <x:c r="G128" s="21"/>
-      <x:c r="H128" s="21"/>
+        <x:v>2026-06-27</x:v>
+      </x:c>
+      <x:c r="G128" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H128" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I128" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J128" s="18" t="n">
-        <x:v>47</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="K128" s="18" t="n">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="L128" s="25"/>
-      <x:c r="M128" s="26"/>
+        <x:v>-57</x:v>
+      </x:c>
+      <x:c r="L128" s="25" t="n">
+        <x:v>0.62</x:v>
+      </x:c>
+      <x:c r="M128" s="26" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
       <x:c r="A129" s="11" t="str">
@@ -4915,32 +4923,24 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E129" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F129" s="21" t="str">
-        <x:v>2026-06-26</x:v>
-      </x:c>
-      <x:c r="G129" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H129" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-27</x:v>
+      </x:c>
+      <x:c r="G129" s="21"/>
+      <x:c r="H129" s="21"/>
       <x:c r="I129" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J129" s="18" t="n">
-        <x:v>67</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="K129" s="18" t="n">
-        <x:v>-33</x:v>
-      </x:c>
-      <x:c r="L129" s="25" t="n">
-        <x:v>0.67</x:v>
-      </x:c>
-      <x:c r="M129" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L129" s="25"/>
+      <x:c r="M129" s="26"/>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
       <x:c r="A130" s="11" t="str">
@@ -4956,10 +4956,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E130" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F130" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G130" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4968,19 +4968,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I130" s="18" t="n">
-        <x:v>300</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J130" s="18" t="n">
-        <x:v>72</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K130" s="18" t="n">
-        <x:v>-228</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L130" s="25" t="n">
-        <x:v>0.24</x:v>
+        <x:v>1.09</x:v>
       </x:c>
       <x:c r="M130" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -4997,10 +4997,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E131" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F131" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G131" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5009,19 +5009,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I131" s="18" t="n">
-        <x:v>200</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J131" s="18" t="n">
-        <x:v>73</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K131" s="18" t="n">
-        <x:v>-127</x:v>
+        <x:v>-189</x:v>
       </x:c>
       <x:c r="L131" s="25" t="n">
-        <x:v>0.365</x:v>
+        <x:v>0.37</x:v>
       </x:c>
       <x:c r="M131" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -5038,10 +5038,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E132" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F132" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G132" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5053,16 +5053,16 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="J132" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K132" s="18" t="n">
-        <x:v>-195</x:v>
+        <x:v>-91</x:v>
       </x:c>
       <x:c r="L132" s="25" t="n">
-        <x:v>0.025</x:v>
+        <x:v>0.545</x:v>
       </x:c>
       <x:c r="M132" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -5073,30 +5073,38 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C133" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D133" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E133" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F133" s="21" t="str">
         <x:v>2026-06-26</x:v>
       </x:c>
-      <x:c r="G133" s="21"/>
-      <x:c r="H133" s="21"/>
+      <x:c r="G133" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H133" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I133" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="J133" s="18" t="n">
-        <x:v>126</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K133" s="18" t="n">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="L133" s="25"/>
-      <x:c r="M133" s="26"/>
+        <x:v>-195</x:v>
+      </x:c>
+      <x:c r="L133" s="25" t="n">
+        <x:v>0.025</x:v>
+      </x:c>
+      <x:c r="M133" s="26" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
       <x:c r="A134" s="11" t="str">
@@ -5112,10 +5120,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E134" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F134" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G134" s="21"/>
       <x:c r="H134" s="21"/>
@@ -5123,10 +5131,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J134" s="18" t="n">
-        <x:v>179</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="K134" s="18" t="n">
-        <x:v>179</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="L134" s="25"/>
       <x:c r="M134" s="26"/>
@@ -5145,10 +5153,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E135" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F135" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G135" s="21"/>
       <x:c r="H135" s="21"/>
@@ -5156,10 +5164,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J135" s="18" t="n">
-        <x:v>117</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="K135" s="18" t="n">
-        <x:v>117</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="L135" s="25"/>
       <x:c r="M135" s="26"/>
@@ -5178,10 +5186,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E136" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F136" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G136" s="21"/>
       <x:c r="H136" s="21"/>
@@ -5189,10 +5197,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J136" s="18" t="n">
-        <x:v>124</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K136" s="18" t="n">
-        <x:v>124</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="L136" s="25"/>
       <x:c r="M136" s="26"/>
@@ -5205,38 +5213,30 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C137" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D137" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E137" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F137" s="21" t="str">
-        <x:v>2026-06-26</x:v>
-      </x:c>
-      <x:c r="G137" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H137" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-27</x:v>
+      </x:c>
+      <x:c r="G137" s="21"/>
+      <x:c r="H137" s="21"/>
       <x:c r="I137" s="18" t="n">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J137" s="18" t="n">
-        <x:v>12</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="K137" s="18" t="n">
-        <x:v>-8</x:v>
-      </x:c>
-      <x:c r="L137" s="25" t="n">
-        <x:v>0.6</x:v>
-      </x:c>
-      <x:c r="M137" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="L137" s="25"/>
+      <x:c r="M137" s="26"/>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
       <x:c r="A138" s="11" t="str">
@@ -5252,10 +5252,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E138" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F138" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G138" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5264,19 +5264,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I138" s="18" t="n">
-        <x:v>50</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J138" s="18" t="n">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K138" s="18" t="n">
-        <x:v>-23</x:v>
+        <x:v>-3</x:v>
       </x:c>
       <x:c r="L138" s="25" t="n">
-        <x:v>0.54</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="M138" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="15" hidden="0" customHeight="1">
@@ -5293,10 +5293,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E139" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F139" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G139" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5305,19 +5305,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I139" s="18" t="n">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J139" s="18" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K139" s="18" t="n">
-        <x:v>-39</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="L139" s="25" t="n">
-        <x:v>0.44285714285714284</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="M139" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -5334,10 +5334,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E140" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F140" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G140" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5346,19 +5346,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I140" s="18" t="n">
-        <x:v>40</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J140" s="18" t="n">
-        <x:v>34</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K140" s="18" t="n">
-        <x:v>-6</x:v>
+        <x:v>-20</x:v>
       </x:c>
       <x:c r="L140" s="25" t="n">
-        <x:v>0.85</x:v>
+        <x:v>0.7142857142857143</x:v>
       </x:c>
       <x:c r="M140" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -5375,10 +5375,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E141" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F141" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G141" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5387,19 +5387,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I141" s="18" t="n">
-        <x:v>70</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J141" s="18" t="n">
-        <x:v>38</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K141" s="18" t="n">
-        <x:v>-32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L141" s="25" t="n">
-        <x:v>0.5428571428571428</x:v>
+        <x:v>1.325</x:v>
       </x:c>
       <x:c r="M141" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -5413,27 +5413,35 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D142" s="18" t="n">
-        <x:v>1880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E142" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F142" s="21" t="str">
-        <x:v>2026-06-24</x:v>
-      </x:c>
-      <x:c r="G142" s="21"/>
-      <x:c r="H142" s="21"/>
+        <x:v>2026-06-27</x:v>
+      </x:c>
+      <x:c r="G142" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H142" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I142" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J142" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K142" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L142" s="25"/>
-      <x:c r="M142" s="26"/>
+        <x:v>-21</x:v>
+      </x:c>
+      <x:c r="L142" s="25" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="M142" s="26" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
       <x:c r="A143" s="11" t="str">
@@ -5446,35 +5454,27 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D143" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>1880</x:v>
       </x:c>
       <x:c r="E143" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F143" s="21" t="str">
-        <x:v>2026-06-26</x:v>
-      </x:c>
-      <x:c r="G143" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H143" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="G143" s="21"/>
+      <x:c r="H143" s="21"/>
       <x:c r="I143" s="18" t="n">
-        <x:v>80</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J143" s="18" t="n">
-        <x:v>34</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K143" s="18" t="n">
-        <x:v>-46</x:v>
-      </x:c>
-      <x:c r="L143" s="25" t="n">
-        <x:v>0.425</x:v>
-      </x:c>
-      <x:c r="M143" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L143" s="25"/>
+      <x:c r="M143" s="26"/>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
       <x:c r="A144" s="11" t="str">
@@ -5490,10 +5490,10 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E144" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F144" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G144" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5502,19 +5502,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I144" s="18" t="n">
-        <x:v>190</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J144" s="18" t="n">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K144" s="18" t="n">
-        <x:v>-146</x:v>
+        <x:v>-40</x:v>
       </x:c>
       <x:c r="L144" s="25" t="n">
-        <x:v>0.23157894736842105</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="M144" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="15" hidden="0" customHeight="1">
@@ -5531,10 +5531,10 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E145" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F145" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G145" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5543,19 +5543,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I145" s="18" t="n">
-        <x:v>260</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="J145" s="18" t="n">
-        <x:v>104</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K145" s="18" t="n">
-        <x:v>-156</x:v>
+        <x:v>-129</x:v>
       </x:c>
       <x:c r="L145" s="25" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.32105263157894737</x:v>
       </x:c>
       <x:c r="M145" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -5572,10 +5572,10 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E146" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F146" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G146" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5584,19 +5584,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I146" s="18" t="n">
-        <x:v>240</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="J146" s="18" t="n">
-        <x:v>86</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="K146" s="18" t="n">
-        <x:v>-154</x:v>
+        <x:v>-132</x:v>
       </x:c>
       <x:c r="L146" s="25" t="n">
-        <x:v>0.35833333333333334</x:v>
+        <x:v>0.49230769230769234</x:v>
       </x:c>
       <x:c r="M146" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -5613,10 +5613,10 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E147" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F147" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G147" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5625,19 +5625,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I147" s="18" t="n">
-        <x:v>260</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="J147" s="18" t="n">
-        <x:v>132</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K147" s="18" t="n">
-        <x:v>-128</x:v>
+        <x:v>-127</x:v>
       </x:c>
       <x:c r="L147" s="25" t="n">
-        <x:v>0.5076923076923077</x:v>
+        <x:v>0.4708333333333333</x:v>
       </x:c>
       <x:c r="M147" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -5645,33 +5645,41 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B148" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C148" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D148" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E148" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F148" s="21" t="str">
-        <x:v>2026-06-22</x:v>
-      </x:c>
-      <x:c r="G148" s="21"/>
-      <x:c r="H148" s="21"/>
+        <x:v>2026-06-27</x:v>
+      </x:c>
+      <x:c r="G148" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H148" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I148" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="J148" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="K148" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L148" s="25"/>
-      <x:c r="M148" s="26"/>
+        <x:v>-95</x:v>
+      </x:c>
+      <x:c r="L148" s="25" t="n">
+        <x:v>0.6346153846153846</x:v>
+      </x:c>
+      <x:c r="M148" s="26" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
       <x:c r="A149" s="11" t="str">
@@ -5687,7 +5695,7 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E149" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F149" s="21" t="str">
         <x:v>2026-06-22</x:v>
@@ -5698,10 +5706,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J149" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K149" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L149" s="25"/>
       <x:c r="M149" s="26"/>
@@ -5720,10 +5728,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E150" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F150" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G150" s="21"/>
       <x:c r="H150" s="21"/>
@@ -5731,10 +5739,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J150" s="18" t="n">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K150" s="18" t="n">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L150" s="25"/>
       <x:c r="M150" s="26"/>
@@ -5753,10 +5761,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E151" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F151" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G151" s="21"/>
       <x:c r="H151" s="21"/>
@@ -5764,32 +5772,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J151" s="18" t="n">
-        <x:v>163</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K151" s="18" t="n">
-        <x:v>163</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L151" s="25"/>
       <x:c r="M151" s="26"/>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
       <x:c r="A152" s="11" t="str">
-        <x:v>自拼</x:v>
+        <x:v>小学</x:v>
       </x:c>
       <x:c r="B152" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C152" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D152" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E152" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F152" s="21" t="str">
-        <x:v>2026-06-22</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G152" s="21"/>
       <x:c r="H152" s="21"/>
@@ -5797,10 +5805,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J152" s="18" t="n">
-        <x:v>218</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="K152" s="18" t="n">
-        <x:v>218</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="L152" s="25"/>
       <x:c r="M152" s="26"/>
@@ -5819,10 +5827,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E153" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F153" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G153" s="21"/>
       <x:c r="H153" s="21"/>
@@ -5830,10 +5838,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J153" s="18" t="n">
-        <x:v>79</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="K153" s="18" t="n">
-        <x:v>79</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="L153" s="25"/>
       <x:c r="M153" s="26"/>
@@ -5852,7 +5860,7 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E154" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F154" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -5863,10 +5871,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J154" s="18" t="n">
-        <x:v>32</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="K154" s="18" t="n">
-        <x:v>32</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="L154" s="25"/>
       <x:c r="M154" s="26"/>
@@ -5879,16 +5887,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C155" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D155" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E155" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F155" s="21" t="str">
-        <x:v>2026-06-22</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G155" s="21"/>
       <x:c r="H155" s="21"/>
@@ -5896,10 +5904,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J155" s="18" t="n">
-        <x:v>314</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K155" s="18" t="n">
-        <x:v>314</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L155" s="25"/>
       <x:c r="M155" s="26"/>
@@ -5918,10 +5926,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E156" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F156" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G156" s="21"/>
       <x:c r="H156" s="21"/>
@@ -5929,10 +5937,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J156" s="18" t="n">
-        <x:v>116</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="K156" s="18" t="n">
-        <x:v>116</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="L156" s="25"/>
       <x:c r="M156" s="26"/>
@@ -5951,7 +5959,7 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E157" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F157" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -5962,10 +5970,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J157" s="18" t="n">
-        <x:v>89</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K157" s="18" t="n">
-        <x:v>89</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="L157" s="25"/>
       <x:c r="M157" s="26"/>
@@ -5978,16 +5986,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C158" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D158" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E158" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F158" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G158" s="21"/>
       <x:c r="H158" s="21"/>
@@ -5995,10 +6003,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J158" s="18" t="n">
-        <x:v>32</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K158" s="18" t="n">
-        <x:v>32</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="L158" s="25"/>
       <x:c r="M158" s="26"/>
@@ -6017,10 +6025,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E159" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F159" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G159" s="21"/>
       <x:c r="H159" s="21"/>
@@ -6028,10 +6036,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J159" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K159" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L159" s="25"/>
       <x:c r="M159" s="26"/>
@@ -6050,7 +6058,7 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E160" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F160" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -6061,10 +6069,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J160" s="18" t="n">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K160" s="18" t="n">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L160" s="25"/>
       <x:c r="M160" s="26"/>
@@ -6077,16 +6085,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C161" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D161" s="18" t="n">
-        <x:v>2990</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E161" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F161" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G161" s="21"/>
       <x:c r="H161" s="21"/>
@@ -6094,10 +6102,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J161" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K161" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L161" s="25"/>
       <x:c r="M161" s="26"/>
@@ -6116,10 +6124,10 @@
         <x:v>2990</x:v>
       </x:c>
       <x:c r="E162" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F162" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G162" s="21"/>
       <x:c r="H162" s="21"/>
@@ -6127,10 +6135,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J162" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K162" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L162" s="25"/>
       <x:c r="M162" s="26"/>
@@ -6149,10 +6157,10 @@
         <x:v>2990</x:v>
       </x:c>
       <x:c r="E163" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F163" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G163" s="21"/>
       <x:c r="H163" s="21"/>
@@ -6160,10 +6168,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J163" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K163" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L163" s="25"/>
       <x:c r="M163" s="26"/>
@@ -6173,19 +6181,19 @@
         <x:v>自拼</x:v>
       </x:c>
       <x:c r="B164" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C164" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D164" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="E164" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F164" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G164" s="21"/>
       <x:c r="H164" s="21"/>
@@ -6193,10 +6201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J164" s="18" t="n">
-        <x:v>282</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K164" s="18" t="n">
-        <x:v>282</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L164" s="25"/>
       <x:c r="M164" s="26"/>
@@ -6215,10 +6223,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E165" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F165" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G165" s="21"/>
       <x:c r="H165" s="21"/>
@@ -6226,10 +6234,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J165" s="18" t="n">
-        <x:v>46</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="K165" s="18" t="n">
-        <x:v>46</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="L165" s="25"/>
       <x:c r="M165" s="26"/>
@@ -6248,10 +6256,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E166" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F166" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G166" s="21"/>
       <x:c r="H166" s="21"/>
@@ -6259,10 +6267,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J166" s="18" t="n">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K166" s="18" t="n">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L166" s="25"/>
       <x:c r="M166" s="26"/>
@@ -6275,13 +6283,13 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C167" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D167" s="18" t="n">
-        <x:v>2990</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E167" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F167" s="21" t="str">
         <x:v>2026-06-26</x:v>
@@ -6292,10 +6300,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J167" s="18" t="n">
-        <x:v>9</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K167" s="18" t="n">
-        <x:v>9</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L167" s="25"/>
       <x:c r="M167" s="26"/>
@@ -6314,10 +6322,10 @@
         <x:v>2990</x:v>
       </x:c>
       <x:c r="E168" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F168" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G168" s="21"/>
       <x:c r="H168" s="21"/>
@@ -6325,10 +6333,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J168" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K168" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L168" s="25"/>
       <x:c r="M168" s="26"/>
@@ -6347,10 +6355,10 @@
         <x:v>2990</x:v>
       </x:c>
       <x:c r="E169" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F169" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G169" s="21"/>
       <x:c r="H169" s="21"/>
@@ -6358,29 +6366,29 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J169" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K169" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L169" s="25"/>
       <x:c r="M169" s="26"/>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
       <x:c r="A170" s="11" t="str">
-        <x:v>高中</x:v>
+        <x:v>自拼</x:v>
       </x:c>
       <x:c r="B170" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C170" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D170" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="E170" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F170" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6391,10 +6399,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J170" s="18" t="n">
-        <x:v>55</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K170" s="18" t="n">
-        <x:v>55</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L170" s="25"/>
       <x:c r="M170" s="26"/>
@@ -6413,7 +6421,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E171" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F171" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6424,10 +6432,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J171" s="18" t="n">
-        <x:v>115</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K171" s="18" t="n">
-        <x:v>115</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="L171" s="25"/>
       <x:c r="M171" s="26"/>
@@ -6446,7 +6454,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E172" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F172" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6457,10 +6465,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J172" s="18" t="n">
-        <x:v>96</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="K172" s="18" t="n">
-        <x:v>96</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="L172" s="25"/>
       <x:c r="M172" s="26"/>
@@ -6473,13 +6481,13 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C173" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D173" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E173" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F173" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6490,10 +6498,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J173" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K173" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="L173" s="25"/>
       <x:c r="M173" s="26"/>
@@ -6512,10 +6520,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E174" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F174" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G174" s="21"/>
       <x:c r="H174" s="21"/>
@@ -6523,10 +6531,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J174" s="18" t="n">
-        <x:v>73</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K174" s="18" t="n">
-        <x:v>73</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="L174" s="25"/>
       <x:c r="M174" s="26"/>
@@ -6545,10 +6553,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E175" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F175" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G175" s="21"/>
       <x:c r="H175" s="21"/>
@@ -6556,10 +6564,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J175" s="18" t="n">
-        <x:v>106</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K175" s="18" t="n">
-        <x:v>106</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="L175" s="25"/>
       <x:c r="M175" s="26"/>
@@ -6572,16 +6580,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C176" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D176" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E176" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F176" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G176" s="21"/>
       <x:c r="H176" s="21"/>
@@ -6589,10 +6597,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J176" s="18" t="n">
-        <x:v>677</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="K176" s="18" t="n">
-        <x:v>677</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="L176" s="25"/>
       <x:c r="M176" s="26"/>
@@ -6611,10 +6619,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E177" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F177" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G177" s="21"/>
       <x:c r="H177" s="21"/>
@@ -6622,10 +6630,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J177" s="18" t="n">
-        <x:v>186</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="K177" s="18" t="n">
-        <x:v>186</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="L177" s="25"/>
       <x:c r="M177" s="26"/>
@@ -6638,13 +6646,13 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C178" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D178" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E178" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F178" s="21" t="str">
         <x:v>2026-06-21</x:v>
@@ -6655,10 +6663,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J178" s="18" t="n">
-        <x:v>9</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="K178" s="18" t="n">
-        <x:v>9</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="L178" s="25"/>
       <x:c r="M178" s="26"/>
@@ -6677,7 +6685,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E179" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F179" s="21" t="str">
         <x:v>2026-06-21</x:v>
@@ -6688,10 +6696,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J179" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K179" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L179" s="25"/>
       <x:c r="M179" s="26"/>
@@ -6710,7 +6718,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E180" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F180" s="21" t="str">
         <x:v>2026-06-21</x:v>
@@ -6721,10 +6729,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J180" s="18" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K180" s="18" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L180" s="25"/>
       <x:c r="M180" s="26"/>
@@ -6740,13 +6748,13 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D181" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E181" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F181" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G181" s="21"/>
       <x:c r="H181" s="21"/>
@@ -6754,10 +6762,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J181" s="18" t="n">
-        <x:v>358</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K181" s="18" t="n">
-        <x:v>358</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L181" s="25"/>
       <x:c r="M181" s="26"/>
@@ -6776,7 +6784,7 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E182" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F182" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6787,10 +6795,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J182" s="18" t="n">
-        <x:v>291</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="K182" s="18" t="n">
-        <x:v>291</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="L182" s="25"/>
       <x:c r="M182" s="26"/>
@@ -6809,7 +6817,7 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E183" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F183" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6820,10 +6828,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J183" s="18" t="n">
-        <x:v>320</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="K183" s="18" t="n">
-        <x:v>320</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="L183" s="25"/>
       <x:c r="M183" s="26"/>
@@ -6836,13 +6844,13 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C184" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D184" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E184" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F184" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6853,10 +6861,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J184" s="18" t="n">
-        <x:v>697</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="K184" s="18" t="n">
-        <x:v>697</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="L184" s="25"/>
       <x:c r="M184" s="26"/>
@@ -6875,7 +6883,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E185" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F185" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6886,10 +6894,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J185" s="18" t="n">
-        <x:v>960</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="K185" s="18" t="n">
-        <x:v>960</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="L185" s="25"/>
       <x:c r="M185" s="26"/>
@@ -6908,7 +6916,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E186" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F186" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6919,10 +6927,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J186" s="18" t="n">
-        <x:v>633</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="K186" s="18" t="n">
-        <x:v>633</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="L186" s="25"/>
       <x:c r="M186" s="26"/>
@@ -6938,10 +6946,10 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D187" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E187" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F187" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6952,10 +6960,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J187" s="18" t="n">
-        <x:v>434</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="K187" s="18" t="n">
-        <x:v>434</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="L187" s="25"/>
       <x:c r="M187" s="26"/>
@@ -6974,7 +6982,7 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E188" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F188" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6985,10 +6993,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J188" s="18" t="n">
-        <x:v>626</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="K188" s="18" t="n">
-        <x:v>626</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="L188" s="25"/>
       <x:c r="M188" s="26"/>
@@ -7007,7 +7015,7 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E189" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F189" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -7018,10 +7026,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J189" s="18" t="n">
-        <x:v>558</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="K189" s="18" t="n">
-        <x:v>558</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="L189" s="25"/>
       <x:c r="M189" s="26"/>
@@ -7031,41 +7039,33 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B190" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C190" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D190" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E190" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F190" s="21" t="str">
-        <x:v>2026-06-26</x:v>
-      </x:c>
-      <x:c r="G190" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H190" s="21" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
+      <x:c r="G190" s="21"/>
+      <x:c r="H190" s="21"/>
       <x:c r="I190" s="18" t="n">
-        <x:v>80</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J190" s="18" t="n">
-        <x:v>12</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="K190" s="18" t="n">
-        <x:v>-68</x:v>
-      </x:c>
-      <x:c r="L190" s="25" t="n">
-        <x:v>0.15</x:v>
-      </x:c>
-      <x:c r="M190" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="L190" s="25"/>
+      <x:c r="M190" s="26"/>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
       <x:c r="A191" s="11" t="str">
@@ -7081,10 +7081,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E191" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F191" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G191" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7093,19 +7093,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I191" s="18" t="n">
-        <x:v>160</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J191" s="18" t="n">
-        <x:v>44</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="K191" s="18" t="n">
-        <x:v>-116</x:v>
+        <x:v>-38</x:v>
       </x:c>
       <x:c r="L191" s="25" t="n">
-        <x:v>0.275</x:v>
+        <x:v>0.525</x:v>
       </x:c>
       <x:c r="M191" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
@@ -7122,10 +7122,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E192" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F192" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G192" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7137,16 +7137,16 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="J192" s="18" t="n">
-        <x:v>19</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K192" s="18" t="n">
-        <x:v>-141</x:v>
+        <x:v>-56</x:v>
       </x:c>
       <x:c r="L192" s="25" t="n">
-        <x:v>0.11875</x:v>
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="M192" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -7157,16 +7157,16 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C193" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D193" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E193" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F193" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G193" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7175,19 +7175,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I193" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="J193" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K193" s="18" t="n">
-        <x:v>-95</x:v>
+        <x:v>-102</x:v>
       </x:c>
       <x:c r="L193" s="25" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.3625</x:v>
       </x:c>
       <x:c r="M193" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -7204,10 +7204,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E194" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F194" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G194" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7216,19 +7216,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I194" s="18" t="n">
-        <x:v>150</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J194" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K194" s="18" t="n">
-        <x:v>-146</x:v>
+        <x:v>-91</x:v>
       </x:c>
       <x:c r="L194" s="25" t="n">
-        <x:v>0.02666666666666667</x:v>
+        <x:v>0.09</x:v>
       </x:c>
       <x:c r="M194" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
@@ -7245,10 +7245,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E195" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F195" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G195" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7260,16 +7260,16 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="J195" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K195" s="18" t="n">
-        <x:v>-145</x:v>
+        <x:v>-143</x:v>
       </x:c>
       <x:c r="L195" s="25" t="n">
-        <x:v>0.03333333333333333</x:v>
+        <x:v>0.04666666666666667</x:v>
       </x:c>
       <x:c r="M195" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
@@ -7280,16 +7280,16 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C196" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D196" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E196" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F196" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G196" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7298,19 +7298,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I196" s="18" t="n">
-        <x:v>50</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J196" s="18" t="n">
-        <x:v>190</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K196" s="18" t="n">
-        <x:v>140</x:v>
+        <x:v>-144</x:v>
       </x:c>
       <x:c r="L196" s="25" t="n">
-        <x:v>3.8</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="M196" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
@@ -7327,10 +7327,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E197" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F197" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G197" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7339,19 +7339,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I197" s="18" t="n">
-        <x:v>900</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J197" s="18" t="n">
-        <x:v>80</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="K197" s="18" t="n">
-        <x:v>-820</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="L197" s="25" t="n">
-        <x:v>0.08888888888888889</x:v>
+        <x:v>10.76</x:v>
       </x:c>
       <x:c r="M197" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
@@ -7368,9 +7368,11 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E198" s="12" t="str">
-        <x:v>高三</x:v>
-      </x:c>
-      <x:c r="F198" s="21"/>
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F198" s="21" t="str">
+        <x:v>2026-06-27</x:v>
+      </x:c>
       <x:c r="G198" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7378,19 +7380,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I198" s="18" t="n">
-        <x:v>200</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="J198" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="K198" s="18" t="n">
-        <x:v>-200</x:v>
+        <x:v>-754</x:v>
       </x:c>
       <x:c r="L198" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>0.1622222222222222</x:v>
       </x:c>
       <x:c r="M198" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
@@ -7401,13 +7403,13 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C199" s="12" t="str">
-        <x:v>图书微转</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D199" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E199" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F199" s="21"/>
       <x:c r="G199" s="21" t="str">
@@ -7417,19 +7419,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I199" s="18" t="n">
-        <x:v>150</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="J199" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K199" s="18" t="n">
-        <x:v>-150</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="L199" s="25" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M199" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
@@ -7440,36 +7442,30 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C200" s="12" t="str">
-        <x:v>图书微转</x:v>
+        <x:v>图书店铺</x:v>
       </x:c>
       <x:c r="D200" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E200" s="12" t="str">
-        <x:v>高二</x:v>
-      </x:c>
-      <x:c r="F200" s="21"/>
-      <x:c r="G200" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H200" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F200" s="21" t="str">
+        <x:v>2026-06-27</x:v>
+      </x:c>
+      <x:c r="G200" s="21"/>
+      <x:c r="H200" s="21"/>
       <x:c r="I200" s="18" t="n">
-        <x:v>200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J200" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K200" s="18" t="n">
-        <x:v>-200</x:v>
-      </x:c>
-      <x:c r="L200" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M200" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="L200" s="25"/>
+      <x:c r="M200" s="26"/>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
       <x:c r="A201" s="11" t="str">
@@ -7479,36 +7475,30 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C201" s="12" t="str">
-        <x:v>图书微转</x:v>
+        <x:v>图书店铺</x:v>
       </x:c>
       <x:c r="D201" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E201" s="12" t="str">
-        <x:v>高三</x:v>
-      </x:c>
-      <x:c r="F201" s="21"/>
-      <x:c r="G201" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H201" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F201" s="21" t="str">
+        <x:v>2026-06-27</x:v>
+      </x:c>
+      <x:c r="G201" s="21"/>
+      <x:c r="H201" s="21"/>
       <x:c r="I201" s="18" t="n">
-        <x:v>150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J201" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K201" s="18" t="n">
-        <x:v>-150</x:v>
-      </x:c>
-      <x:c r="L201" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M201" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L201" s="25"/>
+      <x:c r="M201" s="26"/>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
       <x:c r="A202" s="11" t="str">
@@ -7518,38 +7508,30 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C202" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>图书店铺</x:v>
       </x:c>
       <x:c r="D202" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E202" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F202" s="21" t="str">
-        <x:v>2026-06-26</x:v>
-      </x:c>
-      <x:c r="G202" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H202" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-27</x:v>
+      </x:c>
+      <x:c r="G202" s="21"/>
+      <x:c r="H202" s="21"/>
       <x:c r="I202" s="18" t="n">
-        <x:v>300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J202" s="18" t="n">
-        <x:v>139</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K202" s="18" t="n">
-        <x:v>-161</x:v>
-      </x:c>
-      <x:c r="L202" s="25" t="n">
-        <x:v>0.4633333333333333</x:v>
-      </x:c>
-      <x:c r="M202" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L202" s="25"/>
+      <x:c r="M202" s="26"/>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
       <x:c r="A203" s="11" t="str">
@@ -7559,17 +7541,15 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C203" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>图书微转</x:v>
       </x:c>
       <x:c r="D203" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E203" s="12" t="str">
-        <x:v>高二</x:v>
-      </x:c>
-      <x:c r="F203" s="21" t="str">
-        <x:v>2026-06-26</x:v>
-      </x:c>
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F203" s="21"/>
       <x:c r="G203" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7577,19 +7557,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I203" s="18" t="n">
-        <x:v>530</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J203" s="18" t="n">
-        <x:v>63</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K203" s="18" t="n">
-        <x:v>-467</x:v>
+        <x:v>-150</x:v>
       </x:c>
       <x:c r="L203" s="25" t="n">
-        <x:v>0.11886792452830189</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M203" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -7600,17 +7580,15 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C204" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>图书微转</x:v>
       </x:c>
       <x:c r="D204" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E204" s="12" t="str">
-        <x:v>高三</x:v>
-      </x:c>
-      <x:c r="F204" s="21" t="str">
-        <x:v>2026-06-26</x:v>
-      </x:c>
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F204" s="21"/>
       <x:c r="G204" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7618,19 +7596,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I204" s="18" t="n">
-        <x:v>600</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="J204" s="18" t="n">
-        <x:v>68</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K204" s="18" t="n">
-        <x:v>-532</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="L204" s="25" t="n">
-        <x:v>0.11333333333333333</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M204" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -7641,17 +7619,15 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C205" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>图书微转</x:v>
       </x:c>
       <x:c r="D205" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E205" s="12" t="str">
-        <x:v>高一</x:v>
-      </x:c>
-      <x:c r="F205" s="21" t="str">
-        <x:v>2026-06-26</x:v>
-      </x:c>
+        <x:v>高三</x:v>
+      </x:c>
+      <x:c r="F205" s="21"/>
       <x:c r="G205" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7659,19 +7635,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I205" s="18" t="n">
-        <x:v>180</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J205" s="18" t="n">
-        <x:v>27</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K205" s="18" t="n">
-        <x:v>-153</x:v>
+        <x:v>-150</x:v>
       </x:c>
       <x:c r="L205" s="25" t="n">
-        <x:v>0.15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M205" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -7682,16 +7658,16 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C206" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D206" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E206" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F206" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G206" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7700,19 +7676,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I206" s="18" t="n">
-        <x:v>1500</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J206" s="18" t="n">
-        <x:v>366</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="K206" s="18" t="n">
-        <x:v>-1134</x:v>
+        <x:v>-146</x:v>
       </x:c>
       <x:c r="L206" s="25" t="n">
-        <x:v>0.244</x:v>
+        <x:v>0.5133333333333333</x:v>
       </x:c>
       <x:c r="M206" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -7723,16 +7699,16 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C207" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D207" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E207" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F207" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G207" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7741,19 +7717,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I207" s="18" t="n">
-        <x:v>870</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="J207" s="18" t="n">
-        <x:v>94</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="K207" s="18" t="n">
-        <x:v>-776</x:v>
+        <x:v>-381</x:v>
       </x:c>
       <x:c r="L207" s="25" t="n">
-        <x:v>0.10804597701149425</x:v>
+        <x:v>0.2811320754716981</x:v>
       </x:c>
       <x:c r="M207" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -7764,30 +7740,38 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C208" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D208" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E208" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F208" s="21" t="str">
-        <x:v>2026-06-26</x:v>
-      </x:c>
-      <x:c r="G208" s="21"/>
-      <x:c r="H208" s="21"/>
+        <x:v>2026-06-27</x:v>
+      </x:c>
+      <x:c r="G208" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H208" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I208" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="J208" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="K208" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L208" s="25"/>
-      <x:c r="M208" s="26"/>
+        <x:v>-422</x:v>
+      </x:c>
+      <x:c r="L208" s="25" t="n">
+        <x:v>0.2966666666666667</x:v>
+      </x:c>
+      <x:c r="M208" s="26" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
       <x:c r="A209" s="11" t="str">
@@ -7800,27 +7784,35 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D209" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E209" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F209" s="21" t="str">
-        <x:v>2026-06-26</x:v>
-      </x:c>
-      <x:c r="G209" s="21"/>
-      <x:c r="H209" s="21"/>
+        <x:v>2026-06-27</x:v>
+      </x:c>
+      <x:c r="G209" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H209" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I209" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="J209" s="18" t="n">
-        <x:v>21</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="K209" s="18" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="L209" s="25"/>
-      <x:c r="M209" s="26"/>
+        <x:v>-14</x:v>
+      </x:c>
+      <x:c r="L209" s="25" t="n">
+        <x:v>0.9222222222222223</x:v>
+      </x:c>
+      <x:c r="M209" s="26" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
       <x:c r="A210" s="11" t="str">
@@ -7833,27 +7825,35 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D210" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E210" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F210" s="21" t="str">
-        <x:v>2026-06-26</x:v>
-      </x:c>
-      <x:c r="G210" s="21"/>
-      <x:c r="H210" s="21"/>
+        <x:v>2026-06-27</x:v>
+      </x:c>
+      <x:c r="G210" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H210" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I210" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="J210" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="K210" s="18" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="L210" s="25"/>
-      <x:c r="M210" s="26"/>
+        <x:v>-942</x:v>
+      </x:c>
+      <x:c r="L210" s="25" t="n">
+        <x:v>0.372</x:v>
+      </x:c>
+      <x:c r="M210" s="26" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="211" ht="15" hidden="0" customHeight="1">
       <x:c r="A211" s="11" t="str">
@@ -7866,12 +7866,14 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D211" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E211" s="12" t="str">
-        <x:v>高一</x:v>
-      </x:c>
-      <x:c r="F211" s="21"/>
+        <x:v>高三</x:v>
+      </x:c>
+      <x:c r="F211" s="21" t="str">
+        <x:v>2026-06-27</x:v>
+      </x:c>
       <x:c r="G211" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7879,17 +7881,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I211" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>870</x:v>
       </x:c>
       <x:c r="J211" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="K211" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L211" s="25"/>
+        <x:v>-650</x:v>
+      </x:c>
+      <x:c r="L211" s="25" t="n">
+        <x:v>0.25287356321839083</x:v>
+      </x:c>
       <x:c r="M211" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.5</x:v>
       </x:c>
     </x:row>
     <x:row r="212" ht="15" hidden="0" customHeight="1">
@@ -7903,35 +7907,27 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D212" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E212" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F212" s="21" t="str">
-        <x:v>2026-06-26</x:v>
-      </x:c>
-      <x:c r="G212" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H212" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-27</x:v>
+      </x:c>
+      <x:c r="G212" s="21"/>
+      <x:c r="H212" s="21"/>
       <x:c r="I212" s="18" t="n">
-        <x:v>700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J212" s="18" t="n">
-        <x:v>201</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K212" s="18" t="n">
-        <x:v>-499</x:v>
-      </x:c>
-      <x:c r="L212" s="25" t="n">
-        <x:v>0.28714285714285714</x:v>
-      </x:c>
-      <x:c r="M212" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L212" s="25"/>
+      <x:c r="M212" s="26"/>
     </x:row>
     <x:row r="213" ht="15" hidden="0" customHeight="1">
       <x:c r="A213" s="11" t="str">
@@ -7944,54 +7940,46 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D213" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E213" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F213" s="21" t="str">
-        <x:v>2026-06-26</x:v>
-      </x:c>
-      <x:c r="G213" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H213" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-27</x:v>
+      </x:c>
+      <x:c r="G213" s="21"/>
+      <x:c r="H213" s="21"/>
       <x:c r="I213" s="18" t="n">
-        <x:v>650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J213" s="18" t="n">
-        <x:v>203</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K213" s="18" t="n">
-        <x:v>-447</x:v>
-      </x:c>
-      <x:c r="L213" s="25" t="n">
-        <x:v>0.3123076923076923</x:v>
-      </x:c>
-      <x:c r="M213" s="26" t="n">
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="L213" s="25"/>
+      <x:c r="M213" s="26"/>
     </x:row>
     <x:row r="214" ht="15" hidden="0" customHeight="1">
       <x:c r="A214" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B214" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C214" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D214" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E214" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F214" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G214" s="21"/>
       <x:c r="H214" s="21"/>
@@ -7999,10 +7987,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J214" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K214" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L214" s="25"/>
       <x:c r="M214" s="26"/>
@@ -8012,118 +8000,138 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B215" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C215" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D215" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E215" s="12" t="str">
         <x:v>高一</x:v>
       </x:c>
-      <x:c r="F215" s="21" t="str">
-        <x:v>2026-06-26</x:v>
-      </x:c>
-      <x:c r="G215" s="21"/>
-      <x:c r="H215" s="21"/>
+      <x:c r="F215" s="21"/>
+      <x:c r="G215" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H215" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I215" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J215" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K215" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L215" s="25"/>
-      <x:c r="M215" s="26"/>
+      <x:c r="M215" s="26" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="216" ht="15" hidden="0" customHeight="1">
       <x:c r="A216" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B216" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C216" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D216" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E216" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F216" s="21" t="str">
-        <x:v>2026-06-18</x:v>
-      </x:c>
-      <x:c r="G216" s="21"/>
-      <x:c r="H216" s="21"/>
+        <x:v>2026-06-27</x:v>
+      </x:c>
+      <x:c r="G216" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H216" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I216" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="J216" s="18" t="n">
-        <x:v>27</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="K216" s="18" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="L216" s="25"/>
-      <x:c r="M216" s="26"/>
+        <x:v>-338</x:v>
+      </x:c>
+      <x:c r="L216" s="25" t="n">
+        <x:v>0.5171428571428571</x:v>
+      </x:c>
+      <x:c r="M216" s="26" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="217" ht="15" hidden="0" customHeight="1">
       <x:c r="A217" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B217" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C217" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D217" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E217" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F217" s="21" t="str">
-        <x:v>2026-06-18</x:v>
-      </x:c>
-      <x:c r="G217" s="21"/>
-      <x:c r="H217" s="21"/>
+        <x:v>2026-06-27</x:v>
+      </x:c>
+      <x:c r="G217" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H217" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I217" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="J217" s="18" t="n">
-        <x:v>63</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="K217" s="18" t="n">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="L217" s="25"/>
-      <x:c r="M217" s="26"/>
+        <x:v>-296</x:v>
+      </x:c>
+      <x:c r="L217" s="25" t="n">
+        <x:v>0.5446153846153846</x:v>
+      </x:c>
+      <x:c r="M217" s="26" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
     </x:row>
     <x:row r="218" ht="15" hidden="0" customHeight="1">
       <x:c r="A218" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B218" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C218" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D218" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E218" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F218" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G218" s="21"/>
       <x:c r="H218" s="21"/>
@@ -8131,10 +8139,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J218" s="18" t="n">
-        <x:v>50</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K218" s="18" t="n">
-        <x:v>50</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L218" s="25"/>
       <x:c r="M218" s="26"/>
@@ -8144,19 +8152,19 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B219" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C219" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D219" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E219" s="12" t="str">
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F219" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G219" s="21"/>
       <x:c r="H219" s="21"/>
@@ -8164,10 +8172,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J219" s="18" t="n">
-        <x:v>10</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K219" s="18" t="n">
-        <x:v>10</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L219" s="25"/>
       <x:c r="M219" s="26"/>
@@ -8180,13 +8188,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C220" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D220" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E220" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F220" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8197,10 +8205,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J220" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K220" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L220" s="25"/>
       <x:c r="M220" s="26"/>
@@ -8213,16 +8221,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C221" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D221" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E221" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F221" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G221" s="21"/>
       <x:c r="H221" s="21"/>
@@ -8230,10 +8238,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J221" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K221" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L221" s="25"/>
       <x:c r="M221" s="26"/>
@@ -8246,16 +8254,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C222" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D222" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E222" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F222" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G222" s="21"/>
       <x:c r="H222" s="21"/>
@@ -8263,10 +8271,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J222" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K222" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L222" s="25"/>
       <x:c r="M222" s="26"/>
@@ -8279,13 +8287,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C223" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D223" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E223" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F223" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8296,10 +8304,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J223" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K223" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L223" s="25"/>
       <x:c r="M223" s="26"/>
@@ -8312,13 +8320,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C224" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D224" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E224" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F224" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8329,10 +8337,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J224" s="18" t="n">
-        <x:v>146</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K224" s="18" t="n">
-        <x:v>146</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L224" s="25"/>
       <x:c r="M224" s="26"/>
@@ -8345,16 +8353,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C225" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D225" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E225" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F225" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G225" s="21"/>
       <x:c r="H225" s="21"/>
@@ -8362,10 +8370,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J225" s="18" t="n">
-        <x:v>157</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K225" s="18" t="n">
-        <x:v>157</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L225" s="25"/>
       <x:c r="M225" s="26"/>
@@ -8378,16 +8386,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C226" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D226" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E226" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F226" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G226" s="21"/>
       <x:c r="H226" s="21"/>
@@ -8395,10 +8403,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J226" s="18" t="n">
-        <x:v>136</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K226" s="18" t="n">
-        <x:v>136</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L226" s="25"/>
       <x:c r="M226" s="26"/>
@@ -8411,13 +8419,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C227" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D227" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E227" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F227" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8428,10 +8436,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J227" s="18" t="n">
-        <x:v>51</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K227" s="18" t="n">
-        <x:v>51</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L227" s="25"/>
       <x:c r="M227" s="26"/>
@@ -8447,13 +8455,13 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D228" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E228" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F228" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G228" s="21"/>
       <x:c r="H228" s="21"/>
@@ -8461,10 +8469,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J228" s="18" t="n">
-        <x:v>17</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="K228" s="18" t="n">
-        <x:v>17</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="L228" s="25"/>
       <x:c r="M228" s="26"/>
@@ -8480,10 +8488,10 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D229" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E229" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F229" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8494,10 +8502,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J229" s="18" t="n">
-        <x:v>30</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="K229" s="18" t="n">
-        <x:v>30</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="L229" s="25"/>
       <x:c r="M229" s="26"/>
@@ -8510,13 +8518,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C230" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D230" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E230" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F230" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8543,13 +8551,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C231" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D231" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E231" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F231" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8560,10 +8568,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J231" s="18" t="n">
-        <x:v>293</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K231" s="18" t="n">
-        <x:v>293</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L231" s="25"/>
       <x:c r="M231" s="26"/>
@@ -8576,16 +8584,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C232" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D232" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E232" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F232" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G232" s="21"/>
       <x:c r="H232" s="21"/>
@@ -8593,10 +8601,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J232" s="18" t="n">
-        <x:v>167</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K232" s="18" t="n">
-        <x:v>167</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="L232" s="25"/>
       <x:c r="M232" s="26"/>
@@ -8609,13 +8617,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C233" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D233" s="18" t="n">
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E233" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F233" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8626,10 +8634,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J233" s="18" t="n">
-        <x:v>92</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K233" s="18" t="n">
-        <x:v>92</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L233" s="25"/>
       <x:c r="M233" s="26"/>
@@ -8645,10 +8653,10 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D234" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E234" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F234" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8659,46 +8667,178 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J234" s="18" t="n">
-        <x:v>65</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K234" s="18" t="n">
-        <x:v>65</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="L234" s="25"/>
       <x:c r="M234" s="26"/>
     </x:row>
     <x:row r="235" ht="15" hidden="0" customHeight="1">
-      <x:c r="A235" s="14" t="str">
+      <x:c r="A235" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
-      <x:c r="B235" s="15" t="str">
+      <x:c r="B235" s="12" t="str">
         <x:v>暑_9</x:v>
       </x:c>
-      <x:c r="C235" s="15" t="str">
+      <x:c r="C235" s="12" t="str">
         <x:v>常规外呼</x:v>
       </x:c>
-      <x:c r="D235" s="19" t="n">
+      <x:c r="D235" s="18" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E235" s="12" t="str">
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F235" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G235" s="21"/>
+      <x:c r="H235" s="21"/>
+      <x:c r="I235" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J235" s="18" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="K235" s="18" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="L235" s="25"/>
+      <x:c r="M235" s="26"/>
+    </x:row>
+    <x:row r="236" ht="15" hidden="0" customHeight="1">
+      <x:c r="A236" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B236" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C236" s="12" t="str">
+        <x:v>常规外呼</x:v>
+      </x:c>
+      <x:c r="D236" s="18" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E236" s="12" t="str">
+        <x:v>高三</x:v>
+      </x:c>
+      <x:c r="F236" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G236" s="21"/>
+      <x:c r="H236" s="21"/>
+      <x:c r="I236" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J236" s="18" t="n">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="K236" s="18" t="n">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="L236" s="25"/>
+      <x:c r="M236" s="26"/>
+    </x:row>
+    <x:row r="237" ht="15" hidden="0" customHeight="1">
+      <x:c r="A237" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B237" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C237" s="12" t="str">
+        <x:v>常规外呼</x:v>
+      </x:c>
+      <x:c r="D237" s="18" t="n">
         <x:v>2880</x:v>
       </x:c>
-      <x:c r="E235" s="15" t="str">
+      <x:c r="E237" s="12" t="str">
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F237" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G237" s="21"/>
+      <x:c r="H237" s="21"/>
+      <x:c r="I237" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J237" s="18" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="K237" s="18" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="L237" s="25"/>
+      <x:c r="M237" s="26"/>
+    </x:row>
+    <x:row r="238" ht="15" hidden="0" customHeight="1">
+      <x:c r="A238" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B238" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C238" s="12" t="str">
+        <x:v>常规外呼</x:v>
+      </x:c>
+      <x:c r="D238" s="18" t="n">
+        <x:v>2880</x:v>
+      </x:c>
+      <x:c r="E238" s="12" t="str">
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F238" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G238" s="21"/>
+      <x:c r="H238" s="21"/>
+      <x:c r="I238" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J238" s="18" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="K238" s="18" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L238" s="25"/>
+      <x:c r="M238" s="26"/>
+    </x:row>
+    <x:row r="239" ht="15" hidden="0" customHeight="1">
+      <x:c r="A239" s="14" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B239" s="15" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C239" s="15" t="str">
+        <x:v>常规外呼</x:v>
+      </x:c>
+      <x:c r="D239" s="19" t="n">
+        <x:v>2880</x:v>
+      </x:c>
+      <x:c r="E239" s="15" t="str">
         <x:v>高三</x:v>
       </x:c>
-      <x:c r="F235" s="22" t="str">
+      <x:c r="F239" s="22" t="str">
         <x:v>2026-06-18</x:v>
       </x:c>
-      <x:c r="G235" s="22"/>
-      <x:c r="H235" s="22"/>
-      <x:c r="I235" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J235" s="19" t="n">
+      <x:c r="G239" s="22"/>
+      <x:c r="H239" s="22"/>
+      <x:c r="I239" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J239" s="19" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="K235" s="19" t="n">
+      <x:c r="K239" s="19" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="L235" s="27"/>
-      <x:c r="M235" s="28"/>
+      <x:c r="L239" s="27"/>
+      <x:c r="M239" s="28"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -8738,7 +8878,7 @@
         <x:v>现状原始行数</x:v>
       </x:c>
       <x:c r="B3" s="10" t="n">
-        <x:v>40422</x:v>
+        <x:v>45731</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -8754,7 +8894,7 @@
         <x:v>聚合组合数</x:v>
       </x:c>
       <x:c r="B5" s="13" t="n">
-        <x:v>233</x:v>
+        <x:v>237</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -8770,7 +8910,7 @@
         <x:v>现状合计</x:v>
       </x:c>
       <x:c r="B7" s="13" t="n">
-        <x:v>40422</x:v>
+        <x:v>45731</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -8778,7 +8918,7 @@
         <x:v>完成率整体</x:v>
       </x:c>
       <x:c r="B8" s="13" t="n">
-        <x:v>1.3876416065911432</x:v>
+        <x:v>1.5698935805012015</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -8802,7 +8942,7 @@
         <x:v>最新期次聚合组合数</x:v>
       </x:c>
       <x:c r="B11" s="13" t="n">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -8818,7 +8958,7 @@
         <x:v>最新期次现状合计</x:v>
       </x:c>
       <x:c r="B13" s="13" t="n">
-        <x:v>12127</x:v>
+        <x:v>17351</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -8826,7 +8966,7 @@
         <x:v>最新期次完成率整体</x:v>
       </x:c>
       <x:c r="B14" s="13" t="n">
-        <x:v>0.416306213525575</x:v>
+        <x:v>0.59564023343632</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -8955,7 +9095,7 @@
         <x:v>12100</x:v>
       </x:c>
       <x:c r="C31" s="10" t="n">
-        <x:v>5920</x:v>
+        <x:v>7823</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -8966,7 +9106,7 @@
         <x:v>9250</x:v>
       </x:c>
       <x:c r="C32" s="13" t="n">
-        <x:v>4660</x:v>
+        <x:v>6383</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
@@ -8977,7 +9117,7 @@
         <x:v>7780</x:v>
       </x:c>
       <x:c r="C33" s="16" t="n">
-        <x:v>1547</x:v>
+        <x:v>3145</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="16.799999237060547" hidden="0" customHeight="1">
@@ -9010,7 +9150,7 @@
         <x:v>12100</x:v>
       </x:c>
       <x:c r="C38" s="10" t="n">
-        <x:v>5920</x:v>
+        <x:v>7823</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
@@ -9021,7 +9161,7 @@
         <x:v>9250</x:v>
       </x:c>
       <x:c r="C39" s="13" t="n">
-        <x:v>4660</x:v>
+        <x:v>6383</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -9032,7 +9172,7 @@
         <x:v>7780</x:v>
       </x:c>
       <x:c r="C40" s="16" t="n">
-        <x:v>1547</x:v>
+        <x:v>3145</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="16.799999237060547" hidden="0" customHeight="1">
@@ -9065,7 +9205,7 @@
         <x:v>13420</x:v>
       </x:c>
       <x:c r="C45" s="10" t="n">
-        <x:v>6620</x:v>
+        <x:v>8638</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="15" hidden="0" customHeight="1">
@@ -9076,29 +9216,29 @@
         <x:v>8380</x:v>
       </x:c>
       <x:c r="C46" s="13" t="n">
-        <x:v>3114</x:v>
+        <x:v>4598</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
       <x:c r="A47" s="11" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="B47" s="12" t="n">
-        <x:v>2280</x:v>
+        <x:v>3350</x:v>
       </x:c>
       <x:c r="C47" s="13" t="n">
-        <x:v>1194</x:v>
+        <x:v>1907</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
       <x:c r="A48" s="11" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="B48" s="12" t="n">
-        <x:v>3350</x:v>
+        <x:v>2280</x:v>
       </x:c>
       <x:c r="C48" s="13" t="n">
-        <x:v>1026</x:v>
+        <x:v>1713</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -9109,161 +9249,161 @@
         <x:v>1200</x:v>
       </x:c>
       <x:c r="C49" s="13" t="n">
-        <x:v>173</x:v>
+        <x:v>460</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
-      <x:c r="A50" s="14" t="str">
+      <x:c r="A50" s="11" t="str">
+        <x:v>图书店铺</x:v>
+      </x:c>
+      <x:c r="B50" s="12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C50" s="13" t="n">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="15" hidden="0" customHeight="1">
+      <x:c r="A51" s="14" t="str">
         <x:v>图书微转</x:v>
       </x:c>
-      <x:c r="B50" s="15" t="n">
+      <x:c r="B51" s="15" t="n">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="C50" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" ht="16.799999237060547" hidden="0" customHeight="1">
-      <x:c r="A53" s="4" t="str">
+      <x:c r="C51" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A54" s="4" t="str">
         <x:v>维度分布 - 价体</x:v>
       </x:c>
-      <x:c r="B53" s="4" t="str">
+      <x:c r="B54" s="4" t="str">
         <x:v>维度分布 - 价体</x:v>
       </x:c>
-      <x:c r="C53" s="4" t="str">
+      <x:c r="C54" s="4" t="str">
         <x:v>维度分布 - 价体</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="15" hidden="0" customHeight="1">
-      <x:c r="A54" s="7" t="str">
+    <x:row r="55" ht="15" hidden="0" customHeight="1">
+      <x:c r="A55" s="7" t="str">
         <x:v>价体</x:v>
       </x:c>
-      <x:c r="B54" s="7" t="str">
+      <x:c r="B55" s="7" t="str">
         <x:v>目标</x:v>
       </x:c>
-      <x:c r="C54" s="7" t="str">
+      <x:c r="C55" s="7" t="str">
         <x:v>现状</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="15" hidden="0" customHeight="1">
-      <x:c r="A55" s="8" t="n">
+    <x:row r="56" ht="15" hidden="0" customHeight="1">
+      <x:c r="A56" s="8" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="B55" s="9" t="n">
+      <x:c r="B56" s="9" t="n">
         <x:v>14850</x:v>
       </x:c>
-      <x:c r="C55" s="10" t="n">
-        <x:v>7158</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" ht="15" hidden="0" customHeight="1">
-      <x:c r="A56" s="11" t="n">
-        <x:v>990</x:v>
-      </x:c>
-      <x:c r="B56" s="12" t="n">
-        <x:v>6710</x:v>
-      </x:c>
-      <x:c r="C56" s="13" t="n">
-        <x:v>2905</x:v>
+      <x:c r="C56" s="10" t="n">
+        <x:v>9475</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="15" hidden="0" customHeight="1">
       <x:c r="A57" s="11" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="B57" s="12" t="n">
-        <x:v>6370</x:v>
+        <x:v>6710</x:v>
       </x:c>
       <x:c r="C57" s="13" t="n">
-        <x:v>1890</x:v>
+        <x:v>4563</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
       <x:c r="A58" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="B58" s="12" t="n">
+        <x:v>6370</x:v>
+      </x:c>
+      <x:c r="C58" s="13" t="n">
+        <x:v>2852</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="15" hidden="0" customHeight="1">
+      <x:c r="A59" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B59" s="12" t="n">
         <x:v>1200</x:v>
       </x:c>
-      <x:c r="C58" s="13" t="n">
-        <x:v>173</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" ht="15" hidden="0" customHeight="1">
-      <x:c r="A59" s="14" t="n">
+      <x:c r="C59" s="13" t="n">
+        <x:v>460</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="15" hidden="0" customHeight="1">
+      <x:c r="A60" s="14" t="n">
         <x:v>1880</x:v>
       </x:c>
-      <x:c r="B59" s="15" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C59" s="16" t="n">
+      <x:c r="B60" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C60" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="16.799999237060547" hidden="0" customHeight="1">
-      <x:c r="A62" s="4" t="str">
+    <x:row r="63" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A63" s="4" t="str">
         <x:v>维度分布 - 年级</x:v>
       </x:c>
-      <x:c r="B62" s="4" t="str">
+      <x:c r="B63" s="4" t="str">
         <x:v>维度分布 - 年级</x:v>
       </x:c>
-      <x:c r="C62" s="4" t="str">
+      <x:c r="C63" s="4" t="str">
         <x:v>维度分布 - 年级</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="15" hidden="0" customHeight="1">
-      <x:c r="A63" s="7" t="str">
+    <x:row r="64" ht="15" hidden="0" customHeight="1">
+      <x:c r="A64" s="7" t="str">
         <x:v>年级</x:v>
       </x:c>
-      <x:c r="B63" s="7" t="str">
+      <x:c r="B64" s="7" t="str">
         <x:v>目标</x:v>
       </x:c>
-      <x:c r="C63" s="7" t="str">
+      <x:c r="C64" s="7" t="str">
         <x:v>现状</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="15" hidden="0" customHeight="1">
-      <x:c r="A64" s="8" t="str">
+    <x:row r="65" ht="15" hidden="0" customHeight="1">
+      <x:c r="A65" s="8" t="str">
         <x:v>初二</x:v>
       </x:c>
-      <x:c r="B64" s="9" t="n">
+      <x:c r="B65" s="9" t="n">
         <x:v>3780</x:v>
       </x:c>
-      <x:c r="C64" s="10" t="n">
-        <x:v>1711</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" ht="15" hidden="0" customHeight="1">
-      <x:c r="A65" s="11" t="str">
-        <x:v>四年级</x:v>
-      </x:c>
-      <x:c r="B65" s="12" t="n">
-        <x:v>3400</x:v>
-      </x:c>
-      <x:c r="C65" s="13" t="n">
-        <x:v>1687</x:v>
+      <x:c r="C65" s="10" t="n">
+        <x:v>2461</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
       <x:c r="A66" s="11" t="str">
-        <x:v>初一</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="B66" s="12" t="n">
-        <x:v>1730</x:v>
+        <x:v>3400</x:v>
       </x:c>
       <x:c r="C66" s="13" t="n">
-        <x:v>1538</x:v>
+        <x:v>2214</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
       <x:c r="A67" s="11" t="str">
-        <x:v>三年级</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="B67" s="12" t="n">
-        <x:v>2780</x:v>
+        <x:v>1730</x:v>
       </x:c>
       <x:c r="C67" s="13" t="n">
-        <x:v>1442</x:v>
+        <x:v>1983</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -9274,18 +9414,18 @@
         <x:v>3740</x:v>
       </x:c>
       <x:c r="C68" s="13" t="n">
-        <x:v>1411</x:v>
+        <x:v>1939</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
       <x:c r="A69" s="11" t="str">
-        <x:v>六年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="B69" s="12" t="n">
-        <x:v>3100</x:v>
+        <x:v>2780</x:v>
       </x:c>
       <x:c r="C69" s="13" t="n">
-        <x:v>1355</x:v>
+        <x:v>1939</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -9296,29 +9436,29 @@
         <x:v>2720</x:v>
       </x:c>
       <x:c r="C70" s="13" t="n">
-        <x:v>1343</x:v>
+        <x:v>1796</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
       <x:c r="A71" s="11" t="str">
-        <x:v>高二</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="B71" s="12" t="n">
-        <x:v>4140</x:v>
+        <x:v>3100</x:v>
       </x:c>
       <x:c r="C71" s="13" t="n">
-        <x:v>779</x:v>
+        <x:v>1760</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
       <x:c r="A72" s="11" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="B72" s="12" t="n">
-        <x:v>2780</x:v>
+        <x:v>4140</x:v>
       </x:c>
       <x:c r="C72" s="13" t="n">
-        <x:v>394</x:v>
+        <x:v>1382</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -9329,18 +9469,29 @@
         <x:v>860</x:v>
       </x:c>
       <x:c r="C73" s="13" t="n">
-        <x:v>374</x:v>
+        <x:v>932</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
-      <x:c r="A74" s="14" t="str">
+      <x:c r="A74" s="11" t="str">
+        <x:v>高三</x:v>
+      </x:c>
+      <x:c r="B74" s="12" t="n">
+        <x:v>2780</x:v>
+      </x:c>
+      <x:c r="C74" s="13" t="n">
+        <x:v>831</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="15" hidden="0" customHeight="1">
+      <x:c r="A75" s="14" t="str">
         <x:v>二年级</x:v>
       </x:c>
-      <x:c r="B74" s="15" t="n">
+      <x:c r="B75" s="15" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C74" s="16" t="n">
-        <x:v>93</x:v>
+      <x:c r="C75" s="16" t="n">
+        <x:v>114</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9349,8 +9500,8 @@
     <x:mergeCell ref="A29:C29"/>
     <x:mergeCell ref="A36:C36"/>
     <x:mergeCell ref="A43:C43"/>
-    <x:mergeCell ref="A53:C53"/>
-    <x:mergeCell ref="A62:C62"/>
+    <x:mergeCell ref="A54:C54"/>
+    <x:mergeCell ref="A63:C63"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/outputs/tongji_summary/tongji_summary_current.xlsx
+++ b/outputs/tongji_summary/tongji_summary_current.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目标现状对比" sheetId="1" r:id="R0d233472c4554b79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据概览" sheetId="2" r:id="Re21c6194ae114e23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目标现状对比" sheetId="1" r:id="R3b487c76e2c94d7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据概览" sheetId="2" r:id="Rba48ac16bb0d45e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计算规则" sheetId="3" r:id="R189f3912a3a94277"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -166,7 +167,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="40">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -196,6 +197,39 @@
     <x:xf numFmtId="202" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -512,7 +546,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F3" s="20" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G3" s="20" t="str">
         <x:v>2026-06-30</x:v>
@@ -524,16 +558,16 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="J3" s="17" t="n">
-        <x:v>46</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K3" s="17" t="n">
-        <x:v>-94</x:v>
+        <x:v>-55</x:v>
       </x:c>
       <x:c r="L3" s="23" t="n">
-        <x:v>0.32857142857142857</x:v>
+        <x:v>0.6071428571428571</x:v>
       </x:c>
       <x:c r="M3" s="24" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -553,7 +587,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F4" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G4" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -565,16 +599,16 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="J4" s="18" t="n">
-        <x:v>88</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="K4" s="18" t="n">
-        <x:v>-32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L4" s="25" t="n">
-        <x:v>0.7333333333333333</x:v>
+        <x:v>1.1166666666666667</x:v>
       </x:c>
       <x:c r="M4" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -594,7 +628,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F5" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G5" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -606,16 +640,16 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="J5" s="18" t="n">
-        <x:v>66</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K5" s="18" t="n">
-        <x:v>-74</x:v>
+        <x:v>-38</x:v>
       </x:c>
       <x:c r="L5" s="25" t="n">
-        <x:v>0.4714285714285714</x:v>
+        <x:v>0.7285714285714285</x:v>
       </x:c>
       <x:c r="M5" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -656,7 +690,7 @@
         <x:v>1.6466666666666667</x:v>
       </x:c>
       <x:c r="M6" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -676,7 +710,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F7" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G7" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -688,16 +722,16 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="J7" s="18" t="n">
-        <x:v>505</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="K7" s="18" t="n">
-        <x:v>-95</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="L7" s="25" t="n">
-        <x:v>0.8416666666666667</x:v>
+        <x:v>1.0616666666666668</x:v>
       </x:c>
       <x:c r="M7" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -717,7 +751,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F8" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G8" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -729,16 +763,16 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="J8" s="18" t="n">
-        <x:v>366</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="K8" s="18" t="n">
-        <x:v>-234</x:v>
+        <x:v>-121</x:v>
       </x:c>
       <x:c r="L8" s="25" t="n">
-        <x:v>0.61</x:v>
+        <x:v>0.7983333333333333</x:v>
       </x:c>
       <x:c r="M8" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -758,7 +792,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F9" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G9" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -770,16 +804,16 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="J9" s="18" t="n">
-        <x:v>458</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="K9" s="18" t="n">
-        <x:v>-42</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="L9" s="25" t="n">
-        <x:v>0.916</x:v>
+        <x:v>1.286</x:v>
       </x:c>
       <x:c r="M9" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
@@ -799,7 +833,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F10" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G10" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -811,16 +845,16 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="J10" s="18" t="n">
-        <x:v>440</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="K10" s="18" t="n">
-        <x:v>-260</x:v>
+        <x:v>-65</x:v>
       </x:c>
       <x:c r="L10" s="25" t="n">
-        <x:v>0.6285714285714286</x:v>
+        <x:v>0.9071428571428571</x:v>
       </x:c>
       <x:c r="M10" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
@@ -840,7 +874,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F11" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G11" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -852,16 +886,16 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="J11" s="18" t="n">
-        <x:v>380</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="K11" s="18" t="n">
-        <x:v>-320</x:v>
+        <x:v>-150</x:v>
       </x:c>
       <x:c r="L11" s="25" t="n">
-        <x:v>0.5428571428571428</x:v>
+        <x:v>0.7857142857142857</x:v>
       </x:c>
       <x:c r="M11" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -881,7 +915,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F12" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G12" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -893,16 +927,16 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J12" s="18" t="n">
-        <x:v>361</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="K12" s="18" t="n">
-        <x:v>261</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="L12" s="25" t="n">
-        <x:v>3.61</x:v>
+        <x:v>5.76</x:v>
       </x:c>
       <x:c r="M12" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -922,7 +956,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F13" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G13" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -934,16 +968,16 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="J13" s="18" t="n">
-        <x:v>389</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="K13" s="18" t="n">
-        <x:v>-261</x:v>
+        <x:v>-39</x:v>
       </x:c>
       <x:c r="L13" s="25" t="n">
-        <x:v>0.5984615384615385</x:v>
+        <x:v>0.94</x:v>
       </x:c>
       <x:c r="M13" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -984,7 +1018,7 @@
         <x:v>0.12615384615384614</x:v>
       </x:c>
       <x:c r="M14" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -1004,7 +1038,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F15" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G15" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1016,16 +1050,16 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="J15" s="18" t="n">
-        <x:v>150</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="K15" s="18" t="n">
-        <x:v>-40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L15" s="25" t="n">
-        <x:v>0.7894736842105263</x:v>
+        <x:v>1.0526315789473684</x:v>
       </x:c>
       <x:c r="M15" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
@@ -1045,7 +1079,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F16" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G16" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1057,16 +1091,16 @@
         <x:v>360</x:v>
       </x:c>
       <x:c r="J16" s="18" t="n">
-        <x:v>201</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="K16" s="18" t="n">
-        <x:v>-159</x:v>
+        <x:v>-100</x:v>
       </x:c>
       <x:c r="L16" s="25" t="n">
-        <x:v>0.5583333333333333</x:v>
+        <x:v>0.7222222222222222</x:v>
       </x:c>
       <x:c r="M16" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -1086,7 +1120,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F17" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G17" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1098,16 +1132,16 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J17" s="18" t="n">
-        <x:v>185</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="K17" s="18" t="n">
-        <x:v>-115</x:v>
+        <x:v>-64</x:v>
       </x:c>
       <x:c r="L17" s="25" t="n">
-        <x:v>0.6166666666666667</x:v>
+        <x:v>0.7866666666666666</x:v>
       </x:c>
       <x:c r="M17" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
@@ -1160,7 +1194,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F19" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G19" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1172,16 +1206,16 @@
         <x:v>400</x:v>
       </x:c>
       <x:c r="J19" s="18" t="n">
-        <x:v>391</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="K19" s="18" t="n">
-        <x:v>-9</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L19" s="25" t="n">
-        <x:v>0.9775</x:v>
+        <x:v>1.1425</x:v>
       </x:c>
       <x:c r="M19" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -1201,7 +1235,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F20" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G20" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1213,16 +1247,16 @@
         <x:v>400</x:v>
       </x:c>
       <x:c r="J20" s="18" t="n">
-        <x:v>460</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="K20" s="18" t="n">
-        <x:v>60</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="L20" s="25" t="n">
-        <x:v>1.15</x:v>
+        <x:v>1.3275</x:v>
       </x:c>
       <x:c r="M20" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -1242,7 +1276,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F21" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G21" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1254,16 +1288,16 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="J21" s="18" t="n">
-        <x:v>468</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="K21" s="18" t="n">
-        <x:v>-32</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="L21" s="25" t="n">
-        <x:v>0.936</x:v>
+        <x:v>1.204</x:v>
       </x:c>
       <x:c r="M21" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -1283,7 +1317,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F22" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G22" s="21"/>
       <x:c r="H22" s="21"/>
@@ -1291,10 +1325,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J22" s="18" t="n">
-        <x:v>56</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K22" s="18" t="n">
-        <x:v>56</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="L22" s="25"/>
       <x:c r="M22" s="26"/>
@@ -1316,7 +1350,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F23" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G23" s="21"/>
       <x:c r="H23" s="21"/>
@@ -1324,10 +1358,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J23" s="18" t="n">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="K23" s="18" t="n">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="L23" s="25"/>
       <x:c r="M23" s="26"/>
@@ -1349,7 +1383,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F24" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G24" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1361,16 +1395,16 @@
         <x:v>950</x:v>
       </x:c>
       <x:c r="J24" s="18" t="n">
-        <x:v>391</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="K24" s="18" t="n">
-        <x:v>-559</x:v>
+        <x:v>-482</x:v>
       </x:c>
       <x:c r="L24" s="25" t="n">
-        <x:v>0.41157894736842104</x:v>
+        <x:v>0.4926315789473684</x:v>
       </x:c>
       <x:c r="M24" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
@@ -1390,7 +1424,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F25" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G25" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1402,16 +1436,16 @@
         <x:v>950</x:v>
       </x:c>
       <x:c r="J25" s="18" t="n">
-        <x:v>371</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="K25" s="18" t="n">
-        <x:v>-579</x:v>
+        <x:v>-481</x:v>
       </x:c>
       <x:c r="L25" s="25" t="n">
-        <x:v>0.39052631578947367</x:v>
+        <x:v>0.4936842105263158</x:v>
       </x:c>
       <x:c r="M25" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
@@ -1431,7 +1465,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F26" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G26" s="21"/>
       <x:c r="H26" s="21"/>
@@ -1439,10 +1473,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J26" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K26" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L26" s="25"/>
       <x:c r="M26" s="26"/>
@@ -1464,7 +1498,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F27" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G27" s="21"/>
       <x:c r="H27" s="21"/>
@@ -1472,10 +1506,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J27" s="18" t="n">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K27" s="18" t="n">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L27" s="25"/>
       <x:c r="M27" s="26"/>
@@ -1629,7 +1663,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F32" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G32" s="21"/>
       <x:c r="H32" s="21"/>
@@ -1637,10 +1671,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J32" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K32" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L32" s="25"/>
       <x:c r="M32" s="26"/>
@@ -1662,7 +1696,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F33" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G33" s="21"/>
       <x:c r="H33" s="21"/>
@@ -1670,10 +1704,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J33" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K33" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L33" s="25"/>
       <x:c r="M33" s="26"/>
@@ -2652,7 +2686,7 @@
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F63" s="21" t="str">
-        <x:v>2026-06-19</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G63" s="21"/>
       <x:c r="H63" s="21"/>
@@ -2660,10 +2694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J63" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K63" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L63" s="25"/>
       <x:c r="M63" s="26"/>
@@ -2685,7 +2719,7 @@
         <x:v>四年级</x:v>
       </x:c>
       <x:c r="F64" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G64" s="21"/>
       <x:c r="H64" s="21"/>
@@ -2693,10 +2727,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J64" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K64" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L64" s="25"/>
       <x:c r="M64" s="26"/>
@@ -2718,7 +2752,7 @@
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F65" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G65" s="21"/>
       <x:c r="H65" s="21"/>
@@ -2726,10 +2760,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J65" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K65" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L65" s="25"/>
       <x:c r="M65" s="26"/>
@@ -2817,7 +2851,7 @@
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F68" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G68" s="21"/>
       <x:c r="H68" s="21"/>
@@ -2825,10 +2859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J68" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K68" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L68" s="25"/>
       <x:c r="M68" s="26"/>
@@ -4434,7 +4468,7 @@
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F117" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G117" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4446,16 +4480,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="J117" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K117" s="18" t="n">
-        <x:v>-32</x:v>
+        <x:v>-22</x:v>
       </x:c>
       <x:c r="L117" s="25" t="n">
-        <x:v>0.2</x:v>
+        <x:v>0.45</x:v>
       </x:c>
       <x:c r="M117" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
@@ -4475,7 +4509,7 @@
         <x:v>四年级</x:v>
       </x:c>
       <x:c r="F118" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G118" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4487,16 +4521,16 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="J118" s="18" t="n">
-        <x:v>22</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K118" s="18" t="n">
-        <x:v>-98</x:v>
+        <x:v>-71</x:v>
       </x:c>
       <x:c r="L118" s="25" t="n">
-        <x:v>0.18333333333333332</x:v>
+        <x:v>0.4083333333333333</x:v>
       </x:c>
       <x:c r="M118" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
@@ -4516,7 +4550,7 @@
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F119" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G119" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4528,16 +4562,16 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="J119" s="18" t="n">
-        <x:v>12</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K119" s="18" t="n">
-        <x:v>-108</x:v>
+        <x:v>-80</x:v>
       </x:c>
       <x:c r="L119" s="25" t="n">
-        <x:v>0.1</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
       <x:c r="M119" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
@@ -4557,7 +4591,7 @@
         <x:v>六年级</x:v>
       </x:c>
       <x:c r="F120" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G120" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4569,16 +4603,16 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="J120" s="18" t="n">
-        <x:v>14</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="K120" s="18" t="n">
-        <x:v>-106</x:v>
+        <x:v>-71</x:v>
       </x:c>
       <x:c r="L120" s="25" t="n">
-        <x:v>0.11666666666666667</x:v>
+        <x:v>0.4083333333333333</x:v>
       </x:c>
       <x:c r="M120" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
@@ -4598,7 +4632,7 @@
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F121" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G121" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4610,16 +4644,16 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="J121" s="18" t="n">
-        <x:v>1473</x:v>
+        <x:v>1885</x:v>
       </x:c>
       <x:c r="K121" s="18" t="n">
-        <x:v>-827</x:v>
+        <x:v>-415</x:v>
       </x:c>
       <x:c r="L121" s="25" t="n">
-        <x:v>0.6404347826086957</x:v>
+        <x:v>0.8195652173913044</x:v>
       </x:c>
       <x:c r="M121" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
@@ -4639,7 +4673,7 @@
         <x:v>四年级</x:v>
       </x:c>
       <x:c r="F122" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G122" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4651,16 +4685,16 @@
         <x:v>2500</x:v>
       </x:c>
       <x:c r="J122" s="18" t="n">
-        <x:v>1547</x:v>
+        <x:v>1979</x:v>
       </x:c>
       <x:c r="K122" s="18" t="n">
-        <x:v>-953</x:v>
+        <x:v>-521</x:v>
       </x:c>
       <x:c r="L122" s="25" t="n">
-        <x:v>0.6188</x:v>
+        <x:v>0.7916</x:v>
       </x:c>
       <x:c r="M122" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -4680,7 +4714,7 @@
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F123" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G123" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4692,16 +4726,16 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="J123" s="18" t="n">
-        <x:v>1271</x:v>
+        <x:v>1622</x:v>
       </x:c>
       <x:c r="K123" s="18" t="n">
-        <x:v>-729</x:v>
+        <x:v>-378</x:v>
       </x:c>
       <x:c r="L123" s="25" t="n">
-        <x:v>0.6355</x:v>
+        <x:v>0.811</x:v>
       </x:c>
       <x:c r="M123" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -4721,7 +4755,7 @@
         <x:v>六年级</x:v>
       </x:c>
       <x:c r="F124" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G124" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4733,16 +4767,16 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="J124" s="18" t="n">
-        <x:v>1265</x:v>
+        <x:v>1670</x:v>
       </x:c>
       <x:c r="K124" s="18" t="n">
-        <x:v>-1035</x:v>
+        <x:v>-630</x:v>
       </x:c>
       <x:c r="L124" s="25" t="n">
-        <x:v>0.55</x:v>
+        <x:v>0.7260869565217392</x:v>
       </x:c>
       <x:c r="M124" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -4762,7 +4796,7 @@
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F125" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G125" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4774,16 +4808,16 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J125" s="18" t="n">
-        <x:v>101</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="K125" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L125" s="25" t="n">
-        <x:v>1.01</x:v>
+        <x:v>1.46</x:v>
       </x:c>
       <x:c r="M125" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -4803,7 +4837,7 @@
         <x:v>四年级</x:v>
       </x:c>
       <x:c r="F126" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G126" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4815,16 +4849,16 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="J126" s="18" t="n">
-        <x:v>137</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="K126" s="18" t="n">
-        <x:v>-13</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="L126" s="25" t="n">
-        <x:v>0.9133333333333333</x:v>
+        <x:v>1.2933333333333332</x:v>
       </x:c>
       <x:c r="M126" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -4844,7 +4878,7 @@
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F127" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G127" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4856,16 +4890,16 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="J127" s="18" t="n">
-        <x:v>86</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K127" s="18" t="n">
-        <x:v>-34</x:v>
+        <x:v>-4</x:v>
       </x:c>
       <x:c r="L127" s="25" t="n">
-        <x:v>0.7166666666666667</x:v>
+        <x:v>0.9666666666666667</x:v>
       </x:c>
       <x:c r="M127" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -4885,7 +4919,7 @@
         <x:v>六年级</x:v>
       </x:c>
       <x:c r="F128" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G128" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4897,16 +4931,16 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="J128" s="18" t="n">
-        <x:v>93</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="K128" s="18" t="n">
-        <x:v>-57</x:v>
+        <x:v>-8</x:v>
       </x:c>
       <x:c r="L128" s="25" t="n">
-        <x:v>0.62</x:v>
+        <x:v>0.9466666666666667</x:v>
       </x:c>
       <x:c r="M128" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -4926,7 +4960,7 @@
         <x:v>二年级</x:v>
       </x:c>
       <x:c r="F129" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G129" s="21"/>
       <x:c r="H129" s="21"/>
@@ -4934,10 +4968,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J129" s="18" t="n">
-        <x:v>57</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K129" s="18" t="n">
-        <x:v>57</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="L129" s="25"/>
       <x:c r="M129" s="26"/>
@@ -4959,7 +4993,7 @@
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F130" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G130" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4971,16 +5005,16 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J130" s="18" t="n">
-        <x:v>109</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="K130" s="18" t="n">
-        <x:v>9</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="L130" s="25" t="n">
-        <x:v>1.09</x:v>
+        <x:v>2.01</x:v>
       </x:c>
       <x:c r="M130" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -5000,7 +5034,7 @@
         <x:v>四年级</x:v>
       </x:c>
       <x:c r="F131" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G131" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5012,16 +5046,16 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J131" s="18" t="n">
-        <x:v>111</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="K131" s="18" t="n">
-        <x:v>-189</x:v>
+        <x:v>-82</x:v>
       </x:c>
       <x:c r="L131" s="25" t="n">
-        <x:v>0.37</x:v>
+        <x:v>0.7266666666666667</x:v>
       </x:c>
       <x:c r="M131" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -5041,7 +5075,7 @@
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F132" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G132" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5053,16 +5087,16 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="J132" s="18" t="n">
-        <x:v>109</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="K132" s="18" t="n">
-        <x:v>-91</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L132" s="25" t="n">
-        <x:v>0.545</x:v>
+        <x:v>1.055</x:v>
       </x:c>
       <x:c r="M132" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -5103,7 +5137,7 @@
         <x:v>0.025</x:v>
       </x:c>
       <x:c r="M133" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -5123,7 +5157,7 @@
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F134" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G134" s="21"/>
       <x:c r="H134" s="21"/>
@@ -5131,10 +5165,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J134" s="18" t="n">
-        <x:v>157</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="K134" s="18" t="n">
-        <x:v>157</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="L134" s="25"/>
       <x:c r="M134" s="26"/>
@@ -5156,7 +5190,7 @@
         <x:v>四年级</x:v>
       </x:c>
       <x:c r="F135" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G135" s="21"/>
       <x:c r="H135" s="21"/>
@@ -5164,10 +5198,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J135" s="18" t="n">
-        <x:v>218</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="K135" s="18" t="n">
-        <x:v>218</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="L135" s="25"/>
       <x:c r="M135" s="26"/>
@@ -5189,7 +5223,7 @@
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F136" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G136" s="21"/>
       <x:c r="H136" s="21"/>
@@ -5197,10 +5231,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J136" s="18" t="n">
-        <x:v>152</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="K136" s="18" t="n">
-        <x:v>152</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="L136" s="25"/>
       <x:c r="M136" s="26"/>
@@ -5222,7 +5256,7 @@
         <x:v>六年级</x:v>
       </x:c>
       <x:c r="F137" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G137" s="21"/>
       <x:c r="H137" s="21"/>
@@ -5230,10 +5264,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J137" s="18" t="n">
-        <x:v>169</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="K137" s="18" t="n">
-        <x:v>169</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="L137" s="25"/>
       <x:c r="M137" s="26"/>
@@ -5255,7 +5289,7 @@
         <x:v>二年级</x:v>
       </x:c>
       <x:c r="F138" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G138" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5267,16 +5301,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="J138" s="18" t="n">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K138" s="18" t="n">
-        <x:v>-3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L138" s="25" t="n">
-        <x:v>0.85</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="M138" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="15" hidden="0" customHeight="1">
@@ -5296,7 +5330,7 @@
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F139" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G139" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5308,16 +5342,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="J139" s="18" t="n">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K139" s="18" t="n">
-        <x:v>-20</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="L139" s="25" t="n">
-        <x:v>0.6</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="M139" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
@@ -5337,7 +5371,7 @@
         <x:v>四年级</x:v>
       </x:c>
       <x:c r="F140" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G140" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5349,16 +5383,16 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="J140" s="18" t="n">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K140" s="18" t="n">
-        <x:v>-20</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="L140" s="25" t="n">
-        <x:v>0.7142857142857143</x:v>
+        <x:v>0.8571428571428571</x:v>
       </x:c>
       <x:c r="M140" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
@@ -5378,7 +5412,7 @@
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F141" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G141" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5390,16 +5424,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="J141" s="18" t="n">
-        <x:v>53</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K141" s="18" t="n">
-        <x:v>13</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L141" s="25" t="n">
-        <x:v>1.325</x:v>
+        <x:v>1.8</x:v>
       </x:c>
       <x:c r="M141" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
@@ -5419,7 +5453,7 @@
         <x:v>六年级</x:v>
       </x:c>
       <x:c r="F142" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G142" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5431,16 +5465,16 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="J142" s="18" t="n">
-        <x:v>49</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K142" s="18" t="n">
-        <x:v>-21</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="L142" s="25" t="n">
-        <x:v>0.7</x:v>
+        <x:v>0.9142857142857143</x:v>
       </x:c>
       <x:c r="M142" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
@@ -5493,7 +5527,7 @@
         <x:v>二年级</x:v>
       </x:c>
       <x:c r="F144" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G144" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5505,16 +5539,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="J144" s="18" t="n">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K144" s="18" t="n">
-        <x:v>-40</x:v>
+        <x:v>-30</x:v>
       </x:c>
       <x:c r="L144" s="25" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.625</x:v>
       </x:c>
       <x:c r="M144" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="15" hidden="0" customHeight="1">
@@ -5534,7 +5568,7 @@
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F145" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G145" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5546,16 +5580,16 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="J145" s="18" t="n">
-        <x:v>61</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K145" s="18" t="n">
-        <x:v>-129</x:v>
+        <x:v>-112</x:v>
       </x:c>
       <x:c r="L145" s="25" t="n">
-        <x:v>0.32105263157894737</x:v>
+        <x:v>0.4105263157894737</x:v>
       </x:c>
       <x:c r="M145" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -5575,7 +5609,7 @@
         <x:v>四年级</x:v>
       </x:c>
       <x:c r="F146" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G146" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5587,16 +5621,16 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="J146" s="18" t="n">
-        <x:v>128</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="K146" s="18" t="n">
-        <x:v>-132</x:v>
+        <x:v>-108</x:v>
       </x:c>
       <x:c r="L146" s="25" t="n">
-        <x:v>0.49230769230769234</x:v>
+        <x:v>0.5846153846153846</x:v>
       </x:c>
       <x:c r="M146" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -5616,7 +5650,7 @@
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F147" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G147" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5628,16 +5662,16 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="J147" s="18" t="n">
-        <x:v>113</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K147" s="18" t="n">
-        <x:v>-127</x:v>
+        <x:v>-104</x:v>
       </x:c>
       <x:c r="L147" s="25" t="n">
-        <x:v>0.4708333333333333</x:v>
+        <x:v>0.5666666666666667</x:v>
       </x:c>
       <x:c r="M147" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -5657,7 +5691,7 @@
         <x:v>六年级</x:v>
       </x:c>
       <x:c r="F148" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G148" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5669,16 +5703,16 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="J148" s="18" t="n">
-        <x:v>165</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="K148" s="18" t="n">
-        <x:v>-95</x:v>
+        <x:v>-66</x:v>
       </x:c>
       <x:c r="L148" s="25" t="n">
-        <x:v>0.6346153846153846</x:v>
+        <x:v>0.7461538461538462</x:v>
       </x:c>
       <x:c r="M148" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
@@ -6622,7 +6656,7 @@
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F177" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G177" s="21"/>
       <x:c r="H177" s="21"/>
@@ -6630,10 +6664,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J177" s="18" t="n">
-        <x:v>679</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="K177" s="18" t="n">
-        <x:v>679</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="L177" s="25"/>
       <x:c r="M177" s="26"/>
@@ -7084,7 +7118,7 @@
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F191" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G191" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7096,16 +7130,16 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="J191" s="18" t="n">
-        <x:v>42</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="K191" s="18" t="n">
-        <x:v>-38</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="L191" s="25" t="n">
-        <x:v>0.525</x:v>
+        <x:v>0.9875</x:v>
       </x:c>
       <x:c r="M191" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
@@ -7125,7 +7159,7 @@
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F192" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G192" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7137,16 +7171,16 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="J192" s="18" t="n">
-        <x:v>104</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="K192" s="18" t="n">
-        <x:v>-56</x:v>
+        <x:v>-7</x:v>
       </x:c>
       <x:c r="L192" s="25" t="n">
-        <x:v>0.65</x:v>
+        <x:v>0.95625</x:v>
       </x:c>
       <x:c r="M192" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -7166,7 +7200,7 @@
         <x:v>高三</x:v>
       </x:c>
       <x:c r="F193" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G193" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7178,16 +7212,16 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="J193" s="18" t="n">
-        <x:v>58</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K193" s="18" t="n">
-        <x:v>-102</x:v>
+        <x:v>-57</x:v>
       </x:c>
       <x:c r="L193" s="25" t="n">
-        <x:v>0.3625</x:v>
+        <x:v>0.64375</x:v>
       </x:c>
       <x:c r="M193" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -7207,29 +7241,21 @@
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F194" s="21" t="str">
-        <x:v>2026-06-27</x:v>
-      </x:c>
-      <x:c r="G194" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H194" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="G194" s="21"/>
+      <x:c r="H194" s="21"/>
       <x:c r="I194" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J194" s="18" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K194" s="18" t="n">
-        <x:v>-91</x:v>
-      </x:c>
-      <x:c r="L194" s="25" t="n">
-        <x:v>0.09</x:v>
-      </x:c>
-      <x:c r="M194" s="26" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L194" s="25"/>
+      <x:c r="M194" s="26"/>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
       <x:c r="A195" s="11" t="str">
@@ -7250,27 +7276,19 @@
       <x:c r="F195" s="21" t="str">
         <x:v>2026-06-27</x:v>
       </x:c>
-      <x:c r="G195" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H195" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+      <x:c r="G195" s="21"/>
+      <x:c r="H195" s="21"/>
       <x:c r="I195" s="18" t="n">
-        <x:v>150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J195" s="18" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="K195" s="18" t="n">
-        <x:v>-143</x:v>
-      </x:c>
-      <x:c r="L195" s="25" t="n">
-        <x:v>0.04666666666666667</x:v>
-      </x:c>
-      <x:c r="M195" s="26" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L195" s="25"/>
+      <x:c r="M195" s="26"/>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
       <x:c r="A196" s="11" t="str">
@@ -7289,29 +7307,21 @@
         <x:v>高三</x:v>
       </x:c>
       <x:c r="F196" s="21" t="str">
-        <x:v>2026-06-27</x:v>
-      </x:c>
-      <x:c r="G196" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H196" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-28</x:v>
+      </x:c>
+      <x:c r="G196" s="21"/>
+      <x:c r="H196" s="21"/>
       <x:c r="I196" s="18" t="n">
-        <x:v>150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J196" s="18" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K196" s="18" t="n">
-        <x:v>-144</x:v>
-      </x:c>
-      <x:c r="L196" s="25" t="n">
-        <x:v>0.04</x:v>
-      </x:c>
-      <x:c r="M196" s="26" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L196" s="25"/>
+      <x:c r="M196" s="26"/>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
       <x:c r="A197" s="11" t="str">
@@ -7330,7 +7340,7 @@
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F197" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G197" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7342,16 +7352,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="J197" s="18" t="n">
-        <x:v>538</x:v>
+        <x:v>880</x:v>
       </x:c>
       <x:c r="K197" s="18" t="n">
-        <x:v>488</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="L197" s="25" t="n">
-        <x:v>10.76</x:v>
+        <x:v>17.6</x:v>
       </x:c>
       <x:c r="M197" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
@@ -7371,7 +7381,7 @@
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F198" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G198" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7383,16 +7393,16 @@
         <x:v>900</x:v>
       </x:c>
       <x:c r="J198" s="18" t="n">
-        <x:v>146</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="K198" s="18" t="n">
-        <x:v>-754</x:v>
+        <x:v>-677</x:v>
       </x:c>
       <x:c r="L198" s="25" t="n">
-        <x:v>0.1622222222222222</x:v>
+        <x:v>0.2477777777777778</x:v>
       </x:c>
       <x:c r="M198" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
@@ -7431,7 +7441,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M199" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
@@ -7442,7 +7452,7 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C200" s="12" t="str">
-        <x:v>图书店铺</x:v>
+        <x:v>lec内测</x:v>
       </x:c>
       <x:c r="D200" s="18" t="n">
         <x:v>100</x:v>
@@ -7450,22 +7460,28 @@
       <x:c r="E200" s="12" t="str">
         <x:v>高一</x:v>
       </x:c>
-      <x:c r="F200" s="21" t="str">
-        <x:v>2026-06-27</x:v>
-      </x:c>
-      <x:c r="G200" s="21"/>
-      <x:c r="H200" s="21"/>
+      <x:c r="F200" s="21"/>
+      <x:c r="G200" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H200" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I200" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J200" s="18" t="n">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K200" s="18" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="L200" s="25"/>
-      <x:c r="M200" s="26"/>
+        <x:v>-150</x:v>
+      </x:c>
+      <x:c r="L200" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M200" s="26" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
       <x:c r="A201" s="11" t="str">
@@ -7475,7 +7491,7 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C201" s="12" t="str">
-        <x:v>图书店铺</x:v>
+        <x:v>lec内测</x:v>
       </x:c>
       <x:c r="D201" s="18" t="n">
         <x:v>100</x:v>
@@ -7483,22 +7499,28 @@
       <x:c r="E201" s="12" t="str">
         <x:v>高二</x:v>
       </x:c>
-      <x:c r="F201" s="21" t="str">
-        <x:v>2026-06-27</x:v>
-      </x:c>
-      <x:c r="G201" s="21"/>
-      <x:c r="H201" s="21"/>
+      <x:c r="F201" s="21"/>
+      <x:c r="G201" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H201" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I201" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="J201" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K201" s="18" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="L201" s="25"/>
-      <x:c r="M201" s="26"/>
+        <x:v>-200</x:v>
+      </x:c>
+      <x:c r="L201" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M201" s="26" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
       <x:c r="A202" s="11" t="str">
@@ -7508,7 +7530,7 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C202" s="12" t="str">
-        <x:v>图书店铺</x:v>
+        <x:v>lec内测</x:v>
       </x:c>
       <x:c r="D202" s="18" t="n">
         <x:v>100</x:v>
@@ -7516,22 +7538,28 @@
       <x:c r="E202" s="12" t="str">
         <x:v>高三</x:v>
       </x:c>
-      <x:c r="F202" s="21" t="str">
-        <x:v>2026-06-27</x:v>
-      </x:c>
-      <x:c r="G202" s="21"/>
-      <x:c r="H202" s="21"/>
+      <x:c r="F202" s="21"/>
+      <x:c r="G202" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H202" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I202" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J202" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K202" s="18" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="L202" s="25"/>
-      <x:c r="M202" s="26"/>
+        <x:v>-150</x:v>
+      </x:c>
+      <x:c r="L202" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M202" s="26" t="n">
+        <x:v>0.6666666666666666</x:v>
+      </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
       <x:c r="A203" s="11" t="str">
@@ -7541,7 +7569,7 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C203" s="12" t="str">
-        <x:v>图书微转</x:v>
+        <x:v>图书店铺</x:v>
       </x:c>
       <x:c r="D203" s="18" t="n">
         <x:v>100</x:v>
@@ -7549,7 +7577,9 @@
       <x:c r="E203" s="12" t="str">
         <x:v>高一</x:v>
       </x:c>
-      <x:c r="F203" s="21"/>
+      <x:c r="F203" s="21" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
       <x:c r="G203" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7557,19 +7587,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I203" s="18" t="n">
-        <x:v>150</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J203" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="K203" s="18" t="n">
-        <x:v>-150</x:v>
+        <x:v>-63</x:v>
       </x:c>
       <x:c r="L203" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>0.37</x:v>
       </x:c>
       <x:c r="M203" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
@@ -7580,7 +7610,7 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C204" s="12" t="str">
-        <x:v>图书微转</x:v>
+        <x:v>图书店铺</x:v>
       </x:c>
       <x:c r="D204" s="18" t="n">
         <x:v>100</x:v>
@@ -7588,7 +7618,9 @@
       <x:c r="E204" s="12" t="str">
         <x:v>高二</x:v>
       </x:c>
-      <x:c r="F204" s="21"/>
+      <x:c r="F204" s="21" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
       <x:c r="G204" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7596,19 +7628,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I204" s="18" t="n">
-        <x:v>200</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J204" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="K204" s="18" t="n">
-        <x:v>-200</x:v>
+        <x:v>-129</x:v>
       </x:c>
       <x:c r="L204" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>0.14</x:v>
       </x:c>
       <x:c r="M204" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
@@ -7619,7 +7651,7 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C205" s="12" t="str">
-        <x:v>图书微转</x:v>
+        <x:v>图书店铺</x:v>
       </x:c>
       <x:c r="D205" s="18" t="n">
         <x:v>100</x:v>
@@ -7627,7 +7659,9 @@
       <x:c r="E205" s="12" t="str">
         <x:v>高三</x:v>
       </x:c>
-      <x:c r="F205" s="21"/>
+      <x:c r="F205" s="21" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
       <x:c r="G205" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7638,16 +7672,16 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="J205" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K205" s="18" t="n">
-        <x:v>-150</x:v>
+        <x:v>-139</x:v>
       </x:c>
       <x:c r="L205" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>0.07333333333333333</x:v>
       </x:c>
       <x:c r="M205" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
@@ -7667,7 +7701,7 @@
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F206" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G206" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7679,16 +7713,16 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J206" s="18" t="n">
-        <x:v>154</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="K206" s="18" t="n">
-        <x:v>-146</x:v>
+        <x:v>-102</x:v>
       </x:c>
       <x:c r="L206" s="25" t="n">
-        <x:v>0.5133333333333333</x:v>
+        <x:v>0.66</x:v>
       </x:c>
       <x:c r="M206" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -7708,7 +7742,7 @@
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F207" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G207" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7720,16 +7754,16 @@
         <x:v>530</x:v>
       </x:c>
       <x:c r="J207" s="18" t="n">
-        <x:v>149</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="K207" s="18" t="n">
-        <x:v>-381</x:v>
+        <x:v>-285</x:v>
       </x:c>
       <x:c r="L207" s="25" t="n">
-        <x:v>0.2811320754716981</x:v>
+        <x:v>0.46226415094339623</x:v>
       </x:c>
       <x:c r="M207" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -7749,7 +7783,7 @@
         <x:v>高三</x:v>
       </x:c>
       <x:c r="F208" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G208" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7761,16 +7795,16 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="J208" s="18" t="n">
-        <x:v>178</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="K208" s="18" t="n">
-        <x:v>-422</x:v>
+        <x:v>-297</x:v>
       </x:c>
       <x:c r="L208" s="25" t="n">
-        <x:v>0.2966666666666667</x:v>
+        <x:v>0.505</x:v>
       </x:c>
       <x:c r="M208" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
@@ -7790,7 +7824,7 @@
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F209" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G209" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7802,16 +7836,16 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="J209" s="18" t="n">
-        <x:v>166</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="K209" s="18" t="n">
-        <x:v>-14</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="L209" s="25" t="n">
-        <x:v>0.9222222222222223</x:v>
+        <x:v>1.3111111111111111</x:v>
       </x:c>
       <x:c r="M209" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
@@ -7831,7 +7865,7 @@
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F210" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G210" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7843,16 +7877,16 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="J210" s="18" t="n">
-        <x:v>558</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="K210" s="18" t="n">
-        <x:v>-942</x:v>
+        <x:v>-804</x:v>
       </x:c>
       <x:c r="L210" s="25" t="n">
-        <x:v>0.372</x:v>
+        <x:v>0.464</x:v>
       </x:c>
       <x:c r="M210" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="211" ht="15" hidden="0" customHeight="1">
@@ -7872,7 +7906,7 @@
         <x:v>高三</x:v>
       </x:c>
       <x:c r="F211" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G211" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7884,16 +7918,16 @@
         <x:v>870</x:v>
       </x:c>
       <x:c r="J211" s="18" t="n">
-        <x:v>220</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="K211" s="18" t="n">
-        <x:v>-650</x:v>
+        <x:v>-574</x:v>
       </x:c>
       <x:c r="L211" s="25" t="n">
-        <x:v>0.25287356321839083</x:v>
+        <x:v>0.34022988505747126</x:v>
       </x:c>
       <x:c r="M211" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="212" ht="15" hidden="0" customHeight="1">
@@ -7913,7 +7947,7 @@
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F212" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G212" s="21"/>
       <x:c r="H212" s="21"/>
@@ -7921,10 +7955,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J212" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K212" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L212" s="25"/>
       <x:c r="M212" s="26"/>
@@ -7946,7 +7980,7 @@
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F213" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G213" s="21"/>
       <x:c r="H213" s="21"/>
@@ -7954,10 +7988,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J213" s="18" t="n">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K213" s="18" t="n">
-        <x:v>48</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L213" s="25"/>
       <x:c r="M213" s="26"/>
@@ -7979,7 +8013,7 @@
         <x:v>高三</x:v>
       </x:c>
       <x:c r="F214" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G214" s="21"/>
       <x:c r="H214" s="21"/>
@@ -7987,10 +8021,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J214" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K214" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L214" s="25"/>
       <x:c r="M214" s="26"/>
@@ -8029,7 +8063,7 @@
       </x:c>
       <x:c r="L215" s="25"/>
       <x:c r="M215" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="15" hidden="0" customHeight="1">
@@ -8049,7 +8083,7 @@
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F216" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G216" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -8061,16 +8095,16 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="J216" s="18" t="n">
-        <x:v>362</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="K216" s="18" t="n">
-        <x:v>-338</x:v>
+        <x:v>-148</x:v>
       </x:c>
       <x:c r="L216" s="25" t="n">
-        <x:v>0.5171428571428571</x:v>
+        <x:v>0.7885714285714286</x:v>
       </x:c>
       <x:c r="M216" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="15" hidden="0" customHeight="1">
@@ -8090,7 +8124,7 @@
         <x:v>高三</x:v>
       </x:c>
       <x:c r="F217" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G217" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -8102,16 +8136,16 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="J217" s="18" t="n">
-        <x:v>354</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="K217" s="18" t="n">
-        <x:v>-296</x:v>
+        <x:v>-119</x:v>
       </x:c>
       <x:c r="L217" s="25" t="n">
-        <x:v>0.5446153846153846</x:v>
+        <x:v>0.816923076923077</x:v>
       </x:c>
       <x:c r="M217" s="26" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.6666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="15" hidden="0" customHeight="1">
@@ -8164,7 +8198,7 @@
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F219" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G219" s="21"/>
       <x:c r="H219" s="21"/>
@@ -8172,10 +8206,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J219" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K219" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L219" s="25"/>
       <x:c r="M219" s="26"/>
@@ -8185,19 +8219,19 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B220" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C220" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D220" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E220" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F220" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G220" s="21"/>
       <x:c r="H220" s="21"/>
@@ -8205,10 +8239,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J220" s="18" t="n">
-        <x:v>27</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K220" s="18" t="n">
-        <x:v>27</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L220" s="25"/>
       <x:c r="M220" s="26"/>
@@ -8227,7 +8261,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E221" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F221" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8238,10 +8272,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J221" s="18" t="n">
-        <x:v>63</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K221" s="18" t="n">
-        <x:v>63</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L221" s="25"/>
       <x:c r="M221" s="26"/>
@@ -8260,7 +8294,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E222" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F222" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8271,10 +8305,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J222" s="18" t="n">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K222" s="18" t="n">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L222" s="25"/>
       <x:c r="M222" s="26"/>
@@ -8287,13 +8321,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C223" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D223" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E223" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F223" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8304,10 +8338,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J223" s="18" t="n">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K223" s="18" t="n">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L223" s="25"/>
       <x:c r="M223" s="26"/>
@@ -8326,7 +8360,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E224" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F224" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8337,10 +8371,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J224" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K224" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L224" s="25"/>
       <x:c r="M224" s="26"/>
@@ -8359,10 +8393,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E225" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F225" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G225" s="21"/>
       <x:c r="H225" s="21"/>
@@ -8370,10 +8404,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J225" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K225" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L225" s="25"/>
       <x:c r="M225" s="26"/>
@@ -8386,16 +8420,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C226" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D226" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E226" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F226" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G226" s="21"/>
       <x:c r="H226" s="21"/>
@@ -8403,10 +8437,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J226" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K226" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L226" s="25"/>
       <x:c r="M226" s="26"/>
@@ -8425,10 +8459,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E227" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F227" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G227" s="21"/>
       <x:c r="H227" s="21"/>
@@ -8436,10 +8470,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J227" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K227" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L227" s="25"/>
       <x:c r="M227" s="26"/>
@@ -8452,13 +8486,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C228" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D228" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E228" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F228" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8469,10 +8503,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J228" s="18" t="n">
-        <x:v>146</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K228" s="18" t="n">
-        <x:v>146</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L228" s="25"/>
       <x:c r="M228" s="26"/>
@@ -8491,7 +8525,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E229" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F229" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8502,10 +8536,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J229" s="18" t="n">
-        <x:v>157</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="K229" s="18" t="n">
-        <x:v>157</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="L229" s="25"/>
       <x:c r="M229" s="26"/>
@@ -8524,7 +8558,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E230" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F230" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8535,10 +8569,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J230" s="18" t="n">
-        <x:v>136</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="K230" s="18" t="n">
-        <x:v>136</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="L230" s="25"/>
       <x:c r="M230" s="26"/>
@@ -8554,10 +8588,10 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D231" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E231" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F231" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8568,10 +8602,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J231" s="18" t="n">
-        <x:v>51</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K231" s="18" t="n">
-        <x:v>51</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="L231" s="25"/>
       <x:c r="M231" s="26"/>
@@ -8590,10 +8624,10 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E232" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F232" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G232" s="21"/>
       <x:c r="H232" s="21"/>
@@ -8601,10 +8635,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J232" s="18" t="n">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K232" s="18" t="n">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L232" s="25"/>
       <x:c r="M232" s="26"/>
@@ -8623,10 +8657,10 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E233" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F233" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G233" s="21"/>
       <x:c r="H233" s="21"/>
@@ -8634,10 +8668,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J233" s="18" t="n">
-        <x:v>30</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K233" s="18" t="n">
-        <x:v>30</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="L233" s="25"/>
       <x:c r="M233" s="26"/>
@@ -8650,13 +8684,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C234" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D234" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E234" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F234" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8667,10 +8701,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J234" s="18" t="n">
-        <x:v>136</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K234" s="18" t="n">
-        <x:v>136</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L234" s="25"/>
       <x:c r="M234" s="26"/>
@@ -8689,7 +8723,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E235" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F235" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8700,10 +8734,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J235" s="18" t="n">
-        <x:v>293</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K235" s="18" t="n">
-        <x:v>293</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="L235" s="25"/>
       <x:c r="M235" s="26"/>
@@ -8722,7 +8756,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E236" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F236" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8733,10 +8767,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J236" s="18" t="n">
-        <x:v>167</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="K236" s="18" t="n">
-        <x:v>167</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="L236" s="25"/>
       <x:c r="M236" s="26"/>
@@ -8752,10 +8786,10 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D237" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E237" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F237" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8766,10 +8800,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J237" s="18" t="n">
-        <x:v>92</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="K237" s="18" t="n">
-        <x:v>92</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="L237" s="25"/>
       <x:c r="M237" s="26"/>
@@ -8788,7 +8822,7 @@
         <x:v>2880</x:v>
       </x:c>
       <x:c r="E238" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F238" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8799,46 +8833,79 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J238" s="18" t="n">
-        <x:v>65</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="K238" s="18" t="n">
-        <x:v>65</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="L238" s="25"/>
       <x:c r="M238" s="26"/>
     </x:row>
     <x:row r="239" ht="15" hidden="0" customHeight="1">
-      <x:c r="A239" s="14" t="str">
+      <x:c r="A239" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
-      <x:c r="B239" s="15" t="str">
+      <x:c r="B239" s="12" t="str">
         <x:v>暑_9</x:v>
       </x:c>
-      <x:c r="C239" s="15" t="str">
+      <x:c r="C239" s="12" t="str">
         <x:v>常规外呼</x:v>
       </x:c>
-      <x:c r="D239" s="19" t="n">
+      <x:c r="D239" s="18" t="n">
         <x:v>2880</x:v>
       </x:c>
-      <x:c r="E239" s="15" t="str">
+      <x:c r="E239" s="12" t="str">
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F239" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G239" s="21"/>
+      <x:c r="H239" s="21"/>
+      <x:c r="I239" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J239" s="18" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="K239" s="18" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L239" s="25"/>
+      <x:c r="M239" s="26"/>
+    </x:row>
+    <x:row r="240" ht="15" hidden="0" customHeight="1">
+      <x:c r="A240" s="14" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B240" s="15" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C240" s="15" t="str">
+        <x:v>常规外呼</x:v>
+      </x:c>
+      <x:c r="D240" s="19" t="n">
+        <x:v>2880</x:v>
+      </x:c>
+      <x:c r="E240" s="15" t="str">
         <x:v>高三</x:v>
       </x:c>
-      <x:c r="F239" s="22" t="str">
+      <x:c r="F240" s="22" t="str">
         <x:v>2026-06-18</x:v>
       </x:c>
-      <x:c r="G239" s="22"/>
-      <x:c r="H239" s="22"/>
-      <x:c r="I239" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J239" s="19" t="n">
+      <x:c r="G240" s="22"/>
+      <x:c r="H240" s="22"/>
+      <x:c r="I240" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J240" s="19" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="K239" s="19" t="n">
+      <x:c r="K240" s="19" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="L239" s="27"/>
-      <x:c r="M239" s="28"/>
+      <x:c r="L240" s="27"/>
+      <x:c r="M240" s="28"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -8878,7 +8945,7 @@
         <x:v>现状原始行数</x:v>
       </x:c>
       <x:c r="B3" s="10" t="n">
-        <x:v>45731</x:v>
+        <x:v>51755</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -8894,7 +8961,7 @@
         <x:v>聚合组合数</x:v>
       </x:c>
       <x:c r="B5" s="13" t="n">
-        <x:v>237</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -8910,7 +8977,7 @@
         <x:v>现状合计</x:v>
       </x:c>
       <x:c r="B7" s="13" t="n">
-        <x:v>45731</x:v>
+        <x:v>51755</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -8918,7 +8985,7 @@
         <x:v>完成率整体</x:v>
       </x:c>
       <x:c r="B8" s="13" t="n">
-        <x:v>1.5698935805012015</x:v>
+        <x:v>1.7766906968760727</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -8958,7 +9025,7 @@
         <x:v>最新期次现状合计</x:v>
       </x:c>
       <x:c r="B13" s="13" t="n">
-        <x:v>17351</x:v>
+        <x:v>23353</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -8966,7 +9033,7 @@
         <x:v>最新期次完成率整体</x:v>
       </x:c>
       <x:c r="B14" s="13" t="n">
-        <x:v>0.59564023343632</x:v>
+        <x:v>0.8016821146584278</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -8998,7 +9065,7 @@
         <x:v>进度计算</x:v>
       </x:c>
       <x:c r="B18" s="13" t="str">
-        <x:v>进度=(当前日期-进量日期)/总天数，并限制在 0%-100%</x:v>
+        <x:v>进度=(当前日期-进量日期-1)/总天数，并限制在 0%-100%</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
@@ -9095,7 +9162,7 @@
         <x:v>12100</x:v>
       </x:c>
       <x:c r="C31" s="10" t="n">
-        <x:v>7823</x:v>
+        <x:v>10327</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -9106,7 +9173,7 @@
         <x:v>9250</x:v>
       </x:c>
       <x:c r="C32" s="13" t="n">
-        <x:v>6383</x:v>
+        <x:v>8360</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
@@ -9117,7 +9184,7 @@
         <x:v>7780</x:v>
       </x:c>
       <x:c r="C33" s="16" t="n">
-        <x:v>3145</x:v>
+        <x:v>4666</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="16.799999237060547" hidden="0" customHeight="1">
@@ -9150,7 +9217,7 @@
         <x:v>12100</x:v>
       </x:c>
       <x:c r="C38" s="10" t="n">
-        <x:v>7823</x:v>
+        <x:v>10327</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
@@ -9161,7 +9228,7 @@
         <x:v>9250</x:v>
       </x:c>
       <x:c r="C39" s="13" t="n">
-        <x:v>6383</x:v>
+        <x:v>8360</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -9172,7 +9239,7 @@
         <x:v>7780</x:v>
       </x:c>
       <x:c r="C40" s="16" t="n">
-        <x:v>3145</x:v>
+        <x:v>4666</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="16.799999237060547" hidden="0" customHeight="1">
@@ -9202,10 +9269,10 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="B45" s="9" t="n">
-        <x:v>13420</x:v>
+        <x:v>13020</x:v>
       </x:c>
       <x:c r="C45" s="10" t="n">
-        <x:v>8638</x:v>
+        <x:v>11216</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="15" hidden="0" customHeight="1">
@@ -9216,7 +9283,7 @@
         <x:v>8380</x:v>
       </x:c>
       <x:c r="C46" s="13" t="n">
-        <x:v>4598</x:v>
+        <x:v>5894</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -9227,7 +9294,7 @@
         <x:v>3350</x:v>
       </x:c>
       <x:c r="C47" s="13" t="n">
-        <x:v>1907</x:v>
+        <x:v>3093</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -9238,7 +9305,7 @@
         <x:v>2280</x:v>
       </x:c>
       <x:c r="C48" s="13" t="n">
-        <x:v>1713</x:v>
+        <x:v>2269</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -9249,7 +9316,7 @@
         <x:v>1200</x:v>
       </x:c>
       <x:c r="C49" s="13" t="n">
-        <x:v>460</x:v>
+        <x:v>812</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -9257,15 +9324,15 @@
         <x:v>图书店铺</x:v>
       </x:c>
       <x:c r="B50" s="12" t="n">
-        <x:v>0</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="C50" s="13" t="n">
-        <x:v>35</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
       <x:c r="A51" s="14" t="str">
-        <x:v>图书微转</x:v>
+        <x:v>lec内测</x:v>
       </x:c>
       <x:c r="B51" s="15" t="n">
         <x:v>500</x:v>
@@ -9304,7 +9371,7 @@
         <x:v>14850</x:v>
       </x:c>
       <x:c r="C56" s="10" t="n">
-        <x:v>9475</x:v>
+        <x:v>11908</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="15" hidden="0" customHeight="1">
@@ -9315,7 +9382,7 @@
         <x:v>6710</x:v>
       </x:c>
       <x:c r="C57" s="13" t="n">
-        <x:v>4563</x:v>
+        <x:v>6760</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
@@ -9326,7 +9393,7 @@
         <x:v>6370</x:v>
       </x:c>
       <x:c r="C58" s="13" t="n">
-        <x:v>2852</x:v>
+        <x:v>3872</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
@@ -9337,7 +9404,7 @@
         <x:v>1200</x:v>
       </x:c>
       <x:c r="C59" s="13" t="n">
-        <x:v>460</x:v>
+        <x:v>812</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -9381,7 +9448,7 @@
         <x:v>3780</x:v>
       </x:c>
       <x:c r="C65" s="10" t="n">
-        <x:v>2461</x:v>
+        <x:v>3270</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
@@ -9392,7 +9459,7 @@
         <x:v>3400</x:v>
       </x:c>
       <x:c r="C66" s="13" t="n">
-        <x:v>2214</x:v>
+        <x:v>2905</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -9403,29 +9470,29 @@
         <x:v>1730</x:v>
       </x:c>
       <x:c r="C67" s="13" t="n">
-        <x:v>1983</x:v>
+        <x:v>2606</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
       <x:c r="A68" s="11" t="str">
-        <x:v>初三</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="B68" s="12" t="n">
-        <x:v>3740</x:v>
+        <x:v>2780</x:v>
       </x:c>
       <x:c r="C68" s="13" t="n">
-        <x:v>1939</x:v>
+        <x:v>2551</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
       <x:c r="A69" s="11" t="str">
-        <x:v>三年级</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="B69" s="12" t="n">
-        <x:v>2780</x:v>
+        <x:v>3740</x:v>
       </x:c>
       <x:c r="C69" s="13" t="n">
-        <x:v>1939</x:v>
+        <x:v>2484</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -9436,7 +9503,7 @@
         <x:v>2720</x:v>
       </x:c>
       <x:c r="C70" s="13" t="n">
-        <x:v>1796</x:v>
+        <x:v>2382</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -9447,7 +9514,7 @@
         <x:v>3100</x:v>
       </x:c>
       <x:c r="C71" s="13" t="n">
-        <x:v>1760</x:v>
+        <x:v>2331</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
@@ -9458,7 +9525,7 @@
         <x:v>4140</x:v>
       </x:c>
       <x:c r="C72" s="13" t="n">
-        <x:v>1382</x:v>
+        <x:v>1960</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
@@ -9469,7 +9536,7 @@
         <x:v>860</x:v>
       </x:c>
       <x:c r="C73" s="13" t="n">
-        <x:v>932</x:v>
+        <x:v>1445</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -9480,7 +9547,7 @@
         <x:v>2780</x:v>
       </x:c>
       <x:c r="C74" s="13" t="n">
-        <x:v>831</x:v>
+        <x:v>1261</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
@@ -9491,7 +9558,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="C75" s="16" t="n">
-        <x:v>114</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9505,4 +9572,219 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A1" s="29" t="str">
+        <x:v>Summary 计算规则</x:v>
+      </x:c>
+      <x:c r="B1" s="29" t="str">
+        <x:v>Summary 计算规则</x:v>
+      </x:c>
+      <x:c r="C1" s="29" t="str">
+        <x:v>Summary 计算规则</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="30" t="str">
+        <x:v>分类</x:v>
+      </x:c>
+      <x:c r="B2" s="30" t="str">
+        <x:v>项目</x:v>
+      </x:c>
+      <x:c r="C2" s="30" t="str">
+        <x:v>计算规则</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="31" t="str">
+        <x:v>聚合范围</x:v>
+      </x:c>
+      <x:c r="B3" s="32" t="str">
+        <x:v>统计维度</x:v>
+      </x:c>
+      <x:c r="C3" s="33" t="str">
+        <x:v>按学部、期次、线索渠道二级分类、价体、年级聚合</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="34" t="str">
+        <x:v>字段归并</x:v>
+      </x:c>
+      <x:c r="B4" s="35" t="str">
+        <x:v>线索渠道二级分类</x:v>
+      </x:c>
+      <x:c r="C4" s="36" t="str">
+        <x:v>以“外部微转-”开头的值统一归为“外部微转-*”</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="34" t="str">
+        <x:v>目标</x:v>
+      </x:c>
+      <x:c r="B5" s="35" t="str">
+        <x:v>目标</x:v>
+      </x:c>
+      <x:c r="C5" s="36" t="str">
+        <x:v>同一统计维度下 target 表的目标之和</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="34" t="str">
+        <x:v>目标</x:v>
+      </x:c>
+      <x:c r="B6" s="35" t="str">
+        <x:v>target_time</x:v>
+      </x:c>
+      <x:c r="C6" s="36" t="str">
+        <x:v>同一统计维度下 target 表的最晚 target_time</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="34" t="str">
+        <x:v>目标</x:v>
+      </x:c>
+      <x:c r="B7" s="35" t="str">
+        <x:v>进量日期</x:v>
+      </x:c>
+      <x:c r="C7" s="36" t="str">
+        <x:v>同一统计维度下 target 表的最晚进量日期</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="34" t="str">
+        <x:v>现状</x:v>
+      </x:c>
+      <x:c r="B8" s="35" t="str">
+        <x:v>现状</x:v>
+      </x:c>
+      <x:c r="C8" s="36" t="str">
+        <x:v>同一统计维度下 demo 表的成单量之和</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="34" t="str">
+        <x:v>现状</x:v>
+      </x:c>
+      <x:c r="B9" s="35" t="str">
+        <x:v>下单日期</x:v>
+      </x:c>
+      <x:c r="C9" s="36" t="str">
+        <x:v>同一统计维度下 demo 表的最近一次下单日期，仅用于现状日期参考</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="34" t="str">
+        <x:v>对比指标</x:v>
+      </x:c>
+      <x:c r="B10" s="35" t="str">
+        <x:v>差距</x:v>
+      </x:c>
+      <x:c r="C10" s="36" t="str">
+        <x:v>现状 - 目标</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="34" t="str">
+        <x:v>对比指标</x:v>
+      </x:c>
+      <x:c r="B11" s="35" t="str">
+        <x:v>完成率</x:v>
+      </x:c>
+      <x:c r="C11" s="36" t="str">
+        <x:v>现状 ÷ 目标；目标为 0 时留空</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="34" t="str">
+        <x:v>对比指标</x:v>
+      </x:c>
+      <x:c r="B12" s="35" t="str">
+        <x:v>进度</x:v>
+      </x:c>
+      <x:c r="C12" s="36" t="str">
+        <x:v>（当前日期 - 进量日期 - 1）÷ 总天数；总天数为 6 天，结果限制在 0%～100%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="34" t="str">
+        <x:v>合并规则</x:v>
+      </x:c>
+      <x:c r="B13" s="35" t="str">
+        <x:v>目标与现状</x:v>
+      </x:c>
+      <x:c r="C13" s="36" t="str">
+        <x:v>按统计维度全量合并；仅有目标或仅有现状的组合也保留，缺失的目标/现状按 0 计算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="34" t="str">
+        <x:v>最新期次</x:v>
+      </x:c>
+      <x:c r="B14" s="35" t="str">
+        <x:v>默认范围</x:v>
+      </x:c>
+      <x:c r="C14" s="36" t="str">
+        <x:v>以 target 表中的期次为准，每个学部取数字序号最大的期次</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="34" t="str">
+        <x:v>最新期次</x:v>
+      </x:c>
+      <x:c r="B15" s="35" t="str">
+        <x:v>demo-only 期次</x:v>
+      </x:c>
+      <x:c r="C15" s="36" t="str">
+        <x:v>保留在完整 Summary 中，但不进入默认最新期次范围</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="34" t="str">
+        <x:v>整体指标</x:v>
+      </x:c>
+      <x:c r="B16" s="35" t="str">
+        <x:v>完成率整体</x:v>
+      </x:c>
+      <x:c r="C16" s="36" t="str">
+        <x:v>现状合计 ÷ 目标合计；目标合计为 0 时留空</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="34" t="str">
+        <x:v>整体指标</x:v>
+      </x:c>
+      <x:c r="B17" s="35" t="str">
+        <x:v>平均进度</x:v>
+      </x:c>
+      <x:c r="C17" s="36" t="str">
+        <x:v>所选范围内有有效进度值的各统计项进度算术平均</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="37" t="str">
+        <x:v>整体指标</x:v>
+      </x:c>
+      <x:c r="B18" s="38" t="str">
+        <x:v>落后项</x:v>
+      </x:c>
+      <x:c r="C18" s="39" t="str">
+        <x:v>完成率低于进度，且进度值有效的统计项数量</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:C1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/outputs/tongji_summary/tongji_summary_current.xlsx
+++ b/outputs/tongji_summary/tongji_summary_current.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目标现状对比" sheetId="1" r:id="R3b487c76e2c94d7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据概览" sheetId="2" r:id="Rba48ac16bb0d45e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计算规则" sheetId="3" r:id="R189f3912a3a94277"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目标现状对比" sheetId="1" r:id="R1415d7fdd73a4faf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据概览" sheetId="2" r:id="Rf88bbd92b6ca4621"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计算规则" sheetId="3" r:id="R95077ead9ea34a66"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -280,9 +280,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -546,7 +546,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F3" s="20" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G3" s="20" t="str">
         <x:v>2026-06-30</x:v>
@@ -558,16 +558,16 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="J3" s="17" t="n">
-        <x:v>85</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K3" s="17" t="n">
-        <x:v>-55</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="L3" s="23" t="n">
-        <x:v>0.6071428571428571</x:v>
+        <x:v>0.6714285714285714</x:v>
       </x:c>
       <x:c r="M3" s="24" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -587,7 +587,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F4" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G4" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -599,16 +599,16 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="J4" s="18" t="n">
-        <x:v>134</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="K4" s="18" t="n">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="L4" s="25" t="n">
-        <x:v>1.1166666666666667</x:v>
+        <x:v>1.2916666666666667</x:v>
       </x:c>
       <x:c r="M4" s="26" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -628,7 +628,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F5" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G5" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -640,16 +640,16 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="J5" s="18" t="n">
-        <x:v>102</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="K5" s="18" t="n">
-        <x:v>-38</x:v>
+        <x:v>-19</x:v>
       </x:c>
       <x:c r="L5" s="25" t="n">
-        <x:v>0.7285714285714285</x:v>
+        <x:v>0.8642857142857143</x:v>
       </x:c>
       <x:c r="M5" s="26" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -690,7 +690,7 @@
         <x:v>1.6466666666666667</x:v>
       </x:c>
       <x:c r="M6" s="26" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -731,7 +731,7 @@
         <x:v>1.0616666666666668</x:v>
       </x:c>
       <x:c r="M7" s="26" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -751,7 +751,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F8" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G8" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -763,16 +763,16 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="J8" s="18" t="n">
-        <x:v>479</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="K8" s="18" t="n">
-        <x:v>-121</x:v>
+        <x:v>-56</x:v>
       </x:c>
       <x:c r="L8" s="25" t="n">
-        <x:v>0.7983333333333333</x:v>
+        <x:v>0.9066666666666666</x:v>
       </x:c>
       <x:c r="M8" s="26" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -792,7 +792,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F9" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G9" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -804,16 +804,16 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="J9" s="18" t="n">
-        <x:v>643</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="K9" s="18" t="n">
-        <x:v>143</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="L9" s="25" t="n">
-        <x:v>1.286</x:v>
+        <x:v>1.392</x:v>
       </x:c>
       <x:c r="M9" s="26" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
@@ -833,7 +833,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F10" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G10" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -845,16 +845,16 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="J10" s="18" t="n">
-        <x:v>635</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="K10" s="18" t="n">
-        <x:v>-65</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="L10" s="25" t="n">
-        <x:v>0.9071428571428571</x:v>
+        <x:v>1.1442857142857144</x:v>
       </x:c>
       <x:c r="M10" s="26" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
@@ -874,7 +874,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F11" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G11" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -886,16 +886,16 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="J11" s="18" t="n">
-        <x:v>550</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="K11" s="18" t="n">
-        <x:v>-150</x:v>
+        <x:v>-39</x:v>
       </x:c>
       <x:c r="L11" s="25" t="n">
-        <x:v>0.7857142857142857</x:v>
+        <x:v>0.9442857142857143</x:v>
       </x:c>
       <x:c r="M11" s="26" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -915,7 +915,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F12" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G12" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -927,16 +927,16 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J12" s="18" t="n">
-        <x:v>576</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="K12" s="18" t="n">
-        <x:v>476</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="L12" s="25" t="n">
-        <x:v>5.76</x:v>
+        <x:v>7.27</x:v>
       </x:c>
       <x:c r="M12" s="26" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -956,7 +956,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F13" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G13" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -968,16 +968,16 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="J13" s="18" t="n">
-        <x:v>611</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="K13" s="18" t="n">
-        <x:v>-39</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="L13" s="25" t="n">
-        <x:v>0.94</x:v>
+        <x:v>1.1446153846153846</x:v>
       </x:c>
       <x:c r="M13" s="26" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -1018,7 +1018,7 @@
         <x:v>0.12615384615384614</x:v>
       </x:c>
       <x:c r="M14" s="26" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -1038,7 +1038,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F15" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G15" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1050,16 +1050,16 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="J15" s="18" t="n">
-        <x:v>200</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="K15" s="18" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L15" s="25" t="n">
-        <x:v>1.0526315789473684</x:v>
+        <x:v>1.105263157894737</x:v>
       </x:c>
       <x:c r="M15" s="26" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
@@ -1079,7 +1079,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F16" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G16" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1091,16 +1091,16 @@
         <x:v>360</x:v>
       </x:c>
       <x:c r="J16" s="18" t="n">
-        <x:v>260</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="K16" s="18" t="n">
-        <x:v>-100</x:v>
+        <x:v>-61</x:v>
       </x:c>
       <x:c r="L16" s="25" t="n">
-        <x:v>0.7222222222222222</x:v>
+        <x:v>0.8305555555555556</x:v>
       </x:c>
       <x:c r="M16" s="26" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -1120,7 +1120,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F17" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G17" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1132,16 +1132,16 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J17" s="18" t="n">
-        <x:v>236</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="K17" s="18" t="n">
-        <x:v>-64</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L17" s="25" t="n">
-        <x:v>0.7866666666666666</x:v>
+        <x:v>1.0066666666666666</x:v>
       </x:c>
       <x:c r="M17" s="26" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
@@ -1194,7 +1194,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F19" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G19" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1206,16 +1206,16 @@
         <x:v>400</x:v>
       </x:c>
       <x:c r="J19" s="18" t="n">
-        <x:v>457</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="K19" s="18" t="n">
-        <x:v>57</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="L19" s="25" t="n">
-        <x:v>1.1425</x:v>
+        <x:v>1.38</x:v>
       </x:c>
       <x:c r="M19" s="26" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -1235,7 +1235,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F20" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G20" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1247,16 +1247,16 @@
         <x:v>400</x:v>
       </x:c>
       <x:c r="J20" s="18" t="n">
-        <x:v>531</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="K20" s="18" t="n">
-        <x:v>131</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="L20" s="25" t="n">
-        <x:v>1.3275</x:v>
+        <x:v>1.56</x:v>
       </x:c>
       <x:c r="M20" s="26" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -1297,7 +1297,7 @@
         <x:v>1.204</x:v>
       </x:c>
       <x:c r="M21" s="26" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -1317,7 +1317,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F22" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G22" s="21"/>
       <x:c r="H22" s="21"/>
@@ -1325,10 +1325,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J22" s="18" t="n">
-        <x:v>68</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K22" s="18" t="n">
-        <x:v>68</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="L22" s="25"/>
       <x:c r="M22" s="26"/>
@@ -1350,7 +1350,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F23" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G23" s="21"/>
       <x:c r="H23" s="21"/>
@@ -1358,10 +1358,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J23" s="18" t="n">
-        <x:v>35</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K23" s="18" t="n">
-        <x:v>35</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="L23" s="25"/>
       <x:c r="M23" s="26"/>
@@ -1383,7 +1383,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F24" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G24" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1395,16 +1395,16 @@
         <x:v>950</x:v>
       </x:c>
       <x:c r="J24" s="18" t="n">
-        <x:v>468</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="K24" s="18" t="n">
-        <x:v>-482</x:v>
+        <x:v>-361</x:v>
       </x:c>
       <x:c r="L24" s="25" t="n">
-        <x:v>0.4926315789473684</x:v>
+        <x:v>0.62</x:v>
       </x:c>
       <x:c r="M24" s="26" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
@@ -1424,7 +1424,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F25" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G25" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -1436,16 +1436,16 @@
         <x:v>950</x:v>
       </x:c>
       <x:c r="J25" s="18" t="n">
-        <x:v>469</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="K25" s="18" t="n">
-        <x:v>-481</x:v>
+        <x:v>-372</x:v>
       </x:c>
       <x:c r="L25" s="25" t="n">
-        <x:v>0.4936842105263158</x:v>
+        <x:v>0.608421052631579</x:v>
       </x:c>
       <x:c r="M25" s="26" t="n">
-        <x:v>0.8333333333333334</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
@@ -1456,16 +1456,16 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C26" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D26" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E26" s="12" t="str">
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F26" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G26" s="21"/>
       <x:c r="H26" s="21"/>
@@ -1473,10 +1473,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J26" s="18" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K26" s="18" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L26" s="25"/>
       <x:c r="M26" s="26"/>
@@ -1489,16 +1489,16 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C27" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D27" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E27" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F27" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G27" s="21"/>
       <x:c r="H27" s="21"/>
@@ -1506,10 +1506,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J27" s="18" t="n">
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K27" s="18" t="n">
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L27" s="25"/>
       <x:c r="M27" s="26"/>
@@ -1522,16 +1522,16 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C28" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D28" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E28" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F28" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G28" s="21"/>
       <x:c r="H28" s="21"/>
@@ -1539,10 +1539,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J28" s="18" t="n">
-        <x:v>13</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="K28" s="18" t="n">
-        <x:v>13</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="L28" s="25"/>
       <x:c r="M28" s="26"/>
@@ -1552,7 +1552,7 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B29" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C29" s="12" t="str">
         <x:v>LLM外呼</x:v>
@@ -1564,7 +1564,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F29" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G29" s="21"/>
       <x:c r="H29" s="21"/>
@@ -1572,10 +1572,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J29" s="18" t="n">
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K29" s="18" t="n">
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L29" s="25"/>
       <x:c r="M29" s="26"/>
@@ -1585,7 +1585,7 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B30" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C30" s="12" t="str">
         <x:v>LLM外呼</x:v>
@@ -1597,7 +1597,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F30" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G30" s="21"/>
       <x:c r="H30" s="21"/>
@@ -1605,10 +1605,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J30" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K30" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L30" s="25"/>
       <x:c r="M30" s="26"/>
@@ -1618,7 +1618,7 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B31" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C31" s="12" t="str">
         <x:v>LLM外呼</x:v>
@@ -1630,7 +1630,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F31" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G31" s="21"/>
       <x:c r="H31" s="21"/>
@@ -1638,10 +1638,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J31" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K31" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L31" s="25"/>
       <x:c r="M31" s="26"/>
@@ -1651,10 +1651,10 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B32" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C32" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D32" s="18" t="n">
         <x:v>990</x:v>
@@ -1663,7 +1663,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F32" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G32" s="21"/>
       <x:c r="H32" s="21"/>
@@ -1671,10 +1671,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J32" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K32" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="L32" s="25"/>
       <x:c r="M32" s="26"/>
@@ -1684,19 +1684,19 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B33" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C33" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D33" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E33" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F33" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G33" s="21"/>
       <x:c r="H33" s="21"/>
@@ -1704,10 +1704,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J33" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="K33" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="L33" s="25"/>
       <x:c r="M33" s="26"/>
@@ -1717,19 +1717,19 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B34" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C34" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D34" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E34" s="12" t="str">
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F34" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G34" s="21"/>
       <x:c r="H34" s="21"/>
@@ -1737,10 +1737,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J34" s="18" t="n">
-        <x:v>140</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K34" s="18" t="n">
-        <x:v>140</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L34" s="25"/>
       <x:c r="M34" s="26"/>
@@ -1750,19 +1750,19 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B35" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C35" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D35" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E35" s="12" t="str">
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F35" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G35" s="21"/>
       <x:c r="H35" s="21"/>
@@ -1770,10 +1770,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J35" s="18" t="n">
-        <x:v>142</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K35" s="18" t="n">
-        <x:v>142</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L35" s="25"/>
       <x:c r="M35" s="26"/>
@@ -1783,19 +1783,19 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B36" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C36" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D36" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E36" s="12" t="str">
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F36" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G36" s="21"/>
       <x:c r="H36" s="21"/>
@@ -1803,10 +1803,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J36" s="18" t="n">
-        <x:v>130</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K36" s="18" t="n">
-        <x:v>130</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L36" s="25"/>
       <x:c r="M36" s="26"/>
@@ -1816,19 +1816,19 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B37" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C37" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D37" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E37" s="12" t="str">
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F37" s="21" t="str">
-        <x:v>2026-06-22</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G37" s="21"/>
       <x:c r="H37" s="21"/>
@@ -1836,10 +1836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J37" s="18" t="n">
-        <x:v>711</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K37" s="18" t="n">
-        <x:v>711</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L37" s="25"/>
       <x:c r="M37" s="26"/>
@@ -1849,19 +1849,19 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B38" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C38" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D38" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E38" s="12" t="str">
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F38" s="21" t="str">
-        <x:v>2026-06-22</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G38" s="21"/>
       <x:c r="H38" s="21"/>
@@ -1869,10 +1869,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J38" s="18" t="n">
-        <x:v>1120</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K38" s="18" t="n">
-        <x:v>1120</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L38" s="25"/>
       <x:c r="M38" s="26"/>
@@ -1885,13 +1885,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C39" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D39" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E39" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F39" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -1902,10 +1902,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J39" s="18" t="n">
-        <x:v>910</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="K39" s="18" t="n">
-        <x:v>910</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="L39" s="25"/>
       <x:c r="M39" s="26"/>
@@ -1918,13 +1918,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C40" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D40" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E40" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F40" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -1935,10 +1935,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J40" s="18" t="n">
-        <x:v>479</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="K40" s="18" t="n">
-        <x:v>479</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="L40" s="25"/>
       <x:c r="M40" s="26"/>
@@ -1951,13 +1951,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C41" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D41" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E41" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F41" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -1968,10 +1968,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J41" s="18" t="n">
-        <x:v>385</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="K41" s="18" t="n">
-        <x:v>385</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L41" s="25"/>
       <x:c r="M41" s="26"/>
@@ -1987,13 +1987,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D42" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E42" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F42" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G42" s="21"/>
       <x:c r="H42" s="21"/>
@@ -2001,10 +2001,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J42" s="18" t="n">
-        <x:v>318</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="K42" s="18" t="n">
-        <x:v>318</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="L42" s="25"/>
       <x:c r="M42" s="26"/>
@@ -2017,16 +2017,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C43" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D43" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E43" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F43" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G43" s="21"/>
       <x:c r="H43" s="21"/>
@@ -2034,10 +2034,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J43" s="18" t="n">
-        <x:v>481</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="K43" s="18" t="n">
-        <x:v>481</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="L43" s="25"/>
       <x:c r="M43" s="26"/>
@@ -2050,13 +2050,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C44" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D44" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E44" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F44" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -2067,10 +2067,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J44" s="18" t="n">
-        <x:v>504</x:v>
+        <x:v>910</x:v>
       </x:c>
       <x:c r="K44" s="18" t="n">
-        <x:v>504</x:v>
+        <x:v>910</x:v>
       </x:c>
       <x:c r="L44" s="25"/>
       <x:c r="M44" s="26"/>
@@ -2083,16 +2083,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C45" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D45" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E45" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F45" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G45" s="21"/>
       <x:c r="H45" s="21"/>
@@ -2100,10 +2100,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J45" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="K45" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="L45" s="25"/>
       <x:c r="M45" s="26"/>
@@ -2116,16 +2116,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C46" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D46" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E46" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F46" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G46" s="21"/>
       <x:c r="H46" s="21"/>
@@ -2133,10 +2133,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J46" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="K46" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="L46" s="25"/>
       <x:c r="M46" s="26"/>
@@ -2149,16 +2149,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C47" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D47" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E47" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F47" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G47" s="21"/>
       <x:c r="H47" s="21"/>
@@ -2166,10 +2166,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J47" s="18" t="n">
-        <x:v>9</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="K47" s="18" t="n">
-        <x:v>9</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="L47" s="25"/>
       <x:c r="M47" s="26"/>
@@ -2182,16 +2182,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C48" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D48" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E48" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F48" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G48" s="21"/>
       <x:c r="H48" s="21"/>
@@ -2199,10 +2199,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J48" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="K48" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="L48" s="25"/>
       <x:c r="M48" s="26"/>
@@ -2215,13 +2215,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C49" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D49" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E49" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F49" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -2232,10 +2232,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J49" s="18" t="n">
-        <x:v>134</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="K49" s="18" t="n">
-        <x:v>134</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="L49" s="25"/>
       <x:c r="M49" s="26"/>
@@ -2248,16 +2248,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C50" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D50" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E50" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F50" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G50" s="21"/>
       <x:c r="H50" s="21"/>
@@ -2265,10 +2265,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J50" s="18" t="n">
-        <x:v>43</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K50" s="18" t="n">
-        <x:v>43</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L50" s="25"/>
       <x:c r="M50" s="26"/>
@@ -2284,13 +2284,13 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D51" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E51" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F51" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G51" s="21"/>
       <x:c r="H51" s="21"/>
@@ -2298,10 +2298,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J51" s="18" t="n">
-        <x:v>256</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K51" s="18" t="n">
-        <x:v>256</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L51" s="25"/>
       <x:c r="M51" s="26"/>
@@ -2317,13 +2317,13 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D52" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E52" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F52" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G52" s="21"/>
       <x:c r="H52" s="21"/>
@@ -2331,10 +2331,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J52" s="18" t="n">
-        <x:v>224</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K52" s="18" t="n">
-        <x:v>224</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L52" s="25"/>
       <x:c r="M52" s="26"/>
@@ -2347,16 +2347,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C53" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D53" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E53" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F53" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G53" s="21"/>
       <x:c r="H53" s="21"/>
@@ -2364,10 +2364,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J53" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K53" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L53" s="25"/>
       <x:c r="M53" s="26"/>
@@ -2380,13 +2380,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C54" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D54" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E54" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F54" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -2397,10 +2397,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J54" s="18" t="n">
-        <x:v>318</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="K54" s="18" t="n">
-        <x:v>318</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="L54" s="25"/>
       <x:c r="M54" s="26"/>
@@ -2413,16 +2413,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C55" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D55" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E55" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F55" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G55" s="21"/>
       <x:c r="H55" s="21"/>
@@ -2430,10 +2430,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J55" s="18" t="n">
-        <x:v>336</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K55" s="18" t="n">
-        <x:v>336</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="L55" s="25"/>
       <x:c r="M55" s="26"/>
@@ -2446,13 +2446,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C56" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D56" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E56" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F56" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -2463,10 +2463,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J56" s="18" t="n">
-        <x:v>326</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="K56" s="18" t="n">
-        <x:v>326</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="L56" s="25"/>
       <x:c r="M56" s="26"/>
@@ -2479,13 +2479,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C57" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D57" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E57" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F57" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -2496,10 +2496,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J57" s="18" t="n">
-        <x:v>10</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="K57" s="18" t="n">
-        <x:v>10</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="L57" s="25"/>
       <x:c r="M57" s="26"/>
@@ -2515,13 +2515,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D58" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E58" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F58" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G58" s="21"/>
       <x:c r="H58" s="21"/>
@@ -2529,10 +2529,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J58" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K58" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L58" s="25"/>
       <x:c r="M58" s="26"/>
@@ -2548,13 +2548,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D59" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E59" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F59" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G59" s="21"/>
       <x:c r="H59" s="21"/>
@@ -2562,10 +2562,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J59" s="18" t="n">
-        <x:v>48</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="K59" s="18" t="n">
-        <x:v>48</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="L59" s="25"/>
       <x:c r="M59" s="26"/>
@@ -2581,10 +2581,10 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D60" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E60" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F60" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -2595,10 +2595,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J60" s="18" t="n">
-        <x:v>430</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="K60" s="18" t="n">
-        <x:v>430</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="L60" s="25"/>
       <x:c r="M60" s="26"/>
@@ -2614,10 +2614,10 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D61" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E61" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F61" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -2628,32 +2628,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J61" s="18" t="n">
-        <x:v>374</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="K61" s="18" t="n">
-        <x:v>374</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="L61" s="25"/>
       <x:c r="M61" s="26"/>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
       <x:c r="A62" s="11" t="str">
-        <x:v>小学</x:v>
+        <x:v>初中</x:v>
       </x:c>
       <x:c r="B62" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C62" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D62" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E62" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F62" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G62" s="21"/>
       <x:c r="H62" s="21"/>
@@ -2661,32 +2661,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J62" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K62" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L62" s="25"/>
       <x:c r="M62" s="26"/>
     </x:row>
     <x:row r="63" ht="15" hidden="0" customHeight="1">
       <x:c r="A63" s="11" t="str">
-        <x:v>小学</x:v>
+        <x:v>初中</x:v>
       </x:c>
       <x:c r="B63" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C63" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D63" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E63" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F63" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G63" s="21"/>
       <x:c r="H63" s="21"/>
@@ -2704,22 +2704,22 @@
     </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
       <x:c r="A64" s="11" t="str">
-        <x:v>小学</x:v>
+        <x:v>初中</x:v>
       </x:c>
       <x:c r="B64" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C64" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D64" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E64" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F64" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G64" s="21"/>
       <x:c r="H64" s="21"/>
@@ -2727,32 +2727,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J64" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K64" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L64" s="25"/>
       <x:c r="M64" s="26"/>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
       <x:c r="A65" s="11" t="str">
-        <x:v>小学</x:v>
+        <x:v>初中</x:v>
       </x:c>
       <x:c r="B65" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C65" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D65" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E65" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F65" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G65" s="21"/>
       <x:c r="H65" s="21"/>
@@ -2760,32 +2760,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J65" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="K65" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="L65" s="25"/>
       <x:c r="M65" s="26"/>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
       <x:c r="A66" s="11" t="str">
-        <x:v>小学</x:v>
+        <x:v>初中</x:v>
       </x:c>
       <x:c r="B66" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C66" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D66" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E66" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F66" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G66" s="21"/>
       <x:c r="H66" s="21"/>
@@ -2793,10 +2793,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J66" s="18" t="n">
-        <x:v>133</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="K66" s="18" t="n">
-        <x:v>133</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="L66" s="25"/>
       <x:c r="M66" s="26"/>
@@ -2806,7 +2806,7 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B67" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C67" s="12" t="str">
         <x:v>LLM外呼</x:v>
@@ -2815,10 +2815,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E67" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F67" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G67" s="21"/>
       <x:c r="H67" s="21"/>
@@ -2839,7 +2839,7 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B68" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C68" s="12" t="str">
         <x:v>LLM外呼</x:v>
@@ -2848,10 +2848,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E68" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F68" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G68" s="21"/>
       <x:c r="H68" s="21"/>
@@ -2872,19 +2872,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B69" s="12" t="str">
-        <x:v>暑_6</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C69" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D69" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E69" s="12" t="str">
         <x:v>四年级</x:v>
       </x:c>
       <x:c r="F69" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G69" s="21"/>
       <x:c r="H69" s="21"/>
@@ -2892,10 +2892,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J69" s="18" t="n">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K69" s="18" t="n">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L69" s="25"/>
       <x:c r="M69" s="26"/>
@@ -2905,19 +2905,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B70" s="12" t="str">
-        <x:v>暑_6</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C70" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D70" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E70" s="12" t="str">
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F70" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G70" s="21"/>
       <x:c r="H70" s="21"/>
@@ -2925,10 +2925,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J70" s="18" t="n">
-        <x:v>51</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K70" s="18" t="n">
-        <x:v>51</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L70" s="25"/>
       <x:c r="M70" s="26"/>
@@ -2938,19 +2938,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B71" s="12" t="str">
-        <x:v>暑_6</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C71" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D71" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E71" s="12" t="str">
         <x:v>六年级</x:v>
       </x:c>
       <x:c r="F71" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G71" s="21"/>
       <x:c r="H71" s="21"/>
@@ -2958,10 +2958,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J71" s="18" t="n">
-        <x:v>35</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="K71" s="18" t="n">
-        <x:v>35</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="L71" s="25"/>
       <x:c r="M71" s="26"/>
@@ -2971,10 +2971,10 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B72" s="12" t="str">
-        <x:v>暑_6</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C72" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D72" s="18" t="n">
         <x:v>990</x:v>
@@ -2983,7 +2983,7 @@
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F72" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G72" s="21"/>
       <x:c r="H72" s="21"/>
@@ -2991,10 +2991,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J72" s="18" t="n">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K72" s="18" t="n">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L72" s="25"/>
       <x:c r="M72" s="26"/>
@@ -3004,10 +3004,10 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B73" s="12" t="str">
-        <x:v>暑_6</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C73" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D73" s="18" t="n">
         <x:v>990</x:v>
@@ -3016,7 +3016,7 @@
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F73" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G73" s="21"/>
       <x:c r="H73" s="21"/>
@@ -3024,10 +3024,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J73" s="18" t="n">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K73" s="18" t="n">
-        <x:v>13</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L73" s="25"/>
       <x:c r="M73" s="26"/>
@@ -3040,16 +3040,16 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C74" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D74" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E74" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F74" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G74" s="21"/>
       <x:c r="H74" s="21"/>
@@ -3057,10 +3057,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J74" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K74" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="L74" s="25"/>
       <x:c r="M74" s="26"/>
@@ -3073,16 +3073,16 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C75" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D75" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E75" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F75" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G75" s="21"/>
       <x:c r="H75" s="21"/>
@@ -3090,10 +3090,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J75" s="18" t="n">
-        <x:v>13</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K75" s="18" t="n">
-        <x:v>13</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L75" s="25"/>
       <x:c r="M75" s="26"/>
@@ -3106,16 +3106,16 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C76" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D76" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E76" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F76" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G76" s="21"/>
       <x:c r="H76" s="21"/>
@@ -3123,10 +3123,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J76" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="K76" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="L76" s="25"/>
       <x:c r="M76" s="26"/>
@@ -3139,10 +3139,10 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C77" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D77" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E77" s="12" t="str">
         <x:v>三年级</x:v>
@@ -3156,10 +3156,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J77" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K77" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L77" s="25"/>
       <x:c r="M77" s="26"/>
@@ -3172,10 +3172,10 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C78" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D78" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E78" s="12" t="str">
         <x:v>五年级</x:v>
@@ -3189,10 +3189,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J78" s="18" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K78" s="18" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L78" s="25"/>
       <x:c r="M78" s="26"/>
@@ -3202,19 +3202,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B79" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C79" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D79" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E79" s="12" t="str">
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F79" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G79" s="21"/>
       <x:c r="H79" s="21"/>
@@ -3222,10 +3222,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J79" s="18" t="n">
-        <x:v>24</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K79" s="18" t="n">
-        <x:v>24</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L79" s="25"/>
       <x:c r="M79" s="26"/>
@@ -3235,19 +3235,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B80" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C80" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D80" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E80" s="12" t="str">
         <x:v>四年级</x:v>
       </x:c>
       <x:c r="F80" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G80" s="21"/>
       <x:c r="H80" s="21"/>
@@ -3255,10 +3255,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J80" s="18" t="n">
-        <x:v>35</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K80" s="18" t="n">
-        <x:v>35</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L80" s="25"/>
       <x:c r="M80" s="26"/>
@@ -3268,19 +3268,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B81" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C81" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D81" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E81" s="12" t="str">
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F81" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G81" s="21"/>
       <x:c r="H81" s="21"/>
@@ -3288,10 +3288,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J81" s="18" t="n">
-        <x:v>44</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K81" s="18" t="n">
-        <x:v>44</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L81" s="25"/>
       <x:c r="M81" s="26"/>
@@ -3301,19 +3301,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B82" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C82" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D82" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E82" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F82" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G82" s="21"/>
       <x:c r="H82" s="21"/>
@@ -3321,10 +3321,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J82" s="18" t="n">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K82" s="18" t="n">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L82" s="25"/>
       <x:c r="M82" s="26"/>
@@ -3334,19 +3334,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B83" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C83" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D83" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E83" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F83" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G83" s="21"/>
       <x:c r="H83" s="21"/>
@@ -3354,10 +3354,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J83" s="18" t="n">
-        <x:v>1968</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K83" s="18" t="n">
-        <x:v>1968</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L83" s="25"/>
       <x:c r="M83" s="26"/>
@@ -3370,16 +3370,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C84" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D84" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E84" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F84" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G84" s="21"/>
       <x:c r="H84" s="21"/>
@@ -3387,10 +3387,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J84" s="18" t="n">
-        <x:v>2036</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K84" s="18" t="n">
-        <x:v>2036</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="L84" s="25"/>
       <x:c r="M84" s="26"/>
@@ -3403,16 +3403,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C85" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D85" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E85" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F85" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G85" s="21"/>
       <x:c r="H85" s="21"/>
@@ -3420,10 +3420,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J85" s="18" t="n">
-        <x:v>1513</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="K85" s="18" t="n">
-        <x:v>1513</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="L85" s="25"/>
       <x:c r="M85" s="26"/>
@@ -3436,16 +3436,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C86" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D86" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E86" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F86" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G86" s="21"/>
       <x:c r="H86" s="21"/>
@@ -3453,10 +3453,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J86" s="18" t="n">
-        <x:v>1857</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K86" s="18" t="n">
-        <x:v>1857</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="L86" s="25"/>
       <x:c r="M86" s="26"/>
@@ -3469,16 +3469,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C87" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D87" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E87" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F87" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G87" s="21"/>
       <x:c r="H87" s="21"/>
@@ -3486,10 +3486,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J87" s="18" t="n">
-        <x:v>131</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K87" s="18" t="n">
-        <x:v>131</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="L87" s="25"/>
       <x:c r="M87" s="26"/>
@@ -3505,10 +3505,10 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D88" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E88" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F88" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -3519,10 +3519,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J88" s="18" t="n">
-        <x:v>191</x:v>
+        <x:v>1968</x:v>
       </x:c>
       <x:c r="K88" s="18" t="n">
-        <x:v>191</x:v>
+        <x:v>1968</x:v>
       </x:c>
       <x:c r="L88" s="25"/>
       <x:c r="M88" s="26"/>
@@ -3538,13 +3538,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D89" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E89" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F89" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G89" s="21"/>
       <x:c r="H89" s="21"/>
@@ -3552,10 +3552,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J89" s="18" t="n">
-        <x:v>156</x:v>
+        <x:v>2036</x:v>
       </x:c>
       <x:c r="K89" s="18" t="n">
-        <x:v>156</x:v>
+        <x:v>2036</x:v>
       </x:c>
       <x:c r="L89" s="25"/>
       <x:c r="M89" s="26"/>
@@ -3571,13 +3571,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D90" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E90" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F90" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G90" s="21"/>
       <x:c r="H90" s="21"/>
@@ -3585,10 +3585,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J90" s="18" t="n">
-        <x:v>135</x:v>
+        <x:v>1513</x:v>
       </x:c>
       <x:c r="K90" s="18" t="n">
-        <x:v>135</x:v>
+        <x:v>1513</x:v>
       </x:c>
       <x:c r="L90" s="25"/>
       <x:c r="M90" s="26"/>
@@ -3601,16 +3601,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C91" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D91" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E91" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F91" s="21" t="str">
-        <x:v>2026-06-22</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G91" s="21"/>
       <x:c r="H91" s="21"/>
@@ -3618,10 +3618,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J91" s="18" t="n">
-        <x:v>66</x:v>
+        <x:v>1857</x:v>
       </x:c>
       <x:c r="K91" s="18" t="n">
-        <x:v>66</x:v>
+        <x:v>1857</x:v>
       </x:c>
       <x:c r="L91" s="25"/>
       <x:c r="M91" s="26"/>
@@ -3634,7 +3634,7 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C92" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D92" s="18" t="n">
         <x:v>990</x:v>
@@ -3651,10 +3651,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J92" s="18" t="n">
-        <x:v>239</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="K92" s="18" t="n">
-        <x:v>239</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="L92" s="25"/>
       <x:c r="M92" s="26"/>
@@ -3667,7 +3667,7 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C93" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D93" s="18" t="n">
         <x:v>990</x:v>
@@ -3684,10 +3684,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J93" s="18" t="n">
-        <x:v>252</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="K93" s="18" t="n">
-        <x:v>252</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="L93" s="25"/>
       <x:c r="M93" s="26"/>
@@ -3700,7 +3700,7 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C94" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D94" s="18" t="n">
         <x:v>990</x:v>
@@ -3709,7 +3709,7 @@
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F94" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G94" s="21"/>
       <x:c r="H94" s="21"/>
@@ -3717,10 +3717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J94" s="18" t="n">
-        <x:v>235</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="K94" s="18" t="n">
-        <x:v>235</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="L94" s="25"/>
       <x:c r="M94" s="26"/>
@@ -3733,7 +3733,7 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C95" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D95" s="18" t="n">
         <x:v>990</x:v>
@@ -3750,10 +3750,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J95" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="K95" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L95" s="25"/>
       <x:c r="M95" s="26"/>
@@ -3766,16 +3766,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C96" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D96" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E96" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F96" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G96" s="21"/>
       <x:c r="H96" s="21"/>
@@ -3783,10 +3783,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J96" s="18" t="n">
-        <x:v>181</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K96" s="18" t="n">
-        <x:v>181</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="L96" s="25"/>
       <x:c r="M96" s="26"/>
@@ -3799,16 +3799,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C97" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D97" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E97" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F97" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G97" s="21"/>
       <x:c r="H97" s="21"/>
@@ -3816,10 +3816,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J97" s="18" t="n">
-        <x:v>214</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K97" s="18" t="n">
-        <x:v>214</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="L97" s="25"/>
       <x:c r="M97" s="26"/>
@@ -3832,16 +3832,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C98" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D98" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E98" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F98" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G98" s="21"/>
       <x:c r="H98" s="21"/>
@@ -3849,10 +3849,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J98" s="18" t="n">
-        <x:v>135</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="K98" s="18" t="n">
-        <x:v>135</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="L98" s="25"/>
       <x:c r="M98" s="26"/>
@@ -3865,13 +3865,13 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C99" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D99" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E99" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F99" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -3882,10 +3882,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J99" s="18" t="n">
-        <x:v>191</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="K99" s="18" t="n">
-        <x:v>191</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="L99" s="25"/>
       <x:c r="M99" s="26"/>
@@ -3898,16 +3898,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C100" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D100" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E100" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F100" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G100" s="21"/>
       <x:c r="H100" s="21"/>
@@ -3915,10 +3915,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J100" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K100" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L100" s="25"/>
       <x:c r="M100" s="26"/>
@@ -3931,16 +3931,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C101" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D101" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E101" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F101" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G101" s="21"/>
       <x:c r="H101" s="21"/>
@@ -3948,10 +3948,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J101" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="K101" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="L101" s="25"/>
       <x:c r="M101" s="26"/>
@@ -3964,16 +3964,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C102" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D102" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E102" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F102" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G102" s="21"/>
       <x:c r="H102" s="21"/>
@@ -3981,10 +3981,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J102" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="K102" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="L102" s="25"/>
       <x:c r="M102" s="26"/>
@@ -3997,13 +3997,13 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C103" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D103" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E103" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F103" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -4014,10 +4014,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J103" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="K103" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L103" s="25"/>
       <x:c r="M103" s="26"/>
@@ -4030,16 +4030,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C104" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D104" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E104" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F104" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G104" s="21"/>
       <x:c r="H104" s="21"/>
@@ -4047,10 +4047,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J104" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="K104" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="L104" s="25"/>
       <x:c r="M104" s="26"/>
@@ -4066,13 +4066,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D105" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E105" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F105" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G105" s="21"/>
       <x:c r="H105" s="21"/>
@@ -4080,10 +4080,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J105" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K105" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L105" s="25"/>
       <x:c r="M105" s="26"/>
@@ -4099,13 +4099,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D106" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E106" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F106" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G106" s="21"/>
       <x:c r="H106" s="21"/>
@@ -4113,10 +4113,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J106" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K106" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L106" s="25"/>
       <x:c r="M106" s="26"/>
@@ -4132,10 +4132,10 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D107" s="18" t="n">
-        <x:v>1880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E107" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F107" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -4165,13 +4165,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D108" s="18" t="n">
-        <x:v>1880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E108" s="12" t="str">
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F108" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G108" s="21"/>
       <x:c r="H108" s="21"/>
@@ -4198,13 +4198,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D109" s="18" t="n">
-        <x:v>1880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E109" s="12" t="str">
         <x:v>四年级</x:v>
       </x:c>
       <x:c r="F109" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G109" s="21"/>
       <x:c r="H109" s="21"/>
@@ -4212,10 +4212,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J109" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K109" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L109" s="25"/>
       <x:c r="M109" s="26"/>
@@ -4231,13 +4231,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D110" s="18" t="n">
-        <x:v>1880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E110" s="12" t="str">
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F110" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G110" s="21"/>
       <x:c r="H110" s="21"/>
@@ -4245,10 +4245,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J110" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K110" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L110" s="25"/>
       <x:c r="M110" s="26"/>
@@ -4264,13 +4264,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D111" s="18" t="n">
-        <x:v>1880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E111" s="12" t="str">
         <x:v>六年级</x:v>
       </x:c>
       <x:c r="F111" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G111" s="21"/>
       <x:c r="H111" s="21"/>
@@ -4278,10 +4278,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J111" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K111" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L111" s="25"/>
       <x:c r="M111" s="26"/>
@@ -4297,13 +4297,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D112" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>1880</x:v>
       </x:c>
       <x:c r="E112" s="12" t="str">
         <x:v>二年级</x:v>
       </x:c>
       <x:c r="F112" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G112" s="21"/>
       <x:c r="H112" s="21"/>
@@ -4311,10 +4311,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J112" s="18" t="n">
-        <x:v>89</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K112" s="18" t="n">
-        <x:v>89</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L112" s="25"/>
       <x:c r="M112" s="26"/>
@@ -4330,13 +4330,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D113" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>1880</x:v>
       </x:c>
       <x:c r="E113" s="12" t="str">
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F113" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G113" s="21"/>
       <x:c r="H113" s="21"/>
@@ -4344,10 +4344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J113" s="18" t="n">
-        <x:v>227</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K113" s="18" t="n">
-        <x:v>227</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L113" s="25"/>
       <x:c r="M113" s="26"/>
@@ -4363,13 +4363,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D114" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>1880</x:v>
       </x:c>
       <x:c r="E114" s="12" t="str">
         <x:v>四年级</x:v>
       </x:c>
       <x:c r="F114" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G114" s="21"/>
       <x:c r="H114" s="21"/>
@@ -4377,10 +4377,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J114" s="18" t="n">
-        <x:v>291</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K114" s="18" t="n">
-        <x:v>291</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L114" s="25"/>
       <x:c r="M114" s="26"/>
@@ -4396,13 +4396,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D115" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>1880</x:v>
       </x:c>
       <x:c r="E115" s="12" t="str">
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F115" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G115" s="21"/>
       <x:c r="H115" s="21"/>
@@ -4410,10 +4410,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J115" s="18" t="n">
-        <x:v>229</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K115" s="18" t="n">
-        <x:v>229</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L115" s="25"/>
       <x:c r="M115" s="26"/>
@@ -4429,13 +4429,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D116" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>1880</x:v>
       </x:c>
       <x:c r="E116" s="12" t="str">
         <x:v>六年级</x:v>
       </x:c>
       <x:c r="F116" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G116" s="21"/>
       <x:c r="H116" s="21"/>
@@ -4443,10 +4443,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J116" s="18" t="n">
-        <x:v>264</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K116" s="18" t="n">
-        <x:v>264</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L116" s="25"/>
       <x:c r="M116" s="26"/>
@@ -4456,205 +4456,165 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B117" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C117" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D117" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E117" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F117" s="21" t="str">
-        <x:v>2026-06-29</x:v>
-      </x:c>
-      <x:c r="G117" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H117" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="G117" s="21"/>
+      <x:c r="H117" s="21"/>
       <x:c r="I117" s="18" t="n">
-        <x:v>40</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J117" s="18" t="n">
-        <x:v>18</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K117" s="18" t="n">
-        <x:v>-22</x:v>
-      </x:c>
-      <x:c r="L117" s="25" t="n">
-        <x:v>0.45</x:v>
-      </x:c>
-      <x:c r="M117" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="L117" s="25"/>
+      <x:c r="M117" s="26"/>
     </x:row>
     <x:row r="118" ht="15" hidden="0" customHeight="1">
       <x:c r="A118" s="11" t="str">
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B118" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C118" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D118" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E118" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F118" s="21" t="str">
-        <x:v>2026-06-29</x:v>
-      </x:c>
-      <x:c r="G118" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H118" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="G118" s="21"/>
+      <x:c r="H118" s="21"/>
       <x:c r="I118" s="18" t="n">
-        <x:v>120</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J118" s="18" t="n">
-        <x:v>49</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="K118" s="18" t="n">
-        <x:v>-71</x:v>
-      </x:c>
-      <x:c r="L118" s="25" t="n">
-        <x:v>0.4083333333333333</x:v>
-      </x:c>
-      <x:c r="M118" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="L118" s="25"/>
+      <x:c r="M118" s="26"/>
     </x:row>
     <x:row r="119" ht="15" hidden="0" customHeight="1">
       <x:c r="A119" s="11" t="str">
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B119" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C119" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D119" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E119" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F119" s="21" t="str">
-        <x:v>2026-06-29</x:v>
-      </x:c>
-      <x:c r="G119" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H119" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="G119" s="21"/>
+      <x:c r="H119" s="21"/>
       <x:c r="I119" s="18" t="n">
-        <x:v>120</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J119" s="18" t="n">
-        <x:v>40</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="K119" s="18" t="n">
-        <x:v>-80</x:v>
-      </x:c>
-      <x:c r="L119" s="25" t="n">
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
-      <x:c r="M119" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="L119" s="25"/>
+      <x:c r="M119" s="26"/>
     </x:row>
     <x:row r="120" ht="15" hidden="0" customHeight="1">
       <x:c r="A120" s="11" t="str">
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B120" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C120" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D120" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E120" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F120" s="21" t="str">
-        <x:v>2026-06-29</x:v>
-      </x:c>
-      <x:c r="G120" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H120" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="G120" s="21"/>
+      <x:c r="H120" s="21"/>
       <x:c r="I120" s="18" t="n">
-        <x:v>120</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J120" s="18" t="n">
-        <x:v>49</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="K120" s="18" t="n">
-        <x:v>-71</x:v>
-      </x:c>
-      <x:c r="L120" s="25" t="n">
-        <x:v>0.4083333333333333</x:v>
-      </x:c>
-      <x:c r="M120" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="L120" s="25"/>
+      <x:c r="M120" s="26"/>
     </x:row>
     <x:row r="121" ht="15" hidden="0" customHeight="1">
       <x:c r="A121" s="11" t="str">
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B121" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C121" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D121" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E121" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F121" s="21" t="str">
-        <x:v>2026-06-29</x:v>
-      </x:c>
-      <x:c r="G121" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H121" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="G121" s="21"/>
+      <x:c r="H121" s="21"/>
       <x:c r="I121" s="18" t="n">
-        <x:v>2300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J121" s="18" t="n">
-        <x:v>1885</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="K121" s="18" t="n">
-        <x:v>-415</x:v>
-      </x:c>
-      <x:c r="L121" s="25" t="n">
-        <x:v>0.8195652173913044</x:v>
-      </x:c>
-      <x:c r="M121" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="L121" s="25"/>
+      <x:c r="M121" s="26"/>
     </x:row>
     <x:row r="122" ht="15" hidden="0" customHeight="1">
       <x:c r="A122" s="11" t="str">
@@ -4664,16 +4624,16 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C122" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D122" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E122" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F122" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G122" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4682,19 +4642,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I122" s="18" t="n">
-        <x:v>2500</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J122" s="18" t="n">
-        <x:v>1979</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K122" s="18" t="n">
-        <x:v>-521</x:v>
+        <x:v>-18</x:v>
       </x:c>
       <x:c r="L122" s="25" t="n">
-        <x:v>0.7916</x:v>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="M122" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="15" hidden="0" customHeight="1">
@@ -4705,16 +4665,16 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C123" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D123" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E123" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F123" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G123" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4723,19 +4683,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I123" s="18" t="n">
-        <x:v>2000</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J123" s="18" t="n">
-        <x:v>1622</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K123" s="18" t="n">
-        <x:v>-378</x:v>
+        <x:v>-62</x:v>
       </x:c>
       <x:c r="L123" s="25" t="n">
-        <x:v>0.811</x:v>
+        <x:v>0.48333333333333334</x:v>
       </x:c>
       <x:c r="M123" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="15" hidden="0" customHeight="1">
@@ -4746,16 +4706,16 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C124" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D124" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E124" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F124" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G124" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4764,19 +4724,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I124" s="18" t="n">
-        <x:v>2300</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J124" s="18" t="n">
-        <x:v>1670</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K124" s="18" t="n">
-        <x:v>-630</x:v>
+        <x:v>-69</x:v>
       </x:c>
       <x:c r="L124" s="25" t="n">
-        <x:v>0.7260869565217392</x:v>
+        <x:v>0.425</x:v>
       </x:c>
       <x:c r="M124" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="15" hidden="0" customHeight="1">
@@ -4787,16 +4747,16 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C125" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D125" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E125" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F125" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G125" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4805,19 +4765,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I125" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J125" s="18" t="n">
-        <x:v>146</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K125" s="18" t="n">
-        <x:v>46</x:v>
+        <x:v>-57</x:v>
       </x:c>
       <x:c r="L125" s="25" t="n">
-        <x:v>1.46</x:v>
+        <x:v>0.525</x:v>
       </x:c>
       <x:c r="M125" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="15" hidden="0" customHeight="1">
@@ -4831,13 +4791,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D126" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E126" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F126" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G126" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4846,19 +4806,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I126" s="18" t="n">
-        <x:v>150</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="J126" s="18" t="n">
-        <x:v>194</x:v>
+        <x:v>2099</x:v>
       </x:c>
       <x:c r="K126" s="18" t="n">
-        <x:v>44</x:v>
+        <x:v>-201</x:v>
       </x:c>
       <x:c r="L126" s="25" t="n">
-        <x:v>1.2933333333333332</x:v>
+        <x:v>0.912608695652174</x:v>
       </x:c>
       <x:c r="M126" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="15" hidden="0" customHeight="1">
@@ -4872,13 +4832,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D127" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E127" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F127" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G127" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4887,19 +4847,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I127" s="18" t="n">
-        <x:v>120</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="J127" s="18" t="n">
-        <x:v>116</x:v>
+        <x:v>2227</x:v>
       </x:c>
       <x:c r="K127" s="18" t="n">
-        <x:v>-4</x:v>
+        <x:v>-273</x:v>
       </x:c>
       <x:c r="L127" s="25" t="n">
-        <x:v>0.9666666666666667</x:v>
+        <x:v>0.8908</x:v>
       </x:c>
       <x:c r="M127" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="15" hidden="0" customHeight="1">
@@ -4913,13 +4873,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D128" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E128" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F128" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G128" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -4928,19 +4888,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I128" s="18" t="n">
-        <x:v>150</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="J128" s="18" t="n">
-        <x:v>142</x:v>
+        <x:v>1808</x:v>
       </x:c>
       <x:c r="K128" s="18" t="n">
-        <x:v>-8</x:v>
+        <x:v>-192</x:v>
       </x:c>
       <x:c r="L128" s="25" t="n">
-        <x:v>0.9466666666666667</x:v>
+        <x:v>0.904</x:v>
       </x:c>
       <x:c r="M128" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="15" hidden="0" customHeight="1">
@@ -4951,30 +4911,38 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C129" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D129" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E129" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F129" s="21" t="str">
-        <x:v>2026-06-29</x:v>
-      </x:c>
-      <x:c r="G129" s="21"/>
-      <x:c r="H129" s="21"/>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G129" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H129" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I129" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="J129" s="18" t="n">
-        <x:v>86</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="K129" s="18" t="n">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="L129" s="25"/>
-      <x:c r="M129" s="26"/>
+        <x:v>-300</x:v>
+      </x:c>
+      <x:c r="L129" s="25" t="n">
+        <x:v>0.8695652173913043</x:v>
+      </x:c>
+      <x:c r="M129" s="26" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="130" ht="15" hidden="0" customHeight="1">
       <x:c r="A130" s="11" t="str">
@@ -4984,7 +4952,7 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C130" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D130" s="18" t="n">
         <x:v>990</x:v>
@@ -4993,7 +4961,7 @@
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F130" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G130" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5005,16 +4973,16 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J130" s="18" t="n">
-        <x:v>201</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="K130" s="18" t="n">
-        <x:v>101</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="L130" s="25" t="n">
-        <x:v>2.01</x:v>
+        <x:v>1.72</x:v>
       </x:c>
       <x:c r="M130" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="15" hidden="0" customHeight="1">
@@ -5025,7 +4993,7 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C131" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D131" s="18" t="n">
         <x:v>990</x:v>
@@ -5034,7 +5002,7 @@
         <x:v>四年级</x:v>
       </x:c>
       <x:c r="F131" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G131" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5043,19 +5011,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I131" s="18" t="n">
-        <x:v>300</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J131" s="18" t="n">
-        <x:v>218</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="K131" s="18" t="n">
-        <x:v>-82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="L131" s="25" t="n">
-        <x:v>0.7266666666666667</x:v>
+        <x:v>1.54</x:v>
       </x:c>
       <x:c r="M131" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="15" hidden="0" customHeight="1">
@@ -5066,7 +5034,7 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C132" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D132" s="18" t="n">
         <x:v>990</x:v>
@@ -5075,7 +5043,7 @@
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F132" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G132" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5084,19 +5052,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I132" s="18" t="n">
-        <x:v>200</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J132" s="18" t="n">
-        <x:v>211</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="K132" s="18" t="n">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L132" s="25" t="n">
-        <x:v>1.055</x:v>
+        <x:v>1.125</x:v>
       </x:c>
       <x:c r="M132" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="15" hidden="0" customHeight="1">
@@ -5107,7 +5075,7 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C133" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D133" s="18" t="n">
         <x:v>990</x:v>
@@ -5116,7 +5084,7 @@
         <x:v>六年级</x:v>
       </x:c>
       <x:c r="F133" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G133" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5125,19 +5093,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I133" s="18" t="n">
-        <x:v>200</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J133" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="K133" s="18" t="n">
-        <x:v>-195</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="L133" s="25" t="n">
-        <x:v>0.025</x:v>
+        <x:v>1.1066666666666667</x:v>
       </x:c>
       <x:c r="M133" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="15" hidden="0" customHeight="1">
@@ -5148,16 +5116,16 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C134" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D134" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E134" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F134" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G134" s="21"/>
       <x:c r="H134" s="21"/>
@@ -5165,10 +5133,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J134" s="18" t="n">
-        <x:v>183</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K134" s="18" t="n">
-        <x:v>183</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="L134" s="25"/>
       <x:c r="M134" s="26"/>
@@ -5181,30 +5149,38 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C135" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D135" s="18" t="n">
+        <x:v>990</x:v>
+      </x:c>
+      <x:c r="E135" s="12" t="str">
+        <x:v>三年级</x:v>
+      </x:c>
+      <x:c r="F135" s="21" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G135" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H135" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
+      <x:c r="I135" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="E135" s="12" t="str">
-        <x:v>四年级</x:v>
-      </x:c>
-      <x:c r="F135" s="21" t="str">
-        <x:v>2026-06-28</x:v>
-      </x:c>
-      <x:c r="G135" s="21"/>
-      <x:c r="H135" s="21"/>
-      <x:c r="I135" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="J135" s="18" t="n">
-        <x:v>252</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="K135" s="18" t="n">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="L135" s="25"/>
-      <x:c r="M135" s="26"/>
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="L135" s="25" t="n">
+        <x:v>2.42</x:v>
+      </x:c>
+      <x:c r="M135" s="26" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="136" ht="15" hidden="0" customHeight="1">
       <x:c r="A136" s="11" t="str">
@@ -5214,30 +5190,38 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C136" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D136" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E136" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F136" s="21" t="str">
-        <x:v>2026-06-29</x:v>
-      </x:c>
-      <x:c r="G136" s="21"/>
-      <x:c r="H136" s="21"/>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G136" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H136" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I136" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J136" s="18" t="n">
-        <x:v>185</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="K136" s="18" t="n">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="L136" s="25"/>
-      <x:c r="M136" s="26"/>
+        <x:v>-51</x:v>
+      </x:c>
+      <x:c r="L136" s="25" t="n">
+        <x:v>0.83</x:v>
+      </x:c>
+      <x:c r="M136" s="26" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="137" ht="15" hidden="0" customHeight="1">
       <x:c r="A137" s="11" t="str">
@@ -5247,30 +5231,38 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C137" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D137" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E137" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F137" s="21" t="str">
-        <x:v>2026-06-29</x:v>
-      </x:c>
-      <x:c r="G137" s="21"/>
-      <x:c r="H137" s="21"/>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G137" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H137" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I137" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="J137" s="18" t="n">
-        <x:v>207</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="K137" s="18" t="n">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="L137" s="25"/>
-      <x:c r="M137" s="26"/>
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="L137" s="25" t="n">
+        <x:v>1.18</x:v>
+      </x:c>
+      <x:c r="M137" s="26" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="138" ht="15" hidden="0" customHeight="1">
       <x:c r="A138" s="11" t="str">
@@ -5280,16 +5272,16 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C138" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D138" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E138" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F138" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G138" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5298,19 +5290,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I138" s="18" t="n">
-        <x:v>20</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="J138" s="18" t="n">
-        <x:v>22</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K138" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>-195</x:v>
       </x:c>
       <x:c r="L138" s="25" t="n">
-        <x:v>1.1</x:v>
+        <x:v>0.025</x:v>
       </x:c>
       <x:c r="M138" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="15" hidden="0" customHeight="1">
@@ -5321,38 +5313,30 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C139" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D139" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E139" s="12" t="str">
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F139" s="21" t="str">
-        <x:v>2026-06-28</x:v>
-      </x:c>
-      <x:c r="G139" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H139" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G139" s="21"/>
+      <x:c r="H139" s="21"/>
       <x:c r="I139" s="18" t="n">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J139" s="18" t="n">
-        <x:v>40</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="K139" s="18" t="n">
-        <x:v>-10</x:v>
-      </x:c>
-      <x:c r="L139" s="25" t="n">
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="M139" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="L139" s="25"/>
+      <x:c r="M139" s="26"/>
     </x:row>
     <x:row r="140" ht="15" hidden="0" customHeight="1">
       <x:c r="A140" s="11" t="str">
@@ -5362,38 +5346,30 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C140" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D140" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E140" s="12" t="str">
         <x:v>四年级</x:v>
       </x:c>
       <x:c r="F140" s="21" t="str">
-        <x:v>2026-06-28</x:v>
-      </x:c>
-      <x:c r="G140" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H140" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G140" s="21"/>
+      <x:c r="H140" s="21"/>
       <x:c r="I140" s="18" t="n">
-        <x:v>70</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J140" s="18" t="n">
-        <x:v>60</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="K140" s="18" t="n">
-        <x:v>-10</x:v>
-      </x:c>
-      <x:c r="L140" s="25" t="n">
-        <x:v>0.8571428571428571</x:v>
-      </x:c>
-      <x:c r="M140" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="L140" s="25"/>
+      <x:c r="M140" s="26"/>
     </x:row>
     <x:row r="141" ht="15" hidden="0" customHeight="1">
       <x:c r="A141" s="11" t="str">
@@ -5403,38 +5379,30 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C141" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D141" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E141" s="12" t="str">
         <x:v>五年级</x:v>
       </x:c>
       <x:c r="F141" s="21" t="str">
-        <x:v>2026-06-29</x:v>
-      </x:c>
-      <x:c r="G141" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H141" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G141" s="21"/>
+      <x:c r="H141" s="21"/>
       <x:c r="I141" s="18" t="n">
-        <x:v>40</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J141" s="18" t="n">
-        <x:v>72</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="K141" s="18" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="L141" s="25" t="n">
-        <x:v>1.8</x:v>
-      </x:c>
-      <x:c r="M141" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="L141" s="25"/>
+      <x:c r="M141" s="26"/>
     </x:row>
     <x:row r="142" ht="15" hidden="0" customHeight="1">
       <x:c r="A142" s="11" t="str">
@@ -5444,38 +5412,30 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C142" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D142" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E142" s="12" t="str">
         <x:v>六年级</x:v>
       </x:c>
       <x:c r="F142" s="21" t="str">
-        <x:v>2026-06-28</x:v>
-      </x:c>
-      <x:c r="G142" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H142" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G142" s="21"/>
+      <x:c r="H142" s="21"/>
       <x:c r="I142" s="18" t="n">
-        <x:v>70</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J142" s="18" t="n">
-        <x:v>64</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="K142" s="18" t="n">
-        <x:v>-6</x:v>
-      </x:c>
-      <x:c r="L142" s="25" t="n">
-        <x:v>0.9142857142857143</x:v>
-      </x:c>
-      <x:c r="M142" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="L142" s="25"/>
+      <x:c r="M142" s="26"/>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
       <x:c r="A143" s="11" t="str">
@@ -5488,27 +5448,35 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D143" s="18" t="n">
-        <x:v>1880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E143" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F143" s="21" t="str">
-        <x:v>2026-06-24</x:v>
-      </x:c>
-      <x:c r="G143" s="21"/>
-      <x:c r="H143" s="21"/>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G143" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H143" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I143" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J143" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K143" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L143" s="25"/>
-      <x:c r="M143" s="26"/>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L143" s="25" t="n">
+        <x:v>1.45</x:v>
+      </x:c>
+      <x:c r="M143" s="26" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
       <x:c r="A144" s="11" t="str">
@@ -5521,13 +5489,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D144" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E144" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F144" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G144" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5536,19 +5504,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I144" s="18" t="n">
-        <x:v>80</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J144" s="18" t="n">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K144" s="18" t="n">
-        <x:v>-30</x:v>
+        <x:v>-4</x:v>
       </x:c>
       <x:c r="L144" s="25" t="n">
-        <x:v>0.625</x:v>
+        <x:v>0.92</x:v>
       </x:c>
       <x:c r="M144" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="15" hidden="0" customHeight="1">
@@ -5562,13 +5530,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D145" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E145" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F145" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G145" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5577,19 +5545,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I145" s="18" t="n">
-        <x:v>190</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J145" s="18" t="n">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K145" s="18" t="n">
-        <x:v>-112</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L145" s="25" t="n">
-        <x:v>0.4105263157894737</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="M145" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="15" hidden="0" customHeight="1">
@@ -5603,13 +5571,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D146" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E146" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F146" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G146" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5618,19 +5586,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I146" s="18" t="n">
-        <x:v>260</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J146" s="18" t="n">
-        <x:v>152</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K146" s="18" t="n">
-        <x:v>-108</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L146" s="25" t="n">
-        <x:v>0.5846153846153846</x:v>
+        <x:v>2.275</x:v>
       </x:c>
       <x:c r="M146" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="15" hidden="0" customHeight="1">
@@ -5644,13 +5612,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D147" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E147" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F147" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G147" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5659,19 +5627,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I147" s="18" t="n">
-        <x:v>240</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J147" s="18" t="n">
-        <x:v>136</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K147" s="18" t="n">
-        <x:v>-104</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L147" s="25" t="n">
-        <x:v>0.5666666666666667</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="M147" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="15" hidden="0" customHeight="1">
@@ -5685,210 +5653,242 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D148" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>1880</x:v>
       </x:c>
       <x:c r="E148" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F148" s="21" t="str">
-        <x:v>2026-06-28</x:v>
-      </x:c>
-      <x:c r="G148" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H148" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="G148" s="21"/>
+      <x:c r="H148" s="21"/>
       <x:c r="I148" s="18" t="n">
-        <x:v>260</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J148" s="18" t="n">
-        <x:v>194</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K148" s="18" t="n">
-        <x:v>-66</x:v>
-      </x:c>
-      <x:c r="L148" s="25" t="n">
-        <x:v>0.7461538461538462</x:v>
-      </x:c>
-      <x:c r="M148" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L148" s="25"/>
+      <x:c r="M148" s="26"/>
     </x:row>
     <x:row r="149" ht="15" hidden="0" customHeight="1">
       <x:c r="A149" s="11" t="str">
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B149" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C149" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D149" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E149" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F149" s="21" t="str">
-        <x:v>2026-06-22</x:v>
-      </x:c>
-      <x:c r="G149" s="21"/>
-      <x:c r="H149" s="21"/>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G149" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H149" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I149" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J149" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K149" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L149" s="25"/>
-      <x:c r="M149" s="26"/>
+        <x:v>-7</x:v>
+      </x:c>
+      <x:c r="L149" s="25" t="n">
+        <x:v>0.9125</x:v>
+      </x:c>
+      <x:c r="M149" s="26" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="150" ht="15" hidden="0" customHeight="1">
       <x:c r="A150" s="11" t="str">
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B150" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C150" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D150" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E150" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F150" s="21" t="str">
-        <x:v>2026-06-22</x:v>
-      </x:c>
-      <x:c r="G150" s="21"/>
-      <x:c r="H150" s="21"/>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G150" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H150" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I150" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="J150" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K150" s="18" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="L150" s="25"/>
-      <x:c r="M150" s="26"/>
+        <x:v>-74</x:v>
+      </x:c>
+      <x:c r="L150" s="25" t="n">
+        <x:v>0.6105263157894737</x:v>
+      </x:c>
+      <x:c r="M150" s="26" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="151" ht="15" hidden="0" customHeight="1">
       <x:c r="A151" s="11" t="str">
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B151" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C151" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D151" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E151" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F151" s="21" t="str">
-        <x:v>2026-06-23</x:v>
-      </x:c>
-      <x:c r="G151" s="21"/>
-      <x:c r="H151" s="21"/>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G151" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H151" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I151" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="J151" s="18" t="n">
-        <x:v>11</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="K151" s="18" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="L151" s="25"/>
-      <x:c r="M151" s="26"/>
+        <x:v>-60</x:v>
+      </x:c>
+      <x:c r="L151" s="25" t="n">
+        <x:v>0.7692307692307693</x:v>
+      </x:c>
+      <x:c r="M151" s="26" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="152" ht="15" hidden="0" customHeight="1">
       <x:c r="A152" s="11" t="str">
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B152" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C152" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D152" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E152" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F152" s="21" t="str">
-        <x:v>2026-06-21</x:v>
-      </x:c>
-      <x:c r="G152" s="21"/>
-      <x:c r="H152" s="21"/>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G152" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H152" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I152" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="J152" s="18" t="n">
-        <x:v>163</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="K152" s="18" t="n">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="L152" s="25"/>
-      <x:c r="M152" s="26"/>
+        <x:v>-73</x:v>
+      </x:c>
+      <x:c r="L152" s="25" t="n">
+        <x:v>0.6958333333333333</x:v>
+      </x:c>
+      <x:c r="M152" s="26" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="153" ht="15" hidden="0" customHeight="1">
       <x:c r="A153" s="11" t="str">
-        <x:v>自拼</x:v>
+        <x:v>小学</x:v>
       </x:c>
       <x:c r="B153" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C153" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D153" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E153" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F153" s="21" t="str">
-        <x:v>2026-06-22</x:v>
-      </x:c>
-      <x:c r="G153" s="21"/>
-      <x:c r="H153" s="21"/>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G153" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H153" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I153" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="J153" s="18" t="n">
-        <x:v>218</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="K153" s="18" t="n">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="L153" s="25"/>
-      <x:c r="M153" s="26"/>
+        <x:v>-40</x:v>
+      </x:c>
+      <x:c r="L153" s="25" t="n">
+        <x:v>0.8461538461538461</x:v>
+      </x:c>
+      <x:c r="M153" s="26" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="154" ht="15" hidden="0" customHeight="1">
       <x:c r="A154" s="11" t="str">
-        <x:v>自拼</x:v>
+        <x:v>小学</x:v>
       </x:c>
       <x:c r="B154" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C154" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D154" s="18" t="n">
         <x:v>990</x:v>
@@ -5897,7 +5897,7 @@
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F154" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G154" s="21"/>
       <x:c r="H154" s="21"/>
@@ -5905,23 +5905,23 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J154" s="18" t="n">
-        <x:v>79</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K154" s="18" t="n">
-        <x:v>79</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L154" s="25"/>
       <x:c r="M154" s="26"/>
     </x:row>
     <x:row r="155" ht="15" hidden="0" customHeight="1">
       <x:c r="A155" s="11" t="str">
-        <x:v>自拼</x:v>
+        <x:v>小学</x:v>
       </x:c>
       <x:c r="B155" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C155" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D155" s="18" t="n">
         <x:v>990</x:v>
@@ -5930,7 +5930,7 @@
         <x:v>四年级</x:v>
       </x:c>
       <x:c r="F155" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G155" s="21"/>
       <x:c r="H155" s="21"/>
@@ -5938,32 +5938,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J155" s="18" t="n">
-        <x:v>32</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K155" s="18" t="n">
-        <x:v>32</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L155" s="25"/>
       <x:c r="M155" s="26"/>
     </x:row>
     <x:row r="156" ht="15" hidden="0" customHeight="1">
       <x:c r="A156" s="11" t="str">
-        <x:v>自拼</x:v>
+        <x:v>小学</x:v>
       </x:c>
       <x:c r="B156" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C156" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D156" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E156" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F156" s="21" t="str">
-        <x:v>2026-06-22</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G156" s="21"/>
       <x:c r="H156" s="21"/>
@@ -5971,32 +5971,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J156" s="18" t="n">
-        <x:v>314</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K156" s="18" t="n">
-        <x:v>314</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L156" s="25"/>
       <x:c r="M156" s="26"/>
     </x:row>
     <x:row r="157" ht="15" hidden="0" customHeight="1">
       <x:c r="A157" s="11" t="str">
-        <x:v>自拼</x:v>
+        <x:v>小学</x:v>
       </x:c>
       <x:c r="B157" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C157" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D157" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E157" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F157" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G157" s="21"/>
       <x:c r="H157" s="21"/>
@@ -6004,10 +6004,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J157" s="18" t="n">
-        <x:v>116</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="K157" s="18" t="n">
-        <x:v>116</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="L157" s="25"/>
       <x:c r="M157" s="26"/>
@@ -6020,16 +6020,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C158" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D158" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E158" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F158" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G158" s="21"/>
       <x:c r="H158" s="21"/>
@@ -6037,10 +6037,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J158" s="18" t="n">
-        <x:v>89</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="K158" s="18" t="n">
-        <x:v>89</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="L158" s="25"/>
       <x:c r="M158" s="26"/>
@@ -6053,16 +6053,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C159" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D159" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E159" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F159" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G159" s="21"/>
       <x:c r="H159" s="21"/>
@@ -6070,10 +6070,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J159" s="18" t="n">
-        <x:v>32</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="K159" s="18" t="n">
-        <x:v>32</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="L159" s="25"/>
       <x:c r="M159" s="26"/>
@@ -6086,13 +6086,13 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C160" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D160" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E160" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F160" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -6103,10 +6103,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J160" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K160" s="18" t="n">
-        <x:v>8</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L160" s="25"/>
       <x:c r="M160" s="26"/>
@@ -6119,16 +6119,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C161" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D161" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E161" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F161" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G161" s="21"/>
       <x:c r="H161" s="21"/>
@@ -6136,10 +6136,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J161" s="18" t="n">
-        <x:v>11</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="K161" s="18" t="n">
-        <x:v>11</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="L161" s="25"/>
       <x:c r="M161" s="26"/>
@@ -6152,16 +6152,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C162" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D162" s="18" t="n">
-        <x:v>2990</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E162" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F162" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G162" s="21"/>
       <x:c r="H162" s="21"/>
@@ -6169,10 +6169,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J162" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K162" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="L162" s="25"/>
       <x:c r="M162" s="26"/>
@@ -6185,16 +6185,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C163" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D163" s="18" t="n">
-        <x:v>2990</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E163" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F163" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G163" s="21"/>
       <x:c r="H163" s="21"/>
@@ -6202,10 +6202,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J163" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K163" s="18" t="n">
-        <x:v>2</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="L163" s="25"/>
       <x:c r="M163" s="26"/>
@@ -6218,16 +6218,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C164" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D164" s="18" t="n">
-        <x:v>2990</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E164" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F164" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G164" s="21"/>
       <x:c r="H164" s="21"/>
@@ -6235,10 +6235,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J164" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K164" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L164" s="25"/>
       <x:c r="M164" s="26"/>
@@ -6248,19 +6248,19 @@
         <x:v>自拼</x:v>
       </x:c>
       <x:c r="B165" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C165" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D165" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E165" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F165" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G165" s="21"/>
       <x:c r="H165" s="21"/>
@@ -6268,10 +6268,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J165" s="18" t="n">
-        <x:v>294</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K165" s="18" t="n">
-        <x:v>294</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L165" s="25"/>
       <x:c r="M165" s="26"/>
@@ -6281,19 +6281,19 @@
         <x:v>自拼</x:v>
       </x:c>
       <x:c r="B166" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C166" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D166" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E166" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F166" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G166" s="21"/>
       <x:c r="H166" s="21"/>
@@ -6301,10 +6301,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J166" s="18" t="n">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K166" s="18" t="n">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L166" s="25"/>
       <x:c r="M166" s="26"/>
@@ -6314,19 +6314,19 @@
         <x:v>自拼</x:v>
       </x:c>
       <x:c r="B167" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C167" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D167" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="E167" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F167" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G167" s="21"/>
       <x:c r="H167" s="21"/>
@@ -6334,10 +6334,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J167" s="18" t="n">
-        <x:v>49</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K167" s="18" t="n">
-        <x:v>49</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L167" s="25"/>
       <x:c r="M167" s="26"/>
@@ -6347,7 +6347,7 @@
         <x:v>自拼</x:v>
       </x:c>
       <x:c r="B168" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C168" s="12" t="str">
         <x:v>常规外呼</x:v>
@@ -6356,10 +6356,10 @@
         <x:v>2990</x:v>
       </x:c>
       <x:c r="E168" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F168" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G168" s="21"/>
       <x:c r="H168" s="21"/>
@@ -6367,10 +6367,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J168" s="18" t="n">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K168" s="18" t="n">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L168" s="25"/>
       <x:c r="M168" s="26"/>
@@ -6380,7 +6380,7 @@
         <x:v>自拼</x:v>
       </x:c>
       <x:c r="B169" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C169" s="12" t="str">
         <x:v>常规外呼</x:v>
@@ -6389,10 +6389,10 @@
         <x:v>2990</x:v>
       </x:c>
       <x:c r="E169" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F169" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G169" s="21"/>
       <x:c r="H169" s="21"/>
@@ -6400,10 +6400,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J169" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K169" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L169" s="25"/>
       <x:c r="M169" s="26"/>
@@ -6416,16 +6416,16 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C170" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D170" s="18" t="n">
-        <x:v>2990</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E170" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F170" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G170" s="21"/>
       <x:c r="H170" s="21"/>
@@ -6433,32 +6433,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J170" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="K170" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="L170" s="25"/>
       <x:c r="M170" s="26"/>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
       <x:c r="A171" s="11" t="str">
-        <x:v>高中</x:v>
+        <x:v>自拼</x:v>
       </x:c>
       <x:c r="B171" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C171" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D171" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E171" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F171" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G171" s="21"/>
       <x:c r="H171" s="21"/>
@@ -6466,32 +6466,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J171" s="18" t="n">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K171" s="18" t="n">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="L171" s="25"/>
       <x:c r="M171" s="26"/>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
       <x:c r="A172" s="11" t="str">
-        <x:v>高中</x:v>
+        <x:v>自拼</x:v>
       </x:c>
       <x:c r="B172" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C172" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D172" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E172" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F172" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G172" s="21"/>
       <x:c r="H172" s="21"/>
@@ -6499,32 +6499,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J172" s="18" t="n">
-        <x:v>115</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K172" s="18" t="n">
-        <x:v>115</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L172" s="25"/>
       <x:c r="M172" s="26"/>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
       <x:c r="A173" s="11" t="str">
-        <x:v>高中</x:v>
+        <x:v>自拼</x:v>
       </x:c>
       <x:c r="B173" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C173" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D173" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="E173" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F173" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G173" s="21"/>
       <x:c r="H173" s="21"/>
@@ -6532,32 +6532,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J173" s="18" t="n">
-        <x:v>96</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K173" s="18" t="n">
-        <x:v>96</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L173" s="25"/>
       <x:c r="M173" s="26"/>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
       <x:c r="A174" s="11" t="str">
-        <x:v>高中</x:v>
+        <x:v>自拼</x:v>
       </x:c>
       <x:c r="B174" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C174" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D174" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="E174" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F174" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G174" s="21"/>
       <x:c r="H174" s="21"/>
@@ -6565,32 +6565,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J174" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K174" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L174" s="25"/>
       <x:c r="M174" s="26"/>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
       <x:c r="A175" s="11" t="str">
-        <x:v>高中</x:v>
+        <x:v>自拼</x:v>
       </x:c>
       <x:c r="B175" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C175" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D175" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="E175" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F175" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G175" s="21"/>
       <x:c r="H175" s="21"/>
@@ -6598,32 +6598,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J175" s="18" t="n">
-        <x:v>73</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K175" s="18" t="n">
-        <x:v>73</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L175" s="25"/>
       <x:c r="M175" s="26"/>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
       <x:c r="A176" s="11" t="str">
-        <x:v>高中</x:v>
+        <x:v>自拼</x:v>
       </x:c>
       <x:c r="B176" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C176" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D176" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E176" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F176" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G176" s="21"/>
       <x:c r="H176" s="21"/>
@@ -6631,32 +6631,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J176" s="18" t="n">
-        <x:v>106</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K176" s="18" t="n">
-        <x:v>106</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L176" s="25"/>
       <x:c r="M176" s="26"/>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
       <x:c r="A177" s="11" t="str">
-        <x:v>高中</x:v>
+        <x:v>自拼</x:v>
       </x:c>
       <x:c r="B177" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C177" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D177" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E177" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F177" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G177" s="21"/>
       <x:c r="H177" s="21"/>
@@ -6664,32 +6664,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J177" s="18" t="n">
-        <x:v>681</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K177" s="18" t="n">
-        <x:v>681</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L177" s="25"/>
       <x:c r="M177" s="26"/>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
       <x:c r="A178" s="11" t="str">
-        <x:v>高中</x:v>
+        <x:v>自拼</x:v>
       </x:c>
       <x:c r="B178" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C178" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D178" s="18" t="n">
         <x:v>990</x:v>
       </x:c>
       <x:c r="E178" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F178" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G178" s="21"/>
       <x:c r="H178" s="21"/>
@@ -6697,32 +6697,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J178" s="18" t="n">
-        <x:v>186</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K178" s="18" t="n">
-        <x:v>186</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L178" s="25"/>
       <x:c r="M178" s="26"/>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
       <x:c r="A179" s="11" t="str">
-        <x:v>高中</x:v>
+        <x:v>自拼</x:v>
       </x:c>
       <x:c r="B179" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C179" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D179" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2990</x:v>
       </x:c>
       <x:c r="E179" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F179" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G179" s="21"/>
       <x:c r="H179" s="21"/>
@@ -6730,10 +6730,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J179" s="18" t="n">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K179" s="18" t="n">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L179" s="25"/>
       <x:c r="M179" s="26"/>
@@ -6746,16 +6746,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C180" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D180" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E180" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F180" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G180" s="21"/>
       <x:c r="H180" s="21"/>
@@ -6763,10 +6763,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J180" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K180" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="L180" s="25"/>
       <x:c r="M180" s="26"/>
@@ -6779,16 +6779,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C181" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D181" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E181" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F181" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G181" s="21"/>
       <x:c r="H181" s="21"/>
@@ -6796,10 +6796,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J181" s="18" t="n">
-        <x:v>6</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="K181" s="18" t="n">
-        <x:v>6</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="L181" s="25"/>
       <x:c r="M181" s="26"/>
@@ -6812,13 +6812,13 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C182" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D182" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E182" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F182" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6829,10 +6829,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J182" s="18" t="n">
-        <x:v>358</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K182" s="18" t="n">
-        <x:v>358</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="L182" s="25"/>
       <x:c r="M182" s="26"/>
@@ -6845,13 +6845,13 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C183" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D183" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E183" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F183" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6862,10 +6862,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J183" s="18" t="n">
-        <x:v>291</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K183" s="18" t="n">
-        <x:v>291</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="L183" s="25"/>
       <x:c r="M183" s="26"/>
@@ -6878,16 +6878,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C184" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D184" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E184" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F184" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G184" s="21"/>
       <x:c r="H184" s="21"/>
@@ -6895,10 +6895,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J184" s="18" t="n">
-        <x:v>320</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K184" s="18" t="n">
-        <x:v>320</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="L184" s="25"/>
       <x:c r="M184" s="26"/>
@@ -6911,13 +6911,13 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C185" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D185" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E185" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F185" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -6928,10 +6928,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J185" s="18" t="n">
-        <x:v>697</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="K185" s="18" t="n">
-        <x:v>697</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="L185" s="25"/>
       <x:c r="M185" s="26"/>
@@ -6944,16 +6944,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C186" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D186" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E186" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F186" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G186" s="21"/>
       <x:c r="H186" s="21"/>
@@ -6961,10 +6961,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J186" s="18" t="n">
-        <x:v>960</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="K186" s="18" t="n">
-        <x:v>960</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="L186" s="25"/>
       <x:c r="M186" s="26"/>
@@ -6977,16 +6977,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C187" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D187" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E187" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F187" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G187" s="21"/>
       <x:c r="H187" s="21"/>
@@ -6994,10 +6994,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J187" s="18" t="n">
-        <x:v>633</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="K187" s="18" t="n">
-        <x:v>633</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="L187" s="25"/>
       <x:c r="M187" s="26"/>
@@ -7010,16 +7010,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C188" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D188" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E188" s="12" t="str">
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F188" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G188" s="21"/>
       <x:c r="H188" s="21"/>
@@ -7027,10 +7027,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J188" s="18" t="n">
-        <x:v>434</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K188" s="18" t="n">
-        <x:v>434</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L188" s="25"/>
       <x:c r="M188" s="26"/>
@@ -7043,16 +7043,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C189" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D189" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E189" s="12" t="str">
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F189" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G189" s="21"/>
       <x:c r="H189" s="21"/>
@@ -7060,10 +7060,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J189" s="18" t="n">
-        <x:v>626</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K189" s="18" t="n">
-        <x:v>626</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L189" s="25"/>
       <x:c r="M189" s="26"/>
@@ -7076,16 +7076,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C190" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D190" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E190" s="12" t="str">
         <x:v>高三</x:v>
       </x:c>
       <x:c r="F190" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G190" s="21"/>
       <x:c r="H190" s="21"/>
@@ -7093,10 +7093,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J190" s="18" t="n">
-        <x:v>558</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K190" s="18" t="n">
-        <x:v>558</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L190" s="25"/>
       <x:c r="M190" s="26"/>
@@ -7106,133 +7106,109 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B191" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C191" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D191" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E191" s="12" t="str">
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F191" s="21" t="str">
-        <x:v>2026-06-29</x:v>
-      </x:c>
-      <x:c r="G191" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H191" s="21" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
+      <x:c r="G191" s="21"/>
+      <x:c r="H191" s="21"/>
       <x:c r="I191" s="18" t="n">
-        <x:v>80</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J191" s="18" t="n">
-        <x:v>79</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="K191" s="18" t="n">
-        <x:v>-1</x:v>
-      </x:c>
-      <x:c r="L191" s="25" t="n">
-        <x:v>0.9875</x:v>
-      </x:c>
-      <x:c r="M191" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="L191" s="25"/>
+      <x:c r="M191" s="26"/>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
       <x:c r="A192" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B192" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C192" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D192" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E192" s="12" t="str">
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F192" s="21" t="str">
-        <x:v>2026-06-29</x:v>
-      </x:c>
-      <x:c r="G192" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H192" s="21" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
+      <x:c r="G192" s="21"/>
+      <x:c r="H192" s="21"/>
       <x:c r="I192" s="18" t="n">
-        <x:v>160</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J192" s="18" t="n">
-        <x:v>153</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="K192" s="18" t="n">
-        <x:v>-7</x:v>
-      </x:c>
-      <x:c r="L192" s="25" t="n">
-        <x:v>0.95625</x:v>
-      </x:c>
-      <x:c r="M192" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="L192" s="25"/>
+      <x:c r="M192" s="26"/>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
       <x:c r="A193" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B193" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C193" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D193" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E193" s="12" t="str">
         <x:v>高三</x:v>
       </x:c>
       <x:c r="F193" s="21" t="str">
-        <x:v>2026-06-29</x:v>
-      </x:c>
-      <x:c r="G193" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H193" s="21" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
+      <x:c r="G193" s="21"/>
+      <x:c r="H193" s="21"/>
       <x:c r="I193" s="18" t="n">
-        <x:v>160</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J193" s="18" t="n">
-        <x:v>103</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="K193" s="18" t="n">
-        <x:v>-57</x:v>
-      </x:c>
-      <x:c r="L193" s="25" t="n">
-        <x:v>0.64375</x:v>
-      </x:c>
-      <x:c r="M193" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="L193" s="25"/>
+      <x:c r="M193" s="26"/>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
       <x:c r="A194" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B194" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C194" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D194" s="18" t="n">
         <x:v>100</x:v>
@@ -7241,7 +7217,7 @@
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F194" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G194" s="21"/>
       <x:c r="H194" s="21"/>
@@ -7249,10 +7225,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J194" s="18" t="n">
-        <x:v>10</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="K194" s="18" t="n">
-        <x:v>10</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="L194" s="25"/>
       <x:c r="M194" s="26"/>
@@ -7262,10 +7238,10 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B195" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C195" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D195" s="18" t="n">
         <x:v>100</x:v>
@@ -7274,7 +7250,7 @@
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F195" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G195" s="21"/>
       <x:c r="H195" s="21"/>
@@ -7282,10 +7258,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J195" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="K195" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="L195" s="25"/>
       <x:c r="M195" s="26"/>
@@ -7295,10 +7271,10 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B196" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C196" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D196" s="18" t="n">
         <x:v>100</x:v>
@@ -7307,7 +7283,7 @@
         <x:v>高三</x:v>
       </x:c>
       <x:c r="F196" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G196" s="21"/>
       <x:c r="H196" s="21"/>
@@ -7315,10 +7291,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J196" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="K196" s="18" t="n">
-        <x:v>7</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="L196" s="25"/>
       <x:c r="M196" s="26"/>
@@ -7328,121 +7304,99 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B197" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C197" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D197" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E197" s="12" t="str">
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F197" s="21" t="str">
-        <x:v>2026-06-29</x:v>
-      </x:c>
-      <x:c r="G197" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H197" s="21" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
+      <x:c r="G197" s="21"/>
+      <x:c r="H197" s="21"/>
       <x:c r="I197" s="18" t="n">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J197" s="18" t="n">
-        <x:v>880</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="K197" s="18" t="n">
-        <x:v>830</x:v>
-      </x:c>
-      <x:c r="L197" s="25" t="n">
-        <x:v>17.6</x:v>
-      </x:c>
-      <x:c r="M197" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="L197" s="25"/>
+      <x:c r="M197" s="26"/>
     </x:row>
     <x:row r="198" ht="15" hidden="0" customHeight="1">
       <x:c r="A198" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B198" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C198" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D198" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E198" s="12" t="str">
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F198" s="21" t="str">
-        <x:v>2026-06-28</x:v>
-      </x:c>
-      <x:c r="G198" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H198" s="21" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
+      <x:c r="G198" s="21"/>
+      <x:c r="H198" s="21"/>
       <x:c r="I198" s="18" t="n">
-        <x:v>900</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J198" s="18" t="n">
-        <x:v>223</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="K198" s="18" t="n">
-        <x:v>-677</x:v>
-      </x:c>
-      <x:c r="L198" s="25" t="n">
-        <x:v>0.2477777777777778</x:v>
-      </x:c>
-      <x:c r="M198" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="L198" s="25"/>
+      <x:c r="M198" s="26"/>
     </x:row>
     <x:row r="199" ht="15" hidden="0" customHeight="1">
       <x:c r="A199" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B199" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C199" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D199" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E199" s="12" t="str">
         <x:v>高三</x:v>
       </x:c>
-      <x:c r="F199" s="21"/>
-      <x:c r="G199" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H199" s="21" t="str">
+      <x:c r="F199" s="21" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
+      <x:c r="G199" s="21"/>
+      <x:c r="H199" s="21"/>
       <x:c r="I199" s="18" t="n">
-        <x:v>200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J199" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="K199" s="18" t="n">
-        <x:v>-200</x:v>
-      </x:c>
-      <x:c r="L199" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M199" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="L199" s="25"/>
+      <x:c r="M199" s="26"/>
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
       <x:c r="A200" s="11" t="str">
@@ -7452,15 +7406,17 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C200" s="12" t="str">
-        <x:v>lec内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D200" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E200" s="12" t="str">
         <x:v>高一</x:v>
       </x:c>
-      <x:c r="F200" s="21"/>
+      <x:c r="F200" s="21" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
       <x:c r="G200" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7468,19 +7424,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I200" s="18" t="n">
-        <x:v>150</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J200" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K200" s="18" t="n">
-        <x:v>-150</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L200" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>1.0125</x:v>
       </x:c>
       <x:c r="M200" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
@@ -7491,15 +7447,17 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C201" s="12" t="str">
-        <x:v>lec内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D201" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E201" s="12" t="str">
         <x:v>高二</x:v>
       </x:c>
-      <x:c r="F201" s="21"/>
+      <x:c r="F201" s="21" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
       <x:c r="G201" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7507,19 +7465,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I201" s="18" t="n">
-        <x:v>200</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="J201" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="K201" s="18" t="n">
-        <x:v>-200</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L201" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>1.0625</x:v>
       </x:c>
       <x:c r="M201" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="15" hidden="0" customHeight="1">
@@ -7530,15 +7488,17 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C202" s="12" t="str">
-        <x:v>lec内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D202" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E202" s="12" t="str">
         <x:v>高三</x:v>
       </x:c>
-      <x:c r="F202" s="21"/>
+      <x:c r="F202" s="21" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
       <x:c r="G202" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7546,19 +7506,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I202" s="18" t="n">
-        <x:v>150</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="J202" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="K202" s="18" t="n">
-        <x:v>-150</x:v>
+        <x:v>-42</x:v>
       </x:c>
       <x:c r="L202" s="25" t="n">
-        <x:v>0</x:v>
+        <x:v>0.7375</x:v>
       </x:c>
       <x:c r="M202" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="15" hidden="0" customHeight="1">
@@ -7569,7 +7529,7 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C203" s="12" t="str">
-        <x:v>图书店铺</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D203" s="18" t="n">
         <x:v>100</x:v>
@@ -7578,29 +7538,21 @@
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F203" s="21" t="str">
-        <x:v>2026-06-29</x:v>
-      </x:c>
-      <x:c r="G203" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H203" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G203" s="21"/>
+      <x:c r="H203" s="21"/>
       <x:c r="I203" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J203" s="18" t="n">
-        <x:v>37</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K203" s="18" t="n">
-        <x:v>-63</x:v>
-      </x:c>
-      <x:c r="L203" s="25" t="n">
-        <x:v>0.37</x:v>
-      </x:c>
-      <x:c r="M203" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="L203" s="25"/>
+      <x:c r="M203" s="26"/>
     </x:row>
     <x:row r="204" ht="15" hidden="0" customHeight="1">
       <x:c r="A204" s="11" t="str">
@@ -7610,7 +7562,7 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C204" s="12" t="str">
-        <x:v>图书店铺</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D204" s="18" t="n">
         <x:v>100</x:v>
@@ -7619,29 +7571,21 @@
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F204" s="21" t="str">
-        <x:v>2026-06-29</x:v>
-      </x:c>
-      <x:c r="G204" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H204" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G204" s="21"/>
+      <x:c r="H204" s="21"/>
       <x:c r="I204" s="18" t="n">
-        <x:v>150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J204" s="18" t="n">
-        <x:v>21</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K204" s="18" t="n">
-        <x:v>-129</x:v>
-      </x:c>
-      <x:c r="L204" s="25" t="n">
-        <x:v>0.14</x:v>
-      </x:c>
-      <x:c r="M204" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="L204" s="25"/>
+      <x:c r="M204" s="26"/>
     </x:row>
     <x:row r="205" ht="15" hidden="0" customHeight="1">
       <x:c r="A205" s="11" t="str">
@@ -7651,7 +7595,7 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C205" s="12" t="str">
-        <x:v>图书店铺</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D205" s="18" t="n">
         <x:v>100</x:v>
@@ -7660,29 +7604,21 @@
         <x:v>高三</x:v>
       </x:c>
       <x:c r="F205" s="21" t="str">
-        <x:v>2026-06-29</x:v>
-      </x:c>
-      <x:c r="G205" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H205" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G205" s="21"/>
+      <x:c r="H205" s="21"/>
       <x:c r="I205" s="18" t="n">
-        <x:v>150</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J205" s="18" t="n">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K205" s="18" t="n">
-        <x:v>-139</x:v>
-      </x:c>
-      <x:c r="L205" s="25" t="n">
-        <x:v>0.07333333333333333</x:v>
-      </x:c>
-      <x:c r="M205" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
-      </x:c>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L205" s="25"/>
+      <x:c r="M205" s="26"/>
     </x:row>
     <x:row r="206" ht="15" hidden="0" customHeight="1">
       <x:c r="A206" s="11" t="str">
@@ -7692,10 +7628,10 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C206" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D206" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E206" s="12" t="str">
         <x:v>高一</x:v>
@@ -7710,19 +7646,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I206" s="18" t="n">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J206" s="18" t="n">
-        <x:v>198</x:v>
+        <x:v>880</x:v>
       </x:c>
       <x:c r="K206" s="18" t="n">
-        <x:v>-102</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="L206" s="25" t="n">
-        <x:v>0.66</x:v>
+        <x:v>17.6</x:v>
       </x:c>
       <x:c r="M206" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="15" hidden="0" customHeight="1">
@@ -7733,10 +7669,10 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C207" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D207" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E207" s="12" t="str">
         <x:v>高二</x:v>
@@ -7751,19 +7687,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I207" s="18" t="n">
-        <x:v>530</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="J207" s="18" t="n">
-        <x:v>245</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="K207" s="18" t="n">
-        <x:v>-285</x:v>
+        <x:v>-677</x:v>
       </x:c>
       <x:c r="L207" s="25" t="n">
-        <x:v>0.46226415094339623</x:v>
+        <x:v>0.2477777777777778</x:v>
       </x:c>
       <x:c r="M207" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="15" hidden="0" customHeight="1">
@@ -7774,17 +7710,15 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C208" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D208" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E208" s="12" t="str">
         <x:v>高三</x:v>
       </x:c>
-      <x:c r="F208" s="21" t="str">
-        <x:v>2026-06-28</x:v>
-      </x:c>
+      <x:c r="F208" s="21"/>
       <x:c r="G208" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -7792,19 +7726,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I208" s="18" t="n">
-        <x:v>600</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="J208" s="18" t="n">
-        <x:v>303</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K208" s="18" t="n">
-        <x:v>-297</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="L208" s="25" t="n">
-        <x:v>0.505</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M208" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="15" hidden="0" customHeight="1">
@@ -7815,7 +7749,7 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C209" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>图书店铺</x:v>
       </x:c>
       <x:c r="D209" s="18" t="n">
         <x:v>100</x:v>
@@ -7824,7 +7758,7 @@
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F209" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G209" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7833,19 +7767,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I209" s="18" t="n">
-        <x:v>180</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J209" s="18" t="n">
-        <x:v>236</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="K209" s="18" t="n">
-        <x:v>56</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="L209" s="25" t="n">
-        <x:v>1.3111111111111111</x:v>
+        <x:v>1.29</x:v>
       </x:c>
       <x:c r="M209" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="15" hidden="0" customHeight="1">
@@ -7856,7 +7790,7 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C210" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>图书店铺</x:v>
       </x:c>
       <x:c r="D210" s="18" t="n">
         <x:v>100</x:v>
@@ -7865,7 +7799,7 @@
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F210" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G210" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7874,19 +7808,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I210" s="18" t="n">
-        <x:v>1500</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J210" s="18" t="n">
-        <x:v>696</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K210" s="18" t="n">
-        <x:v>-804</x:v>
+        <x:v>-122</x:v>
       </x:c>
       <x:c r="L210" s="25" t="n">
-        <x:v>0.464</x:v>
+        <x:v>0.18666666666666668</x:v>
       </x:c>
       <x:c r="M210" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="211" ht="15" hidden="0" customHeight="1">
@@ -7897,7 +7831,7 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C211" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>图书店铺</x:v>
       </x:c>
       <x:c r="D211" s="18" t="n">
         <x:v>100</x:v>
@@ -7906,7 +7840,7 @@
         <x:v>高三</x:v>
       </x:c>
       <x:c r="F211" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G211" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -7915,19 +7849,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I211" s="18" t="n">
-        <x:v>870</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J211" s="18" t="n">
-        <x:v>296</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="K211" s="18" t="n">
-        <x:v>-574</x:v>
+        <x:v>-130</x:v>
       </x:c>
       <x:c r="L211" s="25" t="n">
-        <x:v>0.34022988505747126</x:v>
+        <x:v>0.13333333333333333</x:v>
       </x:c>
       <x:c r="M211" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="212" ht="15" hidden="0" customHeight="1">
@@ -7938,30 +7872,36 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C212" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D212" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E212" s="12" t="str">
         <x:v>高一</x:v>
       </x:c>
-      <x:c r="F212" s="21" t="str">
-        <x:v>2026-06-28</x:v>
-      </x:c>
-      <x:c r="G212" s="21"/>
-      <x:c r="H212" s="21"/>
+      <x:c r="F212" s="21"/>
+      <x:c r="G212" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H212" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I212" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J212" s="18" t="n">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K212" s="18" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="L212" s="25"/>
-      <x:c r="M212" s="26"/>
+        <x:v>-150</x:v>
+      </x:c>
+      <x:c r="L212" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M212" s="26" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="213" ht="15" hidden="0" customHeight="1">
       <x:c r="A213" s="11" t="str">
@@ -7971,30 +7911,36 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C213" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D213" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E213" s="12" t="str">
         <x:v>高二</x:v>
       </x:c>
-      <x:c r="F213" s="21" t="str">
-        <x:v>2026-06-28</x:v>
-      </x:c>
-      <x:c r="G213" s="21"/>
-      <x:c r="H213" s="21"/>
+      <x:c r="F213" s="21"/>
+      <x:c r="G213" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H213" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I213" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="J213" s="18" t="n">
-        <x:v>63</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K213" s="18" t="n">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="L213" s="25"/>
-      <x:c r="M213" s="26"/>
+        <x:v>-200</x:v>
+      </x:c>
+      <x:c r="L213" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M213" s="26" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="214" ht="15" hidden="0" customHeight="1">
       <x:c r="A214" s="11" t="str">
@@ -8004,30 +7950,36 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C214" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D214" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E214" s="12" t="str">
         <x:v>高三</x:v>
       </x:c>
-      <x:c r="F214" s="21" t="str">
-        <x:v>2026-06-28</x:v>
-      </x:c>
-      <x:c r="G214" s="21"/>
-      <x:c r="H214" s="21"/>
+      <x:c r="F214" s="21"/>
+      <x:c r="G214" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H214" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I214" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J214" s="18" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K214" s="18" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L214" s="25"/>
-      <x:c r="M214" s="26"/>
+        <x:v>-150</x:v>
+      </x:c>
+      <x:c r="L214" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M214" s="26" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="215" ht="15" hidden="0" customHeight="1">
       <x:c r="A215" s="11" t="str">
@@ -8037,7 +7989,7 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C215" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D215" s="18" t="n">
         <x:v>2880</x:v>
@@ -8045,7 +7997,9 @@
       <x:c r="E215" s="12" t="str">
         <x:v>高一</x:v>
       </x:c>
-      <x:c r="F215" s="21"/>
+      <x:c r="F215" s="21" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
       <x:c r="G215" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -8053,17 +8007,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I215" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J215" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="K215" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L215" s="25"/>
+        <x:v>-2</x:v>
+      </x:c>
+      <x:c r="L215" s="25" t="n">
+        <x:v>0.9933333333333333</x:v>
+      </x:c>
       <x:c r="M215" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="15" hidden="0" customHeight="1">
@@ -8074,7 +8030,7 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C216" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D216" s="18" t="n">
         <x:v>2880</x:v>
@@ -8083,7 +8039,7 @@
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F216" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G216" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -8092,19 +8048,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I216" s="18" t="n">
-        <x:v>700</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="J216" s="18" t="n">
-        <x:v>552</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="K216" s="18" t="n">
-        <x:v>-148</x:v>
+        <x:v>-236</x:v>
       </x:c>
       <x:c r="L216" s="25" t="n">
-        <x:v>0.7885714285714286</x:v>
+        <x:v>0.5547169811320755</x:v>
       </x:c>
       <x:c r="M216" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="15" hidden="0" customHeight="1">
@@ -8115,7 +8071,7 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C217" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D217" s="18" t="n">
         <x:v>2880</x:v>
@@ -8124,7 +8080,7 @@
         <x:v>高三</x:v>
       </x:c>
       <x:c r="F217" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G217" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -8133,19 +8089,19 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I217" s="18" t="n">
-        <x:v>650</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="J217" s="18" t="n">
-        <x:v>531</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="K217" s="18" t="n">
-        <x:v>-119</x:v>
+        <x:v>-215</x:v>
       </x:c>
       <x:c r="L217" s="25" t="n">
-        <x:v>0.816923076923077</x:v>
+        <x:v>0.6416666666666667</x:v>
       </x:c>
       <x:c r="M217" s="26" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="15" hidden="0" customHeight="1">
@@ -8153,118 +8109,142 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B218" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C218" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D218" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E218" s="12" t="str">
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F218" s="21" t="str">
-        <x:v>2026-06-21</x:v>
-      </x:c>
-      <x:c r="G218" s="21"/>
-      <x:c r="H218" s="21"/>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G218" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H218" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I218" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="J218" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="K218" s="18" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="L218" s="25"/>
-      <x:c r="M218" s="26"/>
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="L218" s="25" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="M218" s="26" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="219" ht="15" hidden="0" customHeight="1">
       <x:c r="A219" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B219" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C219" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D219" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E219" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F219" s="21" t="str">
-        <x:v>2026-06-28</x:v>
-      </x:c>
-      <x:c r="G219" s="21"/>
-      <x:c r="H219" s="21"/>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G219" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H219" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I219" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="J219" s="18" t="n">
-        <x:v>6</x:v>
+        <x:v>877</x:v>
       </x:c>
       <x:c r="K219" s="18" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="L219" s="25"/>
-      <x:c r="M219" s="26"/>
+        <x:v>-623</x:v>
+      </x:c>
+      <x:c r="L219" s="25" t="n">
+        <x:v>0.5846666666666667</x:v>
+      </x:c>
+      <x:c r="M219" s="26" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="220" ht="15" hidden="0" customHeight="1">
       <x:c r="A220" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B220" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C220" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D220" s="18" t="n">
-        <x:v>990</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E220" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F220" s="21" t="str">
-        <x:v>2026-06-28</x:v>
-      </x:c>
-      <x:c r="G220" s="21"/>
-      <x:c r="H220" s="21"/>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G220" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H220" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I220" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>870</x:v>
       </x:c>
       <x:c r="J220" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="K220" s="18" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L220" s="25"/>
-      <x:c r="M220" s="26"/>
+        <x:v>-452</x:v>
+      </x:c>
+      <x:c r="L220" s="25" t="n">
+        <x:v>0.4804597701149425</x:v>
+      </x:c>
+      <x:c r="M220" s="26" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="221" ht="15" hidden="0" customHeight="1">
       <x:c r="A221" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B221" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C221" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D221" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E221" s="12" t="str">
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F221" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G221" s="21"/>
       <x:c r="H221" s="21"/>
@@ -8272,10 +8252,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J221" s="18" t="n">
-        <x:v>27</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K221" s="18" t="n">
-        <x:v>27</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L221" s="25"/>
       <x:c r="M221" s="26"/>
@@ -8285,19 +8265,19 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B222" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C222" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D222" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E222" s="12" t="str">
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F222" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G222" s="21"/>
       <x:c r="H222" s="21"/>
@@ -8318,19 +8298,19 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B223" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C223" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D223" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E223" s="12" t="str">
         <x:v>高三</x:v>
       </x:c>
       <x:c r="F223" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G223" s="21"/>
       <x:c r="H223" s="21"/>
@@ -8338,10 +8318,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J223" s="18" t="n">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K223" s="18" t="n">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L223" s="25"/>
       <x:c r="M223" s="26"/>
@@ -8351,106 +8331,126 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B224" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C224" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D224" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E224" s="12" t="str">
         <x:v>高一</x:v>
       </x:c>
-      <x:c r="F224" s="21" t="str">
-        <x:v>2026-06-18</x:v>
-      </x:c>
-      <x:c r="G224" s="21"/>
-      <x:c r="H224" s="21"/>
+      <x:c r="F224" s="21"/>
+      <x:c r="G224" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H224" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I224" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J224" s="18" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K224" s="18" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L224" s="25"/>
-      <x:c r="M224" s="26"/>
+      <x:c r="M224" s="26" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="225" ht="15" hidden="0" customHeight="1">
       <x:c r="A225" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B225" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C225" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D225" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E225" s="12" t="str">
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F225" s="21" t="str">
-        <x:v>2026-06-18</x:v>
-      </x:c>
-      <x:c r="G225" s="21"/>
-      <x:c r="H225" s="21"/>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G225" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H225" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I225" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="J225" s="18" t="n">
-        <x:v>4</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="K225" s="18" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="L225" s="25"/>
-      <x:c r="M225" s="26"/>
+        <x:v>-53</x:v>
+      </x:c>
+      <x:c r="L225" s="25" t="n">
+        <x:v>0.9242857142857143</x:v>
+      </x:c>
+      <x:c r="M225" s="26" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="226" ht="15" hidden="0" customHeight="1">
       <x:c r="A226" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B226" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C226" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D226" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="E226" s="12" t="str">
         <x:v>高三</x:v>
       </x:c>
       <x:c r="F226" s="21" t="str">
-        <x:v>2026-06-17</x:v>
-      </x:c>
-      <x:c r="G226" s="21"/>
-      <x:c r="H226" s="21"/>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G226" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H226" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I226" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="J226" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="K226" s="18" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="L226" s="25"/>
-      <x:c r="M226" s="26"/>
+        <x:v>-36</x:v>
+      </x:c>
+      <x:c r="L226" s="25" t="n">
+        <x:v>0.9446153846153846</x:v>
+      </x:c>
+      <x:c r="M226" s="26" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="227" ht="15" hidden="0" customHeight="1">
       <x:c r="A227" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B227" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C227" s="12" t="str">
         <x:v>LLM外呼</x:v>
@@ -8462,7 +8462,7 @@
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F227" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G227" s="21"/>
       <x:c r="H227" s="21"/>
@@ -8483,7 +8483,7 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B228" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C228" s="12" t="str">
         <x:v>LLM外呼</x:v>
@@ -8492,10 +8492,10 @@
         <x:v>990</x:v>
       </x:c>
       <x:c r="E228" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F228" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G228" s="21"/>
       <x:c r="H228" s="21"/>
@@ -8503,10 +8503,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J228" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K228" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L228" s="25"/>
       <x:c r="M228" s="26"/>
@@ -8516,19 +8516,19 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B229" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C229" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D229" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E229" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F229" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G229" s="21"/>
       <x:c r="H229" s="21"/>
@@ -8536,10 +8536,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J229" s="18" t="n">
-        <x:v>146</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K229" s="18" t="n">
-        <x:v>146</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L229" s="25"/>
       <x:c r="M229" s="26"/>
@@ -8552,13 +8552,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C230" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D230" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E230" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F230" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8569,10 +8569,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J230" s="18" t="n">
-        <x:v>157</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K230" s="18" t="n">
-        <x:v>157</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L230" s="25"/>
       <x:c r="M230" s="26"/>
@@ -8585,13 +8585,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C231" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D231" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E231" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F231" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8602,10 +8602,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J231" s="18" t="n">
-        <x:v>136</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K231" s="18" t="n">
-        <x:v>136</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L231" s="25"/>
       <x:c r="M231" s="26"/>
@@ -8618,13 +8618,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C232" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D232" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E232" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F232" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8635,10 +8635,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J232" s="18" t="n">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K232" s="18" t="n">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L232" s="25"/>
       <x:c r="M232" s="26"/>
@@ -8651,16 +8651,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C233" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D233" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E233" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F233" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G233" s="21"/>
       <x:c r="H233" s="21"/>
@@ -8668,10 +8668,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J233" s="18" t="n">
-        <x:v>17</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K233" s="18" t="n">
-        <x:v>17</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L233" s="25"/>
       <x:c r="M233" s="26"/>
@@ -8684,13 +8684,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C234" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D234" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E234" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F234" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8701,10 +8701,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J234" s="18" t="n">
-        <x:v>30</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K234" s="18" t="n">
-        <x:v>30</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L234" s="25"/>
       <x:c r="M234" s="26"/>
@@ -8717,16 +8717,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C235" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D235" s="18" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="E235" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F235" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G235" s="21"/>
       <x:c r="H235" s="21"/>
@@ -8734,10 +8734,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J235" s="18" t="n">
-        <x:v>136</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K235" s="18" t="n">
-        <x:v>136</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L235" s="25"/>
       <x:c r="M235" s="26"/>
@@ -8750,16 +8750,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C236" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D236" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E236" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F236" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G236" s="21"/>
       <x:c r="H236" s="21"/>
@@ -8767,10 +8767,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J236" s="18" t="n">
-        <x:v>293</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K236" s="18" t="n">
-        <x:v>293</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L236" s="25"/>
       <x:c r="M236" s="26"/>
@@ -8783,13 +8783,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C237" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D237" s="18" t="n">
-        <x:v>100</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="E237" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F237" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -8800,10 +8800,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J237" s="18" t="n">
-        <x:v>167</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K237" s="18" t="n">
-        <x:v>167</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L237" s="25"/>
       <x:c r="M237" s="26"/>
@@ -8816,10 +8816,10 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C238" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D238" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E238" s="12" t="str">
         <x:v>高一</x:v>
@@ -8833,10 +8833,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J238" s="18" t="n">
-        <x:v>92</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="K238" s="18" t="n">
-        <x:v>92</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="L238" s="25"/>
       <x:c r="M238" s="26"/>
@@ -8849,10 +8849,10 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C239" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D239" s="18" t="n">
-        <x:v>2880</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E239" s="12" t="str">
         <x:v>高二</x:v>
@@ -8866,46 +8866,343 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J239" s="18" t="n">
-        <x:v>65</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="K239" s="18" t="n">
-        <x:v>65</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="L239" s="25"/>
       <x:c r="M239" s="26"/>
     </x:row>
     <x:row r="240" ht="15" hidden="0" customHeight="1">
-      <x:c r="A240" s="14" t="str">
+      <x:c r="A240" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
-      <x:c r="B240" s="15" t="str">
+      <x:c r="B240" s="12" t="str">
         <x:v>暑_9</x:v>
       </x:c>
-      <x:c r="C240" s="15" t="str">
+      <x:c r="C240" s="12" t="str">
+        <x:v>外部微转-*</x:v>
+      </x:c>
+      <x:c r="D240" s="18" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E240" s="12" t="str">
+        <x:v>高三</x:v>
+      </x:c>
+      <x:c r="F240" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G240" s="21"/>
+      <x:c r="H240" s="21"/>
+      <x:c r="I240" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J240" s="18" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="K240" s="18" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="L240" s="25"/>
+      <x:c r="M240" s="26"/>
+    </x:row>
+    <x:row r="241" ht="15" hidden="0" customHeight="1">
+      <x:c r="A241" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B241" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C241" s="12" t="str">
+        <x:v>外部微转-*</x:v>
+      </x:c>
+      <x:c r="D241" s="18" t="n">
+        <x:v>2880</x:v>
+      </x:c>
+      <x:c r="E241" s="12" t="str">
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F241" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G241" s="21"/>
+      <x:c r="H241" s="21"/>
+      <x:c r="I241" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J241" s="18" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="K241" s="18" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="L241" s="25"/>
+      <x:c r="M241" s="26"/>
+    </x:row>
+    <x:row r="242" ht="15" hidden="0" customHeight="1">
+      <x:c r="A242" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B242" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C242" s="12" t="str">
+        <x:v>外部微转-*</x:v>
+      </x:c>
+      <x:c r="D242" s="18" t="n">
+        <x:v>2880</x:v>
+      </x:c>
+      <x:c r="E242" s="12" t="str">
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F242" s="21" t="str">
+        <x:v>2026-06-17</x:v>
+      </x:c>
+      <x:c r="G242" s="21"/>
+      <x:c r="H242" s="21"/>
+      <x:c r="I242" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J242" s="18" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K242" s="18" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="L242" s="25"/>
+      <x:c r="M242" s="26"/>
+    </x:row>
+    <x:row r="243" ht="15" hidden="0" customHeight="1">
+      <x:c r="A243" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B243" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C243" s="12" t="str">
+        <x:v>外部微转-*</x:v>
+      </x:c>
+      <x:c r="D243" s="18" t="n">
+        <x:v>2880</x:v>
+      </x:c>
+      <x:c r="E243" s="12" t="str">
+        <x:v>高三</x:v>
+      </x:c>
+      <x:c r="F243" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G243" s="21"/>
+      <x:c r="H243" s="21"/>
+      <x:c r="I243" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J243" s="18" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K243" s="18" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L243" s="25"/>
+      <x:c r="M243" s="26"/>
+    </x:row>
+    <x:row r="244" ht="15" hidden="0" customHeight="1">
+      <x:c r="A244" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B244" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C244" s="12" t="str">
         <x:v>常规外呼</x:v>
       </x:c>
-      <x:c r="D240" s="19" t="n">
+      <x:c r="D244" s="18" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E244" s="12" t="str">
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F244" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G244" s="21"/>
+      <x:c r="H244" s="21"/>
+      <x:c r="I244" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J244" s="18" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="K244" s="18" t="n">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="L244" s="25"/>
+      <x:c r="M244" s="26"/>
+    </x:row>
+    <x:row r="245" ht="15" hidden="0" customHeight="1">
+      <x:c r="A245" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B245" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C245" s="12" t="str">
+        <x:v>常规外呼</x:v>
+      </x:c>
+      <x:c r="D245" s="18" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E245" s="12" t="str">
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F245" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G245" s="21"/>
+      <x:c r="H245" s="21"/>
+      <x:c r="I245" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J245" s="18" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="K245" s="18" t="n">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="L245" s="25"/>
+      <x:c r="M245" s="26"/>
+    </x:row>
+    <x:row r="246" ht="15" hidden="0" customHeight="1">
+      <x:c r="A246" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B246" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C246" s="12" t="str">
+        <x:v>常规外呼</x:v>
+      </x:c>
+      <x:c r="D246" s="18" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E246" s="12" t="str">
+        <x:v>高三</x:v>
+      </x:c>
+      <x:c r="F246" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G246" s="21"/>
+      <x:c r="H246" s="21"/>
+      <x:c r="I246" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J246" s="18" t="n">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="K246" s="18" t="n">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="L246" s="25"/>
+      <x:c r="M246" s="26"/>
+    </x:row>
+    <x:row r="247" ht="15" hidden="0" customHeight="1">
+      <x:c r="A247" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B247" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C247" s="12" t="str">
+        <x:v>常规外呼</x:v>
+      </x:c>
+      <x:c r="D247" s="18" t="n">
         <x:v>2880</x:v>
       </x:c>
-      <x:c r="E240" s="15" t="str">
+      <x:c r="E247" s="12" t="str">
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F247" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G247" s="21"/>
+      <x:c r="H247" s="21"/>
+      <x:c r="I247" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J247" s="18" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="K247" s="18" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="L247" s="25"/>
+      <x:c r="M247" s="26"/>
+    </x:row>
+    <x:row r="248" ht="15" hidden="0" customHeight="1">
+      <x:c r="A248" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B248" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C248" s="12" t="str">
+        <x:v>常规外呼</x:v>
+      </x:c>
+      <x:c r="D248" s="18" t="n">
+        <x:v>2880</x:v>
+      </x:c>
+      <x:c r="E248" s="12" t="str">
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F248" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G248" s="21"/>
+      <x:c r="H248" s="21"/>
+      <x:c r="I248" s="18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J248" s="18" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="K248" s="18" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L248" s="25"/>
+      <x:c r="M248" s="26"/>
+    </x:row>
+    <x:row r="249" ht="15" hidden="0" customHeight="1">
+      <x:c r="A249" s="14" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B249" s="15" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C249" s="15" t="str">
+        <x:v>常规外呼</x:v>
+      </x:c>
+      <x:c r="D249" s="19" t="n">
+        <x:v>2880</x:v>
+      </x:c>
+      <x:c r="E249" s="15" t="str">
         <x:v>高三</x:v>
       </x:c>
-      <x:c r="F240" s="22" t="str">
+      <x:c r="F249" s="22" t="str">
         <x:v>2026-06-18</x:v>
       </x:c>
-      <x:c r="G240" s="22"/>
-      <x:c r="H240" s="22"/>
-      <x:c r="I240" s="19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J240" s="19" t="n">
+      <x:c r="G249" s="22"/>
+      <x:c r="H249" s="22"/>
+      <x:c r="I249" s="19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J249" s="19" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="K240" s="19" t="n">
+      <x:c r="K249" s="19" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="L240" s="27"/>
-      <x:c r="M240" s="28"/>
+      <x:c r="L249" s="27"/>
+      <x:c r="M249" s="28"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -8945,7 +9242,7 @@
         <x:v>现状原始行数</x:v>
       </x:c>
       <x:c r="B3" s="10" t="n">
-        <x:v>51755</x:v>
+        <x:v>55938</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -8961,7 +9258,7 @@
         <x:v>聚合组合数</x:v>
       </x:c>
       <x:c r="B5" s="13" t="n">
-        <x:v>238</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -8977,7 +9274,7 @@
         <x:v>现状合计</x:v>
       </x:c>
       <x:c r="B7" s="13" t="n">
-        <x:v>51755</x:v>
+        <x:v>55938</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -8985,7 +9282,7 @@
         <x:v>完成率整体</x:v>
       </x:c>
       <x:c r="B8" s="13" t="n">
-        <x:v>1.7766906968760727</x:v>
+        <x:v>1.9202883625128733</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -9025,7 +9322,7 @@
         <x:v>最新期次现状合计</x:v>
       </x:c>
       <x:c r="B13" s="13" t="n">
-        <x:v>23353</x:v>
+        <x:v>27187</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -9033,7 +9330,7 @@
         <x:v>最新期次完成率整体</x:v>
       </x:c>
       <x:c r="B14" s="13" t="n">
-        <x:v>0.8016821146584278</x:v>
+        <x:v>0.9332990044627532</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -9097,7 +9394,7 @@
         <x:v>播报图剩余天数</x:v>
       </x:c>
       <x:c r="B22" s="13" t="str">
-        <x:v>总天数-(target_time-进量日期)</x:v>
+        <x:v>总天数-(target_time-进量日期-1)</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -9162,7 +9459,7 @@
         <x:v>12100</x:v>
       </x:c>
       <x:c r="C31" s="10" t="n">
-        <x:v>10327</x:v>
+        <x:v>11895</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -9173,7 +9470,7 @@
         <x:v>9250</x:v>
       </x:c>
       <x:c r="C32" s="13" t="n">
-        <x:v>8360</x:v>
+        <x:v>9674</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
@@ -9184,7 +9481,7 @@
         <x:v>7780</x:v>
       </x:c>
       <x:c r="C33" s="16" t="n">
-        <x:v>4666</x:v>
+        <x:v>5618</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="16.799999237060547" hidden="0" customHeight="1">
@@ -9217,7 +9514,7 @@
         <x:v>12100</x:v>
       </x:c>
       <x:c r="C38" s="10" t="n">
-        <x:v>10327</x:v>
+        <x:v>11895</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
@@ -9228,7 +9525,7 @@
         <x:v>9250</x:v>
       </x:c>
       <x:c r="C39" s="13" t="n">
-        <x:v>8360</x:v>
+        <x:v>9674</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15" hidden="0" customHeight="1">
@@ -9239,7 +9536,7 @@
         <x:v>7780</x:v>
       </x:c>
       <x:c r="C40" s="16" t="n">
-        <x:v>4666</x:v>
+        <x:v>5618</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="16.799999237060547" hidden="0" customHeight="1">
@@ -9272,7 +9569,7 @@
         <x:v>13020</x:v>
       </x:c>
       <x:c r="C45" s="10" t="n">
-        <x:v>11216</x:v>
+        <x:v>12777</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="15" hidden="0" customHeight="1">
@@ -9283,7 +9580,7 @@
         <x:v>8380</x:v>
       </x:c>
       <x:c r="C46" s="13" t="n">
-        <x:v>5894</x:v>
+        <x:v>7097</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -9294,7 +9591,7 @@
         <x:v>3350</x:v>
       </x:c>
       <x:c r="C47" s="13" t="n">
-        <x:v>3093</x:v>
+        <x:v>3474</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15" hidden="0" customHeight="1">
@@ -9302,10 +9599,10 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="B48" s="12" t="n">
-        <x:v>2280</x:v>
+        <x:v>2780</x:v>
       </x:c>
       <x:c r="C48" s="13" t="n">
-        <x:v>2269</x:v>
+        <x:v>2729</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15" hidden="0" customHeight="1">
@@ -9316,183 +9613,183 @@
         <x:v>1200</x:v>
       </x:c>
       <x:c r="C49" s="13" t="n">
-        <x:v>812</x:v>
+        <x:v>933</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
-      <x:c r="A50" s="11" t="str">
+      <x:c r="A50" s="14" t="str">
         <x:v>图书店铺</x:v>
       </x:c>
-      <x:c r="B50" s="12" t="n">
+      <x:c r="B50" s="15" t="n">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="C50" s="13" t="n">
-        <x:v>69</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" ht="15" hidden="0" customHeight="1">
-      <x:c r="A51" s="14" t="str">
-        <x:v>lec内测</x:v>
-      </x:c>
-      <x:c r="B51" s="15" t="n">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="C51" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" ht="16.799999237060547" hidden="0" customHeight="1">
-      <x:c r="A54" s="4" t="str">
+      <x:c r="C50" s="16" t="n">
+        <x:v>177</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A53" s="4" t="str">
         <x:v>维度分布 - 价体</x:v>
       </x:c>
-      <x:c r="B54" s="4" t="str">
+      <x:c r="B53" s="4" t="str">
         <x:v>维度分布 - 价体</x:v>
       </x:c>
-      <x:c r="C54" s="4" t="str">
+      <x:c r="C53" s="4" t="str">
         <x:v>维度分布 - 价体</x:v>
       </x:c>
     </x:row>
+    <x:row r="54" ht="15" hidden="0" customHeight="1">
+      <x:c r="A54" s="7" t="str">
+        <x:v>价体</x:v>
+      </x:c>
+      <x:c r="B54" s="7" t="str">
+        <x:v>目标</x:v>
+      </x:c>
+      <x:c r="C54" s="7" t="str">
+        <x:v>现状</x:v>
+      </x:c>
+    </x:row>
     <x:row r="55" ht="15" hidden="0" customHeight="1">
-      <x:c r="A55" s="7" t="str">
-        <x:v>价体</x:v>
-      </x:c>
-      <x:c r="B55" s="7" t="str">
-        <x:v>目标</x:v>
-      </x:c>
-      <x:c r="C55" s="7" t="str">
-        <x:v>现状</x:v>
+      <x:c r="A55" s="8" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B55" s="9" t="n">
+        <x:v>14850</x:v>
+      </x:c>
+      <x:c r="C55" s="10" t="n">
+        <x:v>13762</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15" hidden="0" customHeight="1">
-      <x:c r="A56" s="8" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="B56" s="9" t="n">
-        <x:v>14850</x:v>
-      </x:c>
-      <x:c r="C56" s="10" t="n">
-        <x:v>11908</x:v>
+      <x:c r="A56" s="11" t="n">
+        <x:v>990</x:v>
+      </x:c>
+      <x:c r="B56" s="12" t="n">
+        <x:v>6710</x:v>
+      </x:c>
+      <x:c r="C56" s="13" t="n">
+        <x:v>7709</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="15" hidden="0" customHeight="1">
       <x:c r="A57" s="11" t="n">
-        <x:v>990</x:v>
+        <x:v>2880</x:v>
       </x:c>
       <x:c r="B57" s="12" t="n">
-        <x:v>6710</x:v>
+        <x:v>6370</x:v>
       </x:c>
       <x:c r="C57" s="13" t="n">
-        <x:v>6760</x:v>
+        <x:v>4782</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15" hidden="0" customHeight="1">
       <x:c r="A58" s="11" t="n">
-        <x:v>2880</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B58" s="12" t="n">
-        <x:v>6370</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="C58" s="13" t="n">
-        <x:v>3872</x:v>
+        <x:v>933</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15" hidden="0" customHeight="1">
-      <x:c r="A59" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B59" s="12" t="n">
-        <x:v>1200</x:v>
-      </x:c>
-      <x:c r="C59" s="13" t="n">
-        <x:v>812</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" ht="15" hidden="0" customHeight="1">
-      <x:c r="A60" s="14" t="n">
+      <x:c r="A59" s="14" t="n">
         <x:v>1880</x:v>
       </x:c>
-      <x:c r="B60" s="15" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C60" s="16" t="n">
+      <x:c r="B59" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C59" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="16.799999237060547" hidden="0" customHeight="1">
-      <x:c r="A63" s="4" t="str">
+    <x:row r="62" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A62" s="4" t="str">
         <x:v>维度分布 - 年级</x:v>
       </x:c>
-      <x:c r="B63" s="4" t="str">
+      <x:c r="B62" s="4" t="str">
         <x:v>维度分布 - 年级</x:v>
       </x:c>
-      <x:c r="C63" s="4" t="str">
+      <x:c r="C62" s="4" t="str">
         <x:v>维度分布 - 年级</x:v>
       </x:c>
     </x:row>
+    <x:row r="63" ht="15" hidden="0" customHeight="1">
+      <x:c r="A63" s="7" t="str">
+        <x:v>年级</x:v>
+      </x:c>
+      <x:c r="B63" s="7" t="str">
+        <x:v>目标</x:v>
+      </x:c>
+      <x:c r="C63" s="7" t="str">
+        <x:v>现状</x:v>
+      </x:c>
+    </x:row>
     <x:row r="64" ht="15" hidden="0" customHeight="1">
-      <x:c r="A64" s="7" t="str">
-        <x:v>年级</x:v>
-      </x:c>
-      <x:c r="B64" s="7" t="str">
-        <x:v>目标</x:v>
-      </x:c>
-      <x:c r="C64" s="7" t="str">
-        <x:v>现状</x:v>
+      <x:c r="A64" s="8" t="str">
+        <x:v>初二</x:v>
+      </x:c>
+      <x:c r="B64" s="9" t="n">
+        <x:v>3780</x:v>
+      </x:c>
+      <x:c r="C64" s="10" t="n">
+        <x:v>3875</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="15" hidden="0" customHeight="1">
-      <x:c r="A65" s="8" t="str">
-        <x:v>初二</x:v>
-      </x:c>
-      <x:c r="B65" s="9" t="n">
-        <x:v>3780</x:v>
-      </x:c>
-      <x:c r="C65" s="10" t="n">
-        <x:v>3270</x:v>
+      <x:c r="A65" s="11" t="str">
+        <x:v>四年级</x:v>
+      </x:c>
+      <x:c r="B65" s="12" t="n">
+        <x:v>3400</x:v>
+      </x:c>
+      <x:c r="C65" s="13" t="n">
+        <x:v>3319</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="15" hidden="0" customHeight="1">
       <x:c r="A66" s="11" t="str">
-        <x:v>四年级</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="B66" s="12" t="n">
-        <x:v>3400</x:v>
+        <x:v>3740</x:v>
       </x:c>
       <x:c r="C66" s="13" t="n">
-        <x:v>2905</x:v>
+        <x:v>2970</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
       <x:c r="A67" s="11" t="str">
-        <x:v>初一</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="B67" s="12" t="n">
-        <x:v>1730</x:v>
+        <x:v>2780</x:v>
       </x:c>
       <x:c r="C67" s="13" t="n">
-        <x:v>2606</x:v>
+        <x:v>2898</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
       <x:c r="A68" s="11" t="str">
-        <x:v>三年级</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="B68" s="12" t="n">
-        <x:v>2780</x:v>
+        <x:v>1730</x:v>
       </x:c>
       <x:c r="C68" s="13" t="n">
-        <x:v>2551</x:v>
+        <x:v>2829</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
       <x:c r="A69" s="11" t="str">
-        <x:v>初三</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="B69" s="12" t="n">
-        <x:v>3740</x:v>
+        <x:v>3100</x:v>
       </x:c>
       <x:c r="C69" s="13" t="n">
-        <x:v>2484</x:v>
+        <x:v>2806</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -9503,62 +9800,51 @@
         <x:v>2720</x:v>
       </x:c>
       <x:c r="C70" s="13" t="n">
-        <x:v>2382</x:v>
+        <x:v>2684</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
       <x:c r="A71" s="11" t="str">
-        <x:v>六年级</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="B71" s="12" t="n">
-        <x:v>3100</x:v>
+        <x:v>4140</x:v>
       </x:c>
       <x:c r="C71" s="13" t="n">
-        <x:v>2331</x:v>
+        <x:v>2341</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
       <x:c r="A72" s="11" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="B72" s="12" t="n">
-        <x:v>4140</x:v>
+        <x:v>860</x:v>
       </x:c>
       <x:c r="C72" s="13" t="n">
-        <x:v>1960</x:v>
+        <x:v>1697</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
       <x:c r="A73" s="11" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="B73" s="12" t="n">
-        <x:v>860</x:v>
+        <x:v>2780</x:v>
       </x:c>
       <x:c r="C73" s="13" t="n">
-        <x:v>1445</x:v>
+        <x:v>1580</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
-      <x:c r="A74" s="11" t="str">
-        <x:v>高三</x:v>
-      </x:c>
-      <x:c r="B74" s="12" t="n">
-        <x:v>2780</x:v>
-      </x:c>
-      <x:c r="C74" s="13" t="n">
-        <x:v>1261</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" ht="15" hidden="0" customHeight="1">
-      <x:c r="A75" s="14" t="str">
+      <x:c r="A74" s="14" t="str">
         <x:v>二年级</x:v>
       </x:c>
-      <x:c r="B75" s="15" t="n">
+      <x:c r="B74" s="15" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C75" s="16" t="n">
-        <x:v>158</x:v>
+      <x:c r="C74" s="16" t="n">
+        <x:v>188</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9567,8 +9853,8 @@
     <x:mergeCell ref="A29:C29"/>
     <x:mergeCell ref="A36:C36"/>
     <x:mergeCell ref="A43:C43"/>
-    <x:mergeCell ref="A54:C54"/>
-    <x:mergeCell ref="A63:C63"/>
+    <x:mergeCell ref="A53:C53"/>
+    <x:mergeCell ref="A62:C62"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/outputs/tongji_summary/tongji_summary_current.xlsx
+++ b/outputs/tongji_summary/tongji_summary_current.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目标现状对比" sheetId="1" r:id="R951c52876f7c45be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据概览" sheetId="2" r:id="R42279697e05c4cc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计算规则" sheetId="3" r:id="Rfecf7c5ade644816"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目标现状对比" sheetId="1" r:id="R431d832819c8493c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据概览" sheetId="2" r:id="Refbf93d1306241a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计算规则" sheetId="3" r:id="R8c8f824bded64bb9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1469,7 +1469,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F26" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-04</x:v>
       </x:c>
       <x:c r="G26" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -1481,16 +1481,16 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="J26" s="24" t="n">
-        <x:v>54</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K26" s="24" t="n">
-        <x:v>-76</x:v>
+        <x:v>-64</x:v>
       </x:c>
       <x:c r="L26" s="28" t="n">
-        <x:v>0.4153846153846154</x:v>
+        <x:v>0.5076923076923077</x:v>
       </x:c>
       <x:c r="M26" s="29" t="n">
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -1510,7 +1510,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F27" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G27" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -1522,16 +1522,16 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="J27" s="24" t="n">
-        <x:v>77</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="K27" s="24" t="n">
-        <x:v>-43</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="L27" s="28" t="n">
-        <x:v>0.6416666666666667</x:v>
+        <x:v>1.8333333333333333</x:v>
       </x:c>
       <x:c r="M27" s="29" t="n">
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -1551,7 +1551,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F28" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G28" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -1563,16 +1563,16 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="J28" s="24" t="n">
-        <x:v>96</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="K28" s="24" t="n">
-        <x:v>-34</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L28" s="28" t="n">
-        <x:v>0.7384615384615385</x:v>
+        <x:v>1.3846153846153846</x:v>
       </x:c>
       <x:c r="M28" s="29" t="n">
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
@@ -1646,7 +1646,7 @@
         <x:v>1.01625</x:v>
       </x:c>
       <x:c r="M30" s="29" t="n">
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
@@ -1666,7 +1666,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F31" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G31" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -1678,16 +1678,16 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="J31" s="24" t="n">
-        <x:v>562</x:v>
+        <x:v>948</x:v>
       </x:c>
       <x:c r="K31" s="24" t="n">
-        <x:v>-438</x:v>
+        <x:v>-52</x:v>
       </x:c>
       <x:c r="L31" s="28" t="n">
-        <x:v>0.562</x:v>
+        <x:v>0.948</x:v>
       </x:c>
       <x:c r="M31" s="29" t="n">
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
@@ -1707,7 +1707,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F32" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G32" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -1719,16 +1719,16 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="J32" s="24" t="n">
-        <x:v>516</x:v>
+        <x:v>908</x:v>
       </x:c>
       <x:c r="K32" s="24" t="n">
-        <x:v>-484</x:v>
+        <x:v>-92</x:v>
       </x:c>
       <x:c r="L32" s="28" t="n">
-        <x:v>0.516</x:v>
+        <x:v>0.908</x:v>
       </x:c>
       <x:c r="M32" s="29" t="n">
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
@@ -1748,7 +1748,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F33" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G33" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -1760,16 +1760,16 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J33" s="24" t="n">
-        <x:v>475</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="K33" s="24" t="n">
-        <x:v>375</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="L33" s="28" t="n">
-        <x:v>4.75</x:v>
+        <x:v>4.79</x:v>
       </x:c>
       <x:c r="M33" s="29" t="n">
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
@@ -1789,7 +1789,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F34" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G34" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -1801,16 +1801,16 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="J34" s="24" t="n">
-        <x:v>427</x:v>
+        <x:v>846</x:v>
       </x:c>
       <x:c r="K34" s="24" t="n">
-        <x:v>-273</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="L34" s="28" t="n">
-        <x:v>0.61</x:v>
+        <x:v>1.2085714285714286</x:v>
       </x:c>
       <x:c r="M34" s="29" t="n">
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="15" hidden="0" customHeight="1">
@@ -1830,7 +1830,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F35" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G35" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -1842,16 +1842,16 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="J35" s="24" t="n">
-        <x:v>13</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="K35" s="24" t="n">
-        <x:v>-687</x:v>
+        <x:v>-186</x:v>
       </x:c>
       <x:c r="L35" s="28" t="n">
-        <x:v>0.018571428571428572</x:v>
+        <x:v>0.7342857142857143</x:v>
       </x:c>
       <x:c r="M35" s="29" t="n">
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="15" hidden="0" customHeight="1">
@@ -1892,7 +1892,7 @@
         <x:v>0.9409090909090909</x:v>
       </x:c>
       <x:c r="M36" s="29" t="n">
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="15" hidden="0" customHeight="1">
@@ -1912,7 +1912,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F37" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G37" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -1924,16 +1924,16 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="J37" s="24" t="n">
-        <x:v>195</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="K37" s="24" t="n">
-        <x:v>-155</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L37" s="28" t="n">
-        <x:v>0.5571428571428572</x:v>
+        <x:v>1.04</x:v>
       </x:c>
       <x:c r="M37" s="29" t="n">
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15" hidden="0" customHeight="1">
@@ -1953,7 +1953,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F38" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G38" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -1965,16 +1965,16 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J38" s="24" t="n">
-        <x:v>218</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="K38" s="24" t="n">
-        <x:v>-82</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="L38" s="28" t="n">
-        <x:v>0.7266666666666667</x:v>
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="M38" s="29" t="n">
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="15" hidden="0" customHeight="1">
@@ -1994,7 +1994,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F39" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-04</x:v>
       </x:c>
       <x:c r="G39" s="21"/>
       <x:c r="H39" s="21"/>
@@ -2002,10 +2002,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J39" s="24" t="n">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="K39" s="24" t="n">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="L39" s="28"/>
       <x:c r="M39" s="29"/>
@@ -2027,7 +2027,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F40" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G40" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -2039,16 +2039,16 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="J40" s="24" t="n">
-        <x:v>453</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="K40" s="24" t="n">
-        <x:v>-197</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L40" s="28" t="n">
-        <x:v>0.696923076923077</x:v>
+        <x:v>1.0015384615384615</x:v>
       </x:c>
       <x:c r="M40" s="29" t="n">
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="15" hidden="0" customHeight="1">
@@ -2068,7 +2068,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F41" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="G41" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -2080,16 +2080,16 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="J41" s="24" t="n">
-        <x:v>442</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="K41" s="24" t="n">
-        <x:v>-208</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L41" s="28" t="n">
-        <x:v>0.68</x:v>
+        <x:v>1.0461538461538462</x:v>
       </x:c>
       <x:c r="M41" s="29" t="n">
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
@@ -2109,7 +2109,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F42" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="G42" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -2121,16 +2121,16 @@
         <x:v>750</x:v>
       </x:c>
       <x:c r="J42" s="24" t="n">
-        <x:v>537</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="K42" s="24" t="n">
-        <x:v>-213</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L42" s="28" t="n">
-        <x:v>0.716</x:v>
+        <x:v>1.0026666666666666</x:v>
       </x:c>
       <x:c r="M42" s="29" t="n">
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="15" hidden="0" customHeight="1">
@@ -2150,7 +2150,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F43" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G43" s="21"/>
       <x:c r="H43" s="21"/>
@@ -2158,10 +2158,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J43" s="24" t="n">
-        <x:v>86</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="K43" s="24" t="n">
-        <x:v>86</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="L43" s="28"/>
       <x:c r="M43" s="29"/>
@@ -2183,7 +2183,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F44" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G44" s="21"/>
       <x:c r="H44" s="21"/>
@@ -2191,10 +2191,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J44" s="24" t="n">
-        <x:v>64</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="K44" s="24" t="n">
-        <x:v>64</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="L44" s="28"/>
       <x:c r="M44" s="29"/>
@@ -2216,7 +2216,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F45" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G45" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -2228,16 +2228,16 @@
         <x:v>900</x:v>
       </x:c>
       <x:c r="J45" s="24" t="n">
-        <x:v>328</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="K45" s="24" t="n">
-        <x:v>-572</x:v>
+        <x:v>-299</x:v>
       </x:c>
       <x:c r="L45" s="28" t="n">
-        <x:v>0.36444444444444446</x:v>
+        <x:v>0.6677777777777778</x:v>
       </x:c>
       <x:c r="M45" s="29" t="n">
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="15" hidden="0" customHeight="1">
@@ -2257,7 +2257,7 @@
         <x:v>初三</x:v>
       </x:c>
       <x:c r="F46" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G46" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -2269,16 +2269,16 @@
         <x:v>950</x:v>
       </x:c>
       <x:c r="J46" s="24" t="n">
-        <x:v>375</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="K46" s="24" t="n">
-        <x:v>-575</x:v>
+        <x:v>-316</x:v>
       </x:c>
       <x:c r="L46" s="28" t="n">
-        <x:v>0.39473684210526316</x:v>
+        <x:v>0.6673684210526316</x:v>
       </x:c>
       <x:c r="M46" s="29" t="n">
-        <x:v>0.5</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15" hidden="0" customHeight="1">
@@ -2331,7 +2331,7 @@
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F48" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="G48" s="21"/>
       <x:c r="H48" s="21"/>
@@ -2339,10 +2339,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J48" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K48" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L48" s="28"/>
       <x:c r="M48" s="29"/>
@@ -2364,7 +2364,7 @@
         <x:v>初二</x:v>
       </x:c>
       <x:c r="F49" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G49" s="21"/>
       <x:c r="H49" s="21"/>
@@ -2372,10 +2372,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J49" s="24" t="n">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K49" s="24" t="n">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="L49" s="28"/>
       <x:c r="M49" s="29"/>
@@ -2385,7 +2385,7 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B50" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_12</x:v>
       </x:c>
       <x:c r="C50" s="12" t="str">
         <x:v>LLM外呼</x:v>
@@ -2394,10 +2394,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E50" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F50" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="G50" s="21"/>
       <x:c r="H50" s="21"/>
@@ -2405,10 +2405,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J50" s="24" t="n">
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K50" s="24" t="n">
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L50" s="28"/>
       <x:c r="M50" s="29"/>
@@ -2427,7 +2427,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E51" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F51" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -2438,10 +2438,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J51" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K51" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L51" s="28"/>
       <x:c r="M51" s="29"/>
@@ -2460,10 +2460,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E52" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F52" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G52" s="21"/>
       <x:c r="H52" s="21"/>
@@ -2471,10 +2471,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J52" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K52" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L52" s="28"/>
       <x:c r="M52" s="29"/>
@@ -2484,7 +2484,7 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B53" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C53" s="12" t="str">
         <x:v>LLM外呼</x:v>
@@ -2493,10 +2493,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E53" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F53" s="21" t="str">
-        <x:v>2026-07-01</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G53" s="21"/>
       <x:c r="H53" s="21"/>
@@ -2504,10 +2504,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J53" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K53" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L53" s="28"/>
       <x:c r="M53" s="29"/>
@@ -2526,10 +2526,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E54" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F54" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-07-01</x:v>
       </x:c>
       <x:c r="G54" s="21"/>
       <x:c r="H54" s="21"/>
@@ -2537,10 +2537,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J54" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K54" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L54" s="28"/>
       <x:c r="M54" s="29"/>
@@ -2550,19 +2550,19 @@
         <x:v>初中</x:v>
       </x:c>
       <x:c r="B55" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C55" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D55" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E55" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F55" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G55" s="21"/>
       <x:c r="H55" s="21"/>
@@ -2570,10 +2570,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J55" s="24" t="n">
-        <x:v>140</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K55" s="24" t="n">
-        <x:v>140</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L55" s="28"/>
       <x:c r="M55" s="29"/>
@@ -2592,7 +2592,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E56" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F56" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -2603,10 +2603,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J56" s="24" t="n">
-        <x:v>142</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="K56" s="24" t="n">
-        <x:v>142</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="L56" s="28"/>
       <x:c r="M56" s="29"/>
@@ -2625,7 +2625,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E57" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F57" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -2636,10 +2636,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J57" s="24" t="n">
-        <x:v>130</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="K57" s="24" t="n">
-        <x:v>130</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="L57" s="28"/>
       <x:c r="M57" s="29"/>
@@ -2652,16 +2652,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C58" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D58" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E58" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F58" s="21" t="str">
-        <x:v>2026-06-22</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G58" s="21"/>
       <x:c r="H58" s="21"/>
@@ -2669,10 +2669,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J58" s="24" t="n">
-        <x:v>711</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="K58" s="24" t="n">
-        <x:v>711</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="L58" s="28"/>
       <x:c r="M58" s="29"/>
@@ -2691,7 +2691,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E59" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F59" s="21" t="str">
         <x:v>2026-06-22</x:v>
@@ -2702,10 +2702,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J59" s="24" t="n">
-        <x:v>1120</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="K59" s="24" t="n">
-        <x:v>1120</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="L59" s="28"/>
       <x:c r="M59" s="29"/>
@@ -2724,10 +2724,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E60" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F60" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G60" s="21"/>
       <x:c r="H60" s="21"/>
@@ -2735,10 +2735,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J60" s="24" t="n">
-        <x:v>910</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="K60" s="24" t="n">
-        <x:v>910</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="L60" s="28"/>
       <x:c r="M60" s="29"/>
@@ -2754,10 +2754,10 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D61" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E61" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F61" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -2768,10 +2768,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J61" s="24" t="n">
-        <x:v>479</x:v>
+        <x:v>910</x:v>
       </x:c>
       <x:c r="K61" s="24" t="n">
-        <x:v>479</x:v>
+        <x:v>910</x:v>
       </x:c>
       <x:c r="L61" s="28"/>
       <x:c r="M61" s="29"/>
@@ -2790,7 +2790,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E62" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F62" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -2801,10 +2801,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J62" s="24" t="n">
-        <x:v>385</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="K62" s="24" t="n">
-        <x:v>385</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="L62" s="28"/>
       <x:c r="M62" s="29"/>
@@ -2823,7 +2823,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E63" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F63" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -2834,10 +2834,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J63" s="24" t="n">
-        <x:v>318</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="K63" s="24" t="n">
-        <x:v>318</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="L63" s="28"/>
       <x:c r="M63" s="29"/>
@@ -2850,16 +2850,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C64" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D64" s="18" t="n">
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E64" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F64" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G64" s="21"/>
       <x:c r="H64" s="21"/>
@@ -2867,10 +2867,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J64" s="24" t="n">
-        <x:v>484</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="K64" s="24" t="n">
-        <x:v>484</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="L64" s="28"/>
       <x:c r="M64" s="29"/>
@@ -2889,7 +2889,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E65" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F65" s="21" t="str">
         <x:v>2026-07-03</x:v>
@@ -2900,10 +2900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J65" s="24" t="n">
-        <x:v>506</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="K65" s="24" t="n">
-        <x:v>506</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="L65" s="28"/>
       <x:c r="M65" s="29"/>
@@ -2922,10 +2922,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E66" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F66" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G66" s="21"/>
       <x:c r="H66" s="21"/>
@@ -2933,10 +2933,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J66" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="K66" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="L66" s="28"/>
       <x:c r="M66" s="29"/>
@@ -2949,16 +2949,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C67" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D67" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E67" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F67" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G67" s="21"/>
       <x:c r="H67" s="21"/>
@@ -2966,10 +2966,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J67" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K67" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L67" s="28"/>
       <x:c r="M67" s="29"/>
@@ -2988,7 +2988,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E68" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F68" s="21" t="str">
         <x:v>2026-06-21</x:v>
@@ -2999,10 +2999,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J68" s="24" t="n">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K68" s="24" t="n">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L68" s="28"/>
       <x:c r="M68" s="29"/>
@@ -3021,7 +3021,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E69" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F69" s="21" t="str">
         <x:v>2026-06-21</x:v>
@@ -3032,10 +3032,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J69" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K69" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L69" s="28"/>
       <x:c r="M69" s="29"/>
@@ -3051,13 +3051,13 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D70" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E70" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F70" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G70" s="21"/>
       <x:c r="H70" s="21"/>
@@ -3065,10 +3065,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J70" s="24" t="n">
-        <x:v>134</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K70" s="24" t="n">
-        <x:v>134</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L70" s="28"/>
       <x:c r="M70" s="29"/>
@@ -3084,13 +3084,13 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D71" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E71" s="12" t="str">
         <x:v>初一</x:v>
       </x:c>
       <x:c r="F71" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G71" s="21"/>
       <x:c r="H71" s="21"/>
@@ -3098,10 +3098,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J71" s="24" t="n">
-        <x:v>43</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="K71" s="24" t="n">
-        <x:v>43</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="L71" s="28"/>
       <x:c r="M71" s="29"/>
@@ -3120,10 +3120,10 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E72" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F72" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G72" s="21"/>
       <x:c r="H72" s="21"/>
@@ -3131,10 +3131,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J72" s="24" t="n">
-        <x:v>256</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K72" s="24" t="n">
-        <x:v>256</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="L72" s="28"/>
       <x:c r="M72" s="29"/>
@@ -3153,7 +3153,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E73" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F73" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -3164,10 +3164,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J73" s="24" t="n">
-        <x:v>224</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="K73" s="24" t="n">
-        <x:v>224</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="L73" s="28"/>
       <x:c r="M73" s="29"/>
@@ -3180,16 +3180,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C74" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D74" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E74" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F74" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G74" s="21"/>
       <x:c r="H74" s="21"/>
@@ -3197,10 +3197,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J74" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="K74" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="L74" s="28"/>
       <x:c r="M74" s="29"/>
@@ -3219,10 +3219,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E75" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F75" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G75" s="21"/>
       <x:c r="H75" s="21"/>
@@ -3230,10 +3230,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J75" s="24" t="n">
-        <x:v>318</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K75" s="24" t="n">
-        <x:v>318</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L75" s="28"/>
       <x:c r="M75" s="29"/>
@@ -3252,7 +3252,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E76" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F76" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -3263,10 +3263,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J76" s="24" t="n">
-        <x:v>335</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="K76" s="24" t="n">
-        <x:v>335</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="L76" s="28"/>
       <x:c r="M76" s="29"/>
@@ -3282,10 +3282,10 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D77" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E77" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F77" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -3296,10 +3296,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J77" s="24" t="n">
-        <x:v>326</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="K77" s="24" t="n">
-        <x:v>326</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="L77" s="28"/>
       <x:c r="M77" s="29"/>
@@ -3318,7 +3318,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E78" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F78" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -3329,10 +3329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J78" s="24" t="n">
-        <x:v>10</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="K78" s="24" t="n">
-        <x:v>10</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="L78" s="28"/>
       <x:c r="M78" s="29"/>
@@ -3351,7 +3351,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E79" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F79" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -3362,10 +3362,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J79" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K79" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L79" s="28"/>
       <x:c r="M79" s="29"/>
@@ -3381,13 +3381,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D80" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E80" s="12" t="str">
-        <x:v>初一</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F80" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G80" s="21"/>
       <x:c r="H80" s="21"/>
@@ -3395,10 +3395,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J80" s="24" t="n">
-        <x:v>48</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K80" s="24" t="n">
-        <x:v>48</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L80" s="28"/>
       <x:c r="M80" s="29"/>
@@ -3417,10 +3417,10 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E81" s="12" t="str">
-        <x:v>初二</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="F81" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G81" s="21"/>
       <x:c r="H81" s="21"/>
@@ -3428,10 +3428,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J81" s="24" t="n">
-        <x:v>430</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K81" s="24" t="n">
-        <x:v>430</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L81" s="28"/>
       <x:c r="M81" s="29"/>
@@ -3450,7 +3450,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E82" s="12" t="str">
-        <x:v>初三</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="F82" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -3461,32 +3461,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J82" s="24" t="n">
-        <x:v>374</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="K82" s="24" t="n">
-        <x:v>374</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="L82" s="28"/>
       <x:c r="M82" s="29"/>
     </x:row>
     <x:row r="83" ht="15" hidden="0" customHeight="1">
       <x:c r="A83" s="11" t="str">
-        <x:v>小学</x:v>
+        <x:v>初中</x:v>
       </x:c>
       <x:c r="B83" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C83" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D83" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E83" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="F83" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G83" s="21"/>
       <x:c r="H83" s="21"/>
@@ -3494,10 +3494,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J83" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="K83" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="L83" s="28"/>
       <x:c r="M83" s="29"/>
@@ -3516,10 +3516,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E84" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F84" s="21" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G84" s="21"/>
       <x:c r="H84" s="21"/>
@@ -3527,10 +3527,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J84" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K84" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L84" s="28"/>
       <x:c r="M84" s="29"/>
@@ -3549,7 +3549,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E85" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F85" s="21" t="str">
         <x:v>2026-06-29</x:v>
@@ -3560,10 +3560,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J85" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K85" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L85" s="28"/>
       <x:c r="M85" s="29"/>
@@ -3582,10 +3582,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E86" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F86" s="21" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="G86" s="21"/>
       <x:c r="H86" s="21"/>
@@ -3593,10 +3593,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J86" s="24" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K86" s="24" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L86" s="28"/>
       <x:c r="M86" s="29"/>
@@ -3615,10 +3615,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E87" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F87" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G87" s="21"/>
       <x:c r="H87" s="21"/>
@@ -3626,10 +3626,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J87" s="24" t="n">
-        <x:v>133</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K87" s="24" t="n">
-        <x:v>133</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L87" s="28"/>
       <x:c r="M87" s="29"/>
@@ -3639,7 +3639,7 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B88" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C88" s="12" t="str">
         <x:v>LLM外呼</x:v>
@@ -3648,10 +3648,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E88" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F88" s="21" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G88" s="21"/>
       <x:c r="H88" s="21"/>
@@ -3659,10 +3659,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J88" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="K88" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="L88" s="28"/>
       <x:c r="M88" s="29"/>
@@ -3681,10 +3681,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E89" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F89" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G89" s="21"/>
       <x:c r="H89" s="21"/>
@@ -3714,10 +3714,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E90" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F90" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G90" s="21"/>
       <x:c r="H90" s="21"/>
@@ -3725,10 +3725,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J90" s="24" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K90" s="24" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L90" s="28"/>
       <x:c r="M90" s="29"/>
@@ -3747,10 +3747,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E91" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F91" s="21" t="str">
-        <x:v>2026-07-01</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G91" s="21"/>
       <x:c r="H91" s="21"/>
@@ -3758,10 +3758,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J91" s="24" t="n">
-        <x:v>83</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K91" s="24" t="n">
-        <x:v>83</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L91" s="28"/>
       <x:c r="M91" s="29"/>
@@ -3771,7 +3771,7 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B92" s="12" t="str">
-        <x:v>暑_12</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C92" s="12" t="str">
         <x:v>LLM外呼</x:v>
@@ -3780,10 +3780,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E92" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F92" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G92" s="21"/>
       <x:c r="H92" s="21"/>
@@ -3791,10 +3791,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J92" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K92" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="L92" s="28"/>
       <x:c r="M92" s="29"/>
@@ -3813,7 +3813,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E93" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F93" s="21" t="str">
         <x:v>2026-07-03</x:v>
@@ -3837,19 +3837,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B94" s="12" t="str">
-        <x:v>暑_6</x:v>
+        <x:v>暑_12</x:v>
       </x:c>
       <x:c r="C94" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D94" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E94" s="12" t="str">
         <x:v>四年级</x:v>
       </x:c>
       <x:c r="F94" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-07-03</x:v>
       </x:c>
       <x:c r="G94" s="21"/>
       <x:c r="H94" s="21"/>
@@ -3857,10 +3857,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J94" s="24" t="n">
-        <x:v>68</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K94" s="24" t="n">
-        <x:v>68</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L94" s="28"/>
       <x:c r="M94" s="29"/>
@@ -3870,19 +3870,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B95" s="12" t="str">
-        <x:v>暑_6</x:v>
+        <x:v>暑_12</x:v>
       </x:c>
       <x:c r="C95" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D95" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E95" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F95" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G95" s="21"/>
       <x:c r="H95" s="21"/>
@@ -3890,10 +3890,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J95" s="24" t="n">
-        <x:v>51</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K95" s="24" t="n">
-        <x:v>51</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L95" s="28"/>
       <x:c r="M95" s="29"/>
@@ -3912,10 +3912,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E96" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F96" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G96" s="21"/>
       <x:c r="H96" s="21"/>
@@ -3923,10 +3923,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J96" s="24" t="n">
-        <x:v>35</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K96" s="24" t="n">
-        <x:v>35</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="L96" s="28"/>
       <x:c r="M96" s="29"/>
@@ -3939,16 +3939,16 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C97" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D97" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E97" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F97" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G97" s="21"/>
       <x:c r="H97" s="21"/>
@@ -3956,10 +3956,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J97" s="24" t="n">
-        <x:v>15</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K97" s="24" t="n">
-        <x:v>15</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L97" s="28"/>
       <x:c r="M97" s="29"/>
@@ -3972,16 +3972,16 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C98" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D98" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E98" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F98" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G98" s="21"/>
       <x:c r="H98" s="21"/>
@@ -3989,10 +3989,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J98" s="24" t="n">
-        <x:v>13</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="K98" s="24" t="n">
-        <x:v>13</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="L98" s="28"/>
       <x:c r="M98" s="29"/>
@@ -4005,7 +4005,7 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C99" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D99" s="18" t="n">
         <x:v>9.9</x:v>
@@ -4022,10 +4022,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J99" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K99" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L99" s="28"/>
       <x:c r="M99" s="29"/>
@@ -4038,13 +4038,13 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C100" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D100" s="18" t="n">
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E100" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F100" s="21" t="str">
         <x:v>2026-06-17</x:v>
@@ -4077,7 +4077,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E101" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F101" s="21" t="str">
         <x:v>2026-06-17</x:v>
@@ -4104,13 +4104,13 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C102" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D102" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E102" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F102" s="21" t="str">
         <x:v>2026-06-17</x:v>
@@ -4121,10 +4121,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J102" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K102" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L102" s="28"/>
       <x:c r="M102" s="29"/>
@@ -4137,10 +4137,10 @@
         <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C103" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D103" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E103" s="12" t="str">
         <x:v>五年级</x:v>
@@ -4154,10 +4154,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J103" s="24" t="n">
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K103" s="24" t="n">
-        <x:v>14</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L103" s="28"/>
       <x:c r="M103" s="29"/>
@@ -4167,19 +4167,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B104" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C104" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D104" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E104" s="12" t="str">
         <x:v>三年级</x:v>
       </x:c>
       <x:c r="F104" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G104" s="21"/>
       <x:c r="H104" s="21"/>
@@ -4187,10 +4187,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J104" s="24" t="n">
-        <x:v>24</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K104" s="24" t="n">
-        <x:v>24</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L104" s="28"/>
       <x:c r="M104" s="29"/>
@@ -4200,19 +4200,19 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B105" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_6</x:v>
       </x:c>
       <x:c r="C105" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D105" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E105" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F105" s="21" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G105" s="21"/>
       <x:c r="H105" s="21"/>
@@ -4220,10 +4220,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J105" s="24" t="n">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K105" s="24" t="n">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L105" s="28"/>
       <x:c r="M105" s="29"/>
@@ -4242,7 +4242,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E106" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F106" s="21" t="str">
         <x:v>2026-06-27</x:v>
@@ -4253,10 +4253,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J106" s="24" t="n">
-        <x:v>44</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K106" s="24" t="n">
-        <x:v>44</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="L106" s="28"/>
       <x:c r="M106" s="29"/>
@@ -4275,7 +4275,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E107" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F107" s="21" t="str">
         <x:v>2026-06-27</x:v>
@@ -4286,10 +4286,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J107" s="24" t="n">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="K107" s="24" t="n">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="L107" s="28"/>
       <x:c r="M107" s="29"/>
@@ -4302,16 +4302,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C108" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D108" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E108" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F108" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G108" s="21"/>
       <x:c r="H108" s="21"/>
@@ -4319,10 +4319,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J108" s="24" t="n">
-        <x:v>1968</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K108" s="24" t="n">
-        <x:v>1968</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="L108" s="28"/>
       <x:c r="M108" s="29"/>
@@ -4335,16 +4335,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C109" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D109" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E109" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F109" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="G109" s="21"/>
       <x:c r="H109" s="21"/>
@@ -4352,10 +4352,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J109" s="24" t="n">
-        <x:v>2036</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K109" s="24" t="n">
-        <x:v>2036</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="L109" s="28"/>
       <x:c r="M109" s="29"/>
@@ -4374,10 +4374,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E110" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F110" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G110" s="21"/>
       <x:c r="H110" s="21"/>
@@ -4385,10 +4385,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J110" s="24" t="n">
-        <x:v>1513</x:v>
+        <x:v>1968</x:v>
       </x:c>
       <x:c r="K110" s="24" t="n">
-        <x:v>1513</x:v>
+        <x:v>1968</x:v>
       </x:c>
       <x:c r="L110" s="28"/>
       <x:c r="M110" s="29"/>
@@ -4407,7 +4407,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E111" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F111" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -4418,10 +4418,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J111" s="24" t="n">
-        <x:v>1857</x:v>
+        <x:v>2036</x:v>
       </x:c>
       <x:c r="K111" s="24" t="n">
-        <x:v>1857</x:v>
+        <x:v>2036</x:v>
       </x:c>
       <x:c r="L111" s="28"/>
       <x:c r="M111" s="29"/>
@@ -4437,13 +4437,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D112" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E112" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F112" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G112" s="21"/>
       <x:c r="H112" s="21"/>
@@ -4451,10 +4451,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J112" s="24" t="n">
-        <x:v>131</x:v>
+        <x:v>1513</x:v>
       </x:c>
       <x:c r="K112" s="24" t="n">
-        <x:v>131</x:v>
+        <x:v>1513</x:v>
       </x:c>
       <x:c r="L112" s="28"/>
       <x:c r="M112" s="29"/>
@@ -4470,13 +4470,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D113" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E113" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F113" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G113" s="21"/>
       <x:c r="H113" s="21"/>
@@ -4484,10 +4484,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J113" s="24" t="n">
-        <x:v>191</x:v>
+        <x:v>1857</x:v>
       </x:c>
       <x:c r="K113" s="24" t="n">
-        <x:v>191</x:v>
+        <x:v>1857</x:v>
       </x:c>
       <x:c r="L113" s="28"/>
       <x:c r="M113" s="29"/>
@@ -4506,7 +4506,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E114" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F114" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -4517,10 +4517,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J114" s="24" t="n">
-        <x:v>156</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="K114" s="24" t="n">
-        <x:v>156</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="L114" s="28"/>
       <x:c r="M114" s="29"/>
@@ -4539,7 +4539,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E115" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F115" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -4550,10 +4550,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J115" s="24" t="n">
-        <x:v>135</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="K115" s="24" t="n">
-        <x:v>135</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="L115" s="28"/>
       <x:c r="M115" s="29"/>
@@ -4566,16 +4566,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C116" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D116" s="18" t="n">
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E116" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F116" s="21" t="str">
-        <x:v>2026-06-22</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G116" s="21"/>
       <x:c r="H116" s="21"/>
@@ -4583,10 +4583,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J116" s="24" t="n">
-        <x:v>66</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="K116" s="24" t="n">
-        <x:v>66</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="L116" s="28"/>
       <x:c r="M116" s="29"/>
@@ -4599,13 +4599,13 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C117" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D117" s="18" t="n">
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E117" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F117" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -4616,10 +4616,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J117" s="24" t="n">
-        <x:v>239</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="K117" s="24" t="n">
-        <x:v>239</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L117" s="28"/>
       <x:c r="M117" s="29"/>
@@ -4638,10 +4638,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E118" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F118" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G118" s="21"/>
       <x:c r="H118" s="21"/>
@@ -4649,10 +4649,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J118" s="24" t="n">
-        <x:v>252</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K118" s="24" t="n">
-        <x:v>252</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="L118" s="28"/>
       <x:c r="M118" s="29"/>
@@ -4671,10 +4671,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E119" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F119" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G119" s="21"/>
       <x:c r="H119" s="21"/>
@@ -4682,10 +4682,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J119" s="24" t="n">
-        <x:v>235</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="K119" s="24" t="n">
-        <x:v>235</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="L119" s="28"/>
       <x:c r="M119" s="29"/>
@@ -4704,7 +4704,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E120" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F120" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -4715,10 +4715,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J120" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="K120" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="L120" s="28"/>
       <x:c r="M120" s="29"/>
@@ -4731,16 +4731,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C121" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D121" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E121" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F121" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G121" s="21"/>
       <x:c r="H121" s="21"/>
@@ -4748,10 +4748,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J121" s="24" t="n">
-        <x:v>181</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="K121" s="24" t="n">
-        <x:v>181</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="L121" s="28"/>
       <x:c r="M121" s="29"/>
@@ -4764,16 +4764,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C122" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D122" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E122" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F122" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G122" s="21"/>
       <x:c r="H122" s="21"/>
@@ -4781,10 +4781,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J122" s="24" t="n">
-        <x:v>214</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K122" s="24" t="n">
-        <x:v>214</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L122" s="28"/>
       <x:c r="M122" s="29"/>
@@ -4803,10 +4803,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E123" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F123" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G123" s="21"/>
       <x:c r="H123" s="21"/>
@@ -4814,10 +4814,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J123" s="24" t="n">
-        <x:v>135</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="K123" s="24" t="n">
-        <x:v>135</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="L123" s="28"/>
       <x:c r="M123" s="29"/>
@@ -4836,7 +4836,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E124" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F124" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -4847,10 +4847,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J124" s="24" t="n">
-        <x:v>191</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="K124" s="24" t="n">
-        <x:v>191</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="L124" s="28"/>
       <x:c r="M124" s="29"/>
@@ -4863,16 +4863,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C125" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D125" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E125" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F125" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G125" s="21"/>
       <x:c r="H125" s="21"/>
@@ -4880,10 +4880,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J125" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="K125" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L125" s="28"/>
       <x:c r="M125" s="29"/>
@@ -4896,16 +4896,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C126" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D126" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E126" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F126" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G126" s="21"/>
       <x:c r="H126" s="21"/>
@@ -4913,10 +4913,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J126" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="K126" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="L126" s="28"/>
       <x:c r="M126" s="29"/>
@@ -4935,7 +4935,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E127" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F127" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -4965,13 +4965,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D128" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E128" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F128" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G128" s="21"/>
       <x:c r="H128" s="21"/>
@@ -4979,10 +4979,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J128" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K128" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L128" s="28"/>
       <x:c r="M128" s="29"/>
@@ -4998,13 +4998,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D129" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E129" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F129" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G129" s="21"/>
       <x:c r="H129" s="21"/>
@@ -5012,10 +5012,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J129" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K129" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L129" s="28"/>
       <x:c r="M129" s="29"/>
@@ -5034,10 +5034,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E130" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F130" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G130" s="21"/>
       <x:c r="H130" s="21"/>
@@ -5045,10 +5045,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J130" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K130" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L130" s="28"/>
       <x:c r="M130" s="29"/>
@@ -5067,7 +5067,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E131" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F131" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -5078,10 +5078,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J131" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K131" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L131" s="28"/>
       <x:c r="M131" s="29"/>
@@ -5097,13 +5097,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D132" s="18" t="n">
-        <x:v>18.8</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E132" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F132" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G132" s="21"/>
       <x:c r="H132" s="21"/>
@@ -5111,10 +5111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J132" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K132" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L132" s="28"/>
       <x:c r="M132" s="29"/>
@@ -5130,13 +5130,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D133" s="18" t="n">
-        <x:v>18.8</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E133" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F133" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G133" s="21"/>
       <x:c r="H133" s="21"/>
@@ -5166,10 +5166,10 @@
         <x:v>18.8</x:v>
       </x:c>
       <x:c r="E134" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F134" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G134" s="21"/>
       <x:c r="H134" s="21"/>
@@ -5177,10 +5177,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J134" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K134" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L134" s="28"/>
       <x:c r="M134" s="29"/>
@@ -5199,7 +5199,7 @@
         <x:v>18.8</x:v>
       </x:c>
       <x:c r="E135" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F135" s="21" t="str">
         <x:v>2026-06-20</x:v>
@@ -5210,10 +5210,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J135" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K135" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L135" s="28"/>
       <x:c r="M135" s="29"/>
@@ -5232,10 +5232,10 @@
         <x:v>18.8</x:v>
       </x:c>
       <x:c r="E136" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F136" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G136" s="21"/>
       <x:c r="H136" s="21"/>
@@ -5262,13 +5262,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D137" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>18.8</x:v>
       </x:c>
       <x:c r="E137" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F137" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G137" s="21"/>
       <x:c r="H137" s="21"/>
@@ -5276,10 +5276,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J137" s="24" t="n">
-        <x:v>89</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K137" s="24" t="n">
-        <x:v>89</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L137" s="28"/>
       <x:c r="M137" s="29"/>
@@ -5295,13 +5295,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D138" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>18.8</x:v>
       </x:c>
       <x:c r="E138" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F138" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G138" s="21"/>
       <x:c r="H138" s="21"/>
@@ -5309,10 +5309,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J138" s="24" t="n">
-        <x:v>227</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K138" s="24" t="n">
-        <x:v>227</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L138" s="28"/>
       <x:c r="M138" s="29"/>
@@ -5331,7 +5331,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E139" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F139" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -5342,10 +5342,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J139" s="24" t="n">
-        <x:v>291</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K139" s="24" t="n">
-        <x:v>291</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="L139" s="28"/>
       <x:c r="M139" s="29"/>
@@ -5364,7 +5364,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E140" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F140" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -5375,10 +5375,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J140" s="24" t="n">
-        <x:v>229</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="K140" s="24" t="n">
-        <x:v>229</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="L140" s="28"/>
       <x:c r="M140" s="29"/>
@@ -5397,7 +5397,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E141" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F141" s="21" t="str">
         <x:v>2026-06-24</x:v>
@@ -5408,10 +5408,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J141" s="24" t="n">
-        <x:v>263</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="K141" s="24" t="n">
-        <x:v>263</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="L141" s="28"/>
       <x:c r="M141" s="29"/>
@@ -5421,82 +5421,66 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B142" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C142" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D142" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E142" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F142" s="21" t="str">
-        <x:v>2026-07-03</x:v>
-      </x:c>
-      <x:c r="G142" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H142" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="G142" s="21"/>
+      <x:c r="H142" s="21"/>
       <x:c r="I142" s="24" t="n">
-        <x:v>40</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J142" s="24" t="n">
-        <x:v>40</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="K142" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L142" s="28" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M142" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="L142" s="28"/>
+      <x:c r="M142" s="29"/>
     </x:row>
     <x:row r="143" ht="15" hidden="0" customHeight="1">
       <x:c r="A143" s="11" t="str">
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B143" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C143" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D143" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E143" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F143" s="21" t="str">
-        <x:v>2026-07-03</x:v>
-      </x:c>
-      <x:c r="G143" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H143" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="G143" s="21"/>
+      <x:c r="H143" s="21"/>
       <x:c r="I143" s="24" t="n">
-        <x:v>120</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J143" s="24" t="n">
-        <x:v>88</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="K143" s="24" t="n">
-        <x:v>-32</x:v>
-      </x:c>
-      <x:c r="L143" s="28" t="n">
-        <x:v>0.7333333333333333</x:v>
-      </x:c>
-      <x:c r="M143" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="L143" s="28"/>
+      <x:c r="M143" s="29"/>
     </x:row>
     <x:row r="144" ht="15" hidden="0" customHeight="1">
       <x:c r="A144" s="11" t="str">
@@ -5512,7 +5496,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E144" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F144" s="21" t="str">
         <x:v>2026-07-03</x:v>
@@ -5524,16 +5508,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I144" s="24" t="n">
-        <x:v>120</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J144" s="24" t="n">
-        <x:v>93</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K144" s="24" t="n">
-        <x:v>-27</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L144" s="28" t="n">
-        <x:v>0.775</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M144" s="29" t="n">
         <x:v>1</x:v>
@@ -5553,10 +5537,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E145" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F145" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-04</x:v>
       </x:c>
       <x:c r="G145" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5568,13 +5552,13 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="J145" s="24" t="n">
-        <x:v>119</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="K145" s="24" t="n">
-        <x:v>-1</x:v>
+        <x:v>-21</x:v>
       </x:c>
       <x:c r="L145" s="28" t="n">
-        <x:v>0.9916666666666667</x:v>
+        <x:v>0.825</x:v>
       </x:c>
       <x:c r="M145" s="29" t="n">
         <x:v>1</x:v>
@@ -5588,16 +5572,16 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C146" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D146" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E146" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F146" s="21" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-07-04</x:v>
       </x:c>
       <x:c r="G146" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5606,16 +5590,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I146" s="24" t="n">
-        <x:v>2300</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J146" s="24" t="n">
-        <x:v>2300</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K146" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-18</x:v>
       </x:c>
       <x:c r="L146" s="28" t="n">
-        <x:v>1</x:v>
+        <x:v>0.85</x:v>
       </x:c>
       <x:c r="M146" s="29" t="n">
         <x:v>1</x:v>
@@ -5629,16 +5613,16 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C147" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D147" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E147" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F147" s="21" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-07-04</x:v>
       </x:c>
       <x:c r="G147" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5647,16 +5631,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I147" s="24" t="n">
-        <x:v>2500</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J147" s="24" t="n">
-        <x:v>2503</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="K147" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L147" s="28" t="n">
-        <x:v>1.0012</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M147" s="29" t="n">
         <x:v>1</x:v>
@@ -5676,7 +5660,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E148" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F148" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -5688,16 +5672,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I148" s="24" t="n">
-        <x:v>2000</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="J148" s="24" t="n">
-        <x:v>2004</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="K148" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L148" s="28" t="n">
-        <x:v>1.002</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M148" s="29" t="n">
         <x:v>1</x:v>
@@ -5717,10 +5701,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E149" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F149" s="21" t="str">
-        <x:v>2026-07-01</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G149" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5729,16 +5713,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I149" s="24" t="n">
-        <x:v>2300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="J149" s="24" t="n">
-        <x:v>2304</x:v>
+        <x:v>2503</x:v>
       </x:c>
       <x:c r="K149" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L149" s="28" t="n">
-        <x:v>1.0017391304347827</x:v>
+        <x:v>1.0012</x:v>
       </x:c>
       <x:c r="M149" s="29" t="n">
         <x:v>1</x:v>
@@ -5755,10 +5739,10 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D150" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E150" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F150" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -5770,16 +5754,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I150" s="24" t="n">
-        <x:v>100</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="J150" s="24" t="n">
-        <x:v>172</x:v>
+        <x:v>2004</x:v>
       </x:c>
       <x:c r="K150" s="24" t="n">
-        <x:v>72</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L150" s="28" t="n">
-        <x:v>1.72</x:v>
+        <x:v>1.002</x:v>
       </x:c>
       <x:c r="M150" s="29" t="n">
         <x:v>1</x:v>
@@ -5796,13 +5780,13 @@
         <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D151" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E151" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F151" s="21" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-07-01</x:v>
       </x:c>
       <x:c r="G151" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -5811,16 +5795,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I151" s="24" t="n">
-        <x:v>150</x:v>
+        <x:v>2300</x:v>
       </x:c>
       <x:c r="J151" s="24" t="n">
-        <x:v>231</x:v>
+        <x:v>2304</x:v>
       </x:c>
       <x:c r="K151" s="24" t="n">
-        <x:v>81</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L151" s="28" t="n">
-        <x:v>1.54</x:v>
+        <x:v>1.0017391304347827</x:v>
       </x:c>
       <x:c r="M151" s="29" t="n">
         <x:v>1</x:v>
@@ -5840,7 +5824,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E152" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F152" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -5852,16 +5836,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I152" s="24" t="n">
-        <x:v>120</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J152" s="24" t="n">
-        <x:v>135</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="K152" s="24" t="n">
-        <x:v>15</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="L152" s="28" t="n">
-        <x:v>1.125</x:v>
+        <x:v>1.72</x:v>
       </x:c>
       <x:c r="M152" s="29" t="n">
         <x:v>1</x:v>
@@ -5881,7 +5865,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E153" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F153" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -5896,13 +5880,13 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="J153" s="24" t="n">
-        <x:v>166</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="K153" s="24" t="n">
-        <x:v>16</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="L153" s="28" t="n">
-        <x:v>1.1066666666666667</x:v>
+        <x:v>1.54</x:v>
       </x:c>
       <x:c r="M153" s="29" t="n">
         <x:v>1</x:v>
@@ -5916,13 +5900,13 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C154" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D154" s="18" t="n">
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E154" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F154" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -5934,16 +5918,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I154" s="24" t="n">
-        <x:v>100</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J154" s="24" t="n">
-        <x:v>242</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="K154" s="24" t="n">
-        <x:v>142</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L154" s="28" t="n">
-        <x:v>2.42</x:v>
+        <x:v>1.125</x:v>
       </x:c>
       <x:c r="M154" s="29" t="n">
         <x:v>1</x:v>
@@ -5957,13 +5941,13 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C155" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D155" s="18" t="n">
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E155" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F155" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -5975,16 +5959,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I155" s="24" t="n">
-        <x:v>300</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J155" s="24" t="n">
-        <x:v>249</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="K155" s="24" t="n">
-        <x:v>-51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="L155" s="28" t="n">
-        <x:v>0.83</x:v>
+        <x:v>1.1066666666666667</x:v>
       </x:c>
       <x:c r="M155" s="29" t="n">
         <x:v>1</x:v>
@@ -6004,7 +5988,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E156" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F156" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -6016,16 +6000,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I156" s="24" t="n">
-        <x:v>200</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J156" s="24" t="n">
-        <x:v>236</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="K156" s="24" t="n">
-        <x:v>36</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="L156" s="28" t="n">
-        <x:v>1.18</x:v>
+        <x:v>2.42</x:v>
       </x:c>
       <x:c r="M156" s="29" t="n">
         <x:v>1</x:v>
@@ -6045,10 +6029,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E157" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F157" s="21" t="str">
-        <x:v>2026-06-26</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G157" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -6057,16 +6041,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I157" s="24" t="n">
-        <x:v>200</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J157" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="K157" s="24" t="n">
-        <x:v>-195</x:v>
+        <x:v>-51</x:v>
       </x:c>
       <x:c r="L157" s="28" t="n">
-        <x:v>0.025</x:v>
+        <x:v>0.83</x:v>
       </x:c>
       <x:c r="M157" s="29" t="n">
         <x:v>1</x:v>
@@ -6080,13 +6064,13 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C158" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D158" s="18" t="n">
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E158" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F158" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -6098,16 +6082,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I158" s="24" t="n">
-        <x:v>20</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="J158" s="24" t="n">
-        <x:v>115</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="K158" s="24" t="n">
-        <x:v>95</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="L158" s="28" t="n">
-        <x:v>5.75</x:v>
+        <x:v>1.18</x:v>
       </x:c>
       <x:c r="M158" s="29" t="n">
         <x:v>1</x:v>
@@ -6121,16 +6105,16 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C159" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D159" s="18" t="n">
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E159" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F159" s="21" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="G159" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -6139,16 +6123,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I159" s="24" t="n">
-        <x:v>50</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="J159" s="24" t="n">
-        <x:v>46</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K159" s="24" t="n">
-        <x:v>-4</x:v>
+        <x:v>-195</x:v>
       </x:c>
       <x:c r="L159" s="28" t="n">
-        <x:v>0.92</x:v>
+        <x:v>0.025</x:v>
       </x:c>
       <x:c r="M159" s="29" t="n">
         <x:v>1</x:v>
@@ -6168,7 +6152,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E160" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F160" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -6180,16 +6164,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I160" s="24" t="n">
-        <x:v>70</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J160" s="24" t="n">
-        <x:v>77</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="K160" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="L160" s="28" t="n">
-        <x:v>1.1</x:v>
+        <x:v>5.75</x:v>
       </x:c>
       <x:c r="M160" s="29" t="n">
         <x:v>1</x:v>
@@ -6209,7 +6193,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E161" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F161" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -6221,16 +6205,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I161" s="24" t="n">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J161" s="24" t="n">
-        <x:v>91</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="K161" s="24" t="n">
-        <x:v>51</x:v>
+        <x:v>-4</x:v>
       </x:c>
       <x:c r="L161" s="28" t="n">
-        <x:v>2.275</x:v>
+        <x:v>0.92</x:v>
       </x:c>
       <x:c r="M161" s="29" t="n">
         <x:v>1</x:v>
@@ -6250,7 +6234,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E162" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F162" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -6265,13 +6249,13 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="J162" s="24" t="n">
-        <x:v>84</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K162" s="24" t="n">
-        <x:v>14</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L162" s="28" t="n">
-        <x:v>1.2</x:v>
+        <x:v>1.1</x:v>
       </x:c>
       <x:c r="M162" s="29" t="n">
         <x:v>1</x:v>
@@ -6288,27 +6272,35 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D163" s="18" t="n">
-        <x:v>18.8</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E163" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F163" s="21" t="str">
-        <x:v>2026-06-24</x:v>
-      </x:c>
-      <x:c r="G163" s="21"/>
-      <x:c r="H163" s="21"/>
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G163" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H163" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I163" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J163" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K163" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L163" s="28"/>
-      <x:c r="M163" s="29"/>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="L163" s="28" t="n">
+        <x:v>2.275</x:v>
+      </x:c>
+      <x:c r="M163" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="164" ht="15" hidden="0" customHeight="1">
       <x:c r="A164" s="11" t="str">
@@ -6321,13 +6313,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D164" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E164" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F164" s="21" t="str">
-        <x:v>2026-07-01</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G164" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -6336,16 +6328,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I164" s="24" t="n">
-        <x:v>80</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J164" s="24" t="n">
-        <x:v>98</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K164" s="24" t="n">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L164" s="28" t="n">
-        <x:v>1.225</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="M164" s="29" t="n">
         <x:v>1</x:v>
@@ -6362,35 +6354,27 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D165" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>18.8</x:v>
       </x:c>
       <x:c r="E165" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F165" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="G165" s="21" t="str">
-        <x:v>2026-07-01</x:v>
-      </x:c>
-      <x:c r="H165" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-24</x:v>
+      </x:c>
+      <x:c r="G165" s="21"/>
+      <x:c r="H165" s="21"/>
       <x:c r="I165" s="24" t="n">
-        <x:v>190</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J165" s="24" t="n">
-        <x:v>138</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K165" s="24" t="n">
-        <x:v>-52</x:v>
-      </x:c>
-      <x:c r="L165" s="28" t="n">
-        <x:v>0.7263157894736842</x:v>
-      </x:c>
-      <x:c r="M165" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L165" s="28"/>
+      <x:c r="M165" s="29"/>
     </x:row>
     <x:row r="166" ht="15" hidden="0" customHeight="1">
       <x:c r="A166" s="11" t="str">
@@ -6406,7 +6390,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E166" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F166" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -6418,16 +6402,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I166" s="24" t="n">
-        <x:v>260</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J166" s="24" t="n">
-        <x:v>270</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K166" s="24" t="n">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="L166" s="28" t="n">
-        <x:v>1.0384615384615385</x:v>
+        <x:v>1.225</x:v>
       </x:c>
       <x:c r="M166" s="29" t="n">
         <x:v>1</x:v>
@@ -6447,7 +6431,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E167" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F167" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -6459,16 +6443,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I167" s="24" t="n">
-        <x:v>240</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="J167" s="24" t="n">
-        <x:v>242</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="K167" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>-52</x:v>
       </x:c>
       <x:c r="L167" s="28" t="n">
-        <x:v>1.0083333333333333</x:v>
+        <x:v>0.7263157894736842</x:v>
       </x:c>
       <x:c r="M167" s="29" t="n">
         <x:v>1</x:v>
@@ -6488,7 +6472,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E168" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F168" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -6503,13 +6487,13 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="J168" s="24" t="n">
-        <x:v>237</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="K168" s="24" t="n">
-        <x:v>-23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L168" s="28" t="n">
-        <x:v>0.9115384615384615</x:v>
+        <x:v>1.0384615384615385</x:v>
       </x:c>
       <x:c r="M168" s="29" t="n">
         <x:v>1</x:v>
@@ -6520,38 +6504,40 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B169" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C169" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D169" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E169" s="12" t="str">
-        <x:v>三年级</x:v>
-      </x:c>
-      <x:c r="F169" s="21"/>
+        <x:v>五年级</x:v>
+      </x:c>
+      <x:c r="F169" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
       <x:c r="G169" s="21" t="str">
-        <x:v>2026-07-08</x:v>
+        <x:v>2026-07-01</x:v>
       </x:c>
       <x:c r="H169" s="21" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I169" s="24" t="n">
-        <x:v>20</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="J169" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="K169" s="24" t="n">
-        <x:v>-20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L169" s="28" t="n">
-        <x:v>0</x:v>
+        <x:v>1.0083333333333333</x:v>
       </x:c>
       <x:c r="M169" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="15" hidden="0" customHeight="1">
@@ -6559,38 +6545,40 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B170" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C170" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D170" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E170" s="12" t="str">
-        <x:v>四年级</x:v>
-      </x:c>
-      <x:c r="F170" s="21"/>
+        <x:v>六年级</x:v>
+      </x:c>
+      <x:c r="F170" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
       <x:c r="G170" s="21" t="str">
-        <x:v>2026-07-08</x:v>
+        <x:v>2026-07-01</x:v>
       </x:c>
       <x:c r="H170" s="21" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I170" s="24" t="n">
-        <x:v>110</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="J170" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="K170" s="24" t="n">
-        <x:v>-110</x:v>
+        <x:v>-23</x:v>
       </x:c>
       <x:c r="L170" s="28" t="n">
-        <x:v>0</x:v>
+        <x:v>0.9115384615384615</x:v>
       </x:c>
       <x:c r="M170" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="15" hidden="0" customHeight="1">
@@ -6607,9 +6595,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E171" s="12" t="str">
-        <x:v>五年级</x:v>
-      </x:c>
-      <x:c r="F171" s="21"/>
+        <x:v>三年级</x:v>
+      </x:c>
+      <x:c r="F171" s="21" t="str">
+        <x:v>2026-07-06</x:v>
+      </x:c>
       <x:c r="G171" s="21" t="str">
         <x:v>2026-07-08</x:v>
       </x:c>
@@ -6617,19 +6607,19 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I171" s="24" t="n">
-        <x:v>110</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J171" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K171" s="24" t="n">
-        <x:v>-110</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="L171" s="28" t="n">
-        <x:v>0</x:v>
+        <x:v>0.55</x:v>
       </x:c>
       <x:c r="M171" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="15" hidden="0" customHeight="1">
@@ -6646,9 +6636,11 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E172" s="12" t="str">
-        <x:v>六年级</x:v>
-      </x:c>
-      <x:c r="F172" s="21"/>
+        <x:v>四年级</x:v>
+      </x:c>
+      <x:c r="F172" s="21" t="str">
+        <x:v>2026-07-06</x:v>
+      </x:c>
       <x:c r="G172" s="21" t="str">
         <x:v>2026-07-08</x:v>
       </x:c>
@@ -6659,16 +6651,16 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="J172" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K172" s="24" t="n">
-        <x:v>-110</x:v>
+        <x:v>-62</x:v>
       </x:c>
       <x:c r="L172" s="28" t="n">
-        <x:v>0</x:v>
+        <x:v>0.43636363636363634</x:v>
       </x:c>
       <x:c r="M172" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="15" hidden="0" customHeight="1">
@@ -6679,16 +6671,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C173" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D173" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E173" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F173" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G173" s="21" t="str">
         <x:v>2026-07-08</x:v>
@@ -6697,19 +6689,19 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I173" s="24" t="n">
-        <x:v>2520</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J173" s="24" t="n">
-        <x:v>955</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="K173" s="24" t="n">
-        <x:v>-1565</x:v>
+        <x:v>-73</x:v>
       </x:c>
       <x:c r="L173" s="28" t="n">
-        <x:v>0.37896825396825395</x:v>
+        <x:v>0.33636363636363636</x:v>
       </x:c>
       <x:c r="M173" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
@@ -6720,16 +6712,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C174" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D174" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E174" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F174" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G174" s="21" t="str">
         <x:v>2026-07-08</x:v>
@@ -6738,19 +6730,19 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I174" s="24" t="n">
-        <x:v>2720</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J174" s="24" t="n">
-        <x:v>1065</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K174" s="24" t="n">
-        <x:v>-1655</x:v>
+        <x:v>-69</x:v>
       </x:c>
       <x:c r="L174" s="28" t="n">
-        <x:v>0.3915441176470588</x:v>
+        <x:v>0.37272727272727274</x:v>
       </x:c>
       <x:c r="M174" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="15" hidden="0" customHeight="1">
@@ -6767,10 +6759,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E175" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F175" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G175" s="21" t="str">
         <x:v>2026-07-08</x:v>
@@ -6779,19 +6771,19 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I175" s="24" t="n">
-        <x:v>2530</x:v>
+        <x:v>2520</x:v>
       </x:c>
       <x:c r="J175" s="24" t="n">
-        <x:v>911</x:v>
+        <x:v>2190</x:v>
       </x:c>
       <x:c r="K175" s="24" t="n">
-        <x:v>-1619</x:v>
+        <x:v>-330</x:v>
       </x:c>
       <x:c r="L175" s="28" t="n">
-        <x:v>0.3600790513833992</x:v>
+        <x:v>0.8690476190476191</x:v>
       </x:c>
       <x:c r="M175" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="15" hidden="0" customHeight="1">
@@ -6808,10 +6800,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E176" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F176" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G176" s="21" t="str">
         <x:v>2026-07-08</x:v>
@@ -6820,19 +6812,19 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I176" s="24" t="n">
-        <x:v>2050</x:v>
+        <x:v>2720</x:v>
       </x:c>
       <x:c r="J176" s="24" t="n">
-        <x:v>873</x:v>
+        <x:v>2328</x:v>
       </x:c>
       <x:c r="K176" s="24" t="n">
-        <x:v>-1177</x:v>
+        <x:v>-392</x:v>
       </x:c>
       <x:c r="L176" s="28" t="n">
-        <x:v>0.42585365853658536</x:v>
+        <x:v>0.8558823529411764</x:v>
       </x:c>
       <x:c r="M176" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="15" hidden="0" customHeight="1">
@@ -6843,30 +6835,38 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C177" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D177" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E177" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F177" s="21" t="str">
-        <x:v>2026-07-03</x:v>
-      </x:c>
-      <x:c r="G177" s="21"/>
-      <x:c r="H177" s="21"/>
+        <x:v>2026-07-06</x:v>
+      </x:c>
+      <x:c r="G177" s="21" t="str">
+        <x:v>2026-07-08</x:v>
+      </x:c>
+      <x:c r="H177" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
       <x:c r="I177" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>2530</x:v>
       </x:c>
       <x:c r="J177" s="24" t="n">
-        <x:v>67</x:v>
+        <x:v>1918</x:v>
       </x:c>
       <x:c r="K177" s="24" t="n">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="L177" s="28"/>
-      <x:c r="M177" s="29"/>
+        <x:v>-612</x:v>
+      </x:c>
+      <x:c r="L177" s="28" t="n">
+        <x:v>0.7581027667984189</x:v>
+      </x:c>
+      <x:c r="M177" s="29" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="178" ht="15" hidden="0" customHeight="1">
       <x:c r="A178" s="11" t="str">
@@ -6876,16 +6876,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C178" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D178" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E178" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F178" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G178" s="21" t="str">
         <x:v>2026-07-08</x:v>
@@ -6894,19 +6894,19 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I178" s="24" t="n">
-        <x:v>150</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="J178" s="24" t="n">
-        <x:v>145</x:v>
+        <x:v>1893</x:v>
       </x:c>
       <x:c r="K178" s="24" t="n">
-        <x:v>-5</x:v>
+        <x:v>-157</x:v>
       </x:c>
       <x:c r="L178" s="28" t="n">
-        <x:v>0.9666666666666667</x:v>
+        <x:v>0.9234146341463415</x:v>
       </x:c>
       <x:c r="M178" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -6923,32 +6923,24 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E179" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F179" s="21" t="str">
         <x:v>2026-07-03</x:v>
       </x:c>
-      <x:c r="G179" s="21" t="str">
-        <x:v>2026-07-08</x:v>
-      </x:c>
-      <x:c r="H179" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
+      <x:c r="G179" s="21"/>
+      <x:c r="H179" s="21"/>
       <x:c r="I179" s="24" t="n">
-        <x:v>350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J179" s="24" t="n">
-        <x:v>155</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="K179" s="24" t="n">
-        <x:v>-195</x:v>
-      </x:c>
-      <x:c r="L179" s="28" t="n">
-        <x:v>0.44285714285714284</x:v>
-      </x:c>
-      <x:c r="M179" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="L179" s="28"/>
+      <x:c r="M179" s="29"/>
     </x:row>
     <x:row r="180" ht="15" hidden="0" customHeight="1">
       <x:c r="A180" s="11" t="str">
@@ -6964,10 +6956,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E180" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F180" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G180" s="21" t="str">
         <x:v>2026-07-08</x:v>
@@ -6976,19 +6968,19 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I180" s="24" t="n">
-        <x:v>250</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J180" s="24" t="n">
-        <x:v>132</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="K180" s="24" t="n">
-        <x:v>-118</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="L180" s="28" t="n">
-        <x:v>0.528</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="M180" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="15" hidden="0" customHeight="1">
@@ -7005,10 +6997,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E181" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F181" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G181" s="21" t="str">
         <x:v>2026-07-08</x:v>
@@ -7017,19 +7009,19 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I181" s="24" t="n">
-        <x:v>250</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="J181" s="24" t="n">
-        <x:v>163</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="K181" s="24" t="n">
-        <x:v>-87</x:v>
+        <x:v>-132</x:v>
       </x:c>
       <x:c r="L181" s="28" t="n">
-        <x:v>0.652</x:v>
+        <x:v>0.6228571428571429</x:v>
       </x:c>
       <x:c r="M181" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="15" hidden="0" customHeight="1">
@@ -7040,30 +7032,38 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C182" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D182" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E182" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F182" s="21" t="str">
-        <x:v>2026-07-03</x:v>
-      </x:c>
-      <x:c r="G182" s="21"/>
-      <x:c r="H182" s="21"/>
+        <x:v>2026-07-06</x:v>
+      </x:c>
+      <x:c r="G182" s="21" t="str">
+        <x:v>2026-07-08</x:v>
+      </x:c>
+      <x:c r="H182" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
       <x:c r="I182" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="J182" s="24" t="n">
-        <x:v>6</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="K182" s="24" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="L182" s="28"/>
-      <x:c r="M182" s="29"/>
+        <x:v>-61</x:v>
+      </x:c>
+      <x:c r="L182" s="28" t="n">
+        <x:v>0.756</x:v>
+      </x:c>
+      <x:c r="M182" s="29" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="183" ht="15" hidden="0" customHeight="1">
       <x:c r="A183" s="11" t="str">
@@ -7073,30 +7073,38 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C183" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D183" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E183" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F183" s="21" t="str">
-        <x:v>2026-07-03</x:v>
-      </x:c>
-      <x:c r="G183" s="21"/>
-      <x:c r="H183" s="21"/>
+        <x:v>2026-07-06</x:v>
+      </x:c>
+      <x:c r="G183" s="21" t="str">
+        <x:v>2026-07-08</x:v>
+      </x:c>
+      <x:c r="H183" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
       <x:c r="I183" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="J183" s="24" t="n">
-        <x:v>6</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="K183" s="24" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="L183" s="28"/>
-      <x:c r="M183" s="29"/>
+        <x:v>-20</x:v>
+      </x:c>
+      <x:c r="L183" s="28" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="M183" s="29" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="184" ht="15" hidden="0" customHeight="1">
       <x:c r="A184" s="11" t="str">
@@ -7112,10 +7120,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E184" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F184" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="G184" s="21"/>
       <x:c r="H184" s="21"/>
@@ -7123,10 +7131,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J184" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K184" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L184" s="28"/>
       <x:c r="M184" s="29"/>
@@ -7145,10 +7153,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E185" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F185" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-04</x:v>
       </x:c>
       <x:c r="G185" s="21"/>
       <x:c r="H185" s="21"/>
@@ -7156,10 +7164,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J185" s="24" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K185" s="24" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L185" s="28"/>
       <x:c r="M185" s="29"/>
@@ -7175,13 +7183,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D186" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E186" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F186" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-04</x:v>
       </x:c>
       <x:c r="G186" s="21"/>
       <x:c r="H186" s="21"/>
@@ -7189,10 +7197,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J186" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K186" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L186" s="28"/>
       <x:c r="M186" s="29"/>
@@ -7208,13 +7216,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D187" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E187" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F187" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="G187" s="21"/>
       <x:c r="H187" s="21"/>
@@ -7222,10 +7230,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J187" s="24" t="n">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K187" s="24" t="n">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="L187" s="28"/>
       <x:c r="M187" s="29"/>
@@ -7244,10 +7252,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E188" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F188" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G188" s="21"/>
       <x:c r="H188" s="21"/>
@@ -7255,10 +7263,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J188" s="24" t="n">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K188" s="24" t="n">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L188" s="28"/>
       <x:c r="M188" s="29"/>
@@ -7277,10 +7285,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E189" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F189" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G189" s="21"/>
       <x:c r="H189" s="21"/>
@@ -7288,10 +7296,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J189" s="24" t="n">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="K189" s="24" t="n">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L189" s="28"/>
       <x:c r="M189" s="29"/>
@@ -7307,35 +7315,27 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D190" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E190" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F190" s="21" t="str">
-        <x:v>2026-07-03</x:v>
-      </x:c>
-      <x:c r="G190" s="21" t="str">
-        <x:v>2026-07-08</x:v>
-      </x:c>
-      <x:c r="H190" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
+        <x:v>2026-07-06</x:v>
+      </x:c>
+      <x:c r="G190" s="21"/>
+      <x:c r="H190" s="21"/>
       <x:c r="I190" s="24" t="n">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J190" s="24" t="n">
-        <x:v>46</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K190" s="24" t="n">
-        <x:v>-54</x:v>
-      </x:c>
-      <x:c r="L190" s="28" t="n">
-        <x:v>0.46</x:v>
-      </x:c>
-      <x:c r="M190" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="L190" s="28"/>
+      <x:c r="M190" s="29"/>
     </x:row>
     <x:row r="191" ht="15" hidden="0" customHeight="1">
       <x:c r="A191" s="11" t="str">
@@ -7348,35 +7348,27 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D191" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E191" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F191" s="21" t="str">
-        <x:v>2026-07-03</x:v>
-      </x:c>
-      <x:c r="G191" s="21" t="str">
-        <x:v>2026-07-08</x:v>
-      </x:c>
-      <x:c r="H191" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
+        <x:v>2026-07-06</x:v>
+      </x:c>
+      <x:c r="G191" s="21"/>
+      <x:c r="H191" s="21"/>
       <x:c r="I191" s="24" t="n">
-        <x:v>230</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J191" s="24" t="n">
-        <x:v>89</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="K191" s="24" t="n">
-        <x:v>-141</x:v>
-      </x:c>
-      <x:c r="L191" s="28" t="n">
-        <x:v>0.3869565217391304</x:v>
-      </x:c>
-      <x:c r="M191" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L191" s="28"/>
+      <x:c r="M191" s="29"/>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
       <x:c r="A192" s="11" t="str">
@@ -7392,10 +7384,10 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E192" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F192" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="G192" s="21" t="str">
         <x:v>2026-07-08</x:v>
@@ -7404,19 +7396,19 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I192" s="24" t="n">
-        <x:v>330</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J192" s="24" t="n">
-        <x:v>137</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="K192" s="24" t="n">
-        <x:v>-193</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="L192" s="28" t="n">
-        <x:v>0.41515151515151516</x:v>
+        <x:v>0.9</x:v>
       </x:c>
       <x:c r="M192" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="15" hidden="0" customHeight="1">
@@ -7433,10 +7425,10 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E193" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F193" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G193" s="21" t="str">
         <x:v>2026-07-08</x:v>
@@ -7445,19 +7437,19 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I193" s="24" t="n">
-        <x:v>330</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="J193" s="24" t="n">
-        <x:v>132</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="K193" s="24" t="n">
-        <x:v>-198</x:v>
+        <x:v>-44</x:v>
       </x:c>
       <x:c r="L193" s="28" t="n">
-        <x:v>0.4</x:v>
+        <x:v>0.808695652173913</x:v>
       </x:c>
       <x:c r="M193" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="15" hidden="0" customHeight="1">
@@ -7474,10 +7466,10 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E194" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F194" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="G194" s="21" t="str">
         <x:v>2026-07-08</x:v>
@@ -7486,86 +7478,102 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I194" s="24" t="n">
-        <x:v>420</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="J194" s="24" t="n">
-        <x:v>198</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="K194" s="24" t="n">
-        <x:v>-222</x:v>
+        <x:v>-54</x:v>
       </x:c>
       <x:c r="L194" s="28" t="n">
-        <x:v>0.4714285714285714</x:v>
+        <x:v>0.8363636363636363</x:v>
       </x:c>
       <x:c r="M194" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="15" hidden="0" customHeight="1">
       <x:c r="A195" s="11" t="str">
-        <x:v>自拼</x:v>
+        <x:v>小学</x:v>
       </x:c>
       <x:c r="B195" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C195" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D195" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E195" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F195" s="21" t="str">
-        <x:v>2026-06-22</x:v>
-      </x:c>
-      <x:c r="G195" s="21"/>
-      <x:c r="H195" s="21"/>
+        <x:v>2026-07-05</x:v>
+      </x:c>
+      <x:c r="G195" s="21" t="str">
+        <x:v>2026-07-08</x:v>
+      </x:c>
+      <x:c r="H195" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
       <x:c r="I195" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="J195" s="24" t="n">
-        <x:v>218</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="K195" s="24" t="n">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="L195" s="28"/>
-      <x:c r="M195" s="29"/>
+        <x:v>-72</x:v>
+      </x:c>
+      <x:c r="L195" s="28" t="n">
+        <x:v>0.7818181818181819</x:v>
+      </x:c>
+      <x:c r="M195" s="29" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
       <x:c r="A196" s="11" t="str">
-        <x:v>自拼</x:v>
+        <x:v>小学</x:v>
       </x:c>
       <x:c r="B196" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C196" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D196" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E196" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F196" s="21" t="str">
-        <x:v>2026-06-23</x:v>
-      </x:c>
-      <x:c r="G196" s="21"/>
-      <x:c r="H196" s="21"/>
+        <x:v>2026-07-05</x:v>
+      </x:c>
+      <x:c r="G196" s="21" t="str">
+        <x:v>2026-07-08</x:v>
+      </x:c>
+      <x:c r="H196" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
       <x:c r="I196" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="J196" s="24" t="n">
-        <x:v>79</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="K196" s="24" t="n">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="L196" s="28"/>
-      <x:c r="M196" s="29"/>
+        <x:v>-51</x:v>
+      </x:c>
+      <x:c r="L196" s="28" t="n">
+        <x:v>0.8785714285714286</x:v>
+      </x:c>
+      <x:c r="M196" s="29" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="197" ht="15" hidden="0" customHeight="1">
       <x:c r="A197" s="11" t="str">
@@ -7581,10 +7589,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E197" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F197" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G197" s="21"/>
       <x:c r="H197" s="21"/>
@@ -7592,10 +7600,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J197" s="24" t="n">
-        <x:v>32</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="K197" s="24" t="n">
-        <x:v>32</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="L197" s="28"/>
       <x:c r="M197" s="29"/>
@@ -7608,16 +7616,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C198" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D198" s="18" t="n">
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E198" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F198" s="21" t="str">
-        <x:v>2026-06-22</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G198" s="21"/>
       <x:c r="H198" s="21"/>
@@ -7625,10 +7633,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J198" s="24" t="n">
-        <x:v>314</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="K198" s="24" t="n">
-        <x:v>314</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="L198" s="28"/>
       <x:c r="M198" s="29"/>
@@ -7641,13 +7649,13 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C199" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D199" s="18" t="n">
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E199" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F199" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -7658,10 +7666,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J199" s="24" t="n">
-        <x:v>116</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K199" s="24" t="n">
-        <x:v>116</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L199" s="28"/>
       <x:c r="M199" s="29"/>
@@ -7680,10 +7688,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E200" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F200" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G200" s="21"/>
       <x:c r="H200" s="21"/>
@@ -7691,10 +7699,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J200" s="24" t="n">
-        <x:v>89</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="K200" s="24" t="n">
-        <x:v>89</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="L200" s="28"/>
       <x:c r="M200" s="29"/>
@@ -7707,16 +7715,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C201" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D201" s="18" t="n">
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E201" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F201" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G201" s="21"/>
       <x:c r="H201" s="21"/>
@@ -7724,10 +7732,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J201" s="24" t="n">
-        <x:v>32</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K201" s="24" t="n">
-        <x:v>32</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="L201" s="28"/>
       <x:c r="M201" s="29"/>
@@ -7740,13 +7748,13 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C202" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D202" s="18" t="n">
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E202" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F202" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -7757,10 +7765,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J202" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K202" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="L202" s="28"/>
       <x:c r="M202" s="29"/>
@@ -7779,10 +7787,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E203" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F203" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G203" s="21"/>
       <x:c r="H203" s="21"/>
@@ -7790,10 +7798,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J203" s="24" t="n">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K203" s="24" t="n">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L203" s="28"/>
       <x:c r="M203" s="29"/>
@@ -7806,16 +7814,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C204" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D204" s="18" t="n">
-        <x:v>29.9</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E204" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F204" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G204" s="21"/>
       <x:c r="H204" s="21"/>
@@ -7823,10 +7831,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J204" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K204" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L204" s="28"/>
       <x:c r="M204" s="29"/>
@@ -7839,16 +7847,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C205" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D205" s="18" t="n">
-        <x:v>29.9</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E205" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F205" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G205" s="21"/>
       <x:c r="H205" s="21"/>
@@ -7856,10 +7864,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J205" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K205" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L205" s="28"/>
       <x:c r="M205" s="29"/>
@@ -7878,10 +7886,10 @@
         <x:v>29.9</x:v>
       </x:c>
       <x:c r="E206" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F206" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G206" s="21"/>
       <x:c r="H206" s="21"/>
@@ -7889,10 +7897,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J206" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K206" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L206" s="28"/>
       <x:c r="M206" s="29"/>
@@ -7902,19 +7910,19 @@
         <x:v>自拼</x:v>
       </x:c>
       <x:c r="B207" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C207" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D207" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="E207" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F207" s="21" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G207" s="21"/>
       <x:c r="H207" s="21"/>
@@ -7922,10 +7930,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J207" s="24" t="n">
-        <x:v>295</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K207" s="24" t="n">
-        <x:v>295</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L207" s="28"/>
       <x:c r="M207" s="29"/>
@@ -7935,19 +7943,19 @@
         <x:v>自拼</x:v>
       </x:c>
       <x:c r="B208" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C208" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D208" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="E208" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F208" s="21" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G208" s="21"/>
       <x:c r="H208" s="21"/>
@@ -7955,10 +7963,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J208" s="24" t="n">
-        <x:v>47</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K208" s="24" t="n">
-        <x:v>47</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L208" s="28"/>
       <x:c r="M208" s="29"/>
@@ -7977,7 +7985,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E209" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F209" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -7988,10 +7996,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J209" s="24" t="n">
-        <x:v>50</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="K209" s="24" t="n">
-        <x:v>50</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="L209" s="28"/>
       <x:c r="M209" s="29"/>
@@ -8004,13 +8012,13 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C210" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D210" s="18" t="n">
-        <x:v>29.9</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E210" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F210" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -8021,10 +8029,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J210" s="24" t="n">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K210" s="24" t="n">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="L210" s="28"/>
       <x:c r="M210" s="29"/>
@@ -8037,13 +8045,13 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C211" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D211" s="18" t="n">
-        <x:v>29.9</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E211" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F211" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -8054,10 +8062,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J211" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K211" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L211" s="28"/>
       <x:c r="M211" s="29"/>
@@ -8076,7 +8084,7 @@
         <x:v>29.9</x:v>
       </x:c>
       <x:c r="E212" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F212" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -8087,10 +8095,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J212" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K212" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L212" s="28"/>
       <x:c r="M212" s="29"/>
@@ -8100,19 +8108,19 @@
         <x:v>自拼</x:v>
       </x:c>
       <x:c r="B213" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C213" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D213" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="E213" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F213" s="21" t="str">
-        <x:v>2026-07-01</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G213" s="21"/>
       <x:c r="H213" s="21"/>
@@ -8120,10 +8128,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J213" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K213" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L213" s="28"/>
       <x:c r="M213" s="29"/>
@@ -8133,19 +8141,19 @@
         <x:v>自拼</x:v>
       </x:c>
       <x:c r="B214" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C214" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D214" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="E214" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F214" s="21" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G214" s="21"/>
       <x:c r="H214" s="21"/>
@@ -8153,10 +8161,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J214" s="24" t="n">
-        <x:v>192</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K214" s="24" t="n">
-        <x:v>192</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L214" s="28"/>
       <x:c r="M214" s="29"/>
@@ -8169,16 +8177,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C215" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D215" s="18" t="n">
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E215" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F215" s="21" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>2026-07-01</x:v>
       </x:c>
       <x:c r="G215" s="21"/>
       <x:c r="H215" s="21"/>
@@ -8186,10 +8194,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J215" s="24" t="n">
-        <x:v>89</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K215" s="24" t="n">
-        <x:v>89</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L215" s="28"/>
       <x:c r="M215" s="29"/>
@@ -8208,7 +8216,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E216" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F216" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -8219,10 +8227,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J216" s="24" t="n">
-        <x:v>50</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="K216" s="24" t="n">
-        <x:v>50</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="L216" s="28"/>
       <x:c r="M216" s="29"/>
@@ -8235,13 +8243,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C217" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D217" s="18" t="n">
-        <x:v>29.9</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E217" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F217" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -8252,10 +8260,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J217" s="24" t="n">
-        <x:v>9</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K217" s="24" t="n">
-        <x:v>9</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="L217" s="28"/>
       <x:c r="M217" s="29"/>
@@ -8268,16 +8276,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C218" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D218" s="18" t="n">
-        <x:v>29.9</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E218" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F218" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="G218" s="21"/>
       <x:c r="H218" s="21"/>
@@ -8285,10 +8293,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J218" s="24" t="n">
-        <x:v>15</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K218" s="24" t="n">
-        <x:v>15</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L218" s="28"/>
       <x:c r="M218" s="29"/>
@@ -8307,10 +8315,10 @@
         <x:v>29.9</x:v>
       </x:c>
       <x:c r="E219" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F219" s="21" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>2026-07-04</x:v>
       </x:c>
       <x:c r="G219" s="21"/>
       <x:c r="H219" s="21"/>
@@ -8318,32 +8326,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J219" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K219" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L219" s="28"/>
       <x:c r="M219" s="29"/>
     </x:row>
     <x:row r="220" ht="15" hidden="0" customHeight="1">
       <x:c r="A220" s="11" t="str">
-        <x:v>高中</x:v>
+        <x:v>自拼</x:v>
       </x:c>
       <x:c r="B220" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C220" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D220" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="E220" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F220" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-07-04</x:v>
       </x:c>
       <x:c r="G220" s="21"/>
       <x:c r="H220" s="21"/>
@@ -8351,32 +8359,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J220" s="24" t="n">
-        <x:v>55</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K220" s="24" t="n">
-        <x:v>55</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="L220" s="28"/>
       <x:c r="M220" s="29"/>
     </x:row>
     <x:row r="221" ht="15" hidden="0" customHeight="1">
       <x:c r="A221" s="11" t="str">
-        <x:v>高中</x:v>
+        <x:v>自拼</x:v>
       </x:c>
       <x:c r="B221" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C221" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D221" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="E221" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F221" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="G221" s="21"/>
       <x:c r="H221" s="21"/>
@@ -8384,10 +8392,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J221" s="24" t="n">
-        <x:v>115</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K221" s="24" t="n">
-        <x:v>115</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L221" s="28"/>
       <x:c r="M221" s="29"/>
@@ -8406,7 +8414,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E222" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F222" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -8417,10 +8425,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J222" s="24" t="n">
-        <x:v>96</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K222" s="24" t="n">
-        <x:v>96</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="L222" s="28"/>
       <x:c r="M222" s="29"/>
@@ -8433,13 +8441,13 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C223" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D223" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E223" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F223" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -8450,10 +8458,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J223" s="24" t="n">
-        <x:v>100</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="K223" s="24" t="n">
-        <x:v>100</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="L223" s="28"/>
       <x:c r="M223" s="29"/>
@@ -8466,16 +8474,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C224" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D224" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E224" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F224" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G224" s="21"/>
       <x:c r="H224" s="21"/>
@@ -8483,10 +8491,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J224" s="24" t="n">
-        <x:v>73</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K224" s="24" t="n">
-        <x:v>73</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="L224" s="28"/>
       <x:c r="M224" s="29"/>
@@ -8505,7 +8513,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E225" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F225" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -8516,10 +8524,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J225" s="24" t="n">
-        <x:v>106</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K225" s="24" t="n">
-        <x:v>106</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="L225" s="28"/>
       <x:c r="M225" s="29"/>
@@ -8532,16 +8540,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C226" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D226" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E226" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F226" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G226" s="21"/>
       <x:c r="H226" s="21"/>
@@ -8549,10 +8557,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J226" s="24" t="n">
-        <x:v>681</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K226" s="24" t="n">
-        <x:v>681</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="L226" s="28"/>
       <x:c r="M226" s="29"/>
@@ -8565,16 +8573,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C227" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D227" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E227" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F227" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G227" s="21"/>
       <x:c r="H227" s="21"/>
@@ -8582,10 +8590,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J227" s="24" t="n">
-        <x:v>186</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="K227" s="24" t="n">
-        <x:v>186</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="L227" s="28"/>
       <x:c r="M227" s="29"/>
@@ -8598,16 +8606,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C228" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D228" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E228" s="12" t="str">
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F228" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G228" s="21"/>
       <x:c r="H228" s="21"/>
@@ -8615,10 +8623,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J228" s="24" t="n">
-        <x:v>9</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="K228" s="24" t="n">
-        <x:v>9</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="L228" s="28"/>
       <x:c r="M228" s="29"/>
@@ -8631,10 +8639,10 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C229" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D229" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E229" s="12" t="str">
         <x:v>高二</x:v>
@@ -8648,10 +8656,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J229" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="K229" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="L229" s="28"/>
       <x:c r="M229" s="29"/>
@@ -8670,7 +8678,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E230" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F230" s="21" t="str">
         <x:v>2026-06-21</x:v>
@@ -8681,10 +8689,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J230" s="24" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K230" s="24" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L230" s="28"/>
       <x:c r="M230" s="29"/>
@@ -8700,13 +8708,13 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D231" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E231" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F231" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G231" s="21"/>
       <x:c r="H231" s="21"/>
@@ -8714,10 +8722,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J231" s="24" t="n">
-        <x:v>357</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K231" s="24" t="n">
-        <x:v>357</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L231" s="28"/>
       <x:c r="M231" s="29"/>
@@ -8733,13 +8741,13 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D232" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E232" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F232" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G232" s="21"/>
       <x:c r="H232" s="21"/>
@@ -8747,10 +8755,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J232" s="24" t="n">
-        <x:v>291</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K232" s="24" t="n">
-        <x:v>291</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L232" s="28"/>
       <x:c r="M232" s="29"/>
@@ -8769,7 +8777,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E233" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F233" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -8780,10 +8788,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J233" s="24" t="n">
-        <x:v>320</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="K233" s="24" t="n">
-        <x:v>320</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="L233" s="28"/>
       <x:c r="M233" s="29"/>
@@ -8796,13 +8804,13 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C234" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D234" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E234" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F234" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -8813,10 +8821,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J234" s="24" t="n">
-        <x:v>697</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="K234" s="24" t="n">
-        <x:v>697</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="L234" s="28"/>
       <x:c r="M234" s="29"/>
@@ -8829,13 +8837,13 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C235" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D235" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E235" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F235" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -8846,10 +8854,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J235" s="24" t="n">
-        <x:v>960</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="K235" s="24" t="n">
-        <x:v>960</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="L235" s="28"/>
       <x:c r="M235" s="29"/>
@@ -8868,7 +8876,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E236" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F236" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -8879,10 +8887,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J236" s="24" t="n">
-        <x:v>633</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="K236" s="24" t="n">
-        <x:v>633</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="L236" s="28"/>
       <x:c r="M236" s="29"/>
@@ -8898,10 +8906,10 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D237" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E237" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F237" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -8912,10 +8920,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J237" s="24" t="n">
-        <x:v>434</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="K237" s="24" t="n">
-        <x:v>434</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="L237" s="28"/>
       <x:c r="M237" s="29"/>
@@ -8931,10 +8939,10 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D238" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E238" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F238" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -8945,10 +8953,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J238" s="24" t="n">
-        <x:v>625</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="K238" s="24" t="n">
-        <x:v>625</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="L238" s="28"/>
       <x:c r="M238" s="29"/>
@@ -8967,7 +8975,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E239" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F239" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -8978,10 +8986,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J239" s="24" t="n">
-        <x:v>558</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="K239" s="24" t="n">
-        <x:v>558</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="L239" s="28"/>
       <x:c r="M239" s="29"/>
@@ -8991,82 +8999,66 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B240" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C240" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D240" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E240" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F240" s="21" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="G240" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H240" s="21" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
+      <x:c r="G240" s="21"/>
+      <x:c r="H240" s="21"/>
       <x:c r="I240" s="24" t="n">
-        <x:v>80</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J240" s="24" t="n">
-        <x:v>81</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="K240" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L240" s="28" t="n">
-        <x:v>1.0125</x:v>
-      </x:c>
-      <x:c r="M240" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="L240" s="28"/>
+      <x:c r="M240" s="29"/>
     </x:row>
     <x:row r="241" ht="15" hidden="0" customHeight="1">
       <x:c r="A241" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B241" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C241" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D241" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E241" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F241" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="G241" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H241" s="21" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
+      <x:c r="G241" s="21"/>
+      <x:c r="H241" s="21"/>
       <x:c r="I241" s="24" t="n">
-        <x:v>160</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J241" s="24" t="n">
-        <x:v>194</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="K241" s="24" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="L241" s="28" t="n">
-        <x:v>1.2125</x:v>
-      </x:c>
-      <x:c r="M241" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="L241" s="28"/>
+      <x:c r="M241" s="29"/>
     </x:row>
     <x:row r="242" ht="15" hidden="0" customHeight="1">
       <x:c r="A242" s="11" t="str">
@@ -9082,10 +9074,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E242" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F242" s="21" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G242" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9094,16 +9086,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I242" s="24" t="n">
-        <x:v>160</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J242" s="24" t="n">
-        <x:v>139</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K242" s="24" t="n">
-        <x:v>-21</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L242" s="28" t="n">
-        <x:v>0.86875</x:v>
+        <x:v>1.0125</x:v>
       </x:c>
       <x:c r="M242" s="29" t="n">
         <x:v>1</x:v>
@@ -9117,16 +9109,16 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C243" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D243" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E243" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F243" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="G243" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9135,16 +9127,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I243" s="24" t="n">
-        <x:v>50</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="J243" s="24" t="n">
-        <x:v>882</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="K243" s="24" t="n">
-        <x:v>832</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L243" s="28" t="n">
-        <x:v>17.64</x:v>
+        <x:v>1.2125</x:v>
       </x:c>
       <x:c r="M243" s="29" t="n">
         <x:v>1</x:v>
@@ -9158,16 +9150,16 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C244" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D244" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E244" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F244" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="G244" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9176,16 +9168,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I244" s="24" t="n">
-        <x:v>900</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="J244" s="24" t="n">
-        <x:v>226</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="K244" s="24" t="n">
-        <x:v>-674</x:v>
+        <x:v>-21</x:v>
       </x:c>
       <x:c r="L244" s="28" t="n">
-        <x:v>0.2511111111111111</x:v>
+        <x:v>0.86875</x:v>
       </x:c>
       <x:c r="M244" s="29" t="n">
         <x:v>1</x:v>
@@ -9205,9 +9197,11 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E245" s="12" t="str">
-        <x:v>高三</x:v>
-      </x:c>
-      <x:c r="F245" s="21"/>
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F245" s="21" t="str">
+        <x:v>2026-07-04</x:v>
+      </x:c>
       <x:c r="G245" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -9215,16 +9209,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I245" s="24" t="n">
-        <x:v>200</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J245" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>883</x:v>
       </x:c>
       <x:c r="K245" s="24" t="n">
-        <x:v>-200</x:v>
+        <x:v>833</x:v>
       </x:c>
       <x:c r="L245" s="28" t="n">
-        <x:v>0</x:v>
+        <x:v>17.66</x:v>
       </x:c>
       <x:c r="M245" s="29" t="n">
         <x:v>1</x:v>
@@ -9238,16 +9232,16 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C246" s="12" t="str">
-        <x:v>图书店铺</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D246" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E246" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F246" s="21" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="G246" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9256,16 +9250,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I246" s="24" t="n">
-        <x:v>100</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="J246" s="24" t="n">
-        <x:v>129</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="K246" s="24" t="n">
-        <x:v>29</x:v>
+        <x:v>-671</x:v>
       </x:c>
       <x:c r="L246" s="28" t="n">
-        <x:v>1.29</x:v>
+        <x:v>0.2544444444444444</x:v>
       </x:c>
       <x:c r="M246" s="29" t="n">
         <x:v>1</x:v>
@@ -9279,16 +9273,16 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C247" s="12" t="str">
-        <x:v>图书店铺</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D247" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E247" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F247" s="21" t="str">
-        <x:v>2026-07-01</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="G247" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9297,16 +9291,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I247" s="24" t="n">
-        <x:v>150</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="J247" s="24" t="n">
-        <x:v>39</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K247" s="24" t="n">
-        <x:v>-111</x:v>
+        <x:v>-198</x:v>
       </x:c>
       <x:c r="L247" s="28" t="n">
-        <x:v>0.26</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="M247" s="29" t="n">
         <x:v>1</x:v>
@@ -9326,10 +9320,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E248" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F248" s="21" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G248" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9338,16 +9332,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I248" s="24" t="n">
-        <x:v>150</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J248" s="24" t="n">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="K248" s="24" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="K248" s="24" t="n">
-        <x:v>-121</x:v>
-      </x:c>
       <x:c r="L248" s="28" t="n">
-        <x:v>0.19333333333333333</x:v>
+        <x:v>1.29</x:v>
       </x:c>
       <x:c r="M248" s="29" t="n">
         <x:v>1</x:v>
@@ -9361,15 +9355,17 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C249" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>图书店铺</x:v>
       </x:c>
       <x:c r="D249" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E249" s="12" t="str">
-        <x:v>高一</x:v>
-      </x:c>
-      <x:c r="F249" s="21"/>
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F249" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
       <x:c r="G249" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -9380,13 +9376,13 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="J249" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K249" s="24" t="n">
-        <x:v>-150</x:v>
+        <x:v>-111</x:v>
       </x:c>
       <x:c r="L249" s="28" t="n">
-        <x:v>0</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="M249" s="29" t="n">
         <x:v>1</x:v>
@@ -9400,15 +9396,17 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C250" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>图书店铺</x:v>
       </x:c>
       <x:c r="D250" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E250" s="12" t="str">
-        <x:v>高二</x:v>
-      </x:c>
-      <x:c r="F250" s="21"/>
+        <x:v>高三</x:v>
+      </x:c>
+      <x:c r="F250" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
       <x:c r="G250" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -9416,16 +9414,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I250" s="24" t="n">
-        <x:v>200</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J250" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K250" s="24" t="n">
-        <x:v>-200</x:v>
+        <x:v>-121</x:v>
       </x:c>
       <x:c r="L250" s="28" t="n">
-        <x:v>0</x:v>
+        <x:v>0.19333333333333333</x:v>
       </x:c>
       <x:c r="M250" s="29" t="n">
         <x:v>1</x:v>
@@ -9445,7 +9443,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E251" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F251" s="21"/>
       <x:c r="G251" s="21" t="str">
@@ -9481,14 +9479,12 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D252" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E252" s="12" t="str">
-        <x:v>高一</x:v>
-      </x:c>
-      <x:c r="F252" s="21" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F252" s="21"/>
       <x:c r="G252" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -9496,16 +9492,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I252" s="24" t="n">
-        <x:v>300</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="J252" s="24" t="n">
-        <x:v>298</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K252" s="24" t="n">
-        <x:v>-2</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="L252" s="28" t="n">
-        <x:v>0.9933333333333333</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M252" s="29" t="n">
         <x:v>1</x:v>
@@ -9522,14 +9518,12 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D253" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E253" s="12" t="str">
-        <x:v>高二</x:v>
-      </x:c>
-      <x:c r="F253" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
+        <x:v>高三</x:v>
+      </x:c>
+      <x:c r="F253" s="21"/>
       <x:c r="G253" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -9537,16 +9531,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I253" s="24" t="n">
-        <x:v>530</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J253" s="24" t="n">
-        <x:v>374</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K253" s="24" t="n">
-        <x:v>-156</x:v>
+        <x:v>-150</x:v>
       </x:c>
       <x:c r="L253" s="28" t="n">
-        <x:v>0.7056603773584905</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M253" s="29" t="n">
         <x:v>1</x:v>
@@ -9566,10 +9560,10 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E254" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F254" s="21" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G254" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9578,16 +9572,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I254" s="24" t="n">
-        <x:v>600</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J254" s="24" t="n">
-        <x:v>485</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="K254" s="24" t="n">
-        <x:v>-115</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="L254" s="28" t="n">
-        <x:v>0.8083333333333333</x:v>
+        <x:v>0.9933333333333333</x:v>
       </x:c>
       <x:c r="M254" s="29" t="n">
         <x:v>1</x:v>
@@ -9601,13 +9595,13 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C255" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D255" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E255" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F255" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9619,16 +9613,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I255" s="24" t="n">
-        <x:v>180</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="J255" s="24" t="n">
-        <x:v>307</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="K255" s="24" t="n">
-        <x:v>127</x:v>
+        <x:v>-156</x:v>
       </x:c>
       <x:c r="L255" s="28" t="n">
-        <x:v>1.7055555555555555</x:v>
+        <x:v>0.7056603773584905</x:v>
       </x:c>
       <x:c r="M255" s="29" t="n">
         <x:v>1</x:v>
@@ -9642,13 +9636,13 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C256" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D256" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E256" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F256" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9660,16 +9654,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I256" s="24" t="n">
-        <x:v>1500</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="J256" s="24" t="n">
-        <x:v>1518</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="K256" s="24" t="n">
-        <x:v>18</x:v>
+        <x:v>-115</x:v>
       </x:c>
       <x:c r="L256" s="28" t="n">
-        <x:v>1.012</x:v>
+        <x:v>0.8083333333333333</x:v>
       </x:c>
       <x:c r="M256" s="29" t="n">
         <x:v>1</x:v>
@@ -9689,7 +9683,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E257" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F257" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9701,16 +9695,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I257" s="24" t="n">
-        <x:v>870</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="J257" s="24" t="n">
-        <x:v>1008</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="K257" s="24" t="n">
-        <x:v>138</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="L257" s="28" t="n">
-        <x:v>1.1586206896551725</x:v>
+        <x:v>1.7055555555555555</x:v>
       </x:c>
       <x:c r="M257" s="29" t="n">
         <x:v>1</x:v>
@@ -9727,27 +9721,35 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D258" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E258" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F258" s="21" t="str">
-        <x:v>2026-06-28</x:v>
-      </x:c>
-      <x:c r="G258" s="21"/>
-      <x:c r="H258" s="21"/>
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="G258" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H258" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I258" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="J258" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>1518</x:v>
       </x:c>
       <x:c r="K258" s="24" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="L258" s="28"/>
-      <x:c r="M258" s="29"/>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L258" s="28" t="n">
+        <x:v>1.012</x:v>
+      </x:c>
+      <x:c r="M258" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="259" ht="15" hidden="0" customHeight="1">
       <x:c r="A259" s="11" t="str">
@@ -9760,27 +9762,35 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D259" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E259" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F259" s="21" t="str">
-        <x:v>2026-06-28</x:v>
-      </x:c>
-      <x:c r="G259" s="21"/>
-      <x:c r="H259" s="21"/>
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="G259" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H259" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I259" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>870</x:v>
       </x:c>
       <x:c r="J259" s="24" t="n">
-        <x:v>63</x:v>
+        <x:v>1008</x:v>
       </x:c>
       <x:c r="K259" s="24" t="n">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="L259" s="28"/>
-      <x:c r="M259" s="29"/>
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="L259" s="28" t="n">
+        <x:v>1.1586206896551725</x:v>
+      </x:c>
+      <x:c r="M259" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="260" ht="15" hidden="0" customHeight="1">
       <x:c r="A260" s="11" t="str">
@@ -9796,7 +9806,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E260" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F260" s="21" t="str">
         <x:v>2026-06-28</x:v>
@@ -9807,10 +9817,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J260" s="24" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K260" s="24" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L260" s="28"/>
       <x:c r="M260" s="29"/>
@@ -9826,31 +9836,27 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D261" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E261" s="12" t="str">
-        <x:v>高一</x:v>
-      </x:c>
-      <x:c r="F261" s="21"/>
-      <x:c r="G261" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H261" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F261" s="21" t="str">
+        <x:v>2026-06-28</x:v>
+      </x:c>
+      <x:c r="G261" s="21"/>
+      <x:c r="H261" s="21"/>
       <x:c r="I261" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J261" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K261" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L261" s="28"/>
-      <x:c r="M261" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="M261" s="29"/>
     </x:row>
     <x:row r="262" ht="15" hidden="0" customHeight="1">
       <x:c r="A262" s="11" t="str">
@@ -9863,35 +9869,27 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D262" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E262" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F262" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="G262" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H262" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-28</x:v>
+      </x:c>
+      <x:c r="G262" s="21"/>
+      <x:c r="H262" s="21"/>
       <x:c r="I262" s="24" t="n">
-        <x:v>700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J262" s="24" t="n">
-        <x:v>788</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K262" s="24" t="n">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="L262" s="28" t="n">
-        <x:v>1.1257142857142857</x:v>
-      </x:c>
-      <x:c r="M262" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L262" s="28"/>
+      <x:c r="M262" s="29"/>
     </x:row>
     <x:row r="263" ht="15" hidden="0" customHeight="1">
       <x:c r="A263" s="11" t="str">
@@ -9907,11 +9905,9 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E263" s="12" t="str">
-        <x:v>高三</x:v>
-      </x:c>
-      <x:c r="F263" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F263" s="21"/>
       <x:c r="G263" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -9919,17 +9915,15 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I263" s="24" t="n">
-        <x:v>650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J263" s="24" t="n">
-        <x:v>731</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K263" s="24" t="n">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="L263" s="28" t="n">
-        <x:v>1.1246153846153846</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L263" s="28"/>
       <x:c r="M263" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -9939,40 +9933,40 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B264" s="12" t="str">
-        <x:v>暑_12</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C264" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D264" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E264" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F264" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="G264" s="21" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="H264" s="21" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I264" s="24" t="n">
-        <x:v>70</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="J264" s="24" t="n">
-        <x:v>25</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="K264" s="24" t="n">
-        <x:v>-45</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="L264" s="28" t="n">
-        <x:v>0.35714285714285715</x:v>
+        <x:v>1.1257142857142857</x:v>
       </x:c>
       <x:c r="M264" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="265" ht="15" hidden="0" customHeight="1">
@@ -9980,40 +9974,40 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B265" s="12" t="str">
-        <x:v>暑_12</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C265" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D265" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E265" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F265" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="G265" s="21" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="H265" s="21" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I265" s="24" t="n">
-        <x:v>140</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="J265" s="24" t="n">
-        <x:v>34</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="K265" s="24" t="n">
-        <x:v>-106</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="L265" s="28" t="n">
-        <x:v>0.24285714285714285</x:v>
+        <x:v>1.1246153846153846</x:v>
       </x:c>
       <x:c r="M265" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="266" ht="15" hidden="0" customHeight="1">
@@ -10030,10 +10024,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E266" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F266" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G266" s="21" t="str">
         <x:v>2026-07-09</x:v>
@@ -10042,19 +10036,19 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I266" s="24" t="n">
-        <x:v>140</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J266" s="24" t="n">
-        <x:v>14</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K266" s="24" t="n">
-        <x:v>-126</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L266" s="28" t="n">
-        <x:v>0.1</x:v>
+        <x:v>1.0285714285714285</x:v>
       </x:c>
       <x:c r="M266" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="267" ht="15" hidden="0" customHeight="1">
@@ -10065,16 +10059,16 @@
         <x:v>暑_12</x:v>
       </x:c>
       <x:c r="C267" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D267" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E267" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F267" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G267" s="21" t="str">
         <x:v>2026-07-09</x:v>
@@ -10083,19 +10077,19 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I267" s="24" t="n">
-        <x:v>100</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J267" s="24" t="n">
-        <x:v>281</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K267" s="24" t="n">
-        <x:v>181</x:v>
+        <x:v>-16</x:v>
       </x:c>
       <x:c r="L267" s="28" t="n">
-        <x:v>2.81</x:v>
+        <x:v>0.8857142857142857</x:v>
       </x:c>
       <x:c r="M267" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="268" ht="15" hidden="0" customHeight="1">
@@ -10106,16 +10100,16 @@
         <x:v>暑_12</x:v>
       </x:c>
       <x:c r="C268" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D268" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E268" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F268" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G268" s="21" t="str">
         <x:v>2026-07-09</x:v>
@@ -10124,19 +10118,19 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I268" s="24" t="n">
-        <x:v>800</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J268" s="24" t="n">
-        <x:v>229</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K268" s="24" t="n">
-        <x:v>-571</x:v>
+        <x:v>-62</x:v>
       </x:c>
       <x:c r="L268" s="28" t="n">
-        <x:v>0.28625</x:v>
+        <x:v>0.5571428571428572</x:v>
       </x:c>
       <x:c r="M268" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="269" ht="15" hidden="0" customHeight="1">
@@ -10153,9 +10147,11 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E269" s="12" t="str">
-        <x:v>高三</x:v>
-      </x:c>
-      <x:c r="F269" s="21"/>
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F269" s="21" t="str">
+        <x:v>2026-07-04</x:v>
+      </x:c>
       <x:c r="G269" s="21" t="str">
         <x:v>2026-07-09</x:v>
       </x:c>
@@ -10163,19 +10159,19 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I269" s="24" t="n">
-        <x:v>700</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J269" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="K269" s="24" t="n">
-        <x:v>-700</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L269" s="28" t="n">
-        <x:v>0</x:v>
+        <x:v>3.4</x:v>
       </x:c>
       <x:c r="M269" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="270" ht="15" hidden="0" customHeight="1">
@@ -10186,15 +10182,17 @@
         <x:v>暑_12</x:v>
       </x:c>
       <x:c r="C270" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D270" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E270" s="12" t="str">
-        <x:v>高一</x:v>
-      </x:c>
-      <x:c r="F270" s="21"/>
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F270" s="21" t="str">
+        <x:v>2026-07-05</x:v>
+      </x:c>
       <x:c r="G270" s="21" t="str">
         <x:v>2026-07-09</x:v>
       </x:c>
@@ -10202,17 +10200,19 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I270" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="J270" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="K270" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L270" s="28"/>
+        <x:v>-14</x:v>
+      </x:c>
+      <x:c r="L270" s="28" t="n">
+        <x:v>0.9825</x:v>
+      </x:c>
       <x:c r="M270" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="271" ht="15" hidden="0" customHeight="1">
@@ -10223,16 +10223,16 @@
         <x:v>暑_12</x:v>
       </x:c>
       <x:c r="C271" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D271" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E271" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F271" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="G271" s="21" t="str">
         <x:v>2026-07-09</x:v>
@@ -10241,19 +10241,19 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I271" s="24" t="n">
-        <x:v>150</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="J271" s="24" t="n">
-        <x:v>59</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="K271" s="24" t="n">
-        <x:v>-91</x:v>
+        <x:v>-233</x:v>
       </x:c>
       <x:c r="L271" s="28" t="n">
-        <x:v>0.3933333333333333</x:v>
+        <x:v>0.6671428571428571</x:v>
       </x:c>
       <x:c r="M271" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="272" ht="15" hidden="0" customHeight="1">
@@ -10270,11 +10270,9 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E272" s="12" t="str">
-        <x:v>高三</x:v>
-      </x:c>
-      <x:c r="F272" s="21" t="str">
-        <x:v>2026-07-03</x:v>
-      </x:c>
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F272" s="21"/>
       <x:c r="G272" s="21" t="str">
         <x:v>2026-07-09</x:v>
       </x:c>
@@ -10282,19 +10280,17 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I272" s="24" t="n">
-        <x:v>485</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J272" s="24" t="n">
-        <x:v>89</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K272" s="24" t="n">
-        <x:v>-396</x:v>
-      </x:c>
-      <x:c r="L272" s="28" t="n">
-        <x:v>0.18350515463917524</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L272" s="28"/>
       <x:c r="M272" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="273" ht="15" hidden="0" customHeight="1">
@@ -10305,16 +10301,16 @@
         <x:v>暑_12</x:v>
       </x:c>
       <x:c r="C273" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D273" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E273" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F273" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G273" s="21" t="str">
         <x:v>2026-07-09</x:v>
@@ -10323,19 +10319,19 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I273" s="24" t="n">
-        <x:v>335</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J273" s="24" t="n">
-        <x:v>111</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="K273" s="24" t="n">
-        <x:v>-224</x:v>
+        <x:v>-30</x:v>
       </x:c>
       <x:c r="L273" s="28" t="n">
-        <x:v>0.33134328358208953</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="M273" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="274" ht="15" hidden="0" customHeight="1">
@@ -10346,16 +10342,16 @@
         <x:v>暑_12</x:v>
       </x:c>
       <x:c r="C274" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D274" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E274" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F274" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="G274" s="21" t="str">
         <x:v>2026-07-09</x:v>
@@ -10364,19 +10360,19 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I274" s="24" t="n">
-        <x:v>980</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="J274" s="24" t="n">
-        <x:v>181</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="K274" s="24" t="n">
-        <x:v>-799</x:v>
+        <x:v>-160</x:v>
       </x:c>
       <x:c r="L274" s="28" t="n">
-        <x:v>0.1846938775510204</x:v>
+        <x:v>0.6701030927835051</x:v>
       </x:c>
       <x:c r="M274" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="275" ht="15" hidden="0" customHeight="1">
@@ -10393,10 +10389,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E275" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F275" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G275" s="21" t="str">
         <x:v>2026-07-09</x:v>
@@ -10405,19 +10401,19 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I275" s="24" t="n">
-        <x:v>1240</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="J275" s="24" t="n">
-        <x:v>202</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="K275" s="24" t="n">
-        <x:v>-1038</x:v>
+        <x:v>-110</x:v>
       </x:c>
       <x:c r="L275" s="28" t="n">
-        <x:v>0.1629032258064516</x:v>
+        <x:v>0.6716417910447762</x:v>
       </x:c>
       <x:c r="M275" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="276" ht="15" hidden="0" customHeight="1">
@@ -10431,27 +10427,35 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D276" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E276" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F276" s="21" t="str">
-        <x:v>2026-07-03</x:v>
-      </x:c>
-      <x:c r="G276" s="21"/>
-      <x:c r="H276" s="21"/>
+        <x:v>2026-07-06</x:v>
+      </x:c>
+      <x:c r="G276" s="21" t="str">
+        <x:v>2026-07-09</x:v>
+      </x:c>
+      <x:c r="H276" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
       <x:c r="I276" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>980</x:v>
       </x:c>
       <x:c r="J276" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="K276" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L276" s="28"/>
-      <x:c r="M276" s="29"/>
+        <x:v>-489</x:v>
+      </x:c>
+      <x:c r="L276" s="28" t="n">
+        <x:v>0.5010204081632653</x:v>
+      </x:c>
+      <x:c r="M276" s="29" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="277" ht="15" hidden="0" customHeight="1">
       <x:c r="A277" s="11" t="str">
@@ -10464,27 +10468,35 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D277" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E277" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F277" s="21" t="str">
-        <x:v>2026-07-03</x:v>
-      </x:c>
-      <x:c r="G277" s="21"/>
-      <x:c r="H277" s="21"/>
+        <x:v>2026-07-05</x:v>
+      </x:c>
+      <x:c r="G277" s="21" t="str">
+        <x:v>2026-07-09</x:v>
+      </x:c>
+      <x:c r="H277" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
       <x:c r="I277" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>1240</x:v>
       </x:c>
       <x:c r="J277" s="24" t="n">
-        <x:v>35</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="K277" s="24" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="L277" s="28"/>
-      <x:c r="M277" s="29"/>
+        <x:v>-749</x:v>
+      </x:c>
+      <x:c r="L277" s="28" t="n">
+        <x:v>0.3959677419354839</x:v>
+      </x:c>
+      <x:c r="M277" s="29" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="278" ht="15" hidden="0" customHeight="1">
       <x:c r="A278" s="11" t="str">
@@ -10500,10 +10512,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E278" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F278" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-04</x:v>
       </x:c>
       <x:c r="G278" s="21"/>
       <x:c r="H278" s="21"/>
@@ -10511,10 +10523,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J278" s="24" t="n">
-        <x:v>38</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K278" s="24" t="n">
-        <x:v>38</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="L278" s="28"/>
       <x:c r="M278" s="29"/>
@@ -10530,33 +10542,27 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D279" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E279" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F279" s="21" t="str">
-        <x:v>2026-07-03</x:v>
-      </x:c>
-      <x:c r="G279" s="21" t="str">
-        <x:v>2026-07-09</x:v>
-      </x:c>
-      <x:c r="H279" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
+        <x:v>2026-07-06</x:v>
+      </x:c>
+      <x:c r="G279" s="21"/>
+      <x:c r="H279" s="21"/>
       <x:c r="I279" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J279" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K279" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="L279" s="28"/>
-      <x:c r="M279" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
+      <x:c r="M279" s="29"/>
     </x:row>
     <x:row r="280" ht="15" hidden="0" customHeight="1">
       <x:c r="A280" s="11" t="str">
@@ -10569,35 +10575,27 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D280" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E280" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F280" s="21" t="str">
-        <x:v>2026-07-03</x:v>
-      </x:c>
-      <x:c r="G280" s="21" t="str">
-        <x:v>2026-07-09</x:v>
-      </x:c>
-      <x:c r="H280" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
+        <x:v>2026-07-05</x:v>
+      </x:c>
+      <x:c r="G280" s="21"/>
+      <x:c r="H280" s="21"/>
       <x:c r="I280" s="24" t="n">
-        <x:v>300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J280" s="24" t="n">
-        <x:v>114</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="K280" s="24" t="n">
-        <x:v>-186</x:v>
-      </x:c>
-      <x:c r="L280" s="28" t="n">
-        <x:v>0.38</x:v>
-      </x:c>
-      <x:c r="M280" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
-      </x:c>
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="L280" s="28"/>
+      <x:c r="M280" s="29"/>
     </x:row>
     <x:row r="281" ht="15" hidden="0" customHeight="1">
       <x:c r="A281" s="11" t="str">
@@ -10613,7 +10611,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E281" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F281" s="21" t="str">
         <x:v>2026-07-03</x:v>
@@ -10625,19 +10623,17 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I281" s="24" t="n">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J281" s="24" t="n">
-        <x:v>175</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K281" s="24" t="n">
-        <x:v>-325</x:v>
-      </x:c>
-      <x:c r="L281" s="28" t="n">
-        <x:v>0.35</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L281" s="28"/>
       <x:c r="M281" s="29" t="n">
-        <x:v>0.3333333333333333</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="282" ht="15" hidden="0" customHeight="1">
@@ -10645,73 +10641,89 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B282" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_12</x:v>
       </x:c>
       <x:c r="C282" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D282" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E282" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F282" s="21" t="str">
-        <x:v>2026-06-21</x:v>
-      </x:c>
-      <x:c r="G282" s="21"/>
-      <x:c r="H282" s="21"/>
+        <x:v>2026-07-06</x:v>
+      </x:c>
+      <x:c r="G282" s="21" t="str">
+        <x:v>2026-07-09</x:v>
+      </x:c>
+      <x:c r="H282" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
       <x:c r="I282" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J282" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="K282" s="24" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="L282" s="28"/>
-      <x:c r="M282" s="29"/>
+        <x:v>-76</x:v>
+      </x:c>
+      <x:c r="L282" s="28" t="n">
+        <x:v>0.7466666666666667</x:v>
+      </x:c>
+      <x:c r="M282" s="29" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="283" ht="15" hidden="0" customHeight="1">
       <x:c r="A283" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B283" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_12</x:v>
       </x:c>
       <x:c r="C283" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D283" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E283" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F283" s="21" t="str">
-        <x:v>2026-06-28</x:v>
-      </x:c>
-      <x:c r="G283" s="21"/>
-      <x:c r="H283" s="21"/>
+        <x:v>2026-07-06</x:v>
+      </x:c>
+      <x:c r="G283" s="21" t="str">
+        <x:v>2026-07-09</x:v>
+      </x:c>
+      <x:c r="H283" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
       <x:c r="I283" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="J283" s="24" t="n">
-        <x:v>6</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="K283" s="24" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="L283" s="28"/>
-      <x:c r="M283" s="29"/>
+        <x:v>-128</x:v>
+      </x:c>
+      <x:c r="L283" s="28" t="n">
+        <x:v>0.744</x:v>
+      </x:c>
+      <x:c r="M283" s="29" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="284" ht="15" hidden="0" customHeight="1">
       <x:c r="A284" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B284" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C284" s="12" t="str">
         <x:v>LLM外呼</x:v>
@@ -10720,10 +10732,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E284" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F284" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G284" s="21"/>
       <x:c r="H284" s="21"/>
@@ -10731,10 +10743,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J284" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K284" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L284" s="28"/>
       <x:c r="M284" s="29"/>
@@ -10744,19 +10756,19 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B285" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C285" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D285" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E285" s="12" t="str">
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F285" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G285" s="21"/>
       <x:c r="H285" s="21"/>
@@ -10764,10 +10776,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J285" s="24" t="n">
-        <x:v>27</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K285" s="24" t="n">
-        <x:v>27</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L285" s="28"/>
       <x:c r="M285" s="29"/>
@@ -10777,19 +10789,19 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B286" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C286" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D286" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E286" s="12" t="str">
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F286" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G286" s="21"/>
       <x:c r="H286" s="21"/>
@@ -10797,10 +10809,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J286" s="24" t="n">
-        <x:v>63</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K286" s="24" t="n">
-        <x:v>63</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L286" s="28"/>
       <x:c r="M286" s="29"/>
@@ -10819,7 +10831,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E287" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F287" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -10830,10 +10842,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J287" s="24" t="n">
-        <x:v>50</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K287" s="24" t="n">
-        <x:v>50</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L287" s="28"/>
       <x:c r="M287" s="29"/>
@@ -10846,13 +10858,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C288" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D288" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E288" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F288" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -10863,10 +10875,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J288" s="24" t="n">
-        <x:v>10</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K288" s="24" t="n">
-        <x:v>10</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L288" s="28"/>
       <x:c r="M288" s="29"/>
@@ -10879,13 +10891,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C289" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D289" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E289" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F289" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -10896,10 +10908,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J289" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K289" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L289" s="28"/>
       <x:c r="M289" s="29"/>
@@ -10918,10 +10930,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E290" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F290" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G290" s="21"/>
       <x:c r="H290" s="21"/>
@@ -10929,10 +10941,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J290" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K290" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L290" s="28"/>
       <x:c r="M290" s="29"/>
@@ -10945,16 +10957,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C291" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D291" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E291" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F291" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G291" s="21"/>
       <x:c r="H291" s="21"/>
@@ -10978,16 +10990,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C292" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D292" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E292" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F292" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G292" s="21"/>
       <x:c r="H292" s="21"/>
@@ -11011,16 +11023,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C293" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D293" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E293" s="12" t="str">
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F293" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G293" s="21"/>
       <x:c r="H293" s="21"/>
@@ -11028,10 +11040,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J293" s="24" t="n">
-        <x:v>146</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K293" s="24" t="n">
-        <x:v>146</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L293" s="28"/>
       <x:c r="M293" s="29"/>
@@ -11044,16 +11056,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C294" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D294" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E294" s="12" t="str">
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F294" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="G294" s="21"/>
       <x:c r="H294" s="21"/>
@@ -11061,10 +11073,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J294" s="24" t="n">
-        <x:v>157</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K294" s="24" t="n">
-        <x:v>157</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L294" s="28"/>
       <x:c r="M294" s="29"/>
@@ -11077,16 +11089,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C295" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D295" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E295" s="12" t="str">
         <x:v>高三</x:v>
       </x:c>
       <x:c r="F295" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="G295" s="21"/>
       <x:c r="H295" s="21"/>
@@ -11094,10 +11106,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J295" s="24" t="n">
-        <x:v>136</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K295" s="24" t="n">
-        <x:v>136</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L295" s="28"/>
       <x:c r="M295" s="29"/>
@@ -11113,7 +11125,7 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D296" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E296" s="12" t="str">
         <x:v>高一</x:v>
@@ -11127,10 +11139,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J296" s="24" t="n">
-        <x:v>51</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="K296" s="24" t="n">
-        <x:v>51</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="L296" s="28"/>
       <x:c r="M296" s="29"/>
@@ -11146,13 +11158,13 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D297" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E297" s="12" t="str">
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F297" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G297" s="21"/>
       <x:c r="H297" s="21"/>
@@ -11160,10 +11172,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J297" s="24" t="n">
-        <x:v>17</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="K297" s="24" t="n">
-        <x:v>17</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="L297" s="28"/>
       <x:c r="M297" s="29"/>
@@ -11179,7 +11191,7 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D298" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E298" s="12" t="str">
         <x:v>高三</x:v>
@@ -11193,10 +11205,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J298" s="24" t="n">
-        <x:v>30</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K298" s="24" t="n">
-        <x:v>30</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="L298" s="28"/>
       <x:c r="M298" s="29"/>
@@ -11209,10 +11221,10 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C299" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D299" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E299" s="12" t="str">
         <x:v>高一</x:v>
@@ -11226,10 +11238,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J299" s="24" t="n">
-        <x:v>136</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K299" s="24" t="n">
-        <x:v>136</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L299" s="28"/>
       <x:c r="M299" s="29"/>
@@ -11242,16 +11254,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C300" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D300" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E300" s="12" t="str">
         <x:v>高二</x:v>
       </x:c>
       <x:c r="F300" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G300" s="21"/>
       <x:c r="H300" s="21"/>
@@ -11259,10 +11271,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J300" s="24" t="n">
-        <x:v>292</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K300" s="24" t="n">
-        <x:v>292</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="L300" s="28"/>
       <x:c r="M300" s="29"/>
@@ -11275,10 +11287,10 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C301" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D301" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E301" s="12" t="str">
         <x:v>高三</x:v>
@@ -11292,10 +11304,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J301" s="24" t="n">
-        <x:v>167</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K301" s="24" t="n">
-        <x:v>167</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L301" s="28"/>
       <x:c r="M301" s="29"/>
@@ -11311,7 +11323,7 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D302" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E302" s="12" t="str">
         <x:v>高一</x:v>
@@ -11325,10 +11337,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J302" s="24" t="n">
-        <x:v>92</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K302" s="24" t="n">
-        <x:v>92</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="L302" s="28"/>
       <x:c r="M302" s="29"/>
@@ -11344,7 +11356,7 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D303" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E303" s="12" t="str">
         <x:v>高二</x:v>
@@ -11358,10 +11370,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J303" s="24" t="n">
-        <x:v>65</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="K303" s="24" t="n">
-        <x:v>65</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="L303" s="28"/>
       <x:c r="M303" s="29"/>
@@ -11377,7 +11389,7 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D304" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E304" s="12" t="str">
         <x:v>高三</x:v>
@@ -11391,34 +11403,112 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J304" s="24" t="n">
-        <x:v>70</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="K304" s="24" t="n">
-        <x:v>70</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="L304" s="28"/>
       <x:c r="M304" s="29"/>
     </x:row>
     <x:row r="305" ht="15" hidden="0" customHeight="1">
-      <x:c r="A305" s="14"/>
-      <x:c r="B305" s="15"/>
-      <x:c r="C305" s="15"/>
-      <x:c r="D305" s="19"/>
-      <x:c r="E305" s="15"/>
-      <x:c r="F305" s="22"/>
-      <x:c r="G305" s="22"/>
-      <x:c r="H305" s="22"/>
-      <x:c r="I305" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J305" s="25" t="n">
-        <x:v>5659</x:v>
-      </x:c>
-      <x:c r="K305" s="25" t="n">
-        <x:v>5659</x:v>
-      </x:c>
-      <x:c r="L305" s="30"/>
-      <x:c r="M305" s="31"/>
+      <x:c r="A305" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B305" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C305" s="12" t="str">
+        <x:v>常规外呼</x:v>
+      </x:c>
+      <x:c r="D305" s="18" t="n">
+        <x:v>28.8</x:v>
+      </x:c>
+      <x:c r="E305" s="12" t="str">
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F305" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G305" s="21"/>
+      <x:c r="H305" s="21"/>
+      <x:c r="I305" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J305" s="24" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="K305" s="24" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="L305" s="28"/>
+      <x:c r="M305" s="29"/>
+    </x:row>
+    <x:row r="306" ht="15" hidden="0" customHeight="1">
+      <x:c r="A306" s="11" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B306" s="12" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C306" s="12" t="str">
+        <x:v>常规外呼</x:v>
+      </x:c>
+      <x:c r="D306" s="18" t="n">
+        <x:v>28.8</x:v>
+      </x:c>
+      <x:c r="E306" s="12" t="str">
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F306" s="21" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G306" s="21"/>
+      <x:c r="H306" s="21"/>
+      <x:c r="I306" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J306" s="24" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="K306" s="24" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L306" s="28"/>
+      <x:c r="M306" s="29"/>
+    </x:row>
+    <x:row r="307" ht="15" hidden="0" customHeight="1">
+      <x:c r="A307" s="14" t="str">
+        <x:v>高中</x:v>
+      </x:c>
+      <x:c r="B307" s="15" t="str">
+        <x:v>暑_9</x:v>
+      </x:c>
+      <x:c r="C307" s="15" t="str">
+        <x:v>常规外呼</x:v>
+      </x:c>
+      <x:c r="D307" s="19" t="n">
+        <x:v>28.8</x:v>
+      </x:c>
+      <x:c r="E307" s="15" t="str">
+        <x:v>高三</x:v>
+      </x:c>
+      <x:c r="F307" s="22" t="str">
+        <x:v>2026-06-18</x:v>
+      </x:c>
+      <x:c r="G307" s="22"/>
+      <x:c r="H307" s="22"/>
+      <x:c r="I307" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J307" s="25" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="K307" s="25" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="L307" s="30"/>
+      <x:c r="M307" s="31"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -11458,7 +11548,7 @@
         <x:v>现状原始行数</x:v>
       </x:c>
       <x:c r="B3" s="10" t="n">
-        <x:v>79104</x:v>
+        <x:v>85417</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -11474,7 +11564,7 @@
         <x:v>聚合组合数</x:v>
       </x:c>
       <x:c r="B5" s="13" t="n">
-        <x:v>303</x:v>
+        <x:v>305</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -11490,7 +11580,7 @@
         <x:v>现状合计</x:v>
       </x:c>
       <x:c r="B7" s="13" t="n">
-        <x:v>76446</x:v>
+        <x:v>82756</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -11498,7 +11588,7 @@
         <x:v>完成率整体</x:v>
       </x:c>
       <x:c r="B8" s="13" t="n">
-        <x:v>1.3388091068301227</x:v>
+        <x:v>1.4493169877408056</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -11538,7 +11628,7 @@
         <x:v>最新期次现状合计</x:v>
       </x:c>
       <x:c r="B13" s="13" t="n">
-        <x:v>12843</x:v>
+        <x:v>24725</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -11546,7 +11636,7 @@
         <x:v>最新期次完成率整体</x:v>
       </x:c>
       <x:c r="B14" s="13" t="n">
-        <x:v>0.45917053986414014</x:v>
+        <x:v>0.8839828387558097</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -11701,24 +11791,24 @@
     </x:row>
     <x:row r="35" ht="15" hidden="0" customHeight="1">
       <x:c r="A35" s="8" t="str">
-        <x:v>初中</x:v>
+        <x:v>小学</x:v>
       </x:c>
       <x:c r="B35" s="9" t="n">
-        <x:v>9450</x:v>
+        <x:v>12580</x:v>
       </x:c>
       <x:c r="C35" s="10" t="n">
-        <x:v>6092</x:v>
+        <x:v>10689</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="15" hidden="0" customHeight="1">
       <x:c r="A36" s="11" t="str">
-        <x:v>小学</x:v>
+        <x:v>初中</x:v>
       </x:c>
       <x:c r="B36" s="12" t="n">
-        <x:v>12580</x:v>
+        <x:v>9450</x:v>
       </x:c>
       <x:c r="C36" s="13" t="n">
-        <x:v>5162</x:v>
+        <x:v>9691</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="15" hidden="0" customHeight="1">
@@ -11729,7 +11819,7 @@
         <x:v>5940</x:v>
       </x:c>
       <x:c r="C37" s="16" t="n">
-        <x:v>1589</x:v>
+        <x:v>4345</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="16.799999237060547" hidden="0" customHeight="1">
@@ -11756,24 +11846,24 @@
     </x:row>
     <x:row r="42" ht="15" hidden="0" customHeight="1">
       <x:c r="A42" s="8" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="B42" s="9" t="n">
-        <x:v>9450</x:v>
+        <x:v>12580</x:v>
       </x:c>
       <x:c r="C42" s="10" t="n">
-        <x:v>6092</x:v>
+        <x:v>10689</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="15" hidden="0" customHeight="1">
       <x:c r="A43" s="11" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="B43" s="12" t="n">
-        <x:v>12580</x:v>
+        <x:v>9450</x:v>
       </x:c>
       <x:c r="C43" s="13" t="n">
-        <x:v>5162</x:v>
+        <x:v>9691</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
@@ -11784,7 +11874,7 @@
         <x:v>5940</x:v>
       </x:c>
       <x:c r="C44" s="16" t="n">
-        <x:v>1589</x:v>
+        <x:v>4345</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="16.799999237060547" hidden="0" customHeight="1">
@@ -11817,7 +11907,7 @@
         <x:v>12620</x:v>
       </x:c>
       <x:c r="C49" s="10" t="n">
-        <x:v>5816</x:v>
+        <x:v>11119</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -11828,7 +11918,7 @@
         <x:v>8665</x:v>
       </x:c>
       <x:c r="C50" s="13" t="n">
-        <x:v>3869</x:v>
+        <x:v>7004</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -11839,7 +11929,7 @@
         <x:v>4100</x:v>
       </x:c>
       <x:c r="C51" s="13" t="n">
-        <x:v>2087</x:v>
+        <x:v>4331</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -11850,7 +11940,7 @@
         <x:v>1505</x:v>
       </x:c>
       <x:c r="C52" s="13" t="n">
-        <x:v>768</x:v>
+        <x:v>1391</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -11861,7 +11951,7 @@
         <x:v>1080</x:v>
       </x:c>
       <x:c r="C53" s="13" t="n">
-        <x:v>300</x:v>
+        <x:v>877</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15" hidden="0" customHeight="1">
@@ -11905,7 +11995,7 @@
         <x:v>13675</x:v>
       </x:c>
       <x:c r="C59" s="10" t="n">
-        <x:v>5377</x:v>
+        <x:v>11071</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -11916,7 +12006,7 @@
         <x:v>7870</x:v>
       </x:c>
       <x:c r="C60" s="13" t="n">
-        <x:v>5010</x:v>
+        <x:v>8582</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15" hidden="0" customHeight="1">
@@ -11927,7 +12017,7 @@
         <x:v>5345</x:v>
       </x:c>
       <x:c r="C61" s="13" t="n">
-        <x:v>2156</x:v>
+        <x:v>4195</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15" hidden="0" customHeight="1">
@@ -11938,7 +12028,7 @@
         <x:v>1080</x:v>
       </x:c>
       <x:c r="C62" s="16" t="n">
-        <x:v>300</x:v>
+        <x:v>877</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="16.799999237060547" hidden="0" customHeight="1">
@@ -11965,46 +12055,46 @@
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
       <x:c r="A67" s="8" t="str">
-        <x:v>初一</x:v>
+        <x:v>初二</x:v>
       </x:c>
       <x:c r="B67" s="9" t="n">
-        <x:v>2000</x:v>
+        <x:v>3720</x:v>
       </x:c>
       <x:c r="C67" s="10" t="n">
-        <x:v>2240</x:v>
+        <x:v>3787</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
       <x:c r="A68" s="11" t="str">
-        <x:v>初二</x:v>
+        <x:v>初三</x:v>
       </x:c>
       <x:c r="B68" s="12" t="n">
-        <x:v>3720</x:v>
+        <x:v>3730</x:v>
       </x:c>
       <x:c r="C68" s="13" t="n">
-        <x:v>2128</x:v>
+        <x:v>3430</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
       <x:c r="A69" s="11" t="str">
-        <x:v>初三</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="B69" s="12" t="n">
-        <x:v>3730</x:v>
+        <x:v>3510</x:v>
       </x:c>
       <x:c r="C69" s="13" t="n">
-        <x:v>1724</x:v>
+        <x:v>2911</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
       <x:c r="A70" s="11" t="str">
-        <x:v>四年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="B70" s="12" t="n">
-        <x:v>3510</x:v>
+        <x:v>2920</x:v>
       </x:c>
       <x:c r="C70" s="13" t="n">
-        <x:v>1388</x:v>
+        <x:v>2607</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -12015,29 +12105,29 @@
         <x:v>2830</x:v>
       </x:c>
       <x:c r="C71" s="13" t="n">
-        <x:v>1257</x:v>
+        <x:v>2573</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
       <x:c r="A72" s="11" t="str">
-        <x:v>五年级</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="B72" s="12" t="n">
-        <x:v>3220</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="C72" s="13" t="n">
-        <x:v>1202</x:v>
+        <x:v>2474</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
       <x:c r="A73" s="11" t="str">
-        <x:v>三年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="B73" s="12" t="n">
-        <x:v>2920</x:v>
+        <x:v>3220</x:v>
       </x:c>
       <x:c r="C73" s="13" t="n">
-        <x:v>1202</x:v>
+        <x:v>2441</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -12048,7 +12138,7 @@
         <x:v>2370</x:v>
       </x:c>
       <x:c r="C74" s="13" t="n">
-        <x:v>652</x:v>
+        <x:v>1855</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="15" hidden="0" customHeight="1">
@@ -12059,7 +12149,7 @@
         <x:v>3065</x:v>
       </x:c>
       <x:c r="C75" s="13" t="n">
-        <x:v>518</x:v>
+        <x:v>1834</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="15" hidden="0" customHeight="1">
@@ -12070,7 +12160,7 @@
         <x:v>505</x:v>
       </x:c>
       <x:c r="C76" s="13" t="n">
-        <x:v>419</x:v>
+        <x:v>656</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="15" hidden="0" customHeight="1">
@@ -12081,7 +12171,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="C77" s="16" t="n">
-        <x:v>113</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/outputs/tongji_summary/tongji_summary_current.xlsx
+++ b/outputs/tongji_summary/tongji_summary_current.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目标现状对比" sheetId="1" r:id="Ra1867b9b68704924"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据概览" sheetId="2" r:id="R9ac7336f52534751"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计算规则" sheetId="3" r:id="R10bace7fa5fa413f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目标现状对比" sheetId="1" r:id="R4ab379b55c8543dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据概览" sheetId="2" r:id="R4cff9adabb5445f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计算规则" sheetId="3" r:id="Rfb3fa1d96a974560"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -931,13 +931,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J12" s="24" t="n">
-        <x:v>727</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="K12" s="24" t="n">
-        <x:v>627</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="L12" s="28" t="n">
-        <x:v>7.27</x:v>
+        <x:v>7.18</x:v>
       </x:c>
       <x:c r="M12" s="29" t="n">
         <x:v>1</x:v>
@@ -972,13 +972,13 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="J13" s="24" t="n">
-        <x:v>744</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="K13" s="24" t="n">
-        <x:v>94</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="L13" s="28" t="n">
-        <x:v>1.1446153846153846</x:v>
+        <x:v>1.1046153846153846</x:v>
       </x:c>
       <x:c r="M13" s="29" t="n">
         <x:v>1</x:v>
@@ -1000,9 +1000,7 @@
       <x:c r="E14" s="12" t="str">
         <x:v>初三</x:v>
       </x:c>
-      <x:c r="F14" s="21" t="str">
-        <x:v>2026-06-21</x:v>
-      </x:c>
+      <x:c r="F14" s="21"/>
       <x:c r="G14" s="21" t="str">
         <x:v>2026-06-30</x:v>
       </x:c>
@@ -1013,13 +1011,13 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="J14" s="24" t="n">
-        <x:v>82</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K14" s="24" t="n">
-        <x:v>-568</x:v>
+        <x:v>-650</x:v>
       </x:c>
       <x:c r="L14" s="28" t="n">
-        <x:v>0.12615384615384614</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M14" s="29" t="n">
         <x:v>1</x:v>
@@ -1481,13 +1479,13 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="J26" s="24" t="n">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="K26" s="24" t="n">
-        <x:v>-64</x:v>
+        <x:v>-65</x:v>
       </x:c>
       <x:c r="L26" s="28" t="n">
-        <x:v>0.5076923076923077</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="M26" s="29" t="n">
         <x:v>1</x:v>
@@ -1563,13 +1561,13 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="J28" s="24" t="n">
-        <x:v>180</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="K28" s="24" t="n">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L28" s="28" t="n">
-        <x:v>1.3846153846153846</x:v>
+        <x:v>1.376923076923077</x:v>
       </x:c>
       <x:c r="M28" s="29" t="n">
         <x:v>1</x:v>
@@ -1637,13 +1635,13 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="J30" s="24" t="n">
-        <x:v>808</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="K30" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>-132</x:v>
       </x:c>
       <x:c r="L30" s="28" t="n">
-        <x:v>1.01</x:v>
+        <x:v>0.835</x:v>
       </x:c>
       <x:c r="M30" s="29" t="n">
         <x:v>1</x:v>
@@ -1760,13 +1758,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="J33" s="24" t="n">
-        <x:v>479</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="K33" s="24" t="n">
-        <x:v>379</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="L33" s="28" t="n">
-        <x:v>4.79</x:v>
+        <x:v>4.68</x:v>
       </x:c>
       <x:c r="M33" s="29" t="n">
         <x:v>1</x:v>
@@ -1801,13 +1799,13 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="J34" s="24" t="n">
-        <x:v>851</x:v>
+        <x:v>836</x:v>
       </x:c>
       <x:c r="K34" s="24" t="n">
-        <x:v>151</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="L34" s="28" t="n">
-        <x:v>1.2157142857142857</x:v>
+        <x:v>1.1942857142857144</x:v>
       </x:c>
       <x:c r="M34" s="29" t="n">
         <x:v>1</x:v>
@@ -1842,13 +1840,13 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="J35" s="24" t="n">
-        <x:v>515</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="K35" s="24" t="n">
-        <x:v>-185</x:v>
+        <x:v>-198</x:v>
       </x:c>
       <x:c r="L35" s="28" t="n">
-        <x:v>0.7357142857142858</x:v>
+        <x:v>0.7171428571428572</x:v>
       </x:c>
       <x:c r="M35" s="29" t="n">
         <x:v>1</x:v>
@@ -1883,13 +1881,13 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="J36" s="24" t="n">
-        <x:v>204</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="K36" s="24" t="n">
-        <x:v>-16</x:v>
+        <x:v>-55</x:v>
       </x:c>
       <x:c r="L36" s="28" t="n">
-        <x:v>0.9272727272727272</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="M36" s="29" t="n">
         <x:v>1</x:v>
@@ -2121,13 +2119,13 @@
         <x:v>750</x:v>
       </x:c>
       <x:c r="J42" s="24" t="n">
-        <x:v>729</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="K42" s="24" t="n">
-        <x:v>-21</x:v>
+        <x:v>-146</x:v>
       </x:c>
       <x:c r="L42" s="28" t="n">
-        <x:v>0.972</x:v>
+        <x:v>0.8053333333333333</x:v>
       </x:c>
       <x:c r="M42" s="29" t="n">
         <x:v>1</x:v>
@@ -5939,13 +5937,13 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="J156" s="24" t="n">
-        <x:v>2300</x:v>
+        <x:v>1949</x:v>
       </x:c>
       <x:c r="K156" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-351</x:v>
       </x:c>
       <x:c r="L156" s="28" t="n">
-        <x:v>1</x:v>
+        <x:v>0.8473913043478261</x:v>
       </x:c>
       <x:c r="M156" s="29" t="n">
         <x:v>1</x:v>
@@ -5980,13 +5978,13 @@
         <x:v>2500</x:v>
       </x:c>
       <x:c r="J157" s="24" t="n">
-        <x:v>2503</x:v>
+        <x:v>1981</x:v>
       </x:c>
       <x:c r="K157" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>-519</x:v>
       </x:c>
       <x:c r="L157" s="28" t="n">
-        <x:v>1.0012</x:v>
+        <x:v>0.7924</x:v>
       </x:c>
       <x:c r="M157" s="29" t="n">
         <x:v>1</x:v>
@@ -6021,13 +6019,13 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="J158" s="24" t="n">
-        <x:v>2004</x:v>
+        <x:v>1632</x:v>
       </x:c>
       <x:c r="K158" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>-368</x:v>
       </x:c>
       <x:c r="L158" s="28" t="n">
-        <x:v>1.002</x:v>
+        <x:v>0.816</x:v>
       </x:c>
       <x:c r="M158" s="29" t="n">
         <x:v>1</x:v>
@@ -6062,13 +6060,13 @@
         <x:v>2300</x:v>
       </x:c>
       <x:c r="J159" s="24" t="n">
-        <x:v>2304</x:v>
+        <x:v>1853</x:v>
       </x:c>
       <x:c r="K159" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>-447</x:v>
       </x:c>
       <x:c r="L159" s="28" t="n">
-        <x:v>1.0017391304347827</x:v>
+        <x:v>0.8056521739130434</x:v>
       </x:c>
       <x:c r="M159" s="29" t="n">
         <x:v>1</x:v>
@@ -6144,13 +6142,13 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="J161" s="24" t="n">
-        <x:v>231</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="K161" s="24" t="n">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="L161" s="28" t="n">
-        <x:v>1.54</x:v>
+        <x:v>1.5333333333333334</x:v>
       </x:c>
       <x:c r="M161" s="29" t="n">
         <x:v>1</x:v>
@@ -6226,13 +6224,13 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="J163" s="24" t="n">
-        <x:v>166</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="K163" s="24" t="n">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L163" s="28" t="n">
-        <x:v>1.1066666666666667</x:v>
+        <x:v>1.0666666666666667</x:v>
       </x:c>
       <x:c r="M163" s="29" t="n">
         <x:v>1</x:v>
@@ -6308,13 +6306,13 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="J165" s="24" t="n">
-        <x:v>249</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="K165" s="24" t="n">
-        <x:v>-51</x:v>
+        <x:v>-56</x:v>
       </x:c>
       <x:c r="L165" s="28" t="n">
-        <x:v>0.83</x:v>
+        <x:v>0.8133333333333334</x:v>
       </x:c>
       <x:c r="M165" s="29" t="n">
         <x:v>1</x:v>
@@ -6390,13 +6388,13 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="J167" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K167" s="24" t="n">
-        <x:v>-195</x:v>
+        <x:v>-196</x:v>
       </x:c>
       <x:c r="L167" s="28" t="n">
-        <x:v>0.025</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="M167" s="29" t="n">
         <x:v>1</x:v>
@@ -6618,27 +6616,35 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D173" s="18" t="n">
-        <x:v>18.8</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E173" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F173" s="21" t="str">
-        <x:v>2026-06-24</x:v>
-      </x:c>
-      <x:c r="G173" s="21"/>
-      <x:c r="H173" s="21"/>
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="G173" s="21" t="str">
+        <x:v>2026-07-01</x:v>
+      </x:c>
+      <x:c r="H173" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I173" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J173" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K173" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L173" s="28"/>
-      <x:c r="M173" s="29"/>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L173" s="28" t="n">
+        <x:v>1.225</x:v>
+      </x:c>
+      <x:c r="M173" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="174" ht="15" hidden="0" customHeight="1">
       <x:c r="A174" s="11" t="str">
@@ -6654,7 +6660,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E174" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F174" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -6666,16 +6672,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I174" s="24" t="n">
-        <x:v>80</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="J174" s="24" t="n">
-        <x:v>98</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="K174" s="24" t="n">
-        <x:v>18</x:v>
+        <x:v>-52</x:v>
       </x:c>
       <x:c r="L174" s="28" t="n">
-        <x:v>1.225</x:v>
+        <x:v>0.7263157894736842</x:v>
       </x:c>
       <x:c r="M174" s="29" t="n">
         <x:v>1</x:v>
@@ -6695,7 +6701,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E175" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F175" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -6707,16 +6713,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I175" s="24" t="n">
-        <x:v>190</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="J175" s="24" t="n">
-        <x:v>138</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="K175" s="24" t="n">
-        <x:v>-52</x:v>
+        <x:v>-4</x:v>
       </x:c>
       <x:c r="L175" s="28" t="n">
-        <x:v>0.7263157894736842</x:v>
+        <x:v>0.9846153846153847</x:v>
       </x:c>
       <x:c r="M175" s="29" t="n">
         <x:v>1</x:v>
@@ -6736,7 +6742,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E176" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F176" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -6748,16 +6754,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I176" s="24" t="n">
-        <x:v>260</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="J176" s="24" t="n">
-        <x:v>270</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="K176" s="24" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L176" s="28" t="n">
-        <x:v>1.0384615384615385</x:v>
+        <x:v>1.0083333333333333</x:v>
       </x:c>
       <x:c r="M176" s="29" t="n">
         <x:v>1</x:v>
@@ -6777,7 +6783,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E177" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F177" s="21" t="str">
         <x:v>2026-07-01</x:v>
@@ -6789,16 +6795,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I177" s="24" t="n">
-        <x:v>240</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="J177" s="24" t="n">
-        <x:v>242</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="K177" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>-47</x:v>
       </x:c>
       <x:c r="L177" s="28" t="n">
-        <x:v>1.0083333333333333</x:v>
+        <x:v>0.8192307692307692</x:v>
       </x:c>
       <x:c r="M177" s="29" t="n">
         <x:v>1</x:v>
@@ -6809,40 +6815,40 @@
         <x:v>小学</x:v>
       </x:c>
       <x:c r="B178" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C178" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D178" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E178" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F178" s="21" t="str">
-        <x:v>2026-07-01</x:v>
+        <x:v>2026-07-07</x:v>
       </x:c>
       <x:c r="G178" s="21" t="str">
-        <x:v>2026-07-01</x:v>
+        <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="H178" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I178" s="24" t="n">
-        <x:v>260</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J178" s="24" t="n">
-        <x:v>237</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K178" s="24" t="n">
-        <x:v>-23</x:v>
+        <x:v>-5</x:v>
       </x:c>
       <x:c r="L178" s="28" t="n">
-        <x:v>0.9115384615384615</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="M178" s="29" t="n">
-        <x:v>1</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="15" hidden="0" customHeight="1">
@@ -6859,7 +6865,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E179" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F179" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -6871,16 +6877,16 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I179" s="24" t="n">
-        <x:v>20</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J179" s="24" t="n">
-        <x:v>15</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="K179" s="24" t="n">
-        <x:v>-5</x:v>
+        <x:v>-56</x:v>
       </x:c>
       <x:c r="L179" s="28" t="n">
-        <x:v>0.75</x:v>
+        <x:v>0.4909090909090909</x:v>
       </x:c>
       <x:c r="M179" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -6900,7 +6906,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E180" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F180" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -6941,7 +6947,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E181" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F181" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -6956,13 +6962,13 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="J181" s="24" t="n">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K181" s="24" t="n">
-        <x:v>-56</x:v>
+        <x:v>-47</x:v>
       </x:c>
       <x:c r="L181" s="28" t="n">
-        <x:v>0.4909090909090909</x:v>
+        <x:v>0.5727272727272728</x:v>
       </x:c>
       <x:c r="M181" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -6976,13 +6982,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C182" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D182" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E182" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F182" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -6994,16 +7000,16 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I182" s="24" t="n">
-        <x:v>110</x:v>
+        <x:v>2520</x:v>
       </x:c>
       <x:c r="J182" s="24" t="n">
-        <x:v>63</x:v>
+        <x:v>2510</x:v>
       </x:c>
       <x:c r="K182" s="24" t="n">
-        <x:v>-47</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="L182" s="28" t="n">
-        <x:v>0.5727272727272728</x:v>
+        <x:v>0.996031746031746</x:v>
       </x:c>
       <x:c r="M182" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -7023,7 +7029,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E183" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F183" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -7035,16 +7041,16 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I183" s="24" t="n">
-        <x:v>2520</x:v>
+        <x:v>2720</x:v>
       </x:c>
       <x:c r="J183" s="24" t="n">
-        <x:v>2510</x:v>
+        <x:v>2713</x:v>
       </x:c>
       <x:c r="K183" s="24" t="n">
-        <x:v>-10</x:v>
+        <x:v>-7</x:v>
       </x:c>
       <x:c r="L183" s="28" t="n">
-        <x:v>0.996031746031746</x:v>
+        <x:v>0.9974264705882353</x:v>
       </x:c>
       <x:c r="M183" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -7064,7 +7070,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E184" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F184" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -7076,16 +7082,16 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I184" s="24" t="n">
-        <x:v>2720</x:v>
+        <x:v>2530</x:v>
       </x:c>
       <x:c r="J184" s="24" t="n">
-        <x:v>2713</x:v>
+        <x:v>2312</x:v>
       </x:c>
       <x:c r="K184" s="24" t="n">
-        <x:v>-7</x:v>
+        <x:v>-218</x:v>
       </x:c>
       <x:c r="L184" s="28" t="n">
-        <x:v>0.9974264705882353</x:v>
+        <x:v>0.9138339920948617</x:v>
       </x:c>
       <x:c r="M184" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -7105,7 +7111,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E185" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F185" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -7117,16 +7123,16 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I185" s="24" t="n">
-        <x:v>2530</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="J185" s="24" t="n">
-        <x:v>2312</x:v>
+        <x:v>2031</x:v>
       </x:c>
       <x:c r="K185" s="24" t="n">
-        <x:v>-218</x:v>
+        <x:v>-19</x:v>
       </x:c>
       <x:c r="L185" s="28" t="n">
-        <x:v>0.9138339920948617</x:v>
+        <x:v>0.9907317073170732</x:v>
       </x:c>
       <x:c r="M185" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -7140,38 +7146,30 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C186" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D186" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E186" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F186" s="21" t="str">
-        <x:v>2026-07-07</x:v>
-      </x:c>
-      <x:c r="G186" s="21" t="str">
-        <x:v>2026-07-08</x:v>
-      </x:c>
-      <x:c r="H186" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
+        <x:v>2026-07-03</x:v>
+      </x:c>
+      <x:c r="G186" s="21"/>
+      <x:c r="H186" s="21"/>
       <x:c r="I186" s="24" t="n">
-        <x:v>2050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J186" s="24" t="n">
-        <x:v>2031</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="K186" s="24" t="n">
-        <x:v>-19</x:v>
-      </x:c>
-      <x:c r="L186" s="28" t="n">
-        <x:v>0.9907317073170732</x:v>
-      </x:c>
-      <x:c r="M186" s="29" t="n">
-        <x:v>0.8333333333333334</x:v>
-      </x:c>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="L186" s="28"/>
+      <x:c r="M186" s="29"/>
     </x:row>
     <x:row r="187" ht="15" hidden="0" customHeight="1">
       <x:c r="A187" s="11" t="str">
@@ -7187,24 +7185,32 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E187" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F187" s="21" t="str">
-        <x:v>2026-07-03</x:v>
-      </x:c>
-      <x:c r="G187" s="21"/>
-      <x:c r="H187" s="21"/>
+        <x:v>2026-07-07</x:v>
+      </x:c>
+      <x:c r="G187" s="21" t="str">
+        <x:v>2026-07-08</x:v>
+      </x:c>
+      <x:c r="H187" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
       <x:c r="I187" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J187" s="24" t="n">
-        <x:v>67</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="K187" s="24" t="n">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="L187" s="28"/>
-      <x:c r="M187" s="29"/>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L187" s="28" t="n">
+        <x:v>1.4133333333333333</x:v>
+      </x:c>
+      <x:c r="M187" s="29" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="188" ht="15" hidden="0" customHeight="1">
       <x:c r="A188" s="11" t="str">
@@ -7220,7 +7226,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E188" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F188" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -7232,16 +7238,16 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I188" s="24" t="n">
-        <x:v>150</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="J188" s="24" t="n">
-        <x:v>213</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="K188" s="24" t="n">
-        <x:v>63</x:v>
+        <x:v>-115</x:v>
       </x:c>
       <x:c r="L188" s="28" t="n">
-        <x:v>1.42</x:v>
+        <x:v>0.6714285714285714</x:v>
       </x:c>
       <x:c r="M188" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -7261,7 +7267,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E189" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F189" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -7273,16 +7279,16 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I189" s="24" t="n">
-        <x:v>350</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="J189" s="24" t="n">
-        <x:v>243</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="K189" s="24" t="n">
-        <x:v>-107</x:v>
+        <x:v>-57</x:v>
       </x:c>
       <x:c r="L189" s="28" t="n">
-        <x:v>0.6942857142857143</x:v>
+        <x:v>0.772</x:v>
       </x:c>
       <x:c r="M189" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -7302,10 +7308,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E190" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F190" s="21" t="str">
-        <x:v>2026-07-07</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="G190" s="21" t="str">
         <x:v>2026-07-08</x:v>
@@ -7317,13 +7323,13 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="J190" s="24" t="n">
-        <x:v>204</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="K190" s="24" t="n">
-        <x:v>-46</x:v>
+        <x:v>-183</x:v>
       </x:c>
       <x:c r="L190" s="28" t="n">
-        <x:v>0.816</x:v>
+        <x:v>0.268</x:v>
       </x:c>
       <x:c r="M190" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -7337,38 +7343,30 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C191" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D191" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E191" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F191" s="21" t="str">
-        <x:v>2026-07-06</x:v>
-      </x:c>
-      <x:c r="G191" s="21" t="str">
-        <x:v>2026-07-08</x:v>
-      </x:c>
-      <x:c r="H191" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
+        <x:v>2026-07-05</x:v>
+      </x:c>
+      <x:c r="G191" s="21"/>
+      <x:c r="H191" s="21"/>
       <x:c r="I191" s="24" t="n">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J191" s="24" t="n">
-        <x:v>230</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K191" s="24" t="n">
-        <x:v>-20</x:v>
-      </x:c>
-      <x:c r="L191" s="28" t="n">
-        <x:v>0.92</x:v>
-      </x:c>
-      <x:c r="M191" s="29" t="n">
-        <x:v>0.8333333333333334</x:v>
-      </x:c>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L191" s="28"/>
+      <x:c r="M191" s="29"/>
     </x:row>
     <x:row r="192" ht="15" hidden="0" customHeight="1">
       <x:c r="A192" s="11" t="str">
@@ -7384,10 +7382,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E192" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F192" s="21" t="str">
-        <x:v>2026-07-05</x:v>
+        <x:v>2026-07-04</x:v>
       </x:c>
       <x:c r="G192" s="21"/>
       <x:c r="H192" s="21"/>
@@ -7395,10 +7393,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J192" s="24" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K192" s="24" t="n">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L192" s="28"/>
       <x:c r="M192" s="29"/>
@@ -7417,10 +7415,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E193" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F193" s="21" t="str">
-        <x:v>2026-07-04</x:v>
+        <x:v>2026-07-07</x:v>
       </x:c>
       <x:c r="G193" s="21"/>
       <x:c r="H193" s="21"/>
@@ -7428,10 +7426,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J193" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K193" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L193" s="28"/>
       <x:c r="M193" s="29"/>
@@ -7450,10 +7448,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E194" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F194" s="21" t="str">
-        <x:v>2026-07-07</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="G194" s="21"/>
       <x:c r="H194" s="21"/>
@@ -7461,10 +7459,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J194" s="24" t="n">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K194" s="24" t="n">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="L194" s="28"/>
       <x:c r="M194" s="29"/>
@@ -7480,27 +7478,35 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D195" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E195" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>二年级</x:v>
       </x:c>
       <x:c r="F195" s="21" t="str">
-        <x:v>2026-07-05</x:v>
-      </x:c>
-      <x:c r="G195" s="21"/>
-      <x:c r="H195" s="21"/>
+        <x:v>2026-07-07</x:v>
+      </x:c>
+      <x:c r="G195" s="21" t="str">
+        <x:v>2026-07-08</x:v>
+      </x:c>
+      <x:c r="H195" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
       <x:c r="I195" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J195" s="24" t="n">
-        <x:v>19</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K195" s="24" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="L195" s="28"/>
-      <x:c r="M195" s="29"/>
+        <x:v>-4</x:v>
+      </x:c>
+      <x:c r="L195" s="28" t="n">
+        <x:v>0.96</x:v>
+      </x:c>
+      <x:c r="M195" s="29" t="n">
+        <x:v>0.8333333333333334</x:v>
+      </x:c>
     </x:row>
     <x:row r="196" ht="15" hidden="0" customHeight="1">
       <x:c r="A196" s="11" t="str">
@@ -7516,7 +7522,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E196" s="12" t="str">
-        <x:v>二年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F196" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -7528,16 +7534,16 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I196" s="24" t="n">
-        <x:v>100</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="J196" s="24" t="n">
-        <x:v>96</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="K196" s="24" t="n">
-        <x:v>-4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L196" s="28" t="n">
-        <x:v>0.96</x:v>
+        <x:v>1.0217391304347827</x:v>
       </x:c>
       <x:c r="M196" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -7557,7 +7563,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E197" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F197" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -7569,16 +7575,16 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I197" s="24" t="n">
-        <x:v>230</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="J197" s="24" t="n">
-        <x:v>235</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="K197" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L197" s="28" t="n">
-        <x:v>1.0217391304347827</x:v>
+        <x:v>1.009090909090909</x:v>
       </x:c>
       <x:c r="M197" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -7598,7 +7604,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E198" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>五年级</x:v>
       </x:c>
       <x:c r="F198" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -7613,13 +7619,13 @@
         <x:v>330</x:v>
       </x:c>
       <x:c r="J198" s="24" t="n">
-        <x:v>333</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="K198" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="L198" s="28" t="n">
-        <x:v>1.009090909090909</x:v>
+        <x:v>0.9727272727272728</x:v>
       </x:c>
       <x:c r="M198" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -7639,7 +7645,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E199" s="12" t="str">
-        <x:v>五年级</x:v>
+        <x:v>六年级</x:v>
       </x:c>
       <x:c r="F199" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -7651,16 +7657,16 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I199" s="24" t="n">
-        <x:v>330</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="J199" s="24" t="n">
-        <x:v>321</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="K199" s="24" t="n">
-        <x:v>-9</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L199" s="28" t="n">
-        <x:v>0.9727272727272728</x:v>
+        <x:v>1.0642857142857143</x:v>
       </x:c>
       <x:c r="M199" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -7668,44 +7674,36 @@
     </x:row>
     <x:row r="200" ht="15" hidden="0" customHeight="1">
       <x:c r="A200" s="11" t="str">
-        <x:v>小学</x:v>
+        <x:v>自拼</x:v>
       </x:c>
       <x:c r="B200" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C200" s="12" t="str">
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D200" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="E200" s="12" t="str">
-        <x:v>六年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F200" s="21" t="str">
         <x:v>2026-07-07</x:v>
       </x:c>
-      <x:c r="G200" s="21" t="str">
-        <x:v>2026-07-08</x:v>
-      </x:c>
-      <x:c r="H200" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
+      <x:c r="G200" s="21"/>
+      <x:c r="H200" s="21"/>
       <x:c r="I200" s="24" t="n">
-        <x:v>420</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J200" s="24" t="n">
-        <x:v>447</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K200" s="24" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="L200" s="28" t="n">
-        <x:v>1.0642857142857143</x:v>
-      </x:c>
-      <x:c r="M200" s="29" t="n">
-        <x:v>0.8333333333333334</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L200" s="28"/>
+      <x:c r="M200" s="29"/>
     </x:row>
     <x:row r="201" ht="15" hidden="0" customHeight="1">
       <x:c r="A201" s="11" t="str">
@@ -7721,7 +7719,7 @@
         <x:v>29.9</x:v>
       </x:c>
       <x:c r="E201" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F201" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -7732,10 +7730,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J201" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K201" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L201" s="28"/>
       <x:c r="M201" s="29"/>
@@ -7754,7 +7752,7 @@
         <x:v>29.9</x:v>
       </x:c>
       <x:c r="E202" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F202" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -7765,10 +7763,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J202" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K202" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L202" s="28"/>
       <x:c r="M202" s="29"/>
@@ -7778,19 +7776,19 @@
         <x:v>自拼</x:v>
       </x:c>
       <x:c r="B203" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C203" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D203" s="18" t="n">
-        <x:v>29.9</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E203" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F203" s="21" t="str">
-        <x:v>2026-07-07</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G203" s="21"/>
       <x:c r="H203" s="21"/>
@@ -7798,10 +7796,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J203" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="K203" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="L203" s="28"/>
       <x:c r="M203" s="29"/>
@@ -7820,10 +7818,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E204" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F204" s="21" t="str">
-        <x:v>2026-06-22</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G204" s="21"/>
       <x:c r="H204" s="21"/>
@@ -7831,10 +7829,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J204" s="24" t="n">
-        <x:v>218</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="K204" s="24" t="n">
-        <x:v>218</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="L204" s="28"/>
       <x:c r="M204" s="29"/>
@@ -7853,7 +7851,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E205" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F205" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -7864,10 +7862,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J205" s="24" t="n">
-        <x:v>79</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K205" s="24" t="n">
-        <x:v>79</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L205" s="28"/>
       <x:c r="M205" s="29"/>
@@ -7880,16 +7878,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C206" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D206" s="18" t="n">
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E206" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F206" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-22</x:v>
       </x:c>
       <x:c r="G206" s="21"/>
       <x:c r="H206" s="21"/>
@@ -7897,10 +7895,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J206" s="24" t="n">
-        <x:v>32</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="K206" s="24" t="n">
-        <x:v>32</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="L206" s="28"/>
       <x:c r="M206" s="29"/>
@@ -7919,10 +7917,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E207" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F207" s="21" t="str">
-        <x:v>2026-06-22</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G207" s="21"/>
       <x:c r="H207" s="21"/>
@@ -7930,10 +7928,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J207" s="24" t="n">
-        <x:v>314</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K207" s="24" t="n">
-        <x:v>314</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="L207" s="28"/>
       <x:c r="M207" s="29"/>
@@ -7952,7 +7950,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E208" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F208" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -7963,10 +7961,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J208" s="24" t="n">
-        <x:v>116</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K208" s="24" t="n">
-        <x:v>116</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="L208" s="28"/>
       <x:c r="M208" s="29"/>
@@ -7979,16 +7977,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C209" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D209" s="18" t="n">
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E209" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F209" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G209" s="21"/>
       <x:c r="H209" s="21"/>
@@ -7996,10 +7994,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J209" s="24" t="n">
-        <x:v>89</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="K209" s="24" t="n">
-        <x:v>89</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L209" s="28"/>
       <x:c r="M209" s="29"/>
@@ -8018,10 +8016,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E210" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F210" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G210" s="21"/>
       <x:c r="H210" s="21"/>
@@ -8029,10 +8027,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J210" s="24" t="n">
-        <x:v>32</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K210" s="24" t="n">
-        <x:v>32</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L210" s="28"/>
       <x:c r="M210" s="29"/>
@@ -8051,7 +8049,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E211" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F211" s="21" t="str">
         <x:v>2026-06-23</x:v>
@@ -8062,10 +8060,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J211" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K211" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L211" s="28"/>
       <x:c r="M211" s="29"/>
@@ -8078,16 +8076,16 @@
         <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C212" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D212" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="E212" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F212" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G212" s="21"/>
       <x:c r="H212" s="21"/>
@@ -8095,10 +8093,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J212" s="24" t="n">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K212" s="24" t="n">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L212" s="28"/>
       <x:c r="M212" s="29"/>
@@ -8117,10 +8115,10 @@
         <x:v>29.9</x:v>
       </x:c>
       <x:c r="E213" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F213" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G213" s="21"/>
       <x:c r="H213" s="21"/>
@@ -8128,10 +8126,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J213" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K213" s="24" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L213" s="28"/>
       <x:c r="M213" s="29"/>
@@ -8150,10 +8148,10 @@
         <x:v>29.9</x:v>
       </x:c>
       <x:c r="E214" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F214" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-23</x:v>
       </x:c>
       <x:c r="G214" s="21"/>
       <x:c r="H214" s="21"/>
@@ -8161,10 +8159,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J214" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K214" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L214" s="28"/>
       <x:c r="M214" s="29"/>
@@ -8174,19 +8172,19 @@
         <x:v>自拼</x:v>
       </x:c>
       <x:c r="B215" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C215" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D215" s="18" t="n">
-        <x:v>29.9</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E215" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F215" s="21" t="str">
-        <x:v>2026-06-23</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G215" s="21"/>
       <x:c r="H215" s="21"/>
@@ -8194,10 +8192,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J215" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="K215" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="L215" s="28"/>
       <x:c r="M215" s="29"/>
@@ -8216,7 +8214,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E216" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F216" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -8227,10 +8225,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J216" s="24" t="n">
-        <x:v>295</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K216" s="24" t="n">
-        <x:v>295</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="L216" s="28"/>
       <x:c r="M216" s="29"/>
@@ -8249,7 +8247,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E217" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F217" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -8260,10 +8258,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J217" s="24" t="n">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K217" s="24" t="n">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L217" s="28"/>
       <x:c r="M217" s="29"/>
@@ -8276,13 +8274,13 @@
         <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C218" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D218" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="E218" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F218" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -8293,10 +8291,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J218" s="24" t="n">
-        <x:v>50</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K218" s="24" t="n">
-        <x:v>50</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L218" s="28"/>
       <x:c r="M218" s="29"/>
@@ -8315,7 +8313,7 @@
         <x:v>29.9</x:v>
       </x:c>
       <x:c r="E219" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F219" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -8326,10 +8324,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J219" s="24" t="n">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K219" s="24" t="n">
-        <x:v>13</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="L219" s="28"/>
       <x:c r="M219" s="29"/>
@@ -8348,7 +8346,7 @@
         <x:v>29.9</x:v>
       </x:c>
       <x:c r="E220" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F220" s="21" t="str">
         <x:v>2026-06-30</x:v>
@@ -8359,10 +8357,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J220" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K220" s="24" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L220" s="28"/>
       <x:c r="M220" s="29"/>
@@ -8372,19 +8370,19 @@
         <x:v>自拼</x:v>
       </x:c>
       <x:c r="B221" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C221" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D221" s="18" t="n">
-        <x:v>29.9</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E221" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F221" s="21" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-07-01</x:v>
       </x:c>
       <x:c r="G221" s="21"/>
       <x:c r="H221" s="21"/>
@@ -8392,10 +8390,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J221" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K221" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L221" s="28"/>
       <x:c r="M221" s="29"/>
@@ -8408,7 +8406,7 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C222" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>WB</x:v>
       </x:c>
       <x:c r="D222" s="18" t="n">
         <x:v>9.9</x:v>
@@ -8417,7 +8415,7 @@
         <x:v>一年级</x:v>
       </x:c>
       <x:c r="F222" s="21" t="str">
-        <x:v>2026-07-01</x:v>
+        <x:v>2026-07-07</x:v>
       </x:c>
       <x:c r="G222" s="21"/>
       <x:c r="H222" s="21"/>
@@ -8425,10 +8423,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J222" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="K222" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="L222" s="28"/>
       <x:c r="M222" s="29"/>
@@ -8447,10 +8445,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E223" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F223" s="21" t="str">
-        <x:v>2026-07-07</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="G223" s="21"/>
       <x:c r="H223" s="21"/>
@@ -8458,10 +8456,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J223" s="24" t="n">
-        <x:v>192</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K223" s="24" t="n">
-        <x:v>192</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="L223" s="28"/>
       <x:c r="M223" s="29"/>
@@ -8480,10 +8478,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E224" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F224" s="21" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>2026-07-07</x:v>
       </x:c>
       <x:c r="G224" s="21"/>
       <x:c r="H224" s="21"/>
@@ -8491,10 +8489,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J224" s="24" t="n">
-        <x:v>89</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K224" s="24" t="n">
-        <x:v>89</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="L224" s="28"/>
       <x:c r="M224" s="29"/>
@@ -8507,16 +8505,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C225" s="12" t="str">
-        <x:v>WB</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D225" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>29.9</x:v>
       </x:c>
       <x:c r="E225" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>一年级</x:v>
       </x:c>
       <x:c r="F225" s="21" t="str">
-        <x:v>2026-07-07</x:v>
+        <x:v>2026-07-04</x:v>
       </x:c>
       <x:c r="G225" s="21"/>
       <x:c r="H225" s="21"/>
@@ -8524,10 +8522,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J225" s="24" t="n">
-        <x:v>58</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K225" s="24" t="n">
-        <x:v>58</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L225" s="28"/>
       <x:c r="M225" s="29"/>
@@ -8546,7 +8544,7 @@
         <x:v>29.9</x:v>
       </x:c>
       <x:c r="E226" s="12" t="str">
-        <x:v>一年级</x:v>
+        <x:v>三年级</x:v>
       </x:c>
       <x:c r="F226" s="21" t="str">
         <x:v>2026-07-04</x:v>
@@ -8557,10 +8555,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J226" s="24" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K226" s="24" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="L226" s="28"/>
       <x:c r="M226" s="29"/>
@@ -8579,10 +8577,10 @@
         <x:v>29.9</x:v>
       </x:c>
       <x:c r="E227" s="12" t="str">
-        <x:v>三年级</x:v>
+        <x:v>四年级</x:v>
       </x:c>
       <x:c r="F227" s="21" t="str">
-        <x:v>2026-07-04</x:v>
+        <x:v>2026-07-07</x:v>
       </x:c>
       <x:c r="G227" s="21"/>
       <x:c r="H227" s="21"/>
@@ -8590,32 +8588,32 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J227" s="24" t="n">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K227" s="24" t="n">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="L227" s="28"/>
       <x:c r="M227" s="29"/>
     </x:row>
     <x:row r="228" ht="15" hidden="0" customHeight="1">
       <x:c r="A228" s="11" t="str">
-        <x:v>自拼</x:v>
+        <x:v>高中</x:v>
       </x:c>
       <x:c r="B228" s="12" t="str">
-        <x:v>暑_9</x:v>
+        <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C228" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D228" s="18" t="n">
-        <x:v>29.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E228" s="12" t="str">
-        <x:v>四年级</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F228" s="21" t="str">
-        <x:v>2026-07-07</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G228" s="21"/>
       <x:c r="H228" s="21"/>
@@ -8623,10 +8621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J228" s="24" t="n">
-        <x:v>18</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K228" s="24" t="n">
-        <x:v>18</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="L228" s="28"/>
       <x:c r="M228" s="29"/>
@@ -8645,7 +8643,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E229" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F229" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -8656,10 +8654,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J229" s="24" t="n">
-        <x:v>55</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="K229" s="24" t="n">
-        <x:v>55</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="L229" s="28"/>
       <x:c r="M229" s="29"/>
@@ -8678,7 +8676,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E230" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F230" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -8689,10 +8687,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J230" s="24" t="n">
-        <x:v>115</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K230" s="24" t="n">
-        <x:v>115</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="L230" s="28"/>
       <x:c r="M230" s="29"/>
@@ -8705,13 +8703,13 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C231" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D231" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E231" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F231" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -8722,10 +8720,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J231" s="24" t="n">
-        <x:v>96</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K231" s="24" t="n">
-        <x:v>96</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="L231" s="28"/>
       <x:c r="M231" s="29"/>
@@ -8744,10 +8742,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E232" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F232" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="G232" s="21"/>
       <x:c r="H232" s="21"/>
@@ -8755,10 +8753,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J232" s="24" t="n">
-        <x:v>100</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="K232" s="24" t="n">
-        <x:v>100</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="L232" s="28"/>
       <x:c r="M232" s="29"/>
@@ -8777,10 +8775,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E233" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F233" s="21" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G233" s="21"/>
       <x:c r="H233" s="21"/>
@@ -8788,10 +8786,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J233" s="24" t="n">
-        <x:v>73</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="K233" s="24" t="n">
-        <x:v>73</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="L233" s="28"/>
       <x:c r="M233" s="29"/>
@@ -8804,16 +8802,16 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C234" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D234" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E234" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F234" s="21" t="str">
-        <x:v>2026-06-25</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G234" s="21"/>
       <x:c r="H234" s="21"/>
@@ -8821,10 +8819,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J234" s="24" t="n">
-        <x:v>106</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="K234" s="24" t="n">
-        <x:v>106</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="L234" s="28"/>
       <x:c r="M234" s="29"/>
@@ -8843,10 +8841,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E235" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F235" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-21</x:v>
       </x:c>
       <x:c r="G235" s="21"/>
       <x:c r="H235" s="21"/>
@@ -8854,10 +8852,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J235" s="24" t="n">
-        <x:v>681</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="K235" s="24" t="n">
-        <x:v>681</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="L235" s="28"/>
       <x:c r="M235" s="29"/>
@@ -8870,13 +8868,13 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C236" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D236" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E236" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F236" s="21" t="str">
         <x:v>2026-06-21</x:v>
@@ -8887,10 +8885,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J236" s="24" t="n">
-        <x:v>186</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K236" s="24" t="n">
-        <x:v>186</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L236" s="28"/>
       <x:c r="M236" s="29"/>
@@ -8909,7 +8907,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E237" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F237" s="21" t="str">
         <x:v>2026-06-21</x:v>
@@ -8920,10 +8918,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J237" s="24" t="n">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K237" s="24" t="n">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L237" s="28"/>
       <x:c r="M237" s="29"/>
@@ -8942,7 +8940,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E238" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F238" s="21" t="str">
         <x:v>2026-06-21</x:v>
@@ -8953,10 +8951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J238" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K238" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L238" s="28"/>
       <x:c r="M238" s="29"/>
@@ -8972,13 +8970,13 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D239" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E239" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F239" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="G239" s="21"/>
       <x:c r="H239" s="21"/>
@@ -8986,10 +8984,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J239" s="24" t="n">
-        <x:v>6</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="K239" s="24" t="n">
-        <x:v>6</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="L239" s="28"/>
       <x:c r="M239" s="29"/>
@@ -9008,7 +9006,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E240" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F240" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -9019,10 +9017,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J240" s="24" t="n">
-        <x:v>357</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="K240" s="24" t="n">
-        <x:v>357</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="L240" s="28"/>
       <x:c r="M240" s="29"/>
@@ -9041,7 +9039,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E241" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F241" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -9052,10 +9050,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J241" s="24" t="n">
-        <x:v>291</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="K241" s="24" t="n">
-        <x:v>291</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="L241" s="28"/>
       <x:c r="M241" s="29"/>
@@ -9068,13 +9066,13 @@
         <x:v>暑_10</x:v>
       </x:c>
       <x:c r="C242" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D242" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E242" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F242" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -9085,10 +9083,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J242" s="24" t="n">
-        <x:v>320</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="K242" s="24" t="n">
-        <x:v>320</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="L242" s="28"/>
       <x:c r="M242" s="29"/>
@@ -9107,7 +9105,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E243" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F243" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -9118,10 +9116,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J243" s="24" t="n">
-        <x:v>697</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="K243" s="24" t="n">
-        <x:v>697</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="L243" s="28"/>
       <x:c r="M243" s="29"/>
@@ -9140,7 +9138,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E244" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F244" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -9151,10 +9149,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J244" s="24" t="n">
-        <x:v>960</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="K244" s="24" t="n">
-        <x:v>960</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="L244" s="28"/>
       <x:c r="M244" s="29"/>
@@ -9170,10 +9168,10 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D245" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E245" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F245" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -9184,10 +9182,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J245" s="24" t="n">
-        <x:v>633</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="K245" s="24" t="n">
-        <x:v>633</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="L245" s="28"/>
       <x:c r="M245" s="29"/>
@@ -9206,7 +9204,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E246" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F246" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -9217,10 +9215,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J246" s="24" t="n">
-        <x:v>434</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="K246" s="24" t="n">
-        <x:v>434</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="L246" s="28"/>
       <x:c r="M246" s="29"/>
@@ -9239,7 +9237,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E247" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F247" s="21" t="str">
         <x:v>2026-06-25</x:v>
@@ -9250,10 +9248,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J247" s="24" t="n">
-        <x:v>625</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="K247" s="24" t="n">
-        <x:v>625</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="L247" s="28"/>
       <x:c r="M247" s="29"/>
@@ -9263,33 +9261,41 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B248" s="12" t="str">
-        <x:v>暑_10</x:v>
+        <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C248" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D248" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E248" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F248" s="21" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G248" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H248" s="21" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
-      <x:c r="G248" s="21"/>
-      <x:c r="H248" s="21"/>
       <x:c r="I248" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J248" s="24" t="n">
-        <x:v>558</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K248" s="24" t="n">
-        <x:v>558</x:v>
-      </x:c>
-      <x:c r="L248" s="28"/>
-      <x:c r="M248" s="29"/>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L248" s="28" t="n">
+        <x:v>1.0125</x:v>
+      </x:c>
+      <x:c r="M248" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="249" ht="15" hidden="0" customHeight="1">
       <x:c r="A249" s="11" t="str">
@@ -9305,10 +9311,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E249" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F249" s="21" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="G249" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9317,16 +9323,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I249" s="24" t="n">
-        <x:v>80</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="J249" s="24" t="n">
-        <x:v>81</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="K249" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="L249" s="28" t="n">
-        <x:v>1.0125</x:v>
+        <x:v>1.2125</x:v>
       </x:c>
       <x:c r="M249" s="29" t="n">
         <x:v>1</x:v>
@@ -9346,7 +9352,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E250" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F250" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9361,13 +9367,13 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="J250" s="24" t="n">
-        <x:v>194</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="K250" s="24" t="n">
-        <x:v>34</x:v>
+        <x:v>-21</x:v>
       </x:c>
       <x:c r="L250" s="28" t="n">
-        <x:v>1.2125</x:v>
+        <x:v>0.86875</x:v>
       </x:c>
       <x:c r="M250" s="29" t="n">
         <x:v>1</x:v>
@@ -9381,16 +9387,16 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C251" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D251" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E251" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F251" s="21" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>2026-07-04</x:v>
       </x:c>
       <x:c r="G251" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9399,16 +9405,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I251" s="24" t="n">
-        <x:v>160</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J251" s="24" t="n">
-        <x:v>139</x:v>
+        <x:v>883</x:v>
       </x:c>
       <x:c r="K251" s="24" t="n">
-        <x:v>-21</x:v>
+        <x:v>833</x:v>
       </x:c>
       <x:c r="L251" s="28" t="n">
-        <x:v>0.86875</x:v>
+        <x:v>17.66</x:v>
       </x:c>
       <x:c r="M251" s="29" t="n">
         <x:v>1</x:v>
@@ -9428,10 +9434,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E252" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F252" s="21" t="str">
-        <x:v>2026-07-04</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="G252" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9440,16 +9446,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I252" s="24" t="n">
-        <x:v>50</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="J252" s="24" t="n">
-        <x:v>883</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="K252" s="24" t="n">
-        <x:v>833</x:v>
+        <x:v>-671</x:v>
       </x:c>
       <x:c r="L252" s="28" t="n">
-        <x:v>17.66</x:v>
+        <x:v>0.2544444444444444</x:v>
       </x:c>
       <x:c r="M252" s="29" t="n">
         <x:v>1</x:v>
@@ -9469,7 +9475,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E253" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F253" s="21" t="str">
         <x:v>2026-07-05</x:v>
@@ -9481,16 +9487,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I253" s="24" t="n">
-        <x:v>900</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="J253" s="24" t="n">
-        <x:v>229</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K253" s="24" t="n">
-        <x:v>-671</x:v>
+        <x:v>-198</x:v>
       </x:c>
       <x:c r="L253" s="28" t="n">
-        <x:v>0.2544444444444444</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="M253" s="29" t="n">
         <x:v>1</x:v>
@@ -9504,16 +9510,16 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C254" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>图书店铺</x:v>
       </x:c>
       <x:c r="D254" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E254" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F254" s="21" t="str">
-        <x:v>2026-07-05</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G254" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9522,16 +9528,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I254" s="24" t="n">
-        <x:v>200</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J254" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="K254" s="24" t="n">
-        <x:v>-198</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="L254" s="28" t="n">
-        <x:v>0.01</x:v>
+        <x:v>1.29</x:v>
       </x:c>
       <x:c r="M254" s="29" t="n">
         <x:v>1</x:v>
@@ -9551,10 +9557,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E255" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F255" s="21" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-07-01</x:v>
       </x:c>
       <x:c r="G255" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9563,16 +9569,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I255" s="24" t="n">
-        <x:v>100</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J255" s="24" t="n">
-        <x:v>129</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="K255" s="24" t="n">
-        <x:v>29</x:v>
+        <x:v>-111</x:v>
       </x:c>
       <x:c r="L255" s="28" t="n">
-        <x:v>1.29</x:v>
+        <x:v>0.26</x:v>
       </x:c>
       <x:c r="M255" s="29" t="n">
         <x:v>1</x:v>
@@ -9592,10 +9598,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E256" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F256" s="21" t="str">
-        <x:v>2026-07-01</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="G256" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9607,13 +9613,13 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="J256" s="24" t="n">
-        <x:v>39</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K256" s="24" t="n">
-        <x:v>-111</x:v>
+        <x:v>-121</x:v>
       </x:c>
       <x:c r="L256" s="28" t="n">
-        <x:v>0.26</x:v>
+        <x:v>0.19333333333333333</x:v>
       </x:c>
       <x:c r="M256" s="29" t="n">
         <x:v>1</x:v>
@@ -9627,17 +9633,15 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C257" s="12" t="str">
-        <x:v>图书店铺</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D257" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E257" s="12" t="str">
-        <x:v>高三</x:v>
-      </x:c>
-      <x:c r="F257" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F257" s="21"/>
       <x:c r="G257" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -9648,13 +9652,13 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="J257" s="24" t="n">
-        <x:v>29</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K257" s="24" t="n">
-        <x:v>-121</x:v>
+        <x:v>-150</x:v>
       </x:c>
       <x:c r="L257" s="28" t="n">
-        <x:v>0.19333333333333333</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M257" s="29" t="n">
         <x:v>1</x:v>
@@ -9674,7 +9678,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E258" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F258" s="21"/>
       <x:c r="G258" s="21" t="str">
@@ -9684,13 +9688,13 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I258" s="24" t="n">
-        <x:v>150</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="J258" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K258" s="24" t="n">
-        <x:v>-150</x:v>
+        <x:v>-200</x:v>
       </x:c>
       <x:c r="L258" s="28" t="n">
         <x:v>0</x:v>
@@ -9713,7 +9717,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E259" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F259" s="21"/>
       <x:c r="G259" s="21" t="str">
@@ -9723,13 +9727,13 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I259" s="24" t="n">
-        <x:v>200</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J259" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K259" s="24" t="n">
-        <x:v>-200</x:v>
+        <x:v>-150</x:v>
       </x:c>
       <x:c r="L259" s="28" t="n">
         <x:v>0</x:v>
@@ -9749,12 +9753,14 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D260" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E260" s="12" t="str">
-        <x:v>高三</x:v>
-      </x:c>
-      <x:c r="F260" s="21"/>
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F260" s="21" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
       <x:c r="G260" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -9762,16 +9768,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I260" s="24" t="n">
-        <x:v>150</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J260" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="K260" s="24" t="n">
-        <x:v>-150</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="L260" s="28" t="n">
-        <x:v>0</x:v>
+        <x:v>0.9933333333333333</x:v>
       </x:c>
       <x:c r="M260" s="29" t="n">
         <x:v>1</x:v>
@@ -9791,10 +9797,10 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E261" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F261" s="21" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="G261" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9803,16 +9809,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I261" s="24" t="n">
-        <x:v>300</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="J261" s="24" t="n">
-        <x:v>298</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="K261" s="24" t="n">
-        <x:v>-2</x:v>
+        <x:v>-156</x:v>
       </x:c>
       <x:c r="L261" s="28" t="n">
-        <x:v>0.9933333333333333</x:v>
+        <x:v>0.7056603773584905</x:v>
       </x:c>
       <x:c r="M261" s="29" t="n">
         <x:v>1</x:v>
@@ -9832,7 +9838,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E262" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F262" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9844,16 +9850,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I262" s="24" t="n">
-        <x:v>530</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="J262" s="24" t="n">
-        <x:v>374</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="K262" s="24" t="n">
-        <x:v>-156</x:v>
+        <x:v>-115</x:v>
       </x:c>
       <x:c r="L262" s="28" t="n">
-        <x:v>0.7056603773584905</x:v>
+        <x:v>0.8083333333333333</x:v>
       </x:c>
       <x:c r="M262" s="29" t="n">
         <x:v>1</x:v>
@@ -9867,13 +9873,13 @@
         <x:v>暑_11</x:v>
       </x:c>
       <x:c r="C263" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D263" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E263" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F263" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9885,16 +9891,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I263" s="24" t="n">
-        <x:v>600</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="J263" s="24" t="n">
-        <x:v>485</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="K263" s="24" t="n">
-        <x:v>-115</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="L263" s="28" t="n">
-        <x:v>0.8083333333333333</x:v>
+        <x:v>1.7055555555555555</x:v>
       </x:c>
       <x:c r="M263" s="29" t="n">
         <x:v>1</x:v>
@@ -9914,7 +9920,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E264" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F264" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9926,16 +9932,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I264" s="24" t="n">
-        <x:v>180</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="J264" s="24" t="n">
-        <x:v>307</x:v>
+        <x:v>1313</x:v>
       </x:c>
       <x:c r="K264" s="24" t="n">
-        <x:v>127</x:v>
+        <x:v>-187</x:v>
       </x:c>
       <x:c r="L264" s="28" t="n">
-        <x:v>1.7055555555555555</x:v>
+        <x:v>0.8753333333333333</x:v>
       </x:c>
       <x:c r="M264" s="29" t="n">
         <x:v>1</x:v>
@@ -9955,7 +9961,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E265" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F265" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -9967,16 +9973,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I265" s="24" t="n">
-        <x:v>1500</x:v>
+        <x:v>870</x:v>
       </x:c>
       <x:c r="J265" s="24" t="n">
-        <x:v>1313</x:v>
+        <x:v>854</x:v>
       </x:c>
       <x:c r="K265" s="24" t="n">
-        <x:v>-187</x:v>
+        <x:v>-16</x:v>
       </x:c>
       <x:c r="L265" s="28" t="n">
-        <x:v>0.8753333333333333</x:v>
+        <x:v>0.9816091954022989</x:v>
       </x:c>
       <x:c r="M265" s="29" t="n">
         <x:v>1</x:v>
@@ -9993,35 +9999,27 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D266" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E266" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F266" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="G266" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H266" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
+        <x:v>2026-06-28</x:v>
+      </x:c>
+      <x:c r="G266" s="21"/>
+      <x:c r="H266" s="21"/>
       <x:c r="I266" s="24" t="n">
-        <x:v>870</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J266" s="24" t="n">
-        <x:v>854</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K266" s="24" t="n">
-        <x:v>-16</x:v>
-      </x:c>
-      <x:c r="L266" s="28" t="n">
-        <x:v>0.9816091954022989</x:v>
-      </x:c>
-      <x:c r="M266" s="29" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L266" s="28"/>
+      <x:c r="M266" s="29"/>
     </x:row>
     <x:row r="267" ht="15" hidden="0" customHeight="1">
       <x:c r="A267" s="11" t="str">
@@ -10037,7 +10035,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E267" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F267" s="21" t="str">
         <x:v>2026-06-28</x:v>
@@ -10048,10 +10046,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J267" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K267" s="24" t="n">
-        <x:v>5</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L267" s="28"/>
       <x:c r="M267" s="29"/>
@@ -10070,7 +10068,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E268" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F268" s="21" t="str">
         <x:v>2026-06-28</x:v>
@@ -10081,10 +10079,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J268" s="24" t="n">
-        <x:v>63</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K268" s="24" t="n">
-        <x:v>63</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L268" s="28"/>
       <x:c r="M268" s="29"/>
@@ -10100,27 +10098,31 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D269" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E269" s="12" t="str">
-        <x:v>高三</x:v>
-      </x:c>
-      <x:c r="F269" s="21" t="str">
-        <x:v>2026-06-28</x:v>
-      </x:c>
-      <x:c r="G269" s="21"/>
-      <x:c r="H269" s="21"/>
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F269" s="21"/>
+      <x:c r="G269" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="H269" s="21" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
       <x:c r="I269" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J269" s="24" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K269" s="24" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L269" s="28"/>
-      <x:c r="M269" s="29"/>
+      <x:c r="M269" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="270" ht="15" hidden="0" customHeight="1">
       <x:c r="A270" s="11" t="str">
@@ -10136,9 +10138,11 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E270" s="12" t="str">
-        <x:v>高一</x:v>
-      </x:c>
-      <x:c r="F270" s="21"/>
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F270" s="21" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
       <x:c r="G270" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
@@ -10146,15 +10150,17 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I270" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="J270" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="K270" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L270" s="28"/>
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="L270" s="28" t="n">
+        <x:v>1.1257142857142857</x:v>
+      </x:c>
       <x:c r="M270" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -10173,7 +10179,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E271" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F271" s="21" t="str">
         <x:v>2026-07-02</x:v>
@@ -10185,16 +10191,16 @@
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="I271" s="24" t="n">
-        <x:v>700</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="J271" s="24" t="n">
-        <x:v>788</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="K271" s="24" t="n">
-        <x:v>88</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="L271" s="28" t="n">
-        <x:v>1.1257142857142857</x:v>
+        <x:v>1.1246153846153846</x:v>
       </x:c>
       <x:c r="M271" s="29" t="n">
         <x:v>1</x:v>
@@ -10205,40 +10211,40 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B272" s="12" t="str">
-        <x:v>暑_11</x:v>
+        <x:v>暑_12</x:v>
       </x:c>
       <x:c r="C272" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D272" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E272" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F272" s="21" t="str">
+        <x:v>2026-07-07</x:v>
+      </x:c>
+      <x:c r="G272" s="21" t="str">
+        <x:v>2026-07-09</x:v>
+      </x:c>
+      <x:c r="H272" s="21" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
-      <x:c r="G272" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="H272" s="21" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
       <x:c r="I272" s="24" t="n">
-        <x:v>650</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J272" s="24" t="n">
-        <x:v>731</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="K272" s="24" t="n">
-        <x:v>81</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L272" s="28" t="n">
-        <x:v>1.1246153846153846</x:v>
+        <x:v>1.3857142857142857</x:v>
       </x:c>
       <x:c r="M272" s="29" t="n">
-        <x:v>1</x:v>
+        <x:v>0.8333333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="273" ht="15" hidden="0" customHeight="1">
@@ -10255,7 +10261,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E273" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F273" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -10267,16 +10273,16 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I273" s="24" t="n">
-        <x:v>70</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="J273" s="24" t="n">
-        <x:v>97</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="K273" s="24" t="n">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="L273" s="28" t="n">
-        <x:v>1.3857142857142857</x:v>
+        <x:v>1.1285714285714286</x:v>
       </x:c>
       <x:c r="M273" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -10296,7 +10302,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E274" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F274" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -10311,13 +10317,13 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="J274" s="24" t="n">
-        <x:v>158</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="K274" s="24" t="n">
-        <x:v>18</x:v>
+        <x:v>-39</x:v>
       </x:c>
       <x:c r="L274" s="28" t="n">
-        <x:v>1.1285714285714286</x:v>
+        <x:v>0.7214285714285714</x:v>
       </x:c>
       <x:c r="M274" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -10331,16 +10337,16 @@
         <x:v>暑_12</x:v>
       </x:c>
       <x:c r="C275" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D275" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E275" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F275" s="21" t="str">
-        <x:v>2026-07-07</x:v>
+        <x:v>2026-07-04</x:v>
       </x:c>
       <x:c r="G275" s="21" t="str">
         <x:v>2026-07-09</x:v>
@@ -10349,16 +10355,16 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I275" s="24" t="n">
-        <x:v>140</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J275" s="24" t="n">
-        <x:v>101</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="K275" s="24" t="n">
-        <x:v>-39</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="L275" s="28" t="n">
-        <x:v>0.7214285714285714</x:v>
+        <x:v>3.4</x:v>
       </x:c>
       <x:c r="M275" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -10378,10 +10384,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E276" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F276" s="21" t="str">
-        <x:v>2026-07-04</x:v>
+        <x:v>2026-07-07</x:v>
       </x:c>
       <x:c r="G276" s="21" t="str">
         <x:v>2026-07-09</x:v>
@@ -10390,16 +10396,16 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I276" s="24" t="n">
-        <x:v>100</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="J276" s="24" t="n">
-        <x:v>340</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="K276" s="24" t="n">
-        <x:v>240</x:v>
+        <x:v>-13</x:v>
       </x:c>
       <x:c r="L276" s="28" t="n">
-        <x:v>3.4</x:v>
+        <x:v>0.98375</x:v>
       </x:c>
       <x:c r="M276" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -10419,10 +10425,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E277" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F277" s="21" t="str">
-        <x:v>2026-07-07</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="G277" s="21" t="str">
         <x:v>2026-07-09</x:v>
@@ -10431,16 +10437,16 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I277" s="24" t="n">
-        <x:v>800</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="J277" s="24" t="n">
-        <x:v>787</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="K277" s="24" t="n">
-        <x:v>-13</x:v>
+        <x:v>-233</x:v>
       </x:c>
       <x:c r="L277" s="28" t="n">
-        <x:v>0.98375</x:v>
+        <x:v>0.6671428571428571</x:v>
       </x:c>
       <x:c r="M277" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -10454,17 +10460,15 @@
         <x:v>暑_12</x:v>
       </x:c>
       <x:c r="C278" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D278" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E278" s="12" t="str">
-        <x:v>高三</x:v>
-      </x:c>
-      <x:c r="F278" s="21" t="str">
-        <x:v>2026-07-05</x:v>
-      </x:c>
+        <x:v>高一</x:v>
+      </x:c>
+      <x:c r="F278" s="21"/>
       <x:c r="G278" s="21" t="str">
         <x:v>2026-07-09</x:v>
       </x:c>
@@ -10472,17 +10476,15 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I278" s="24" t="n">
-        <x:v>700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J278" s="24" t="n">
-        <x:v>467</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K278" s="24" t="n">
-        <x:v>-233</x:v>
-      </x:c>
-      <x:c r="L278" s="28" t="n">
-        <x:v>0.6671428571428571</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L278" s="28"/>
       <x:c r="M278" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
       </x:c>
@@ -10501,9 +10503,11 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E279" s="12" t="str">
-        <x:v>高一</x:v>
-      </x:c>
-      <x:c r="F279" s="21"/>
+        <x:v>高二</x:v>
+      </x:c>
+      <x:c r="F279" s="21" t="str">
+        <x:v>2026-07-07</x:v>
+      </x:c>
       <x:c r="G279" s="21" t="str">
         <x:v>2026-07-09</x:v>
       </x:c>
@@ -10511,15 +10515,17 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I279" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="J279" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K279" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L279" s="28"/>
+      <x:c r="L279" s="28" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="M279" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
       </x:c>
@@ -10538,7 +10544,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E280" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F280" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -10550,16 +10556,16 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I280" s="24" t="n">
-        <x:v>150</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="J280" s="24" t="n">
-        <x:v>150</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="K280" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-88</x:v>
       </x:c>
       <x:c r="L280" s="28" t="n">
-        <x:v>1</x:v>
+        <x:v>0.8185567010309278</x:v>
       </x:c>
       <x:c r="M280" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -10573,13 +10579,13 @@
         <x:v>暑_12</x:v>
       </x:c>
       <x:c r="C281" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D281" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E281" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F281" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -10591,16 +10597,16 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I281" s="24" t="n">
-        <x:v>485</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="J281" s="24" t="n">
-        <x:v>397</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="K281" s="24" t="n">
-        <x:v>-88</x:v>
+        <x:v>-32</x:v>
       </x:c>
       <x:c r="L281" s="28" t="n">
-        <x:v>0.8185567010309278</x:v>
+        <x:v>0.9044776119402985</x:v>
       </x:c>
       <x:c r="M281" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -10620,7 +10626,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E282" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F282" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -10632,16 +10638,16 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I282" s="24" t="n">
-        <x:v>335</x:v>
+        <x:v>980</x:v>
       </x:c>
       <x:c r="J282" s="24" t="n">
-        <x:v>303</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="K282" s="24" t="n">
-        <x:v>-32</x:v>
+        <x:v>-173</x:v>
       </x:c>
       <x:c r="L282" s="28" t="n">
-        <x:v>0.9044776119402985</x:v>
+        <x:v>0.823469387755102</x:v>
       </x:c>
       <x:c r="M282" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -10661,7 +10667,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E283" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F283" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -10673,16 +10679,16 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I283" s="24" t="n">
-        <x:v>980</x:v>
+        <x:v>1240</x:v>
       </x:c>
       <x:c r="J283" s="24" t="n">
-        <x:v>807</x:v>
+        <x:v>702</x:v>
       </x:c>
       <x:c r="K283" s="24" t="n">
-        <x:v>-173</x:v>
+        <x:v>-538</x:v>
       </x:c>
       <x:c r="L283" s="28" t="n">
-        <x:v>0.823469387755102</x:v>
+        <x:v>0.5661290322580645</x:v>
       </x:c>
       <x:c r="M283" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -10699,13 +10705,13 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D284" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E284" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F284" s="21" t="str">
-        <x:v>2026-07-07</x:v>
+        <x:v>2026-07-03</x:v>
       </x:c>
       <x:c r="G284" s="21" t="str">
         <x:v>2026-07-09</x:v>
@@ -10714,17 +10720,15 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I284" s="24" t="n">
-        <x:v>1240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J284" s="24" t="n">
-        <x:v>702</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K284" s="24" t="n">
-        <x:v>-538</x:v>
-      </x:c>
-      <x:c r="L284" s="28" t="n">
-        <x:v>0.5661290322580645</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L284" s="28"/>
       <x:c r="M284" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
       </x:c>
@@ -10743,10 +10747,10 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E285" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F285" s="21" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-07-07</x:v>
       </x:c>
       <x:c r="G285" s="21" t="str">
         <x:v>2026-07-09</x:v>
@@ -10755,15 +10759,17 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I285" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="J285" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="K285" s="24" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L285" s="28"/>
+        <x:v>-30</x:v>
+      </x:c>
+      <x:c r="L285" s="28" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
       <x:c r="M285" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
       </x:c>
@@ -10782,7 +10788,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E286" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F286" s="21" t="str">
         <x:v>2026-07-07</x:v>
@@ -10794,16 +10800,16 @@
         <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="I286" s="24" t="n">
-        <x:v>300</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="J286" s="24" t="n">
-        <x:v>270</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="K286" s="24" t="n">
-        <x:v>-30</x:v>
+        <x:v>-68</x:v>
       </x:c>
       <x:c r="L286" s="28" t="n">
-        <x:v>0.9</x:v>
+        <x:v>0.864</x:v>
       </x:c>
       <x:c r="M286" s="29" t="n">
         <x:v>0.8333333333333334</x:v>
@@ -10814,48 +10820,40 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B287" s="12" t="str">
-        <x:v>暑_12</x:v>
+        <x:v>暑_7</x:v>
       </x:c>
       <x:c r="C287" s="12" t="str">
-        <x:v>常规外呼</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D287" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E287" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F287" s="21" t="str">
-        <x:v>2026-07-07</x:v>
-      </x:c>
-      <x:c r="G287" s="21" t="str">
-        <x:v>2026-07-09</x:v>
-      </x:c>
-      <x:c r="H287" s="21" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
+        <x:v>2026-06-21</x:v>
+      </x:c>
+      <x:c r="G287" s="21"/>
+      <x:c r="H287" s="21"/>
       <x:c r="I287" s="24" t="n">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J287" s="24" t="n">
-        <x:v>432</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K287" s="24" t="n">
-        <x:v>-68</x:v>
-      </x:c>
-      <x:c r="L287" s="28" t="n">
-        <x:v>0.864</x:v>
-      </x:c>
-      <x:c r="M287" s="29" t="n">
-        <x:v>0.8333333333333334</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L287" s="28"/>
+      <x:c r="M287" s="29"/>
     </x:row>
     <x:row r="288" ht="15" hidden="0" customHeight="1">
       <x:c r="A288" s="11" t="str">
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B288" s="12" t="str">
-        <x:v>暑_7</x:v>
+        <x:v>暑_8</x:v>
       </x:c>
       <x:c r="C288" s="12" t="str">
         <x:v>LLM外呼</x:v>
@@ -10867,7 +10865,7 @@
         <x:v>高一</x:v>
       </x:c>
       <x:c r="F288" s="21" t="str">
-        <x:v>2026-06-21</x:v>
+        <x:v>2026-06-28</x:v>
       </x:c>
       <x:c r="G288" s="21"/>
       <x:c r="H288" s="21"/>
@@ -10875,10 +10873,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J288" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K288" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L288" s="28"/>
       <x:c r="M288" s="29"/>
@@ -10897,7 +10895,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E289" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F289" s="21" t="str">
         <x:v>2026-06-28</x:v>
@@ -10908,10 +10906,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J289" s="24" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K289" s="24" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L289" s="28"/>
       <x:c r="M289" s="29"/>
@@ -10921,19 +10919,19 @@
         <x:v>高中</x:v>
       </x:c>
       <x:c r="B290" s="12" t="str">
-        <x:v>暑_8</x:v>
+        <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C290" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>AI托管</x:v>
       </x:c>
       <x:c r="D290" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E290" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F290" s="21" t="str">
-        <x:v>2026-06-28</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G290" s="21"/>
       <x:c r="H290" s="21"/>
@@ -10941,10 +10939,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J290" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="K290" s="24" t="n">
-        <x:v>1</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="L290" s="28"/>
       <x:c r="M290" s="29"/>
@@ -10963,7 +10961,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E291" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F291" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -10974,10 +10972,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J291" s="24" t="n">
-        <x:v>27</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K291" s="24" t="n">
-        <x:v>27</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L291" s="28"/>
       <x:c r="M291" s="29"/>
@@ -10996,7 +10994,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E292" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F292" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -11007,10 +11005,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J292" s="24" t="n">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K292" s="24" t="n">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L292" s="28"/>
       <x:c r="M292" s="29"/>
@@ -11023,13 +11021,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C293" s="12" t="str">
-        <x:v>AI托管</x:v>
+        <x:v>LEC内测</x:v>
       </x:c>
       <x:c r="D293" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E293" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F293" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -11040,10 +11038,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J293" s="24" t="n">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K293" s="24" t="n">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L293" s="28"/>
       <x:c r="M293" s="29"/>
@@ -11062,7 +11060,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E294" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F294" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -11073,10 +11071,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J294" s="24" t="n">
-        <x:v>10</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K294" s="24" t="n">
-        <x:v>10</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L294" s="28"/>
       <x:c r="M294" s="29"/>
@@ -11095,10 +11093,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E295" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F295" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G295" s="21"/>
       <x:c r="H295" s="21"/>
@@ -11106,10 +11104,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J295" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K295" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L295" s="28"/>
       <x:c r="M295" s="29"/>
@@ -11122,16 +11120,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C296" s="12" t="str">
-        <x:v>LEC内测</x:v>
+        <x:v>LLM外呼</x:v>
       </x:c>
       <x:c r="D296" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>9.9</x:v>
       </x:c>
       <x:c r="E296" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F296" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="G296" s="21"/>
       <x:c r="H296" s="21"/>
@@ -11139,10 +11137,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J296" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K296" s="24" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L296" s="28"/>
       <x:c r="M296" s="29"/>
@@ -11161,10 +11159,10 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E297" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F297" s="21" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-07-05</x:v>
       </x:c>
       <x:c r="G297" s="21"/>
       <x:c r="H297" s="21"/>
@@ -11172,10 +11170,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J297" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K297" s="24" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="L297" s="28"/>
       <x:c r="M297" s="29"/>
@@ -11194,7 +11192,7 @@
         <x:v>9.9</x:v>
       </x:c>
       <x:c r="E298" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F298" s="21" t="str">
         <x:v>2026-07-05</x:v>
@@ -11205,10 +11203,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J298" s="24" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K298" s="24" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L298" s="28"/>
       <x:c r="M298" s="29"/>
@@ -11221,16 +11219,16 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C299" s="12" t="str">
-        <x:v>LLM外呼</x:v>
+        <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D299" s="18" t="n">
-        <x:v>9.9</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E299" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F299" s="21" t="str">
-        <x:v>2026-07-05</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G299" s="21"/>
       <x:c r="H299" s="21"/>
@@ -11238,10 +11236,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J299" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="K299" s="24" t="n">
-        <x:v>2</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="L299" s="28"/>
       <x:c r="M299" s="29"/>
@@ -11260,7 +11258,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E300" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F300" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -11271,10 +11269,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J300" s="24" t="n">
-        <x:v>146</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="K300" s="24" t="n">
-        <x:v>146</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="L300" s="28"/>
       <x:c r="M300" s="29"/>
@@ -11293,7 +11291,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E301" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F301" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -11304,10 +11302,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J301" s="24" t="n">
-        <x:v>157</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K301" s="24" t="n">
-        <x:v>157</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="L301" s="28"/>
       <x:c r="M301" s="29"/>
@@ -11323,10 +11321,10 @@
         <x:v>外部微转-*</x:v>
       </x:c>
       <x:c r="D302" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E302" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F302" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -11337,10 +11335,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J302" s="24" t="n">
-        <x:v>136</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K302" s="24" t="n">
-        <x:v>136</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L302" s="28"/>
       <x:c r="M302" s="29"/>
@@ -11359,10 +11357,10 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E303" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F303" s="21" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="G303" s="21"/>
       <x:c r="H303" s="21"/>
@@ -11370,10 +11368,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J303" s="24" t="n">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="K303" s="24" t="n">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="L303" s="28"/>
       <x:c r="M303" s="29"/>
@@ -11392,10 +11390,10 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E304" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F304" s="21" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="G304" s="21"/>
       <x:c r="H304" s="21"/>
@@ -11403,10 +11401,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J304" s="24" t="n">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K304" s="24" t="n">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L304" s="28"/>
       <x:c r="M304" s="29"/>
@@ -11419,13 +11417,13 @@
         <x:v>暑_9</x:v>
       </x:c>
       <x:c r="C305" s="12" t="str">
-        <x:v>外部微转-*</x:v>
+        <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D305" s="18" t="n">
-        <x:v>28.8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E305" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F305" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -11436,10 +11434,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J305" s="24" t="n">
-        <x:v>30</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K305" s="24" t="n">
-        <x:v>30</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="L305" s="28"/>
       <x:c r="M305" s="29"/>
@@ -11458,7 +11456,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E306" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F306" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -11469,10 +11467,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J306" s="24" t="n">
-        <x:v>136</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="K306" s="24" t="n">
-        <x:v>136</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="L306" s="28"/>
       <x:c r="M306" s="29"/>
@@ -11491,7 +11489,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E307" s="12" t="str">
-        <x:v>高二</x:v>
+        <x:v>高三</x:v>
       </x:c>
       <x:c r="F307" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -11502,10 +11500,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J307" s="24" t="n">
-        <x:v>292</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="K307" s="24" t="n">
-        <x:v>292</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="L307" s="28"/>
       <x:c r="M307" s="29"/>
@@ -11521,10 +11519,10 @@
         <x:v>常规外呼</x:v>
       </x:c>
       <x:c r="D308" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>28.8</x:v>
       </x:c>
       <x:c r="E308" s="12" t="str">
-        <x:v>高三</x:v>
+        <x:v>高一</x:v>
       </x:c>
       <x:c r="F308" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -11535,10 +11533,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J308" s="24" t="n">
-        <x:v>167</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="K308" s="24" t="n">
-        <x:v>167</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="L308" s="28"/>
       <x:c r="M308" s="29"/>
@@ -11557,7 +11555,7 @@
         <x:v>28.8</x:v>
       </x:c>
       <x:c r="E309" s="12" t="str">
-        <x:v>高一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="F309" s="21" t="str">
         <x:v>2026-06-18</x:v>
@@ -11568,79 +11566,46 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J309" s="24" t="n">
-        <x:v>92</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="K309" s="24" t="n">
-        <x:v>92</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="L309" s="28"/>
       <x:c r="M309" s="29"/>
     </x:row>
     <x:row r="310" ht="15" hidden="0" customHeight="1">
-      <x:c r="A310" s="11" t="str">
+      <x:c r="A310" s="14" t="str">
         <x:v>高中</x:v>
       </x:c>
-      <x:c r="B310" s="12" t="str">
+      <x:c r="B310" s="15" t="str">
         <x:v>暑_9</x:v>
       </x:c>
-      <x:c r="C310" s="12" t="str">
+      <x:c r="C310" s="15" t="str">
         <x:v>常规外呼</x:v>
       </x:c>
-      <x:c r="D310" s="18" t="n">
+      <x:c r="D310" s="19" t="n">
         <x:v>28.8</x:v>
       </x:c>
-      <x:c r="E310" s="12" t="str">
-        <x:v>高二</x:v>
-      </x:c>
-      <x:c r="F310" s="21" t="str">
+      <x:c r="E310" s="15" t="str">
+        <x:v>高三</x:v>
+      </x:c>
+      <x:c r="F310" s="22" t="str">
         <x:v>2026-06-18</x:v>
       </x:c>
-      <x:c r="G310" s="21"/>
-      <x:c r="H310" s="21"/>
-      <x:c r="I310" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J310" s="24" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="K310" s="24" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="L310" s="28"/>
-      <x:c r="M310" s="29"/>
-    </x:row>
-    <x:row r="311" ht="15" hidden="0" customHeight="1">
-      <x:c r="A311" s="14" t="str">
-        <x:v>高中</x:v>
-      </x:c>
-      <x:c r="B311" s="15" t="str">
-        <x:v>暑_9</x:v>
-      </x:c>
-      <x:c r="C311" s="15" t="str">
-        <x:v>常规外呼</x:v>
-      </x:c>
-      <x:c r="D311" s="19" t="n">
-        <x:v>28.8</x:v>
-      </x:c>
-      <x:c r="E311" s="15" t="str">
-        <x:v>高三</x:v>
-      </x:c>
-      <x:c r="F311" s="22" t="str">
-        <x:v>2026-06-18</x:v>
-      </x:c>
-      <x:c r="G311" s="22"/>
-      <x:c r="H311" s="22"/>
-      <x:c r="I311" s="25" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J311" s="25" t="n">
+      <x:c r="G310" s="22"/>
+      <x:c r="H310" s="22"/>
+      <x:c r="I310" s="25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J310" s="25" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="K311" s="25" t="n">
+      <x:c r="K310" s="25" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="L311" s="30"/>
-      <x:c r="M311" s="31"/>
+      <x:c r="L310" s="30"/>
+      <x:c r="M310" s="31"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -11696,7 +11661,7 @@
         <x:v>聚合组合数</x:v>
       </x:c>
       <x:c r="B5" s="13" t="n">
-        <x:v>309</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -11712,7 +11677,7 @@
         <x:v>现状合计</x:v>
       </x:c>
       <x:c r="B7" s="13" t="n">
-        <x:v>85277</x:v>
+        <x:v>82884</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -11720,7 +11685,7 @@
         <x:v>完成率整体</x:v>
       </x:c>
       <x:c r="B8" s="13" t="n">
-        <x:v>1.4934676007005254</x:v>
+        <x:v>1.4515586690017512</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -11760,7 +11725,7 @@
         <x:v>最新期次现状合计</x:v>
       </x:c>
       <x:c r="B13" s="13" t="n">
-        <x:v>27157</x:v>
+        <x:v>26629</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -11768,7 +11733,7 @@
         <x:v>最新期次完成率整体</x:v>
       </x:c>
       <x:c r="B14" s="13" t="n">
-        <x:v>0.9709331426528424</x:v>
+        <x:v>0.9520557740436182</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -11888,7 +11853,7 @@
         <x:v>现状计算</x:v>
       </x:c>
       <x:c r="B29" s="13" t="str">
-        <x:v>同一统计维度下按 custom_uid 去重计数；custom_uid 缺失的行分别计数</x:v>
+        <x:v>同学部、同一期次有 target 进量日期时，仅统计下单日期不早于进量日期的 demo；同一统计维度下按 custom_uid 去重计数，custom_uid 缺失的行分别计数</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
@@ -11929,7 +11894,7 @@
         <x:v>12580</x:v>
       </x:c>
       <x:c r="C35" s="10" t="n">
-        <x:v>12189</x:v>
+        <x:v>12006</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="15" hidden="0" customHeight="1">
@@ -11940,7 +11905,7 @@
         <x:v>9450</x:v>
       </x:c>
       <x:c r="C36" s="13" t="n">
-        <x:v>9956</x:v>
+        <x:v>9611</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="15" hidden="0" customHeight="1">
@@ -11984,7 +11949,7 @@
         <x:v>12580</x:v>
       </x:c>
       <x:c r="C42" s="10" t="n">
-        <x:v>12189</x:v>
+        <x:v>12006</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="15" hidden="0" customHeight="1">
@@ -11995,7 +11960,7 @@
         <x:v>9450</x:v>
       </x:c>
       <x:c r="C43" s="13" t="n">
-        <x:v>9956</x:v>
+        <x:v>9611</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15" hidden="0" customHeight="1">
@@ -12039,7 +12004,7 @@
         <x:v>12620</x:v>
       </x:c>
       <x:c r="C49" s="10" t="n">
-        <x:v>12641</x:v>
+        <x:v>12501</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15" hidden="0" customHeight="1">
@@ -12050,7 +12015,7 @@
         <x:v>8665</x:v>
       </x:c>
       <x:c r="C50" s="13" t="n">
-        <x:v>7431</x:v>
+        <x:v>7306</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15" hidden="0" customHeight="1">
@@ -12061,7 +12026,7 @@
         <x:v>4100</x:v>
       </x:c>
       <x:c r="C51" s="13" t="n">
-        <x:v>4396</x:v>
+        <x:v>4174</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15" hidden="0" customHeight="1">
@@ -12072,7 +12037,7 @@
         <x:v>1505</x:v>
       </x:c>
       <x:c r="C52" s="13" t="n">
-        <x:v>1681</x:v>
+        <x:v>1642</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15" hidden="0" customHeight="1">
@@ -12083,7 +12048,7 @@
         <x:v>1080</x:v>
       </x:c>
       <x:c r="C53" s="16" t="n">
-        <x:v>1008</x:v>
+        <x:v>1006</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="16.799999237060547" hidden="0" customHeight="1">
@@ -12127,7 +12092,7 @@
         <x:v>7870</x:v>
       </x:c>
       <x:c r="C59" s="13" t="n">
-        <x:v>8328</x:v>
+        <x:v>7802</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15" hidden="0" customHeight="1">
@@ -12149,7 +12114,7 @@
         <x:v>1080</x:v>
       </x:c>
       <x:c r="C61" s="16" t="n">
-        <x:v>1008</x:v>
+        <x:v>1006</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="16.799999237060547" hidden="0" customHeight="1">
@@ -12182,7 +12147,7 @@
         <x:v>3720</x:v>
       </x:c>
       <x:c r="C66" s="10" t="n">
-        <x:v>3936</x:v>
+        <x:v>3921</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="15" hidden="0" customHeight="1">
@@ -12193,7 +12158,7 @@
         <x:v>3730</x:v>
       </x:c>
       <x:c r="C67" s="13" t="n">
-        <x:v>3580</x:v>
+        <x:v>3566</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="15" hidden="0" customHeight="1">
@@ -12204,7 +12169,7 @@
         <x:v>3510</x:v>
       </x:c>
       <x:c r="C68" s="13" t="n">
-        <x:v>3350</x:v>
+        <x:v>3342</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="15" hidden="0" customHeight="1">
@@ -12215,7 +12180,7 @@
         <x:v>2920</x:v>
       </x:c>
       <x:c r="C69" s="13" t="n">
-        <x:v>2983</x:v>
+        <x:v>2982</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="15" hidden="0" customHeight="1">
@@ -12226,7 +12191,7 @@
         <x:v>3220</x:v>
       </x:c>
       <x:c r="C70" s="13" t="n">
-        <x:v>2903</x:v>
+        <x:v>2892</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="15" hidden="0" customHeight="1">
@@ -12237,29 +12202,29 @@
         <x:v>2830</x:v>
       </x:c>
       <x:c r="C71" s="13" t="n">
-        <x:v>2790</x:v>
+        <x:v>2627</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="15" hidden="0" customHeight="1">
       <x:c r="A72" s="11" t="str">
-        <x:v>初一</x:v>
+        <x:v>高二</x:v>
       </x:c>
       <x:c r="B72" s="12" t="n">
-        <x:v>2000</x:v>
+        <x:v>2370</x:v>
       </x:c>
       <x:c r="C72" s="13" t="n">
-        <x:v>2440</x:v>
+        <x:v>2172</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="15" hidden="0" customHeight="1">
       <x:c r="A73" s="11" t="str">
-        <x:v>高二</x:v>
+        <x:v>初一</x:v>
       </x:c>
       <x:c r="B73" s="12" t="n">
-        <x:v>2370</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="C73" s="13" t="n">
-        <x:v>2172</x:v>
+        <x:v>2124</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="15" hidden="0" customHeight="1">
@@ -12416,7 +12381,7 @@
         <x:v>同一统计维度下 target 表的最晚进量日期</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
+    <x:row r="10" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A10" s="37" t="str">
         <x:v>现状</x:v>
       </x:c>
@@ -12424,7 +12389,7 @@
         <x:v>现状</x:v>
       </x:c>
       <x:c r="C10" s="39" t="str">
-        <x:v>同一统计维度下按 custom_uid 去重计数；custom_uid 缺失的行分别计数</x:v>
+        <x:v>同学部、同一期次有 target 进量日期时，仅统计下单日期不早于进量日期的 demo；同一统计维度下按 custom_uid 去重计数，custom_uid 缺失的行分别计数</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">

--- a/outputs/tongji_summary/tongji_summary_current.xlsx
+++ b/outputs/tongji_summary/tongji_summary_current.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目标现状对比" sheetId="1" r:id="R588ee566bb7d423e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据概览" sheetId="2" r:id="R1bba5b7693c4429e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计算规则" sheetId="3" r:id="R009fe6ab59864e49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目标现状对比" sheetId="1" r:id="Rfcb7d7ab10034452"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据概览" sheetId="2" r:id="Rd0c4a5415cdd47b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计算规则" sheetId="3" r:id="R6eab0f50afc34de0"/>
   </x:sheets>
 </x:workbook>
 </file>
